--- a/Mck_Murta.xlsx
+++ b/Mck_Murta.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://santos.sharepoint.com/sites/Dev-CoopOil/Shared Documents/Limestone Creek (Area)/McKinlay/Horizontal Well Sample Description Spreadsheets/Well Tops/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_59B50741D280066C621D9BC3C55C92FFBC81284F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D01488AD-E291-49A4-8516-67991FD23853}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_59B50741D280066C621D9BC3C55C92FFBC81284F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{300CC169-9450-42FB-B687-07A289D86DF8}"/>
   <bookViews>
-    <workbookView xWindow="19530" yWindow="4305" windowWidth="26850" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19185" yWindow="3960" windowWidth="26850" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AI$183</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="74">
   <si>
     <t>Well identifier (Well name)</t>
   </si>
@@ -206,9 +209,6 @@
     <t>HOBBES 6</t>
   </si>
   <si>
-    <t>Jena Dev C Oil Lateral 1_Ops</t>
-  </si>
-  <si>
     <t>03/20/2026 09:40:10</t>
   </si>
   <si>
@@ -219,30 +219,6 @@
   </si>
   <si>
     <t>03/20/2026 09:41:37</t>
-  </si>
-  <si>
-    <t>Jena Dev C Oil Lateral 2_Ops</t>
-  </si>
-  <si>
-    <t>03/20/2026 10:30:15</t>
-  </si>
-  <si>
-    <t>03/20/2026 09:41:12</t>
-  </si>
-  <si>
-    <t>03/20/2026 10:27:54</t>
-  </si>
-  <si>
-    <t>03/20/2026 09:41:25</t>
-  </si>
-  <si>
-    <t>03/20/2026 09:41:27</t>
-  </si>
-  <si>
-    <t>03/20/2026 10:29:38</t>
-  </si>
-  <si>
-    <t>03/20/2026 10:29:42</t>
   </si>
   <si>
     <t>MCKINLAY 20</t>
@@ -279,6 +255,12 @@
   </si>
   <si>
     <t>TERINGIE 6</t>
+  </si>
+  <si>
+    <t>JENA 31DW1</t>
+  </si>
+  <si>
+    <t>JENA 31 OPS</t>
   </si>
 </sst>
 </file>
@@ -597,8 +579,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI175"/>
+  <dimension ref="A1:AI184"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="31.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
@@ -706,7 +691,7 @@
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>9405</v>
+        <v>9402</v>
       </c>
       <c r="B2" t="s">
         <v>34</v>
@@ -762,7 +747,7 @@
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>9532</v>
+        <v>9528</v>
       </c>
       <c r="B3" t="s">
         <v>34</v>
@@ -809,7 +794,7 @@
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>9533</v>
+        <v>9534</v>
       </c>
       <c r="B4" t="s">
         <v>34</v>
@@ -821,19 +806,19 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>436404.99</v>
+        <v>436403.56</v>
       </c>
       <c r="F4">
-        <v>6842650.9199999999</v>
+        <v>6842645.7699999996</v>
       </c>
       <c r="G4">
-        <v>-1196.72</v>
+        <v>-1196.8599999999999</v>
       </c>
       <c r="H4">
-        <v>2138.77</v>
+        <v>2133.4299999999998</v>
       </c>
       <c r="K4">
-        <v>-1196.72</v>
+        <v>-1196.8599999999999</v>
       </c>
       <c r="O4" t="s">
         <v>39</v>
@@ -851,12 +836,12 @@
         <v>1</v>
       </c>
       <c r="AI4" s="1">
-        <v>46210.364421296297</v>
+        <v>46210.364733796298</v>
       </c>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>9534</v>
+        <v>9529</v>
       </c>
       <c r="B5" t="s">
         <v>34</v>
@@ -868,19 +853,19 @@
         <v>35</v>
       </c>
       <c r="E5">
-        <v>436464.85</v>
+        <v>436404.99</v>
       </c>
       <c r="F5">
-        <v>6842826.1699999999</v>
+        <v>6842650.9199999999</v>
       </c>
       <c r="G5">
-        <v>-1194.7</v>
+        <v>-1196.72</v>
       </c>
       <c r="H5">
-        <v>2324.12</v>
+        <v>2138.77</v>
       </c>
       <c r="K5">
-        <v>-1194.7</v>
+        <v>-1196.72</v>
       </c>
       <c r="O5" t="s">
         <v>39</v>
@@ -898,12 +883,12 @@
         <v>1</v>
       </c>
       <c r="AI5" s="1">
-        <v>46210.364444444444</v>
+        <v>46210.364421296297</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>9535</v>
+        <v>9530</v>
       </c>
       <c r="B6" t="s">
         <v>34</v>
@@ -915,19 +900,19 @@
         <v>35</v>
       </c>
       <c r="E6">
-        <v>436577.55</v>
+        <v>436464.85</v>
       </c>
       <c r="F6">
-        <v>6843126.1299999999</v>
+        <v>6842826.1699999999</v>
       </c>
       <c r="G6">
-        <v>-1199.45</v>
+        <v>-1194.7</v>
       </c>
       <c r="H6">
-        <v>2644.93</v>
+        <v>2324.12</v>
       </c>
       <c r="K6">
-        <v>-1199.45</v>
+        <v>-1194.7</v>
       </c>
       <c r="O6" t="s">
         <v>39</v>
@@ -945,12 +930,12 @@
         <v>1</v>
       </c>
       <c r="AI6" s="1">
-        <v>46210.364490740743</v>
+        <v>46210.364444444444</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>9536</v>
+        <v>9531</v>
       </c>
       <c r="B7" t="s">
         <v>34</v>
@@ -962,19 +947,19 @@
         <v>35</v>
       </c>
       <c r="E7">
-        <v>436783.43</v>
+        <v>436577.55</v>
       </c>
       <c r="F7">
-        <v>6843613.6100000003</v>
+        <v>6843126.1299999999</v>
       </c>
       <c r="G7">
-        <v>-1194.3599999999999</v>
+        <v>-1199.45</v>
       </c>
       <c r="H7">
-        <v>3176.03</v>
+        <v>2644.93</v>
       </c>
       <c r="K7">
-        <v>-1194.3599999999999</v>
+        <v>-1199.45</v>
       </c>
       <c r="O7" t="s">
         <v>39</v>
@@ -992,12 +977,12 @@
         <v>1</v>
       </c>
       <c r="AI7" s="1">
-        <v>46210.364525462966</v>
+        <v>46210.364490740743</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>9537</v>
+        <v>9532</v>
       </c>
       <c r="B8" t="s">
         <v>34</v>
@@ -1009,19 +994,19 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>436892.21</v>
+        <v>436783.43</v>
       </c>
       <c r="F8">
-        <v>6843834.0800000001</v>
+        <v>6843613.6100000003</v>
       </c>
       <c r="G8">
-        <v>-1194.96</v>
+        <v>-1194.3599999999999</v>
       </c>
       <c r="H8">
-        <v>3421.98</v>
+        <v>3176.03</v>
       </c>
       <c r="K8">
-        <v>-1194.96</v>
+        <v>-1194.3599999999999</v>
       </c>
       <c r="O8" t="s">
         <v>39</v>
@@ -1039,12 +1024,12 @@
         <v>1</v>
       </c>
       <c r="AI8" s="1">
-        <v>46210.364560185182</v>
+        <v>46210.364525462966</v>
       </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>9538</v>
+        <v>9533</v>
       </c>
       <c r="B9" t="s">
         <v>34</v>
@@ -1056,19 +1041,19 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>436403.56</v>
+        <v>436892.21</v>
       </c>
       <c r="F9">
-        <v>6842645.7699999996</v>
+        <v>6843834.0800000001</v>
       </c>
       <c r="G9">
-        <v>-1196.8599999999999</v>
+        <v>-1194.96</v>
       </c>
       <c r="H9">
-        <v>2133.4299999999998</v>
+        <v>3421.98</v>
       </c>
       <c r="K9">
-        <v>-1196.8599999999999</v>
+        <v>-1194.96</v>
       </c>
       <c r="O9" t="s">
         <v>39</v>
@@ -1086,12 +1071,12 @@
         <v>1</v>
       </c>
       <c r="AI9" s="1">
-        <v>46210.364733796298</v>
+        <v>46210.364560185182</v>
       </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>9402</v>
+        <v>9399</v>
       </c>
       <c r="B10" t="s">
         <v>34</v>
@@ -1147,7 +1132,7 @@
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>9521</v>
+        <v>9517</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
@@ -1194,7 +1179,7 @@
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>9522</v>
+        <v>9520</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
@@ -1206,19 +1191,19 @@
         <v>40</v>
       </c>
       <c r="E12">
-        <v>436466.81</v>
+        <v>436389.76</v>
       </c>
       <c r="F12">
-        <v>6842831.1399999997</v>
+        <v>6842592.2999999998</v>
       </c>
       <c r="G12">
-        <v>-1194.7</v>
+        <v>-1197.57</v>
       </c>
       <c r="H12">
-        <v>2329.4699999999998</v>
+        <v>2078.1799999999998</v>
       </c>
       <c r="K12">
-        <v>-1194.7</v>
+        <v>-1197.57</v>
       </c>
       <c r="O12" t="s">
         <v>39</v>
@@ -1236,12 +1221,12 @@
         <v>1</v>
       </c>
       <c r="AI12" s="1">
-        <v>46210.364050925928</v>
+        <v>46210.36409722222</v>
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>9523</v>
+        <v>9519</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
@@ -1288,7 +1273,7 @@
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>9524</v>
+        <v>9535</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
@@ -1300,19 +1285,19 @@
         <v>40</v>
       </c>
       <c r="E14">
-        <v>436389.76</v>
+        <v>436414.48</v>
       </c>
       <c r="F14">
-        <v>6842592.2999999998</v>
+        <v>6842683.3899999997</v>
       </c>
       <c r="G14">
-        <v>-1197.57</v>
+        <v>-1195.68</v>
       </c>
       <c r="H14">
-        <v>2078.1799999999998</v>
+        <v>2172.63</v>
       </c>
       <c r="K14">
-        <v>-1197.57</v>
+        <v>-1195.68</v>
       </c>
       <c r="O14" t="s">
         <v>39</v>
@@ -1330,12 +1315,12 @@
         <v>1</v>
       </c>
       <c r="AI14" s="1">
-        <v>46210.36409722222</v>
+        <v>46210.364756944444</v>
       </c>
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>9525</v>
+        <v>9518</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
@@ -1347,19 +1332,19 @@
         <v>40</v>
       </c>
       <c r="E15">
-        <v>436502.51</v>
+        <v>436466.81</v>
       </c>
       <c r="F15">
-        <v>6842922.2400000002</v>
+        <v>6842831.1399999997</v>
       </c>
       <c r="G15">
-        <v>-1199.3900000000001</v>
+        <v>-1194.7</v>
       </c>
       <c r="H15">
-        <v>2427.4899999999998</v>
+        <v>2329.4699999999998</v>
       </c>
       <c r="K15">
-        <v>-1199.3900000000001</v>
+        <v>-1194.7</v>
       </c>
       <c r="O15" t="s">
         <v>39</v>
@@ -1377,12 +1362,12 @@
         <v>1</v>
       </c>
       <c r="AI15" s="1">
-        <v>46210.364120370374</v>
+        <v>46210.364050925928</v>
       </c>
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>9526</v>
+        <v>9521</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
@@ -1394,19 +1379,19 @@
         <v>40</v>
       </c>
       <c r="E16">
-        <v>436578.68</v>
+        <v>436502.51</v>
       </c>
       <c r="F16">
-        <v>6843129.5099999998</v>
+        <v>6842922.2400000002</v>
       </c>
       <c r="G16">
-        <v>-1199.4000000000001</v>
+        <v>-1199.3900000000001</v>
       </c>
       <c r="H16">
-        <v>2648.49</v>
+        <v>2427.4899999999998</v>
       </c>
       <c r="K16">
-        <v>-1199.4000000000001</v>
+        <v>-1199.3900000000001</v>
       </c>
       <c r="O16" t="s">
         <v>39</v>
@@ -1424,12 +1409,12 @@
         <v>1</v>
       </c>
       <c r="AI16" s="1">
-        <v>46210.36414351852</v>
+        <v>46210.364120370374</v>
       </c>
     </row>
     <row r="17" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>9527</v>
+        <v>9522</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
@@ -1441,19 +1426,19 @@
         <v>40</v>
       </c>
       <c r="E17">
-        <v>436607.87</v>
+        <v>436578.68</v>
       </c>
       <c r="F17">
-        <v>6843219.2800000003</v>
+        <v>6843129.5099999998</v>
       </c>
       <c r="G17">
-        <v>-1201.1500000000001</v>
+        <v>-1199.4000000000001</v>
       </c>
       <c r="H17">
-        <v>2742.95</v>
+        <v>2648.49</v>
       </c>
       <c r="K17">
-        <v>-1201.1500000000001</v>
+        <v>-1199.4000000000001</v>
       </c>
       <c r="O17" t="s">
         <v>39</v>
@@ -1471,12 +1456,12 @@
         <v>1</v>
       </c>
       <c r="AI17" s="1">
-        <v>46210.364155092589</v>
+        <v>46210.36414351852</v>
       </c>
     </row>
     <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>9528</v>
+        <v>9523</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -1488,19 +1473,19 @@
         <v>40</v>
       </c>
       <c r="E18">
-        <v>436782.63</v>
+        <v>436607.87</v>
       </c>
       <c r="F18">
-        <v>6843612.0199999996</v>
+        <v>6843219.2800000003</v>
       </c>
       <c r="G18">
-        <v>-1194.3900000000001</v>
+        <v>-1201.1500000000001</v>
       </c>
       <c r="H18">
-        <v>3174.25</v>
+        <v>2742.95</v>
       </c>
       <c r="K18">
-        <v>-1194.3900000000001</v>
+        <v>-1201.1500000000001</v>
       </c>
       <c r="O18" t="s">
         <v>39</v>
@@ -1518,12 +1503,12 @@
         <v>1</v>
       </c>
       <c r="AI18" s="1">
-        <v>46210.364189814813</v>
+        <v>46210.364155092589</v>
       </c>
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>9529</v>
+        <v>9524</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
@@ -1535,19 +1520,19 @@
         <v>40</v>
       </c>
       <c r="E19">
-        <v>436806.54</v>
+        <v>436782.63</v>
       </c>
       <c r="F19">
-        <v>6843659.8200000003</v>
+        <v>6843612.0199999996</v>
       </c>
       <c r="G19">
-        <v>-1193.95</v>
+        <v>-1194.3900000000001</v>
       </c>
       <c r="H19">
-        <v>3227.71</v>
+        <v>3174.25</v>
       </c>
       <c r="K19">
-        <v>-1193.95</v>
+        <v>-1194.3900000000001</v>
       </c>
       <c r="O19" t="s">
         <v>39</v>
@@ -1565,12 +1550,12 @@
         <v>1</v>
       </c>
       <c r="AI19" s="1">
-        <v>46210.364201388889</v>
+        <v>46210.364189814813</v>
       </c>
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>9530</v>
+        <v>9525</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
@@ -1582,19 +1567,19 @@
         <v>40</v>
       </c>
       <c r="E20">
-        <v>436891.45</v>
+        <v>436806.54</v>
       </c>
       <c r="F20">
-        <v>6843832.4699999997</v>
+        <v>6843659.8200000003</v>
       </c>
       <c r="G20">
-        <v>-1194.94</v>
+        <v>-1193.95</v>
       </c>
       <c r="H20">
-        <v>3420.2</v>
+        <v>3227.71</v>
       </c>
       <c r="K20">
-        <v>-1194.94</v>
+        <v>-1193.95</v>
       </c>
       <c r="O20" t="s">
         <v>39</v>
@@ -1612,12 +1597,12 @@
         <v>1</v>
       </c>
       <c r="AI20" s="1">
-        <v>46210.364236111112</v>
+        <v>46210.364201388889</v>
       </c>
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>9531</v>
+        <v>9526</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
@@ -1629,19 +1614,19 @@
         <v>40</v>
       </c>
       <c r="E21">
-        <v>436896.6</v>
+        <v>436891.45</v>
       </c>
       <c r="F21">
-        <v>6843843.8300000001</v>
+        <v>6843832.4699999997</v>
       </c>
       <c r="G21">
-        <v>-1195.1199999999999</v>
+        <v>-1194.94</v>
       </c>
       <c r="H21">
-        <v>3432.67</v>
+        <v>3420.2</v>
       </c>
       <c r="K21">
-        <v>-1195.1199999999999</v>
+        <v>-1194.94</v>
       </c>
       <c r="O21" t="s">
         <v>39</v>
@@ -1659,12 +1644,12 @@
         <v>1</v>
       </c>
       <c r="AI21" s="1">
-        <v>46210.364259259259</v>
+        <v>46210.364236111112</v>
       </c>
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>9539</v>
+        <v>9527</v>
       </c>
       <c r="B22" t="s">
         <v>34</v>
@@ -1676,19 +1661,19 @@
         <v>40</v>
       </c>
       <c r="E22">
-        <v>436414.48</v>
+        <v>436896.6</v>
       </c>
       <c r="F22">
-        <v>6842683.3899999997</v>
+        <v>6843843.8300000001</v>
       </c>
       <c r="G22">
-        <v>-1195.68</v>
+        <v>-1195.1199999999999</v>
       </c>
       <c r="H22">
-        <v>2172.63</v>
+        <v>3432.67</v>
       </c>
       <c r="K22">
-        <v>-1195.68</v>
+        <v>-1195.1199999999999</v>
       </c>
       <c r="O22" t="s">
         <v>39</v>
@@ -1706,12 +1691,12 @@
         <v>1</v>
       </c>
       <c r="AI22" s="1">
-        <v>46210.364756944444</v>
+        <v>46210.364259259259</v>
       </c>
     </row>
     <row r="23" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>9423</v>
+        <v>9420</v>
       </c>
       <c r="B23" t="s">
         <v>41</v>
@@ -1767,7 +1752,7 @@
     </row>
     <row r="24" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>9479</v>
+        <v>9475</v>
       </c>
       <c r="B24" t="s">
         <v>41</v>
@@ -1779,19 +1764,19 @@
         <v>35</v>
       </c>
       <c r="E24">
-        <v>438229.47</v>
+        <v>438186.23</v>
       </c>
       <c r="F24">
-        <v>6843490.5700000003</v>
+        <v>6843517.8499999996</v>
       </c>
       <c r="G24">
-        <v>-1190.4000000000001</v>
+        <v>-1189.1400000000001</v>
       </c>
       <c r="H24">
-        <v>1875.54</v>
+        <v>1926.7</v>
       </c>
       <c r="K24">
-        <v>-1190.4000000000001</v>
+        <v>-1189.1400000000001</v>
       </c>
       <c r="O24" t="s">
         <v>39</v>
@@ -1809,12 +1794,12 @@
         <v>1</v>
       </c>
       <c r="AI24" s="1">
-        <v>46210.354942129627</v>
+        <v>46210.470902777779</v>
       </c>
     </row>
     <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>9480</v>
+        <v>9476</v>
       </c>
       <c r="B25" t="s">
         <v>41</v>
@@ -1861,7 +1846,7 @@
     </row>
     <row r="26" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>9481</v>
+        <v>9477</v>
       </c>
       <c r="B26" t="s">
         <v>41</v>
@@ -1908,7 +1893,7 @@
     </row>
     <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>9482</v>
+        <v>9478</v>
       </c>
       <c r="B27" t="s">
         <v>41</v>
@@ -1955,7 +1940,7 @@
     </row>
     <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>9483</v>
+        <v>9479</v>
       </c>
       <c r="B28" t="s">
         <v>41</v>
@@ -2002,7 +1987,7 @@
     </row>
     <row r="29" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>9484</v>
+        <v>9480</v>
       </c>
       <c r="B29" t="s">
         <v>41</v>
@@ -2049,7 +2034,7 @@
     </row>
     <row r="30" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>9421</v>
+        <v>9418</v>
       </c>
       <c r="B30" t="s">
         <v>41</v>
@@ -2105,37 +2090,34 @@
     </row>
     <row r="31" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>9418</v>
+        <v>9548</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C31">
-        <v>350233020918</v>
+        <v>350233020912</v>
       </c>
       <c r="D31" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E31">
-        <v>438773.21</v>
+        <v>438186.23</v>
       </c>
       <c r="F31">
-        <v>6844295.4199999999</v>
+        <v>6843517.8499999996</v>
       </c>
       <c r="G31">
-        <v>-1152.67</v>
+        <v>-1189.1400000000001</v>
       </c>
       <c r="H31">
-        <v>1496</v>
+        <v>1926.7</v>
       </c>
       <c r="K31">
-        <v>-1152.67</v>
+        <v>-1189.1400000000001</v>
       </c>
       <c r="O31" t="s">
-        <v>36</v>
-      </c>
-      <c r="P31">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U31" t="b">
         <v>1</v>
@@ -2149,43 +2131,37 @@
       <c r="X31" t="b">
         <v>1</v>
       </c>
-      <c r="AD31">
-        <v>1</v>
-      </c>
-      <c r="AF31" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI31" t="s">
-        <v>42</v>
+      <c r="AI31" s="1">
+        <v>46210.470925925925</v>
       </c>
     </row>
     <row r="32" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>9485</v>
+        <v>9549</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C32">
-        <v>350233020918</v>
+        <v>350233020912</v>
       </c>
       <c r="D32" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E32">
-        <v>439321.59</v>
+        <v>438080.63</v>
       </c>
       <c r="F32">
-        <v>6844697.9500000002</v>
+        <v>6843582.8099999996</v>
       </c>
       <c r="G32">
-        <v>-1192.57</v>
+        <v>-1189.43</v>
       </c>
       <c r="H32">
-        <v>2180.02</v>
+        <v>2050.75</v>
       </c>
       <c r="K32">
-        <v>-1192.57</v>
+        <v>-1189.43</v>
       </c>
       <c r="O32" t="s">
         <v>39</v>
@@ -2203,36 +2179,36 @@
         <v>1</v>
       </c>
       <c r="AI32" s="1">
-        <v>46210.355092592596</v>
+        <v>46210.470590277779</v>
       </c>
     </row>
     <row r="33" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>9486</v>
+        <v>9550</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C33">
-        <v>350233020918</v>
+        <v>350233020912</v>
       </c>
       <c r="D33" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E33">
-        <v>439568.52</v>
+        <v>438044.17</v>
       </c>
       <c r="F33">
-        <v>6844880.6900000004</v>
+        <v>6843605.0999999996</v>
       </c>
       <c r="G33">
-        <v>-1194.08</v>
+        <v>-1190.67</v>
       </c>
       <c r="H33">
-        <v>2487.4499999999998</v>
+        <v>2093.52</v>
       </c>
       <c r="K33">
-        <v>-1194.08</v>
+        <v>-1190.67</v>
       </c>
       <c r="O33" t="s">
         <v>39</v>
@@ -2250,36 +2226,36 @@
         <v>1</v>
       </c>
       <c r="AI33" s="1">
-        <v>46210.355104166665</v>
+        <v>46210.470625000002</v>
       </c>
     </row>
     <row r="34" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>9487</v>
+        <v>9551</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C34">
-        <v>350233020918</v>
+        <v>350233020912</v>
       </c>
       <c r="D34" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E34">
-        <v>439858.53</v>
+        <v>437962.27</v>
       </c>
       <c r="F34">
-        <v>6845107.1100000003</v>
+        <v>6843655.5599999996</v>
       </c>
       <c r="G34">
-        <v>-1192.99</v>
+        <v>-1191.6099999999999</v>
       </c>
       <c r="H34">
-        <v>2855.78</v>
+        <v>2189.7600000000002</v>
       </c>
       <c r="K34">
-        <v>-1192.99</v>
+        <v>-1191.6099999999999</v>
       </c>
       <c r="O34" t="s">
         <v>39</v>
@@ -2297,36 +2273,36 @@
         <v>1</v>
       </c>
       <c r="AI34" s="1">
-        <v>46210.355127314811</v>
+        <v>46210.470648148148</v>
       </c>
     </row>
     <row r="35" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>9488</v>
+        <v>9552</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C35">
-        <v>350233020918</v>
+        <v>350233020912</v>
       </c>
       <c r="D35" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E35">
-        <v>440068.05</v>
+        <v>437919.35</v>
       </c>
       <c r="F35">
-        <v>6845252.75</v>
+        <v>6843683.6799999997</v>
       </c>
       <c r="G35">
-        <v>-1191.6199999999999</v>
+        <v>-1191.9100000000001</v>
       </c>
       <c r="H35">
-        <v>3111.23</v>
+        <v>2241.09</v>
       </c>
       <c r="K35">
-        <v>-1191.6199999999999</v>
+        <v>-1191.9100000000001</v>
       </c>
       <c r="O35" t="s">
         <v>39</v>
@@ -2344,42 +2320,39 @@
         <v>1</v>
       </c>
       <c r="AI35" s="1">
-        <v>46210.355150462965</v>
+        <v>46210.470671296294</v>
       </c>
     </row>
     <row r="36" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>9414</v>
+        <v>9553</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C36">
-        <v>350233020918</v>
+        <v>350233020912</v>
       </c>
       <c r="D36" t="s">
         <v>40</v>
       </c>
       <c r="E36">
-        <v>439117.61</v>
+        <v>437866.27</v>
       </c>
       <c r="F36">
-        <v>6844540.2800000003</v>
+        <v>6843719.5800000001</v>
       </c>
       <c r="G36">
-        <v>-1196.21</v>
+        <v>-1194.48</v>
       </c>
       <c r="H36">
-        <v>1922</v>
+        <v>2305.25</v>
       </c>
       <c r="K36">
-        <v>-1196.21</v>
+        <v>-1194.48</v>
       </c>
       <c r="O36" t="s">
-        <v>36</v>
-      </c>
-      <c r="P36">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U36" t="b">
         <v>1</v>
@@ -2393,43 +2366,37 @@
       <c r="X36" t="b">
         <v>1</v>
       </c>
-      <c r="AD36">
-        <v>1</v>
-      </c>
-      <c r="AF36" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI36" t="s">
-        <v>43</v>
+      <c r="AI36" s="1">
+        <v>46210.470694444448</v>
       </c>
     </row>
     <row r="37" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>9501</v>
+        <v>9554</v>
       </c>
       <c r="B37" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C37">
-        <v>350233020918</v>
+        <v>350233020912</v>
       </c>
       <c r="D37" t="s">
         <v>40</v>
       </c>
       <c r="E37">
-        <v>439320.41</v>
+        <v>437688.75</v>
       </c>
       <c r="F37">
-        <v>6844697.04</v>
+        <v>6843838.4699999997</v>
       </c>
       <c r="G37">
-        <v>-1192.56</v>
+        <v>-1195.69</v>
       </c>
       <c r="H37">
-        <v>2178.5300000000002</v>
+        <v>2519.12</v>
       </c>
       <c r="K37">
-        <v>-1192.56</v>
+        <v>-1195.69</v>
       </c>
       <c r="O37" t="s">
         <v>39</v>
@@ -2447,36 +2414,36 @@
         <v>1</v>
       </c>
       <c r="AI37" s="1">
-        <v>46210.356064814812</v>
+        <v>46210.470729166664</v>
       </c>
     </row>
     <row r="38" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>9502</v>
+        <v>9555</v>
       </c>
       <c r="B38" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C38">
-        <v>350233020918</v>
+        <v>350233020912</v>
       </c>
       <c r="D38" t="s">
         <v>40</v>
       </c>
       <c r="E38">
-        <v>439570.83</v>
+        <v>437621.78</v>
       </c>
       <c r="F38">
-        <v>6844882.5599999996</v>
+        <v>6843880.5</v>
       </c>
       <c r="G38">
-        <v>-1194.08</v>
+        <v>-1195.71</v>
       </c>
       <c r="H38">
-        <v>2490.42</v>
+        <v>2598.25</v>
       </c>
       <c r="K38">
-        <v>-1194.08</v>
+        <v>-1195.71</v>
       </c>
       <c r="O38" t="s">
         <v>39</v>
@@ -2494,36 +2461,36 @@
         <v>1</v>
       </c>
       <c r="AI38" s="1">
-        <v>46210.356099537035</v>
+        <v>46210.47074074074</v>
       </c>
     </row>
     <row r="39" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>9503</v>
+        <v>9556</v>
       </c>
       <c r="B39" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C39">
-        <v>350233020918</v>
+        <v>350233020912</v>
       </c>
       <c r="D39" t="s">
         <v>40</v>
       </c>
       <c r="E39">
-        <v>439859.69</v>
+        <v>437313.51</v>
       </c>
       <c r="F39">
-        <v>6845108.0300000003</v>
+        <v>6844080.8099999996</v>
       </c>
       <c r="G39">
-        <v>-1192.96</v>
+        <v>-1195.1199999999999</v>
       </c>
       <c r="H39">
-        <v>2857.27</v>
+        <v>2966.1</v>
       </c>
       <c r="K39">
-        <v>-1192.96</v>
+        <v>-1195.1199999999999</v>
       </c>
       <c r="O39" t="s">
         <v>39</v>
@@ -2541,36 +2508,36 @@
         <v>1</v>
       </c>
       <c r="AI39" s="1">
-        <v>46210.356134259258</v>
+        <v>46210.47078703704</v>
       </c>
     </row>
     <row r="40" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>9504</v>
+        <v>9557</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C40">
-        <v>350233020918</v>
+        <v>350233020912</v>
       </c>
       <c r="D40" t="s">
         <v>40</v>
       </c>
       <c r="E40">
-        <v>440068.05</v>
+        <v>437277.84</v>
       </c>
       <c r="F40">
-        <v>6845252.75</v>
+        <v>6844104.3399999999</v>
       </c>
       <c r="G40">
-        <v>-1191.6199999999999</v>
+        <v>-1196.52</v>
       </c>
       <c r="H40">
-        <v>3111.23</v>
+        <v>3008.87</v>
       </c>
       <c r="K40">
-        <v>-1191.6199999999999</v>
+        <v>-1196.52</v>
       </c>
       <c r="O40" t="s">
         <v>39</v>
@@ -2588,42 +2555,39 @@
         <v>1</v>
       </c>
       <c r="AI40" s="1">
-        <v>46210.356180555558</v>
+        <v>46210.47079861111</v>
       </c>
     </row>
     <row r="41" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>204</v>
+        <v>9558</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C41">
-        <v>170663036</v>
+        <v>350233020912</v>
       </c>
       <c r="D41" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E41">
-        <v>441222.09</v>
+        <v>437059.97</v>
       </c>
       <c r="F41">
-        <v>6851676.21</v>
+        <v>6844247.6200000001</v>
       </c>
       <c r="G41">
-        <v>-1171.48</v>
+        <v>-1197.8699999999999</v>
       </c>
       <c r="H41">
-        <v>1366.82</v>
+        <v>3269.79</v>
       </c>
       <c r="K41">
-        <v>-1171.48</v>
+        <v>-1197.8699999999999</v>
       </c>
       <c r="O41" t="s">
-        <v>36</v>
-      </c>
-      <c r="P41">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U41" t="b">
         <v>1</v>
@@ -2635,54 +2599,45 @@
         <v>37</v>
       </c>
       <c r="X41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD41">
-        <v>1</v>
-      </c>
-      <c r="AE41" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF41" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI41" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="AI41" s="1">
+        <v>46210.470833333333</v>
       </c>
     </row>
     <row r="42" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>9475</v>
+        <v>9415</v>
       </c>
       <c r="B42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C42">
-        <v>170663036</v>
+        <v>350233020918</v>
       </c>
       <c r="D42" t="s">
         <v>35</v>
       </c>
       <c r="E42">
-        <v>441033.44</v>
+        <v>438773.21</v>
       </c>
       <c r="F42">
-        <v>6851386.8600000003</v>
+        <v>6844295.4199999999</v>
       </c>
       <c r="G42">
-        <v>-1220.9100000000001</v>
+        <v>-1152.67</v>
       </c>
       <c r="H42">
-        <v>1719.13</v>
+        <v>1496</v>
       </c>
       <c r="K42">
-        <v>-1220.9100000000001</v>
+        <v>-1152.67</v>
       </c>
       <c r="O42" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P42">
+        <v>1</v>
       </c>
       <c r="U42" t="b">
         <v>1</v>
@@ -2696,37 +2651,43 @@
       <c r="X42" t="b">
         <v>1</v>
       </c>
-      <c r="AI42" s="1">
-        <v>46210.356400462966</v>
+      <c r="AD42">
+        <v>1</v>
+      </c>
+      <c r="AF42" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI42" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>9476</v>
+        <v>9481</v>
       </c>
       <c r="B43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C43">
-        <v>170663036</v>
+        <v>350233020918</v>
       </c>
       <c r="D43" t="s">
         <v>35</v>
       </c>
       <c r="E43">
-        <v>440512.21</v>
+        <v>439321.59</v>
       </c>
       <c r="F43">
-        <v>6850770.25</v>
+        <v>6844697.9500000002</v>
       </c>
       <c r="G43">
-        <v>-1224.01</v>
+        <v>-1192.57</v>
       </c>
       <c r="H43">
-        <v>2527.08</v>
+        <v>2180.02</v>
       </c>
       <c r="K43">
-        <v>-1224.01</v>
+        <v>-1192.57</v>
       </c>
       <c r="O43" t="s">
         <v>39</v>
@@ -2744,36 +2705,36 @@
         <v>1</v>
       </c>
       <c r="AI43" s="1">
-        <v>46210.354733796295</v>
+        <v>46210.355092592596</v>
       </c>
     </row>
     <row r="44" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>9477</v>
+        <v>9482</v>
       </c>
       <c r="B44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C44">
-        <v>170663036</v>
+        <v>350233020918</v>
       </c>
       <c r="D44" t="s">
         <v>35</v>
       </c>
       <c r="E44">
-        <v>440341.22</v>
+        <v>439568.52</v>
       </c>
       <c r="F44">
-        <v>6850564.9400000004</v>
+        <v>6844880.6900000004</v>
       </c>
       <c r="G44">
-        <v>-1223.3499999999999</v>
+        <v>-1194.08</v>
       </c>
       <c r="H44">
-        <v>2794.41</v>
+        <v>2487.4499999999998</v>
       </c>
       <c r="K44">
-        <v>-1223.3499999999999</v>
+        <v>-1194.08</v>
       </c>
       <c r="O44" t="s">
         <v>39</v>
@@ -2791,36 +2752,36 @@
         <v>1</v>
       </c>
       <c r="AI44" s="1">
-        <v>46210.356458333335</v>
+        <v>46210.355104166665</v>
       </c>
     </row>
     <row r="45" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>9478</v>
+        <v>9483</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C45">
-        <v>170663036</v>
+        <v>350233020918</v>
       </c>
       <c r="D45" t="s">
         <v>35</v>
       </c>
       <c r="E45">
-        <v>439767.53</v>
+        <v>439858.53</v>
       </c>
       <c r="F45">
-        <v>6849879.8799999999</v>
+        <v>6845107.1100000003</v>
       </c>
       <c r="G45">
-        <v>-1223.93</v>
+        <v>-1192.99</v>
       </c>
       <c r="H45">
-        <v>3688.49</v>
+        <v>2855.78</v>
       </c>
       <c r="K45">
-        <v>-1223.93</v>
+        <v>-1192.99</v>
       </c>
       <c r="O45" t="s">
         <v>39</v>
@@ -2838,42 +2799,39 @@
         <v>1</v>
       </c>
       <c r="AI45" s="1">
-        <v>46210.354861111111</v>
+        <v>46210.355127314811</v>
       </c>
     </row>
     <row r="46" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>2803</v>
+        <v>9484</v>
       </c>
       <c r="B46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C46">
-        <v>170663036</v>
+        <v>350233020918</v>
       </c>
       <c r="D46" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E46">
-        <v>440342.86</v>
+        <v>440068.05</v>
       </c>
       <c r="F46">
-        <v>6850566.7999999998</v>
+        <v>6845252.75</v>
       </c>
       <c r="G46">
-        <v>-1223.3599999999999</v>
+        <v>-1191.6199999999999</v>
       </c>
       <c r="H46">
-        <v>2791.93</v>
+        <v>3111.23</v>
       </c>
       <c r="K46">
-        <v>-1223.3599999999999</v>
+        <v>-1191.6199999999999</v>
       </c>
       <c r="O46" t="s">
-        <v>36</v>
-      </c>
-      <c r="P46">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="U46" t="b">
         <v>1</v>
@@ -2885,57 +2843,45 @@
         <v>37</v>
       </c>
       <c r="X46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD46">
-        <v>2</v>
-      </c>
-      <c r="AE46" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF46" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI46" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI46" s="1">
+        <v>46210.355150462965</v>
       </c>
     </row>
     <row r="47" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>2829</v>
+        <v>9411</v>
       </c>
       <c r="B47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C47">
-        <v>170663036</v>
+        <v>350233020918</v>
       </c>
       <c r="D47" t="s">
         <v>40</v>
       </c>
       <c r="E47">
-        <v>441032.23</v>
+        <v>439117.61</v>
       </c>
       <c r="F47">
-        <v>6851385.3399999999</v>
+        <v>6844540.2800000003</v>
       </c>
       <c r="G47">
-        <v>-1220.92</v>
+        <v>-1196.21</v>
       </c>
       <c r="H47">
-        <v>1721.08</v>
+        <v>1922</v>
       </c>
       <c r="K47">
-        <v>-1220.92</v>
+        <v>-1196.21</v>
       </c>
       <c r="O47" t="s">
         <v>36</v>
       </c>
       <c r="P47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U47" t="b">
         <v>1</v>
@@ -2947,19 +2893,13 @@
         <v>37</v>
       </c>
       <c r="X47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC47" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="AD47">
-        <v>2</v>
-      </c>
-      <c r="AE47" t="s">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="AF47" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AI47" t="s">
         <v>43</v>
@@ -2967,37 +2907,34 @@
     </row>
     <row r="48" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>2842</v>
+        <v>9497</v>
       </c>
       <c r="B48" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C48">
-        <v>170663036</v>
+        <v>350233020918</v>
       </c>
       <c r="D48" t="s">
         <v>40</v>
       </c>
       <c r="E48">
-        <v>440418.16</v>
+        <v>439320.41</v>
       </c>
       <c r="F48">
-        <v>6850655.1900000004</v>
+        <v>6844697.04</v>
       </c>
       <c r="G48">
-        <v>-1224.54</v>
+        <v>-1192.56</v>
       </c>
       <c r="H48">
-        <v>2675.74</v>
+        <v>2178.5300000000002</v>
       </c>
       <c r="K48">
-        <v>-1224.54</v>
+        <v>-1192.56</v>
       </c>
       <c r="O48" t="s">
-        <v>36</v>
-      </c>
-      <c r="P48">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="U48" t="b">
         <v>1</v>
@@ -3009,57 +2946,42 @@
         <v>37</v>
       </c>
       <c r="X48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD48">
-        <v>2</v>
-      </c>
-      <c r="AE48" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF48" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI48" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI48" s="1">
+        <v>46210.356064814812</v>
       </c>
     </row>
     <row r="49" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>2889</v>
+        <v>9498</v>
       </c>
       <c r="B49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C49">
-        <v>170663036</v>
+        <v>350233020918</v>
       </c>
       <c r="D49" t="s">
         <v>40</v>
       </c>
       <c r="E49">
-        <v>441096.49</v>
+        <v>439570.83</v>
       </c>
       <c r="F49">
-        <v>6851469.9900000002</v>
+        <v>6844882.5599999996</v>
       </c>
       <c r="G49">
-        <v>-1220.21</v>
+        <v>-1194.08</v>
       </c>
       <c r="H49">
-        <v>1614.73</v>
+        <v>2490.42</v>
       </c>
       <c r="K49">
-        <v>-1220.21</v>
+        <v>-1194.08</v>
       </c>
       <c r="O49" t="s">
-        <v>36</v>
-      </c>
-      <c r="P49">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U49" t="b">
         <v>1</v>
@@ -3071,57 +2993,42 @@
         <v>37</v>
       </c>
       <c r="X49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC49" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD49">
-        <v>1</v>
-      </c>
-      <c r="AE49" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF49" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI49" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI49" s="1">
+        <v>46210.356099537035</v>
       </c>
     </row>
     <row r="50" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>2906</v>
+        <v>9499</v>
       </c>
       <c r="B50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C50">
-        <v>170663036</v>
+        <v>350233020918</v>
       </c>
       <c r="D50" t="s">
         <v>40</v>
       </c>
       <c r="E50">
-        <v>440333.56</v>
+        <v>439859.69</v>
       </c>
       <c r="F50">
-        <v>6850556.2999999998</v>
+        <v>6845108.0300000003</v>
       </c>
       <c r="G50">
-        <v>-1223.3800000000001</v>
+        <v>-1192.96</v>
       </c>
       <c r="H50">
-        <v>2805.96</v>
+        <v>2857.27</v>
       </c>
       <c r="K50">
-        <v>-1223.3800000000001</v>
+        <v>-1192.96</v>
       </c>
       <c r="O50" t="s">
-        <v>36</v>
-      </c>
-      <c r="P50">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="U50" t="b">
         <v>1</v>
@@ -3133,57 +3040,42 @@
         <v>37</v>
       </c>
       <c r="X50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD50">
-        <v>2</v>
-      </c>
-      <c r="AE50" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF50" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI50" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI50" s="1">
+        <v>46210.356134259258</v>
       </c>
     </row>
     <row r="51" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>2931</v>
+        <v>9500</v>
       </c>
       <c r="B51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C51">
-        <v>170663036</v>
+        <v>350233020918</v>
       </c>
       <c r="D51" t="s">
         <v>40</v>
       </c>
       <c r="E51">
-        <v>440510.27</v>
+        <v>440068.05</v>
       </c>
       <c r="F51">
-        <v>6850767.8700000001</v>
+        <v>6845252.75</v>
       </c>
       <c r="G51">
-        <v>-1224.02</v>
+        <v>-1191.6199999999999</v>
       </c>
       <c r="H51">
-        <v>2530.15</v>
+        <v>3111.23</v>
       </c>
       <c r="K51">
-        <v>-1224.02</v>
+        <v>-1191.6199999999999</v>
       </c>
       <c r="O51" t="s">
-        <v>36</v>
-      </c>
-      <c r="P51">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="U51" t="b">
         <v>1</v>
@@ -3195,27 +3087,15 @@
         <v>37</v>
       </c>
       <c r="X51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD51">
-        <v>2</v>
-      </c>
-      <c r="AE51" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF51" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI51" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI51" s="1">
+        <v>46210.356180555558</v>
       </c>
     </row>
     <row r="52" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>3003</v>
+        <v>204</v>
       </c>
       <c r="B52" t="s">
         <v>45</v>
@@ -3224,28 +3104,28 @@
         <v>170663036</v>
       </c>
       <c r="D52" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E52">
-        <v>440341.15</v>
+        <v>441222.09</v>
       </c>
       <c r="F52">
-        <v>6850564.8700000001</v>
+        <v>6851676.21</v>
       </c>
       <c r="G52">
-        <v>-1223.3499999999999</v>
+        <v>-1171.48</v>
       </c>
       <c r="H52">
-        <v>2794.51</v>
+        <v>1366.82</v>
       </c>
       <c r="K52">
-        <v>-1223.3499999999999</v>
+        <v>-1171.48</v>
       </c>
       <c r="O52" t="s">
         <v>36</v>
       </c>
       <c r="P52">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="U52" t="b">
         <v>1</v>
@@ -3263,21 +3143,21 @@
         <v>46</v>
       </c>
       <c r="AD52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE52" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AF52" t="s">
         <v>48</v>
       </c>
       <c r="AI52" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>3106</v>
+        <v>9471</v>
       </c>
       <c r="B53" t="s">
         <v>45</v>
@@ -3286,28 +3166,25 @@
         <v>170663036</v>
       </c>
       <c r="D53" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E53">
-        <v>439766.64</v>
+        <v>441033.44</v>
       </c>
       <c r="F53">
-        <v>6849878.79</v>
+        <v>6851386.8600000003</v>
       </c>
       <c r="G53">
-        <v>-1223.93</v>
+        <v>-1220.9100000000001</v>
       </c>
       <c r="H53">
-        <v>3689.9</v>
+        <v>1719.13</v>
       </c>
       <c r="K53">
-        <v>-1223.93</v>
+        <v>-1220.9100000000001</v>
       </c>
       <c r="O53" t="s">
-        <v>36</v>
-      </c>
-      <c r="P53">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="U53" t="b">
         <v>1</v>
@@ -3319,27 +3196,15 @@
         <v>37</v>
       </c>
       <c r="X53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD53">
-        <v>2</v>
-      </c>
-      <c r="AE53" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF53" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI53" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI53" s="1">
+        <v>46210.356400462966</v>
       </c>
     </row>
     <row r="54" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>3137</v>
+        <v>9472</v>
       </c>
       <c r="B54" t="s">
         <v>45</v>
@@ -3348,28 +3213,25 @@
         <v>170663036</v>
       </c>
       <c r="D54" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E54">
-        <v>441009.95</v>
+        <v>440512.21</v>
       </c>
       <c r="F54">
-        <v>6851357.1299999999</v>
+        <v>6850770.25</v>
       </c>
       <c r="G54">
-        <v>-1221.3699999999999</v>
+        <v>-1224.01</v>
       </c>
       <c r="H54">
-        <v>1757.04</v>
+        <v>2527.08</v>
       </c>
       <c r="K54">
-        <v>-1221.3699999999999</v>
+        <v>-1224.01</v>
       </c>
       <c r="O54" t="s">
-        <v>36</v>
-      </c>
-      <c r="P54">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="U54" t="b">
         <v>1</v>
@@ -3381,27 +3243,15 @@
         <v>37</v>
       </c>
       <c r="X54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC54" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD54">
-        <v>2</v>
-      </c>
-      <c r="AE54" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF54" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI54" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI54" s="1">
+        <v>46210.354733796295</v>
       </c>
     </row>
     <row r="55" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>3150</v>
+        <v>9473</v>
       </c>
       <c r="B55" t="s">
         <v>45</v>
@@ -3410,28 +3260,25 @@
         <v>170663036</v>
       </c>
       <c r="D55" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E55">
-        <v>440337.49</v>
+        <v>440354.39</v>
       </c>
       <c r="F55">
-        <v>6850560.7400000002</v>
+        <v>6850579.9800000004</v>
       </c>
       <c r="G55">
-        <v>-1223.3499999999999</v>
+        <v>-1223.6300000000001</v>
       </c>
       <c r="H55">
-        <v>2800.03</v>
+        <v>2774.4</v>
       </c>
       <c r="K55">
-        <v>-1223.3499999999999</v>
+        <v>-1223.6300000000001</v>
       </c>
       <c r="O55" t="s">
-        <v>36</v>
-      </c>
-      <c r="P55">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="U55" t="b">
         <v>1</v>
@@ -3443,57 +3290,42 @@
         <v>37</v>
       </c>
       <c r="X55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC55" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD55">
-        <v>2</v>
-      </c>
-      <c r="AE55" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF55" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI55" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI55" s="1">
+        <v>46210.471307870372</v>
       </c>
     </row>
     <row r="56" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>8975</v>
+        <v>9474</v>
       </c>
       <c r="B56" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C56">
-        <v>350114731284</v>
+        <v>170663036</v>
       </c>
       <c r="D56" t="s">
         <v>35</v>
       </c>
       <c r="E56">
-        <v>446199.44</v>
+        <v>439767.53</v>
       </c>
       <c r="F56">
-        <v>6850194.21</v>
+        <v>6849879.8799999999</v>
       </c>
       <c r="G56">
-        <v>-1158.96</v>
+        <v>-1223.93</v>
       </c>
       <c r="H56">
-        <v>1395.4</v>
+        <v>3688.49</v>
       </c>
       <c r="K56">
-        <v>-1158.96</v>
+        <v>-1223.93</v>
       </c>
       <c r="O56" t="s">
-        <v>36</v>
-      </c>
-      <c r="P56">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U56" t="b">
         <v>1</v>
@@ -3505,51 +3337,45 @@
         <v>37</v>
       </c>
       <c r="X56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD56">
-        <v>1</v>
-      </c>
-      <c r="AF56" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI56" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="AI56" s="1">
+        <v>46210.354861111111</v>
       </c>
     </row>
     <row r="57" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>8981</v>
+        <v>2888</v>
       </c>
       <c r="B57" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C57">
-        <v>350114731284</v>
+        <v>170663036</v>
       </c>
       <c r="D57" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E57">
-        <v>446583.23</v>
+        <v>441096.49</v>
       </c>
       <c r="F57">
-        <v>6849647.3499999996</v>
+        <v>6851469.9900000002</v>
       </c>
       <c r="G57">
-        <v>-1207.8499999999999</v>
+        <v>-1220.21</v>
       </c>
       <c r="H57">
-        <v>2068</v>
+        <v>1614.73</v>
       </c>
       <c r="K57">
-        <v>-1207.8499999999999</v>
+        <v>-1220.21</v>
       </c>
       <c r="O57" t="s">
         <v>36</v>
       </c>
       <c r="P57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U57" t="b">
         <v>1</v>
@@ -3563,46 +3389,55 @@
       <c r="X57" t="b">
         <v>0</v>
       </c>
+      <c r="AC57" t="s">
+        <v>46</v>
+      </c>
       <c r="AD57">
         <v>1</v>
       </c>
+      <c r="AE57" t="s">
+        <v>47</v>
+      </c>
       <c r="AF57" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AI57" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>9492</v>
+        <v>2828</v>
       </c>
       <c r="B58" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C58">
-        <v>350114731284</v>
+        <v>170663036</v>
       </c>
       <c r="D58" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E58">
-        <v>446427.76</v>
+        <v>441032.23</v>
       </c>
       <c r="F58">
-        <v>6849872.9299999997</v>
+        <v>6851385.3399999999</v>
       </c>
       <c r="G58">
-        <v>-1202.22</v>
+        <v>-1220.92</v>
       </c>
       <c r="H58">
-        <v>1793.72</v>
+        <v>1721.08</v>
       </c>
       <c r="K58">
-        <v>-1202.22</v>
+        <v>-1220.92</v>
       </c>
       <c r="O58" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P58">
+        <v>2</v>
       </c>
       <c r="U58" t="b">
         <v>1</v>
@@ -3614,45 +3449,57 @@
         <v>37</v>
       </c>
       <c r="X58" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI58" s="1">
-        <v>46210.355532407404</v>
+        <v>0</v>
+      </c>
+      <c r="AC58" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD58">
+        <v>2</v>
+      </c>
+      <c r="AE58" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF58" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI58" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>8973</v>
+        <v>3135</v>
       </c>
       <c r="B59" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C59">
-        <v>350114731284</v>
+        <v>170663036</v>
       </c>
       <c r="D59" t="s">
         <v>40</v>
       </c>
       <c r="E59">
-        <v>446360.95</v>
+        <v>441009.95</v>
       </c>
       <c r="F59">
-        <v>6849967.1799999997</v>
+        <v>6851357.1299999999</v>
       </c>
       <c r="G59">
-        <v>-1203.1600000000001</v>
+        <v>-1221.3699999999999</v>
       </c>
       <c r="H59">
-        <v>1678.1</v>
+        <v>1757.04</v>
       </c>
       <c r="K59">
-        <v>-1203.1600000000001</v>
+        <v>-1221.3699999999999</v>
       </c>
       <c r="O59" t="s">
         <v>36</v>
       </c>
       <c r="P59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U59" t="b">
         <v>1</v>
@@ -3666,11 +3513,17 @@
       <c r="X59" t="b">
         <v>0</v>
       </c>
+      <c r="AC59" t="s">
+        <v>46</v>
+      </c>
       <c r="AD59">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AE59" t="s">
+        <v>49</v>
       </c>
       <c r="AF59" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AI59" t="s">
         <v>43</v>
@@ -3678,37 +3531,37 @@
     </row>
     <row r="60" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>8979</v>
+        <v>2929</v>
       </c>
       <c r="B60" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C60">
-        <v>350114731284</v>
+        <v>170663036</v>
       </c>
       <c r="D60" t="s">
         <v>40</v>
       </c>
       <c r="E60">
-        <v>446595.09</v>
+        <v>440510.27</v>
       </c>
       <c r="F60">
-        <v>6849630.04</v>
+        <v>6850767.8700000001</v>
       </c>
       <c r="G60">
-        <v>-1207.8699999999999</v>
+        <v>-1224.02</v>
       </c>
       <c r="H60">
-        <v>2089</v>
+        <v>2530.15</v>
       </c>
       <c r="K60">
-        <v>-1207.8699999999999</v>
+        <v>-1224.02</v>
       </c>
       <c r="O60" t="s">
         <v>36</v>
       </c>
       <c r="P60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U60" t="b">
         <v>1</v>
@@ -3722,11 +3575,17 @@
       <c r="X60" t="b">
         <v>0</v>
       </c>
+      <c r="AC60" t="s">
+        <v>46</v>
+      </c>
       <c r="AD60">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AE60" t="s">
+        <v>49</v>
       </c>
       <c r="AF60" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AI60" t="s">
         <v>43</v>
@@ -3734,34 +3593,37 @@
     </row>
     <row r="61" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>9493</v>
+        <v>2841</v>
       </c>
       <c r="B61" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C61">
-        <v>350114731284</v>
+        <v>170663036</v>
       </c>
       <c r="D61" t="s">
         <v>40</v>
       </c>
       <c r="E61">
-        <v>446426.88</v>
+        <v>440418.16</v>
       </c>
       <c r="F61">
-        <v>6849874.1200000001</v>
+        <v>6850655.1900000004</v>
       </c>
       <c r="G61">
-        <v>-1202.21</v>
+        <v>-1224.54</v>
       </c>
       <c r="H61">
-        <v>1792.24</v>
+        <v>2675.74</v>
       </c>
       <c r="K61">
-        <v>-1202.21</v>
+        <v>-1224.54</v>
       </c>
       <c r="O61" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P61">
+        <v>5</v>
       </c>
       <c r="U61" t="b">
         <v>1</v>
@@ -3773,45 +3635,57 @@
         <v>37</v>
       </c>
       <c r="X61" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI61" s="1">
-        <v>46210.35564814815</v>
+        <v>0</v>
+      </c>
+      <c r="AC61" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD61">
+        <v>2</v>
+      </c>
+      <c r="AE61" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF61" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI61" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>245</v>
+        <v>3001</v>
       </c>
       <c r="B62" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C62">
-        <v>171358708</v>
+        <v>170663036</v>
       </c>
       <c r="D62" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E62">
-        <v>447157.34</v>
+        <v>440352.99</v>
       </c>
       <c r="F62">
-        <v>6851044.4000000004</v>
+        <v>6850578.3700000001</v>
       </c>
       <c r="G62">
-        <v>-1157.73</v>
+        <v>-1223.5899999999999</v>
       </c>
       <c r="H62">
-        <v>1353.5</v>
+        <v>2776.54</v>
       </c>
       <c r="K62">
-        <v>-1157.73</v>
+        <v>-1223.5899999999999</v>
       </c>
       <c r="O62" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P62">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U62" t="b">
         <v>1</v>
@@ -3829,45 +3703,45 @@
         <v>46</v>
       </c>
       <c r="AD62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE62" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF62" t="s">
         <v>48</v>
       </c>
-      <c r="AI62" t="s">
-        <v>42</v>
+      <c r="AI62" s="1">
+        <v>46210.471331018518</v>
       </c>
     </row>
     <row r="63" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>9489</v>
+        <v>9559</v>
       </c>
       <c r="B63" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C63">
-        <v>171358708</v>
+        <v>170663036</v>
       </c>
       <c r="D63" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E63">
-        <v>447229.67</v>
+        <v>440333.21</v>
       </c>
       <c r="F63">
-        <v>6851368.8399999999</v>
+        <v>6850555.9100000001</v>
       </c>
       <c r="G63">
-        <v>-1206.44</v>
+        <v>-1223.3900000000001</v>
       </c>
       <c r="H63">
-        <v>1692.63</v>
+        <v>2806.48</v>
       </c>
       <c r="K63">
-        <v>-1206.44</v>
+        <v>-1223.3900000000001</v>
       </c>
       <c r="O63" t="s">
         <v>39</v>
@@ -3885,42 +3759,42 @@
         <v>1</v>
       </c>
       <c r="AI63" s="1">
-        <v>46210.355243055557</v>
+        <v>46210.471365740741</v>
       </c>
     </row>
     <row r="64" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>2805</v>
+        <v>3104</v>
       </c>
       <c r="B64" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C64">
-        <v>171358708</v>
+        <v>170663036</v>
       </c>
       <c r="D64" t="s">
         <v>40</v>
       </c>
       <c r="E64">
-        <v>447429.37</v>
+        <v>439766.64</v>
       </c>
       <c r="F64">
-        <v>6852318.0099999998</v>
+        <v>6849878.79</v>
       </c>
       <c r="G64">
-        <v>-1204.4000000000001</v>
+        <v>-1223.93</v>
       </c>
       <c r="H64">
-        <v>2663.2</v>
+        <v>3689.9</v>
       </c>
       <c r="K64">
-        <v>-1204.4000000000001</v>
+        <v>-1223.93</v>
       </c>
       <c r="O64" t="s">
         <v>36</v>
       </c>
       <c r="P64">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="U64" t="b">
         <v>1</v>
@@ -3938,10 +3812,10 @@
         <v>46</v>
       </c>
       <c r="AD64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE64" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="AF64" t="s">
         <v>48</v>
@@ -3952,31 +3826,31 @@
     </row>
     <row r="65" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>2865</v>
+        <v>8972</v>
       </c>
       <c r="B65" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C65">
-        <v>171358708</v>
+        <v>350114731284</v>
       </c>
       <c r="D65" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E65">
-        <v>447220.24</v>
+        <v>446199.44</v>
       </c>
       <c r="F65">
-        <v>6851308.7800000003</v>
+        <v>6850194.21</v>
       </c>
       <c r="G65">
-        <v>-1206.0999999999999</v>
+        <v>-1158.96</v>
       </c>
       <c r="H65">
-        <v>1631.8</v>
+        <v>1395.4</v>
       </c>
       <c r="K65">
-        <v>-1206.0999999999999</v>
+        <v>-1158.96</v>
       </c>
       <c r="O65" t="s">
         <v>36</v>
@@ -3996,56 +3870,47 @@
       <c r="X65" t="b">
         <v>0</v>
       </c>
-      <c r="AC65" t="s">
-        <v>46</v>
-      </c>
       <c r="AD65">
         <v>1</v>
       </c>
-      <c r="AE65" t="s">
-        <v>47</v>
-      </c>
       <c r="AF65" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AI65" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="66" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>2986</v>
+        <v>9488</v>
       </c>
       <c r="B66" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C66">
-        <v>171358708</v>
+        <v>350114731284</v>
       </c>
       <c r="D66" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E66">
-        <v>447241.46</v>
+        <v>446427.76</v>
       </c>
       <c r="F66">
-        <v>6851440.6200000001</v>
+        <v>6849872.9299999997</v>
       </c>
       <c r="G66">
-        <v>-1206.8800000000001</v>
+        <v>-1202.22</v>
       </c>
       <c r="H66">
-        <v>1765.4</v>
+        <v>1793.72</v>
       </c>
       <c r="K66">
-        <v>-1206.8800000000001</v>
+        <v>-1202.22</v>
       </c>
       <c r="O66" t="s">
         <v>39</v>
       </c>
-      <c r="P66">
-        <v>3</v>
-      </c>
       <c r="U66" t="b">
         <v>1</v>
       </c>
@@ -4056,51 +3921,39 @@
         <v>37</v>
       </c>
       <c r="X66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC66" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD66">
-        <v>2</v>
-      </c>
-      <c r="AE66" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF66" t="s">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="AI66" s="1">
-        <v>46210.355995370373</v>
+        <v>46210.355532407404</v>
       </c>
     </row>
     <row r="67" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>3045</v>
+        <v>8978</v>
       </c>
       <c r="B67" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C67">
-        <v>171358708</v>
+        <v>350114731284</v>
       </c>
       <c r="D67" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E67">
-        <v>447230.21</v>
+        <v>446583.23</v>
       </c>
       <c r="F67">
-        <v>6851372.5800000001</v>
+        <v>6849647.3499999996</v>
       </c>
       <c r="G67">
-        <v>-1206.48</v>
+        <v>-1207.8499999999999</v>
       </c>
       <c r="H67">
-        <v>1696.4</v>
+        <v>2068</v>
       </c>
       <c r="K67">
-        <v>-1206.48</v>
+        <v>-1207.8499999999999</v>
       </c>
       <c r="O67" t="s">
         <v>36</v>
@@ -4120,55 +3973,49 @@
       <c r="X67" t="b">
         <v>0</v>
       </c>
-      <c r="AC67" t="s">
-        <v>46</v>
-      </c>
       <c r="AD67">
-        <v>2</v>
-      </c>
-      <c r="AE67" t="s">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="AF67" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AI67" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="68" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>8985</v>
+        <v>8970</v>
       </c>
       <c r="B68" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C68">
-        <v>350114731303</v>
+        <v>350114731284</v>
       </c>
       <c r="D68" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E68">
-        <v>448096.1</v>
+        <v>446360.95</v>
       </c>
       <c r="F68">
-        <v>6852067.3700000001</v>
+        <v>6849967.1799999997</v>
       </c>
       <c r="G68">
-        <v>-1207.47</v>
+        <v>-1203.1600000000001</v>
       </c>
       <c r="H68">
-        <v>2005</v>
+        <v>1678.1</v>
       </c>
       <c r="K68">
-        <v>-1207.47</v>
+        <v>-1203.1600000000001</v>
       </c>
       <c r="O68" t="s">
         <v>36</v>
       </c>
       <c r="P68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U68" t="b">
         <v>1</v>
@@ -4189,42 +4036,39 @@
         <v>38</v>
       </c>
       <c r="AI68" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="69" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>8992</v>
+        <v>9489</v>
       </c>
       <c r="B69" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C69">
-        <v>350114731303</v>
+        <v>350114731284</v>
       </c>
       <c r="D69" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E69">
-        <v>448285.57</v>
+        <v>446426.88</v>
       </c>
       <c r="F69">
-        <v>6851907.6799999997</v>
+        <v>6849874.1200000001</v>
       </c>
       <c r="G69">
-        <v>-1203.48</v>
+        <v>-1202.21</v>
       </c>
       <c r="H69">
-        <v>1757</v>
+        <v>1792.24</v>
       </c>
       <c r="K69">
-        <v>-1203.48</v>
+        <v>-1202.21</v>
       </c>
       <c r="O69" t="s">
-        <v>36</v>
-      </c>
-      <c r="P69">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="U69" t="b">
         <v>1</v>
@@ -4236,51 +4080,42 @@
         <v>37</v>
       </c>
       <c r="X69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD69">
-        <v>1</v>
-      </c>
-      <c r="AF69" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI69" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="AI69" s="1">
+        <v>46210.35564814815</v>
       </c>
     </row>
     <row r="70" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>8994</v>
+        <v>9560</v>
       </c>
       <c r="B70" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C70">
-        <v>350114731303</v>
+        <v>350114731284</v>
       </c>
       <c r="D70" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E70">
-        <v>447884.53</v>
+        <v>446582.4</v>
       </c>
       <c r="F70">
-        <v>6852236.4400000004</v>
+        <v>6849648.5599999996</v>
       </c>
       <c r="G70">
-        <v>-1208.18</v>
+        <v>-1207.8800000000001</v>
       </c>
       <c r="H70">
-        <v>2276</v>
+        <v>2066.54</v>
       </c>
       <c r="K70">
-        <v>-1208.18</v>
+        <v>-1207.8800000000001</v>
       </c>
       <c r="O70" t="s">
-        <v>36</v>
-      </c>
-      <c r="P70">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="U70" t="b">
         <v>1</v>
@@ -4292,51 +4127,45 @@
         <v>37</v>
       </c>
       <c r="X70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD70">
-        <v>1</v>
-      </c>
-      <c r="AF70" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI70" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="AI70" s="1">
+        <v>46210.472997685189</v>
       </c>
     </row>
     <row r="71" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>8996</v>
+        <v>8976</v>
       </c>
       <c r="B71" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C71">
-        <v>350114731303</v>
+        <v>350114731284</v>
       </c>
       <c r="D71" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E71">
-        <v>447688.97</v>
+        <v>446595.09</v>
       </c>
       <c r="F71">
-        <v>6852406.0199999996</v>
+        <v>6849630.04</v>
       </c>
       <c r="G71">
-        <v>-1209.8699999999999</v>
+        <v>-1207.8699999999999</v>
       </c>
       <c r="H71">
-        <v>2535</v>
+        <v>2089</v>
       </c>
       <c r="K71">
-        <v>-1209.8699999999999</v>
+        <v>-1207.8699999999999</v>
       </c>
       <c r="O71" t="s">
         <v>36</v>
       </c>
       <c r="P71">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U71" t="b">
         <v>1</v>
@@ -4357,36 +4186,36 @@
         <v>38</v>
       </c>
       <c r="AI71" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="72" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>8999</v>
+        <v>245</v>
       </c>
       <c r="B72" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C72">
-        <v>350114731303</v>
+        <v>171358708</v>
       </c>
       <c r="D72" t="s">
         <v>35</v>
       </c>
       <c r="E72">
-        <v>448579.78</v>
+        <v>447157.34</v>
       </c>
       <c r="F72">
-        <v>6851659.8300000001</v>
+        <v>6851044.4000000004</v>
       </c>
       <c r="G72">
-        <v>-1156.74</v>
+        <v>-1157.73</v>
       </c>
       <c r="H72">
-        <v>1366.67</v>
+        <v>1353.5</v>
       </c>
       <c r="K72">
-        <v>-1156.74</v>
+        <v>-1157.73</v>
       </c>
       <c r="O72" t="s">
         <v>36</v>
@@ -4406,49 +4235,52 @@
       <c r="X72" t="b">
         <v>0</v>
       </c>
+      <c r="AC72" t="s">
+        <v>46</v>
+      </c>
       <c r="AD72">
         <v>1</v>
       </c>
+      <c r="AE72" t="s">
+        <v>52</v>
+      </c>
       <c r="AF72" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI72" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI72" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="73" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>8984</v>
+        <v>9485</v>
       </c>
       <c r="B73" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C73">
-        <v>350114731303</v>
+        <v>171358708</v>
       </c>
       <c r="D73" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E73">
-        <v>448219.09</v>
+        <v>447229.67</v>
       </c>
       <c r="F73">
-        <v>6851962.1200000001</v>
+        <v>6851368.8399999999</v>
       </c>
       <c r="G73">
-        <v>-1205.44</v>
+        <v>-1206.44</v>
       </c>
       <c r="H73">
-        <v>1843</v>
+        <v>1692.63</v>
       </c>
       <c r="K73">
-        <v>-1205.44</v>
+        <v>-1206.44</v>
       </c>
       <c r="O73" t="s">
-        <v>36</v>
-      </c>
-      <c r="P73">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="U73" t="b">
         <v>1</v>
@@ -4460,51 +4292,45 @@
         <v>37</v>
       </c>
       <c r="X73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD73">
-        <v>1</v>
-      </c>
-      <c r="AF73" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI73" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI73" s="1">
+        <v>46210.355243055557</v>
       </c>
     </row>
     <row r="74" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>8988</v>
+        <v>2864</v>
       </c>
       <c r="B74" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C74">
-        <v>350114731303</v>
+        <v>171358708</v>
       </c>
       <c r="D74" t="s">
         <v>40</v>
       </c>
       <c r="E74">
-        <v>447883.8</v>
+        <v>447220.24</v>
       </c>
       <c r="F74">
-        <v>6852237.0300000003</v>
+        <v>6851308.7800000003</v>
       </c>
       <c r="G74">
-        <v>-1208.1600000000001</v>
+        <v>-1206.0999999999999</v>
       </c>
       <c r="H74">
-        <v>2276.94</v>
+        <v>1631.8</v>
       </c>
       <c r="K74">
-        <v>-1208.1600000000001</v>
+        <v>-1206.0999999999999</v>
       </c>
       <c r="O74" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="P74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U74" t="b">
         <v>1</v>
@@ -4518,49 +4344,55 @@
       <c r="X74" t="b">
         <v>0</v>
       </c>
+      <c r="AC74" t="s">
+        <v>46</v>
+      </c>
       <c r="AD74">
         <v>1</v>
       </c>
+      <c r="AE74" t="s">
+        <v>47</v>
+      </c>
       <c r="AF74" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI74" s="1">
-        <v>46210.355763888889</v>
+        <v>48</v>
+      </c>
+      <c r="AI74" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="75" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>8989</v>
+        <v>3043</v>
       </c>
       <c r="B75" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C75">
-        <v>350114731303</v>
+        <v>171358708</v>
       </c>
       <c r="D75" t="s">
         <v>40</v>
       </c>
       <c r="E75">
-        <v>447968.5</v>
+        <v>447230.21</v>
       </c>
       <c r="F75">
-        <v>6852170.2400000002</v>
+        <v>6851372.5800000001</v>
       </c>
       <c r="G75">
-        <v>-1209.29</v>
+        <v>-1206.48</v>
       </c>
       <c r="H75">
-        <v>2169</v>
+        <v>1696.4</v>
       </c>
       <c r="K75">
-        <v>-1209.29</v>
+        <v>-1206.48</v>
       </c>
       <c r="O75" t="s">
         <v>36</v>
       </c>
       <c r="P75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U75" t="b">
         <v>1</v>
@@ -4574,49 +4406,55 @@
       <c r="X75" t="b">
         <v>0</v>
       </c>
+      <c r="AC75" t="s">
+        <v>46</v>
+      </c>
       <c r="AD75">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AE75" t="s">
+        <v>49</v>
       </c>
       <c r="AF75" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI75" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI75" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="76" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>8993</v>
+        <v>2984</v>
       </c>
       <c r="B76" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C76">
-        <v>350114731303</v>
+        <v>171358708</v>
       </c>
       <c r="D76" t="s">
         <v>40</v>
       </c>
       <c r="E76">
-        <v>448328.5</v>
+        <v>447241.46</v>
       </c>
       <c r="F76">
-        <v>6851873.6500000004</v>
+        <v>6851440.6200000001</v>
       </c>
       <c r="G76">
-        <v>-1203.79</v>
+        <v>-1206.8800000000001</v>
       </c>
       <c r="H76">
-        <v>1702.19</v>
+        <v>1765.4</v>
       </c>
       <c r="K76">
-        <v>-1203.79</v>
+        <v>-1206.8800000000001</v>
       </c>
       <c r="O76" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U76" t="b">
         <v>1</v>
@@ -4630,46 +4468,55 @@
       <c r="X76" t="b">
         <v>0</v>
       </c>
+      <c r="AC76" t="s">
+        <v>46</v>
+      </c>
       <c r="AD76">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AE76" t="s">
+        <v>49</v>
       </c>
       <c r="AF76" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI76" t="s">
-        <v>43</v>
+        <v>48</v>
+      </c>
+      <c r="AI76" s="1">
+        <v>46210.355995370373</v>
       </c>
     </row>
     <row r="77" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>9494</v>
+        <v>2804</v>
       </c>
       <c r="B77" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C77">
-        <v>350114731303</v>
+        <v>171358708</v>
       </c>
       <c r="D77" t="s">
         <v>40</v>
       </c>
       <c r="E77">
-        <v>448284.31</v>
+        <v>447429.37</v>
       </c>
       <c r="F77">
-        <v>6851908.6799999997</v>
+        <v>6852318.0099999998</v>
       </c>
       <c r="G77">
-        <v>-1203.48</v>
+        <v>-1204.4000000000001</v>
       </c>
       <c r="H77">
-        <v>1758.61</v>
+        <v>2663.2</v>
       </c>
       <c r="K77">
-        <v>-1203.48</v>
+        <v>-1204.4000000000001</v>
       </c>
       <c r="O77" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P77">
+        <v>4</v>
       </c>
       <c r="U77" t="b">
         <v>1</v>
@@ -4681,15 +4528,27 @@
         <v>37</v>
       </c>
       <c r="X77" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI77" s="1">
-        <v>46210.355844907404</v>
+        <v>0</v>
+      </c>
+      <c r="AC77" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD77">
+        <v>1</v>
+      </c>
+      <c r="AE77" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF77" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI77" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="78" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>9495</v>
+        <v>8996</v>
       </c>
       <c r="B78" t="s">
         <v>54</v>
@@ -4698,25 +4557,28 @@
         <v>350114731303</v>
       </c>
       <c r="D78" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E78">
-        <v>448097.12</v>
+        <v>448579.78</v>
       </c>
       <c r="F78">
-        <v>6852066.5099999998</v>
+        <v>6851659.8300000001</v>
       </c>
       <c r="G78">
-        <v>-1207.42</v>
+        <v>-1156.74</v>
       </c>
       <c r="H78">
-        <v>2003.67</v>
+        <v>1366.67</v>
       </c>
       <c r="K78">
-        <v>-1207.42</v>
+        <v>-1156.74</v>
       </c>
       <c r="O78" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P78">
+        <v>1</v>
       </c>
       <c r="U78" t="b">
         <v>1</v>
@@ -4728,15 +4590,21 @@
         <v>37</v>
       </c>
       <c r="X78" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI78" s="1">
-        <v>46210.355694444443</v>
+        <v>0</v>
+      </c>
+      <c r="AD78">
+        <v>1</v>
+      </c>
+      <c r="AF78" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI78" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="79" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>9496</v>
+        <v>8989</v>
       </c>
       <c r="B79" t="s">
         <v>54</v>
@@ -4745,25 +4613,28 @@
         <v>350114731303</v>
       </c>
       <c r="D79" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E79">
-        <v>447855.09</v>
+        <v>448285.57</v>
       </c>
       <c r="F79">
-        <v>6852260.5499999998</v>
+        <v>6851907.6799999997</v>
       </c>
       <c r="G79">
-        <v>-1208.06</v>
+        <v>-1203.48</v>
       </c>
       <c r="H79">
-        <v>2314.0700000000002</v>
+        <v>1757</v>
       </c>
       <c r="K79">
-        <v>-1208.06</v>
+        <v>-1203.48</v>
       </c>
       <c r="O79" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P79">
+        <v>2</v>
       </c>
       <c r="U79" t="b">
         <v>1</v>
@@ -4775,15 +4646,21 @@
         <v>37</v>
       </c>
       <c r="X79" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI79" s="1">
-        <v>46210.355775462966</v>
+        <v>0</v>
+      </c>
+      <c r="AD79">
+        <v>1</v>
+      </c>
+      <c r="AF79" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI79" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="80" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>9497</v>
+        <v>8982</v>
       </c>
       <c r="B80" t="s">
         <v>54</v>
@@ -4792,25 +4669,28 @@
         <v>350114731303</v>
       </c>
       <c r="D80" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E80">
-        <v>447689.83</v>
+        <v>448096.1</v>
       </c>
       <c r="F80">
-        <v>6852405.3099999996</v>
+        <v>6852067.3700000001</v>
       </c>
       <c r="G80">
-        <v>-1209.8800000000001</v>
+        <v>-1207.47</v>
       </c>
       <c r="H80">
-        <v>2533.88</v>
+        <v>2005</v>
       </c>
       <c r="K80">
-        <v>-1209.8800000000001</v>
+        <v>-1207.47</v>
       </c>
       <c r="O80" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P80">
+        <v>3</v>
       </c>
       <c r="U80" t="b">
         <v>1</v>
@@ -4822,45 +4702,51 @@
         <v>37</v>
       </c>
       <c r="X80" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI80" s="1">
-        <v>46210.355798611112</v>
+        <v>0</v>
+      </c>
+      <c r="AD80">
+        <v>1</v>
+      </c>
+      <c r="AF80" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI80" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="81" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>9001</v>
+        <v>8991</v>
       </c>
       <c r="B81" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C81">
-        <v>350162787959</v>
+        <v>350114731303</v>
       </c>
       <c r="D81" t="s">
         <v>35</v>
       </c>
       <c r="E81">
-        <v>448691.87</v>
+        <v>447884.53</v>
       </c>
       <c r="F81">
-        <v>6851989.5999999996</v>
+        <v>6852236.4400000004</v>
       </c>
       <c r="G81">
-        <v>-1155.94</v>
+        <v>-1208.18</v>
       </c>
       <c r="H81">
-        <v>1365.7</v>
+        <v>2276</v>
       </c>
       <c r="K81">
-        <v>-1155.94</v>
+        <v>-1208.18</v>
       </c>
       <c r="O81" t="s">
         <v>36</v>
       </c>
       <c r="P81">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U81" t="b">
         <v>1</v>
@@ -4886,37 +4772,37 @@
     </row>
     <row r="82" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>9003</v>
+        <v>8993</v>
       </c>
       <c r="B82" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C82">
-        <v>350162787959</v>
+        <v>350114731303</v>
       </c>
       <c r="D82" t="s">
         <v>35</v>
       </c>
       <c r="E82">
-        <v>448313.83</v>
+        <v>447688.97</v>
       </c>
       <c r="F82">
-        <v>6851106.7599999998</v>
+        <v>6852406.0199999996</v>
       </c>
       <c r="G82">
-        <v>-1206.3399999999999</v>
+        <v>-1209.8699999999999</v>
       </c>
       <c r="H82">
-        <v>2332</v>
+        <v>2535</v>
       </c>
       <c r="K82">
-        <v>-1206.3399999999999</v>
+        <v>-1209.8699999999999</v>
       </c>
       <c r="O82" t="s">
         <v>36</v>
       </c>
       <c r="P82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U82" t="b">
         <v>1</v>
@@ -4942,34 +4828,37 @@
     </row>
     <row r="83" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>9490</v>
+        <v>8990</v>
       </c>
       <c r="B83" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C83">
-        <v>350162787959</v>
+        <v>350114731303</v>
       </c>
       <c r="D83" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E83">
-        <v>448465.03</v>
+        <v>448328.5</v>
       </c>
       <c r="F83">
-        <v>6851472</v>
+        <v>6851873.6500000004</v>
       </c>
       <c r="G83">
-        <v>-1203.0999999999999</v>
+        <v>-1203.79</v>
       </c>
       <c r="H83">
-        <v>1936.48</v>
+        <v>1702.19</v>
       </c>
       <c r="K83">
-        <v>-1203.0999999999999</v>
+        <v>-1203.79</v>
       </c>
       <c r="O83" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P83">
+        <v>1</v>
       </c>
       <c r="U83" t="b">
         <v>1</v>
@@ -4981,39 +4870,45 @@
         <v>37</v>
       </c>
       <c r="X83" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI83" s="1">
-        <v>46210.35527777778</v>
+        <v>0</v>
+      </c>
+      <c r="AD83">
+        <v>1</v>
+      </c>
+      <c r="AF83" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI83" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="84" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>9491</v>
+        <v>9490</v>
       </c>
       <c r="B84" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C84">
-        <v>350162787959</v>
+        <v>350114731303</v>
       </c>
       <c r="D84" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E84">
-        <v>448424.85</v>
+        <v>448284.31</v>
       </c>
       <c r="F84">
-        <v>6851374.5700000003</v>
+        <v>6851908.6799999997</v>
       </c>
       <c r="G84">
-        <v>-1204.57</v>
+        <v>-1203.48</v>
       </c>
       <c r="H84">
-        <v>2041.92</v>
+        <v>1758.61</v>
       </c>
       <c r="K84">
-        <v>-1204.57</v>
+        <v>-1203.48</v>
       </c>
       <c r="O84" t="s">
         <v>39</v>
@@ -5031,42 +4926,42 @@
         <v>1</v>
       </c>
       <c r="AI84" s="1">
-        <v>46210.35528935185</v>
+        <v>46210.355844907404</v>
       </c>
     </row>
     <row r="85" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>9008</v>
+        <v>8981</v>
       </c>
       <c r="B85" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C85">
-        <v>350162787959</v>
+        <v>350114731303</v>
       </c>
       <c r="D85" t="s">
         <v>40</v>
       </c>
       <c r="E85">
-        <v>448565.55</v>
+        <v>448219.09</v>
       </c>
       <c r="F85">
-        <v>6851701.5499999998</v>
+        <v>6851962.1200000001</v>
       </c>
       <c r="G85">
-        <v>-1204.78</v>
+        <v>-1205.44</v>
       </c>
       <c r="H85">
-        <v>1685.7</v>
+        <v>1843</v>
       </c>
       <c r="K85">
-        <v>-1204.78</v>
+        <v>-1205.44</v>
       </c>
       <c r="O85" t="s">
         <v>36</v>
       </c>
       <c r="P85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U85" t="b">
         <v>1</v>
@@ -5086,37 +4981,37 @@
       <c r="AF85" t="s">
         <v>38</v>
       </c>
-      <c r="AI85" t="s">
+      <c r="AI85" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="86" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>9498</v>
+        <v>9491</v>
       </c>
       <c r="B86" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C86">
-        <v>350162787959</v>
+        <v>350114731303</v>
       </c>
       <c r="D86" t="s">
         <v>40</v>
       </c>
       <c r="E86">
-        <v>448465.59</v>
+        <v>448097.12</v>
       </c>
       <c r="F86">
-        <v>6851473.3700000001</v>
+        <v>6852066.5099999998</v>
       </c>
       <c r="G86">
-        <v>-1203.0999999999999</v>
+        <v>-1207.42</v>
       </c>
       <c r="H86">
-        <v>1934.99</v>
+        <v>2003.67</v>
       </c>
       <c r="K86">
-        <v>-1203.0999999999999</v>
+        <v>-1207.42</v>
       </c>
       <c r="O86" t="s">
         <v>39</v>
@@ -5134,39 +5029,42 @@
         <v>1</v>
       </c>
       <c r="AI86" s="1">
-        <v>46210.355879629627</v>
+        <v>46210.355694444443</v>
       </c>
     </row>
     <row r="87" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>9499</v>
+        <v>8986</v>
       </c>
       <c r="B87" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C87">
-        <v>350162787959</v>
+        <v>350114731303</v>
       </c>
       <c r="D87" t="s">
         <v>40</v>
       </c>
       <c r="E87">
-        <v>448424.85</v>
+        <v>447968.5</v>
       </c>
       <c r="F87">
-        <v>6851374.5700000003</v>
+        <v>6852170.2400000002</v>
       </c>
       <c r="G87">
-        <v>-1204.57</v>
+        <v>-1209.29</v>
       </c>
       <c r="H87">
-        <v>2041.92</v>
+        <v>2169</v>
       </c>
       <c r="K87">
-        <v>-1204.57</v>
+        <v>-1209.29</v>
       </c>
       <c r="O87" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P87">
+        <v>3</v>
       </c>
       <c r="U87" t="b">
         <v>1</v>
@@ -5178,43 +5076,52 @@
         <v>37</v>
       </c>
       <c r="X87" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI87" s="1">
-        <v>46210.355902777781</v>
+        <v>0</v>
+      </c>
+      <c r="AD87">
+        <v>1</v>
+      </c>
+      <c r="AF87" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI87" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="88" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>9500</v>
+        <v>8985</v>
       </c>
       <c r="B88" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C88">
-        <v>350162787959</v>
+        <v>350114731303</v>
       </c>
       <c r="D88" t="s">
         <v>40</v>
       </c>
       <c r="E88">
-        <v>448312.87</v>
+        <v>447883.8</v>
       </c>
       <c r="F88">
-        <v>6851104.4400000004</v>
+        <v>6852237.0300000003</v>
       </c>
       <c r="G88">
-        <v>-1206.3399999999999</v>
+        <v>-1208.1600000000001</v>
       </c>
       <c r="H88">
-        <v>2334.5100000000002</v>
+        <v>2276.94</v>
       </c>
       <c r="K88">
-        <v>-1206.3399999999999</v>
+        <v>-1208.1600000000001</v>
       </c>
       <c r="O88" t="s">
         <v>39</v>
       </c>
+      <c r="P88">
+        <v>4</v>
+      </c>
       <c r="U88" t="b">
         <v>1</v>
       </c>
@@ -5225,36 +5132,45 @@
         <v>37</v>
       </c>
       <c r="X88" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AD88">
+        <v>1</v>
+      </c>
+      <c r="AF88" t="s">
+        <v>38</v>
       </c>
       <c r="AI88" s="1">
-        <v>46210.355937499997</v>
+        <v>46210.355763888889</v>
       </c>
     </row>
     <row r="89" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>9454</v>
+        <v>9492</v>
       </c>
       <c r="B89" t="s">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="C89">
+        <v>350114731303</v>
       </c>
       <c r="D89" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E89">
-        <v>431838.76</v>
+        <v>447855.09</v>
       </c>
       <c r="F89">
-        <v>6845910.9699999997</v>
+        <v>6852260.5499999998</v>
       </c>
       <c r="G89">
-        <v>-1190.74</v>
+        <v>-1208.06</v>
       </c>
       <c r="H89">
-        <v>2791.94</v>
+        <v>2314.0700000000002</v>
       </c>
       <c r="K89">
-        <v>-1190.74</v>
+        <v>-1208.06</v>
       </c>
       <c r="O89" t="s">
         <v>39</v>
@@ -5272,33 +5188,36 @@
         <v>1</v>
       </c>
       <c r="AI89" s="1">
-        <v>46210.351863425924</v>
+        <v>46210.355775462966</v>
       </c>
     </row>
     <row r="90" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>9455</v>
+        <v>9493</v>
       </c>
       <c r="B90" t="s">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="C90">
+        <v>350114731303</v>
       </c>
       <c r="D90" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E90">
-        <v>431743.19</v>
+        <v>447689.83</v>
       </c>
       <c r="F90">
-        <v>6845476.0199999996</v>
+        <v>6852405.3099999996</v>
       </c>
       <c r="G90">
-        <v>-1192.93</v>
+        <v>-1209.8800000000001</v>
       </c>
       <c r="H90">
-        <v>3237.5</v>
+        <v>2533.88</v>
       </c>
       <c r="K90">
-        <v>-1192.93</v>
+        <v>-1209.8800000000001</v>
       </c>
       <c r="O90" t="s">
         <v>39</v>
@@ -5316,36 +5235,42 @@
         <v>1</v>
       </c>
       <c r="AI90" s="1">
-        <v>46210.35193287037</v>
+        <v>46210.355798611112</v>
       </c>
     </row>
     <row r="91" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>9456</v>
+        <v>8998</v>
       </c>
       <c r="B91" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="C91">
+        <v>350162787959</v>
       </c>
       <c r="D91" t="s">
         <v>35</v>
       </c>
       <c r="E91">
-        <v>431751.39</v>
+        <v>448691.87</v>
       </c>
       <c r="F91">
-        <v>6845514.9100000001</v>
+        <v>6851989.5999999996</v>
       </c>
       <c r="G91">
-        <v>-1191.79</v>
+        <v>-1155.94</v>
       </c>
       <c r="H91">
-        <v>3197.73</v>
+        <v>1365.7</v>
       </c>
       <c r="K91">
-        <v>-1191.79</v>
+        <v>-1155.94</v>
       </c>
       <c r="O91" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P91">
+        <v>1</v>
       </c>
       <c r="U91" t="b">
         <v>1</v>
@@ -5357,36 +5282,45 @@
         <v>37</v>
       </c>
       <c r="X91" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI91" s="1">
-        <v>46210.352025462962</v>
+        <v>0</v>
+      </c>
+      <c r="AD91">
+        <v>1</v>
+      </c>
+      <c r="AF91" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI91" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="92" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>9458</v>
+        <v>9486</v>
       </c>
       <c r="B92" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="C92">
+        <v>350162787959</v>
       </c>
       <c r="D92" t="s">
         <v>35</v>
       </c>
       <c r="E92">
-        <v>431723.49</v>
+        <v>448465.03</v>
       </c>
       <c r="F92">
-        <v>6845384.0999999996</v>
+        <v>6851472</v>
       </c>
       <c r="G92">
-        <v>-1194.23</v>
+        <v>-1203.0999999999999</v>
       </c>
       <c r="H92">
-        <v>3331.56</v>
+        <v>1936.48</v>
       </c>
       <c r="K92">
-        <v>-1194.23</v>
+        <v>-1203.0999999999999</v>
       </c>
       <c r="O92" t="s">
         <v>39</v>
@@ -5404,33 +5338,36 @@
         <v>1</v>
       </c>
       <c r="AI92" s="1">
-        <v>46210.352210648147</v>
+        <v>46210.35527777778</v>
       </c>
     </row>
     <row r="93" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>9439</v>
+        <v>9487</v>
       </c>
       <c r="B93" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="C93">
+        <v>350162787959</v>
       </c>
       <c r="D93" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E93">
-        <v>431952.53</v>
+        <v>448424.85</v>
       </c>
       <c r="F93">
-        <v>6846439.9100000001</v>
+        <v>6851374.5700000003</v>
       </c>
       <c r="G93">
-        <v>-1194.1400000000001</v>
+        <v>-1204.57</v>
       </c>
       <c r="H93">
-        <v>2250.62</v>
+        <v>2041.92</v>
       </c>
       <c r="K93">
-        <v>-1194.1400000000001</v>
+        <v>-1204.57</v>
       </c>
       <c r="O93" t="s">
         <v>39</v>
@@ -5448,36 +5385,42 @@
         <v>1</v>
       </c>
       <c r="AI93" s="1">
-        <v>46359.700694444444</v>
+        <v>46210.35528935185</v>
       </c>
     </row>
     <row r="94" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>9441</v>
+        <v>9000</v>
       </c>
       <c r="B94" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="C94">
+        <v>350162787959</v>
       </c>
       <c r="D94" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E94">
-        <v>431838.19</v>
+        <v>448313.83</v>
       </c>
       <c r="F94">
-        <v>6845908.1699999999</v>
+        <v>6851106.7599999998</v>
       </c>
       <c r="G94">
-        <v>-1190.68</v>
+        <v>-1206.3399999999999</v>
       </c>
       <c r="H94">
-        <v>2794.81</v>
+        <v>2332</v>
       </c>
       <c r="K94">
-        <v>-1190.68</v>
+        <v>-1206.3399999999999</v>
       </c>
       <c r="O94" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P94">
+        <v>2</v>
       </c>
       <c r="U94" t="b">
         <v>1</v>
@@ -5489,39 +5432,51 @@
         <v>37</v>
       </c>
       <c r="X94" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI94" t="s">
-        <v>57</v>
+        <v>0</v>
+      </c>
+      <c r="AD94">
+        <v>1</v>
+      </c>
+      <c r="AF94" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI94" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="95" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>9442</v>
+        <v>9005</v>
       </c>
       <c r="B95" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="C95">
+        <v>350162787959</v>
       </c>
       <c r="D95" t="s">
         <v>40</v>
       </c>
       <c r="E95">
-        <v>431751.39</v>
+        <v>448565.55</v>
       </c>
       <c r="F95">
-        <v>6845514.9100000001</v>
+        <v>6851701.5499999998</v>
       </c>
       <c r="G95">
-        <v>-1191.79</v>
+        <v>-1204.78</v>
       </c>
       <c r="H95">
-        <v>3197.73</v>
+        <v>1685.7</v>
       </c>
       <c r="K95">
-        <v>-1191.79</v>
+        <v>-1204.78</v>
       </c>
       <c r="O95" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P95">
+        <v>1</v>
       </c>
       <c r="U95" t="b">
         <v>1</v>
@@ -5533,36 +5488,45 @@
         <v>37</v>
       </c>
       <c r="X95" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI95" t="s">
-        <v>58</v>
+        <v>0</v>
+      </c>
+      <c r="AD95">
+        <v>1</v>
+      </c>
+      <c r="AF95" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI95" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="96" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>9443</v>
+        <v>9494</v>
       </c>
       <c r="B96" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="C96">
+        <v>350162787959</v>
       </c>
       <c r="D96" t="s">
         <v>40</v>
       </c>
       <c r="E96">
-        <v>431723.31</v>
+        <v>448465.59</v>
       </c>
       <c r="F96">
-        <v>6845383.2800000003</v>
+        <v>6851473.3700000001</v>
       </c>
       <c r="G96">
-        <v>-1194.23</v>
+        <v>-1203.0999999999999</v>
       </c>
       <c r="H96">
-        <v>3332.41</v>
+        <v>1934.99</v>
       </c>
       <c r="K96">
-        <v>-1194.23</v>
+        <v>-1203.0999999999999</v>
       </c>
       <c r="O96" t="s">
         <v>39</v>
@@ -5579,34 +5543,37 @@
       <c r="X96" t="b">
         <v>1</v>
       </c>
-      <c r="AI96" t="s">
-        <v>59</v>
+      <c r="AI96" s="1">
+        <v>46210.355879629627</v>
       </c>
     </row>
     <row r="97" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>9449</v>
+        <v>9495</v>
       </c>
       <c r="B97" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="C97">
+        <v>350162787959</v>
       </c>
       <c r="D97" t="s">
         <v>40</v>
       </c>
       <c r="E97">
-        <v>431828.8</v>
+        <v>448424.85</v>
       </c>
       <c r="F97">
-        <v>6845861.2599999998</v>
+        <v>6851374.5700000003</v>
       </c>
       <c r="G97">
-        <v>-1190.75</v>
+        <v>-1204.57</v>
       </c>
       <c r="H97">
-        <v>2842.67</v>
+        <v>2041.92</v>
       </c>
       <c r="K97">
-        <v>-1190.75</v>
+        <v>-1204.57</v>
       </c>
       <c r="O97" t="s">
         <v>39</v>
@@ -5623,34 +5590,37 @@
       <c r="X97" t="b">
         <v>1</v>
       </c>
-      <c r="AI97" t="s">
-        <v>60</v>
+      <c r="AI97" s="1">
+        <v>46210.355902777781</v>
       </c>
     </row>
     <row r="98" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>9450</v>
+        <v>9496</v>
       </c>
       <c r="B98" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="C98">
+        <v>350162787959</v>
       </c>
       <c r="D98" t="s">
         <v>40</v>
       </c>
       <c r="E98">
-        <v>431743.08</v>
+        <v>448312.87</v>
       </c>
       <c r="F98">
-        <v>6845475.5</v>
+        <v>6851104.4400000004</v>
       </c>
       <c r="G98">
-        <v>-1192.95</v>
+        <v>-1206.3399999999999</v>
       </c>
       <c r="H98">
-        <v>3238.04</v>
+        <v>2334.5100000000002</v>
       </c>
       <c r="K98">
-        <v>-1192.95</v>
+        <v>-1206.3399999999999</v>
       </c>
       <c r="O98" t="s">
         <v>39</v>
@@ -5668,33 +5638,33 @@
         <v>1</v>
       </c>
       <c r="AI98" s="1">
-        <v>46210.351273148146</v>
+        <v>46210.355937499997</v>
       </c>
     </row>
     <row r="99" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>9453</v>
+        <v>9451</v>
       </c>
       <c r="B99" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D99" t="s">
         <v>35</v>
       </c>
       <c r="E99">
-        <v>432542.61</v>
+        <v>431838.22</v>
       </c>
       <c r="F99">
-        <v>6846585.29</v>
+        <v>6845908.3200000003</v>
       </c>
       <c r="G99">
-        <v>-1191.17</v>
+        <v>-1190.68</v>
       </c>
       <c r="H99">
-        <v>2378.94</v>
+        <v>2794.65</v>
       </c>
       <c r="K99">
-        <v>-1191.17</v>
+        <v>-1190.68</v>
       </c>
       <c r="O99" t="s">
         <v>39</v>
@@ -5712,33 +5682,33 @@
         <v>1</v>
       </c>
       <c r="AI99" s="1">
-        <v>46210.351805555554</v>
+        <v>46210.446180555555</v>
       </c>
     </row>
     <row r="100" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>9457</v>
+        <v>9452</v>
       </c>
       <c r="B100" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D100" t="s">
         <v>35</v>
       </c>
       <c r="E100">
-        <v>432869.44</v>
+        <v>431751.39</v>
       </c>
       <c r="F100">
-        <v>6846097.4299999997</v>
+        <v>6845514.9100000001</v>
       </c>
       <c r="G100">
-        <v>-1194.3800000000001</v>
+        <v>-1191.79</v>
       </c>
       <c r="H100">
-        <v>2973.01</v>
+        <v>3197.73</v>
       </c>
       <c r="K100">
-        <v>-1194.3800000000001</v>
+        <v>-1191.79</v>
       </c>
       <c r="O100" t="s">
         <v>39</v>
@@ -5756,33 +5726,33 @@
         <v>1</v>
       </c>
       <c r="AI100" s="1">
-        <v>46210.352152777778</v>
+        <v>46210.352025462962</v>
       </c>
     </row>
     <row r="101" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>9459</v>
+        <v>9454</v>
       </c>
       <c r="B101" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D101" t="s">
         <v>35</v>
       </c>
       <c r="E101">
-        <v>432921.48</v>
+        <v>431723.49</v>
       </c>
       <c r="F101">
-        <v>6845707.2599999998</v>
+        <v>6845384.0999999996</v>
       </c>
       <c r="G101">
-        <v>-1191.47</v>
+        <v>-1194.23</v>
       </c>
       <c r="H101">
-        <v>3367.83</v>
+        <v>3331.56</v>
       </c>
       <c r="K101">
-        <v>-1191.47</v>
+        <v>-1194.23</v>
       </c>
       <c r="O101" t="s">
         <v>39</v>
@@ -5800,33 +5770,33 @@
         <v>1</v>
       </c>
       <c r="AI101" s="1">
-        <v>46210.35224537037</v>
+        <v>46210.352210648147</v>
       </c>
     </row>
     <row r="102" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>9460</v>
+        <v>9436</v>
       </c>
       <c r="B102" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D102" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E102">
-        <v>433021.17</v>
+        <v>431952.53</v>
       </c>
       <c r="F102">
-        <v>6845469.3700000001</v>
+        <v>6846439.9100000001</v>
       </c>
       <c r="G102">
-        <v>-1194.3599999999999</v>
+        <v>-1194.1400000000001</v>
       </c>
       <c r="H102">
-        <v>3626.5</v>
+        <v>2250.62</v>
       </c>
       <c r="K102">
-        <v>-1194.3599999999999</v>
+        <v>-1194.1400000000001</v>
       </c>
       <c r="O102" t="s">
         <v>39</v>
@@ -5844,33 +5814,33 @@
         <v>1</v>
       </c>
       <c r="AI102" s="1">
-        <v>46210.352303240739</v>
+        <v>46359.700694444444</v>
       </c>
     </row>
     <row r="103" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>9440</v>
+        <v>9438</v>
       </c>
       <c r="B103" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D103" t="s">
         <v>40</v>
       </c>
       <c r="E103">
-        <v>432268.31</v>
+        <v>431838.19</v>
       </c>
       <c r="F103">
-        <v>6846739.2000000002</v>
+        <v>6845908.1699999999</v>
       </c>
       <c r="G103">
-        <v>-1194.18</v>
+        <v>-1190.68</v>
       </c>
       <c r="H103">
-        <v>2060.98</v>
+        <v>2794.81</v>
       </c>
       <c r="K103">
-        <v>-1194.18</v>
+        <v>-1190.68</v>
       </c>
       <c r="O103" t="s">
         <v>39</v>
@@ -5887,34 +5857,34 @@
       <c r="X103" t="b">
         <v>1</v>
       </c>
-      <c r="AI103" s="1">
-        <v>46359.700752314813</v>
+      <c r="AI103" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="104" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>9444</v>
+        <v>9446</v>
       </c>
       <c r="B104" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D104" t="s">
         <v>40</v>
       </c>
       <c r="E104">
-        <v>432869.24</v>
+        <v>431828.8</v>
       </c>
       <c r="F104">
-        <v>6846098.29</v>
+        <v>6845861.2599999998</v>
       </c>
       <c r="G104">
-        <v>-1194.3800000000001</v>
+        <v>-1190.75</v>
       </c>
       <c r="H104">
-        <v>2972.13</v>
+        <v>2842.67</v>
       </c>
       <c r="K104">
-        <v>-1194.3800000000001</v>
+        <v>-1190.75</v>
       </c>
       <c r="O104" t="s">
         <v>39</v>
@@ -5932,33 +5902,33 @@
         <v>1</v>
       </c>
       <c r="AI104" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="105" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>9445</v>
+        <v>9439</v>
       </c>
       <c r="B105" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D105" t="s">
         <v>40</v>
       </c>
       <c r="E105">
-        <v>432894.94</v>
+        <v>431751.39</v>
       </c>
       <c r="F105">
-        <v>6845832.5599999996</v>
+        <v>6845514.9100000001</v>
       </c>
       <c r="G105">
-        <v>-1194.08</v>
+        <v>-1191.79</v>
       </c>
       <c r="H105">
-        <v>3239.5</v>
+        <v>3197.73</v>
       </c>
       <c r="K105">
-        <v>-1194.08</v>
+        <v>-1191.79</v>
       </c>
       <c r="O105" t="s">
         <v>39</v>
@@ -5975,34 +5945,34 @@
       <c r="X105" t="b">
         <v>1</v>
       </c>
-      <c r="AI105" t="s">
-        <v>63</v>
+      <c r="AI105" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="106" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>9446</v>
+        <v>9447</v>
       </c>
       <c r="B106" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D106" t="s">
         <v>40</v>
       </c>
       <c r="E106">
-        <v>433022.29</v>
+        <v>431743.08</v>
       </c>
       <c r="F106">
-        <v>6845467</v>
+        <v>6845475.5</v>
       </c>
       <c r="G106">
-        <v>-1194.3</v>
+        <v>-1192.95</v>
       </c>
       <c r="H106">
-        <v>3629.12</v>
+        <v>3238.04</v>
       </c>
       <c r="K106">
-        <v>-1194.3</v>
+        <v>-1192.95</v>
       </c>
       <c r="O106" t="s">
         <v>39</v>
@@ -6019,34 +5989,34 @@
       <c r="X106" t="b">
         <v>1</v>
       </c>
-      <c r="AI106" t="s">
-        <v>64</v>
+      <c r="AI106" s="1">
+        <v>46210.351273148146</v>
       </c>
     </row>
     <row r="107" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>9447</v>
+        <v>9440</v>
       </c>
       <c r="B107" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D107" t="s">
         <v>40</v>
       </c>
       <c r="E107">
-        <v>432542.62</v>
+        <v>431723.31</v>
       </c>
       <c r="F107">
-        <v>6846585.2800000003</v>
+        <v>6845383.2800000003</v>
       </c>
       <c r="G107">
-        <v>-1191.17</v>
+        <v>-1194.23</v>
       </c>
       <c r="H107">
-        <v>2378.9499999999998</v>
+        <v>3332.41</v>
       </c>
       <c r="K107">
-        <v>-1191.17</v>
+        <v>-1194.23</v>
       </c>
       <c r="O107" t="s">
         <v>39</v>
@@ -6063,34 +6033,37 @@
       <c r="X107" t="b">
         <v>1</v>
       </c>
-      <c r="AI107" t="s">
-        <v>65</v>
+      <c r="AI107" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="108" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>9448</v>
+        <v>9545</v>
       </c>
       <c r="B108" t="s">
-        <v>61</v>
+        <v>72</v>
+      </c>
+      <c r="C108">
+        <v>350370847072</v>
       </c>
       <c r="D108" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E108">
-        <v>432567.32</v>
+        <v>432539.86</v>
       </c>
       <c r="F108">
-        <v>6846562.0199999996</v>
+        <v>6846587.6299999999</v>
       </c>
       <c r="G108">
-        <v>-1191.4000000000001</v>
+        <v>-1191.19</v>
       </c>
       <c r="H108">
-        <v>2412.9</v>
+        <v>2375.4299999999998</v>
       </c>
       <c r="K108">
-        <v>-1191.4000000000001</v>
+        <v>-1191.19</v>
       </c>
       <c r="O108" t="s">
         <v>39</v>
@@ -6107,34 +6080,37 @@
       <c r="X108" t="b">
         <v>1</v>
       </c>
-      <c r="AI108" t="s">
-        <v>66</v>
+      <c r="AI108" s="1">
+        <v>46210.467766203707</v>
       </c>
     </row>
     <row r="109" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>9451</v>
+        <v>9546</v>
       </c>
       <c r="B109" t="s">
-        <v>61</v>
+        <v>72</v>
+      </c>
+      <c r="C109">
+        <v>350370847072</v>
       </c>
       <c r="D109" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E109">
-        <v>432921.56</v>
+        <v>432868.05</v>
       </c>
       <c r="F109">
-        <v>6845707.0099999998</v>
+        <v>6846102.4199999999</v>
       </c>
       <c r="G109">
-        <v>-1191.46</v>
+        <v>-1194.3800000000001</v>
       </c>
       <c r="H109">
-        <v>3368.09</v>
+        <v>2967.84</v>
       </c>
       <c r="K109">
-        <v>-1191.46</v>
+        <v>-1194.3800000000001</v>
       </c>
       <c r="O109" t="s">
         <v>39</v>
@@ -6151,34 +6127,37 @@
       <c r="X109" t="b">
         <v>1</v>
       </c>
-      <c r="AI109" t="s">
-        <v>67</v>
+      <c r="AI109" s="1">
+        <v>46210.46802083333</v>
       </c>
     </row>
     <row r="110" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>9452</v>
+        <v>9547</v>
       </c>
       <c r="B110" t="s">
-        <v>61</v>
+        <v>72</v>
+      </c>
+      <c r="C110">
+        <v>350370847072</v>
       </c>
       <c r="D110" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E110">
-        <v>432935.71</v>
+        <v>432920.68</v>
       </c>
       <c r="F110">
-        <v>6845662.29</v>
+        <v>6845709.3099999996</v>
       </c>
       <c r="G110">
-        <v>-1191.33</v>
+        <v>-1191.54</v>
       </c>
       <c r="H110">
-        <v>3415.01</v>
+        <v>3365.64</v>
       </c>
       <c r="K110">
-        <v>-1191.33</v>
+        <v>-1191.54</v>
       </c>
       <c r="O110" t="s">
         <v>39</v>
@@ -6195,43 +6174,40 @@
       <c r="X110" t="b">
         <v>1</v>
       </c>
-      <c r="AI110" t="s">
-        <v>68</v>
+      <c r="AI110" s="1">
+        <v>46210.468263888892</v>
       </c>
     </row>
     <row r="111" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>108</v>
+        <v>9538</v>
       </c>
       <c r="B111" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C111">
-        <v>171682391</v>
+        <v>350370847072</v>
       </c>
       <c r="D111" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E111">
-        <v>449073.88</v>
+        <v>432274.21</v>
       </c>
       <c r="F111">
-        <v>6850773.5499999998</v>
+        <v>6846736.8700000001</v>
       </c>
       <c r="G111">
-        <v>-1148.77</v>
+        <v>-1194.1300000000001</v>
       </c>
       <c r="H111">
-        <v>1335.1</v>
+        <v>2067.46</v>
       </c>
       <c r="K111">
-        <v>-1148.77</v>
+        <v>-1194.1300000000001</v>
       </c>
       <c r="O111" t="s">
-        <v>36</v>
-      </c>
-      <c r="P111">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U111" t="b">
         <v>1</v>
@@ -6243,51 +6219,39 @@
         <v>37</v>
       </c>
       <c r="X111" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC111" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD111">
-        <v>2</v>
-      </c>
-      <c r="AE111" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF111" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI111" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="AI111" s="1">
+        <v>46210.466782407406</v>
       </c>
     </row>
     <row r="112" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>9472</v>
+        <v>9539</v>
       </c>
       <c r="B112" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C112">
-        <v>171682391</v>
+        <v>350370847072</v>
       </c>
       <c r="D112" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E112">
-        <v>450074.78</v>
+        <v>432541.44</v>
       </c>
       <c r="F112">
-        <v>6850786.1100000003</v>
+        <v>6846586.1799999997</v>
       </c>
       <c r="G112">
-        <v>-1190.1300000000001</v>
+        <v>-1191.18</v>
       </c>
       <c r="H112">
-        <v>2342.56</v>
+        <v>2377.5700000000002</v>
       </c>
       <c r="K112">
-        <v>-1190.1300000000001</v>
+        <v>-1191.18</v>
       </c>
       <c r="O112" t="s">
         <v>39</v>
@@ -6305,36 +6269,36 @@
         <v>1</v>
       </c>
       <c r="AI112" s="1">
-        <v>46210.354317129626</v>
+        <v>46210.466863425929</v>
       </c>
     </row>
     <row r="113" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>9473</v>
+        <v>9540</v>
       </c>
       <c r="B113" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C113">
-        <v>171682391</v>
+        <v>350370847072</v>
       </c>
       <c r="D113" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E113">
-        <v>450424.17</v>
+        <v>432563.25</v>
       </c>
       <c r="F113">
-        <v>6850785.9400000004</v>
+        <v>6846565.6900000004</v>
       </c>
       <c r="G113">
-        <v>-1195.07</v>
+        <v>-1191.33</v>
       </c>
       <c r="H113">
-        <v>2692.2</v>
+        <v>2407.5100000000002</v>
       </c>
       <c r="K113">
-        <v>-1195.07</v>
+        <v>-1191.33</v>
       </c>
       <c r="O113" t="s">
         <v>39</v>
@@ -6352,36 +6316,36 @@
         <v>1</v>
       </c>
       <c r="AI113" s="1">
-        <v>46210.354351851849</v>
+        <v>46210.466967592591</v>
       </c>
     </row>
     <row r="114" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>9505</v>
+        <v>9541</v>
       </c>
       <c r="B114" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C114">
-        <v>171682391</v>
+        <v>350370847072</v>
       </c>
       <c r="D114" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E114">
-        <v>450074.91</v>
+        <v>432867.5</v>
       </c>
       <c r="F114">
-        <v>6850786.1100000003</v>
+        <v>6846104.4800000004</v>
       </c>
       <c r="G114">
-        <v>-1190.1300000000001</v>
+        <v>-1194.3900000000001</v>
       </c>
       <c r="H114">
-        <v>2342.69</v>
+        <v>2965.71</v>
       </c>
       <c r="K114">
-        <v>-1190.1300000000001</v>
+        <v>-1194.3900000000001</v>
       </c>
       <c r="O114" t="s">
         <v>39</v>
@@ -6399,42 +6363,39 @@
         <v>1</v>
       </c>
       <c r="AI114" s="1">
-        <v>46210.356724537036</v>
+        <v>46210.467106481483</v>
       </c>
     </row>
     <row r="115" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>2885</v>
+        <v>9542</v>
       </c>
       <c r="B115" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C115">
-        <v>171682391</v>
+        <v>350370847072</v>
       </c>
       <c r="D115" t="s">
         <v>40</v>
       </c>
       <c r="E115">
-        <v>449366.27</v>
+        <v>432895.5</v>
       </c>
       <c r="F115">
-        <v>6850785.0499999998</v>
+        <v>6845828.3499999996</v>
       </c>
       <c r="G115">
-        <v>-1196.1300000000001</v>
+        <v>-1194.1500000000001</v>
       </c>
       <c r="H115">
-        <v>1633.5</v>
+        <v>3243.73</v>
       </c>
       <c r="K115">
-        <v>-1196.1300000000001</v>
+        <v>-1194.1500000000001</v>
       </c>
       <c r="O115" t="s">
-        <v>36</v>
-      </c>
-      <c r="P115">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U115" t="b">
         <v>1</v>
@@ -6446,58 +6407,43 @@
         <v>37</v>
       </c>
       <c r="X115" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC115" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD115">
-        <v>2</v>
-      </c>
-      <c r="AE115" t="s">
-        <v>72</v>
-      </c>
-      <c r="AF115" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI115" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI115" s="1">
+        <v>46210.467222222222</v>
       </c>
     </row>
     <row r="116" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>3080</v>
+        <v>9543</v>
       </c>
       <c r="B116" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C116">
-        <v>171682391</v>
+        <v>350370847072</v>
       </c>
       <c r="D116" t="s">
         <v>40</v>
       </c>
       <c r="E116">
-        <v>450074.78</v>
+        <v>432921.95</v>
       </c>
       <c r="F116">
-        <v>6850786.1100000003</v>
+        <v>6845705.2300000004</v>
       </c>
       <c r="G116">
-        <v>-1190.1300000000001</v>
+        <v>-1191.42</v>
       </c>
       <c r="H116">
-        <v>2342.56</v>
+        <v>3369.92</v>
       </c>
       <c r="K116">
-        <v>-1190.1300000000001</v>
+        <v>-1191.42</v>
       </c>
       <c r="O116" t="s">
         <v>39</v>
       </c>
-      <c r="P116">
-        <v>2</v>
-      </c>
       <c r="U116" t="b">
         <v>1</v>
       </c>
@@ -6508,58 +6454,43 @@
         <v>37</v>
       </c>
       <c r="X116" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC116" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD116">
-        <v>2</v>
-      </c>
-      <c r="AE116" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF116" t="s">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="AI116" s="1">
-        <v>46210.354409722226</v>
+        <v>46210.467303240737</v>
       </c>
     </row>
     <row r="117" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>3088</v>
+        <v>9544</v>
       </c>
       <c r="B117" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C117">
-        <v>171682391</v>
+        <v>350370847072</v>
       </c>
       <c r="D117" t="s">
         <v>40</v>
       </c>
       <c r="E117">
-        <v>450107.56</v>
+        <v>432934.19</v>
       </c>
       <c r="F117">
-        <v>6850786.5300000003</v>
+        <v>6845666.5099999998</v>
       </c>
       <c r="G117">
-        <v>-1190.97</v>
+        <v>-1191.3</v>
       </c>
       <c r="H117">
-        <v>2375.37</v>
+        <v>3410.55</v>
       </c>
       <c r="K117">
-        <v>-1190.97</v>
+        <v>-1191.3</v>
       </c>
       <c r="O117" t="s">
         <v>39</v>
       </c>
-      <c r="P117">
-        <v>3</v>
-      </c>
       <c r="U117" t="b">
         <v>1</v>
       </c>
@@ -6570,57 +6501,45 @@
         <v>37</v>
       </c>
       <c r="X117" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC117" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD117">
-        <v>2</v>
-      </c>
-      <c r="AE117" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF117" t="s">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="AI117" s="1">
-        <v>46210.35670138889</v>
+        <v>46210.467407407406</v>
       </c>
     </row>
     <row r="118" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>3104</v>
+        <v>108</v>
       </c>
       <c r="B118" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C118">
         <v>171682391</v>
       </c>
       <c r="D118" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E118">
-        <v>450425.21</v>
+        <v>449073.88</v>
       </c>
       <c r="F118">
-        <v>6850785.9299999997</v>
+        <v>6850773.5499999998</v>
       </c>
       <c r="G118">
-        <v>-1195.07</v>
+        <v>-1148.77</v>
       </c>
       <c r="H118">
-        <v>2693.23</v>
+        <v>1335.1</v>
       </c>
       <c r="K118">
-        <v>-1195.07</v>
+        <v>-1148.77</v>
       </c>
       <c r="O118" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="P118">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U118" t="b">
         <v>1</v>
@@ -6641,48 +6560,45 @@
         <v>2</v>
       </c>
       <c r="AE118" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="AF118" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI118" s="1">
-        <v>46210.354375000003</v>
+        <v>62</v>
+      </c>
+      <c r="AI118" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="119" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>74</v>
+        <v>9468</v>
       </c>
       <c r="B119" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C119">
-        <v>171358584</v>
+        <v>171682391</v>
       </c>
       <c r="D119" t="s">
         <v>35</v>
       </c>
       <c r="E119">
-        <v>450318.68</v>
+        <v>450074.78</v>
       </c>
       <c r="F119">
-        <v>6849921.4400000004</v>
+        <v>6850786.1100000003</v>
       </c>
       <c r="G119">
-        <v>-1144.51</v>
+        <v>-1190.1300000000001</v>
       </c>
       <c r="H119">
-        <v>1433.4</v>
+        <v>2342.56</v>
       </c>
       <c r="K119">
-        <v>-1144.51</v>
+        <v>-1190.1300000000001</v>
       </c>
       <c r="O119" t="s">
-        <v>36</v>
-      </c>
-      <c r="P119">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U119" t="b">
         <v>1</v>
@@ -6694,51 +6610,39 @@
         <v>37</v>
       </c>
       <c r="X119" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC119" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD119">
-        <v>1</v>
-      </c>
-      <c r="AE119" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF119" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI119" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="AI119" s="1">
+        <v>46210.354317129626</v>
       </c>
     </row>
     <row r="120" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>9506</v>
+        <v>9501</v>
       </c>
       <c r="B120" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C120">
-        <v>171358584</v>
+        <v>171682391</v>
       </c>
       <c r="D120" t="s">
         <v>35</v>
       </c>
       <c r="E120">
-        <v>449862.88</v>
+        <v>450074.91</v>
       </c>
       <c r="F120">
-        <v>6850537.8499999996</v>
+        <v>6850786.1100000003</v>
       </c>
       <c r="G120">
-        <v>-1191.3699999999999</v>
+        <v>-1190.1300000000001</v>
       </c>
       <c r="H120">
-        <v>2210.33</v>
+        <v>2342.69</v>
       </c>
       <c r="K120">
-        <v>-1191.3699999999999</v>
+        <v>-1190.1300000000001</v>
       </c>
       <c r="O120" t="s">
         <v>39</v>
@@ -6756,42 +6660,39 @@
         <v>1</v>
       </c>
       <c r="AI120" s="1">
-        <v>46210.35696759259</v>
+        <v>46210.356724537036</v>
       </c>
     </row>
     <row r="121" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>2899</v>
+        <v>9469</v>
       </c>
       <c r="B121" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C121">
-        <v>171358584</v>
+        <v>171682391</v>
       </c>
       <c r="D121" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E121">
-        <v>450097.05</v>
+        <v>450424.17</v>
       </c>
       <c r="F121">
-        <v>6850165.4900000002</v>
+        <v>6850785.9400000004</v>
       </c>
       <c r="G121">
-        <v>-1192.58</v>
+        <v>-1195.07</v>
       </c>
       <c r="H121">
-        <v>1770.1</v>
+        <v>2692.2</v>
       </c>
       <c r="K121">
-        <v>-1192.58</v>
+        <v>-1195.07</v>
       </c>
       <c r="O121" t="s">
-        <v>36</v>
-      </c>
-      <c r="P121">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U121" t="b">
         <v>1</v>
@@ -6803,57 +6704,45 @@
         <v>37</v>
       </c>
       <c r="X121" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC121" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD121">
-        <v>1</v>
-      </c>
-      <c r="AE121" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF121" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI121" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI121" s="1">
+        <v>46210.354351851849</v>
       </c>
     </row>
     <row r="122" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>3070</v>
+        <v>2884</v>
       </c>
       <c r="B122" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C122">
-        <v>171358584</v>
+        <v>171682391</v>
       </c>
       <c r="D122" t="s">
         <v>40</v>
       </c>
       <c r="E122">
-        <v>449861.96</v>
+        <v>449366.27</v>
       </c>
       <c r="F122">
-        <v>6850539.2400000002</v>
+        <v>6850785.0499999998</v>
       </c>
       <c r="G122">
-        <v>-1191.42</v>
+        <v>-1196.1300000000001</v>
       </c>
       <c r="H122">
-        <v>2212</v>
+        <v>1633.5</v>
       </c>
       <c r="K122">
-        <v>-1191.42</v>
+        <v>-1196.1300000000001</v>
       </c>
       <c r="O122" t="s">
         <v>36</v>
       </c>
       <c r="P122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U122" t="b">
         <v>1</v>
@@ -6874,48 +6763,48 @@
         <v>2</v>
       </c>
       <c r="AE122" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="AF122" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI122" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI122" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="123" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>3143</v>
+        <v>3078</v>
       </c>
       <c r="B123" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C123">
-        <v>171358584</v>
+        <v>171682391</v>
       </c>
       <c r="D123" t="s">
         <v>40</v>
       </c>
       <c r="E123">
-        <v>449853.39</v>
+        <v>450074.78</v>
       </c>
       <c r="F123">
-        <v>6850552.25</v>
+        <v>6850786.1100000003</v>
       </c>
       <c r="G123">
-        <v>-1191.8800000000001</v>
+        <v>-1190.1300000000001</v>
       </c>
       <c r="H123">
-        <v>2227.6</v>
+        <v>2342.56</v>
       </c>
       <c r="K123">
-        <v>-1191.8800000000001</v>
+        <v>-1190.1300000000001</v>
       </c>
       <c r="O123" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P123">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U123" t="b">
         <v>1</v>
@@ -6936,48 +6825,48 @@
         <v>2</v>
       </c>
       <c r="AE123" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="AF123" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI123" t="s">
-        <v>43</v>
+        <v>62</v>
+      </c>
+      <c r="AI123" s="1">
+        <v>46210.354409722226</v>
       </c>
     </row>
     <row r="124" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>26</v>
+        <v>3086</v>
       </c>
       <c r="B124" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C124">
-        <v>171358586</v>
+        <v>171682391</v>
       </c>
       <c r="D124" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E124">
-        <v>449423.46</v>
+        <v>450107.56</v>
       </c>
       <c r="F124">
-        <v>6851149.6799999997</v>
+        <v>6850786.5300000003</v>
       </c>
       <c r="G124">
-        <v>-1145.92</v>
+        <v>-1190.97</v>
       </c>
       <c r="H124">
-        <v>1379.1</v>
+        <v>2375.37</v>
       </c>
       <c r="K124">
-        <v>-1145.92</v>
+        <v>-1190.97</v>
       </c>
       <c r="O124" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P124">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U124" t="b">
         <v>1</v>
@@ -6995,51 +6884,51 @@
         <v>46</v>
       </c>
       <c r="AD124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE124" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="AF124" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI124" t="s">
-        <v>42</v>
+        <v>62</v>
+      </c>
+      <c r="AI124" s="1">
+        <v>46210.35670138889</v>
       </c>
     </row>
     <row r="125" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>3040</v>
+        <v>3102</v>
       </c>
       <c r="B125" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C125">
-        <v>171358586</v>
+        <v>171682391</v>
       </c>
       <c r="D125" t="s">
         <v>40</v>
       </c>
       <c r="E125">
-        <v>449701.81</v>
+        <v>450425.21</v>
       </c>
       <c r="F125">
-        <v>6851220.0499999998</v>
+        <v>6850785.9299999997</v>
       </c>
       <c r="G125">
-        <v>-1192.8699999999999</v>
+        <v>-1195.07</v>
       </c>
       <c r="H125">
-        <v>1672.5</v>
+        <v>2693.23</v>
       </c>
       <c r="K125">
-        <v>-1192.8699999999999</v>
+        <v>-1195.07</v>
       </c>
       <c r="O125" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P125">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U125" t="b">
         <v>1</v>
@@ -7057,45 +6946,45 @@
         <v>46</v>
       </c>
       <c r="AD125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE125" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="AF125" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI125" t="s">
-        <v>43</v>
+        <v>62</v>
+      </c>
+      <c r="AI125" s="1">
+        <v>46210.354375000003</v>
       </c>
     </row>
     <row r="126" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>187</v>
+        <v>74</v>
       </c>
       <c r="B126" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C126">
-        <v>171358679</v>
+        <v>171358584</v>
       </c>
       <c r="D126" t="s">
         <v>35</v>
       </c>
       <c r="E126">
-        <v>448968.29</v>
+        <v>450318.68</v>
       </c>
       <c r="F126">
-        <v>6849117.6200000001</v>
+        <v>6849921.4400000004</v>
       </c>
       <c r="G126">
-        <v>-1149.3599999999999</v>
+        <v>-1144.51</v>
       </c>
       <c r="H126">
-        <v>1366.2</v>
+        <v>1433.4</v>
       </c>
       <c r="K126">
-        <v>-1149.3599999999999</v>
+        <v>-1144.51</v>
       </c>
       <c r="O126" t="s">
         <v>36</v>
@@ -7127,44 +7016,41 @@
       <c r="AF126" t="s">
         <v>48</v>
       </c>
-      <c r="AI126" t="s">
+      <c r="AI126" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="127" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>2822</v>
+        <v>9502</v>
       </c>
       <c r="B127" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C127">
-        <v>171358679</v>
+        <v>171358584</v>
       </c>
       <c r="D127" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E127">
-        <v>449185.07</v>
+        <v>449862.88</v>
       </c>
       <c r="F127">
-        <v>6849334.2800000003</v>
+        <v>6850537.8499999996</v>
       </c>
       <c r="G127">
-        <v>-1198.07</v>
+        <v>-1191.3699999999999</v>
       </c>
       <c r="H127">
-        <v>1679.01</v>
+        <v>2210.33</v>
       </c>
       <c r="K127">
-        <v>-1198.07</v>
+        <v>-1191.3699999999999</v>
       </c>
       <c r="O127" t="s">
         <v>39</v>
       </c>
-      <c r="P127">
-        <v>1</v>
-      </c>
       <c r="U127" t="b">
         <v>1</v>
       </c>
@@ -7175,51 +7061,39 @@
         <v>37</v>
       </c>
       <c r="X127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC127" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD127">
-        <v>1</v>
-      </c>
-      <c r="AE127" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF127" t="s">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="AI127" s="1">
-        <v>46210.34814814815</v>
+        <v>46210.35696759259</v>
       </c>
     </row>
     <row r="128" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>59</v>
+        <v>2898</v>
       </c>
       <c r="B128" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C128">
-        <v>171358704</v>
+        <v>171358584</v>
       </c>
       <c r="D128" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E128">
-        <v>450281.34</v>
+        <v>450097.05</v>
       </c>
       <c r="F128">
-        <v>6851348.8200000003</v>
+        <v>6850165.4900000002</v>
       </c>
       <c r="G128">
-        <v>-1145.3399999999999</v>
+        <v>-1192.58</v>
       </c>
       <c r="H128">
-        <v>1352</v>
+        <v>1770.1</v>
       </c>
       <c r="K128">
-        <v>-1145.3399999999999</v>
+        <v>-1192.58</v>
       </c>
       <c r="O128" t="s">
         <v>36</v>
@@ -7246,45 +7120,48 @@
         <v>1</v>
       </c>
       <c r="AE128" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="AF128" t="s">
         <v>48</v>
       </c>
       <c r="AI128" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="129" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>9468</v>
+        <v>3068</v>
       </c>
       <c r="B129" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C129">
-        <v>171358704</v>
+        <v>171358584</v>
       </c>
       <c r="D129" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E129">
-        <v>450515.09</v>
+        <v>449861.96</v>
       </c>
       <c r="F129">
-        <v>6851683.5599999996</v>
+        <v>6850539.2400000002</v>
       </c>
       <c r="G129">
-        <v>-1196.98</v>
+        <v>-1191.42</v>
       </c>
       <c r="H129">
-        <v>1768.35</v>
+        <v>2212</v>
       </c>
       <c r="K129">
-        <v>-1196.98</v>
+        <v>-1191.42</v>
       </c>
       <c r="O129" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P129">
+        <v>2</v>
       </c>
       <c r="U129" t="b">
         <v>1</v>
@@ -7296,42 +7173,57 @@
         <v>37</v>
       </c>
       <c r="X129" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI129" s="1">
-        <v>46210.353865740741</v>
+        <v>0</v>
+      </c>
+      <c r="AC129" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD129">
+        <v>2</v>
+      </c>
+      <c r="AE129" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF129" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI129" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="130" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>9469</v>
+        <v>3141</v>
       </c>
       <c r="B130" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C130">
-        <v>171358704</v>
+        <v>171358584</v>
       </c>
       <c r="D130" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E130">
-        <v>450845</v>
+        <v>449853.39</v>
       </c>
       <c r="F130">
-        <v>6852362.7199999997</v>
+        <v>6850552.25</v>
       </c>
       <c r="G130">
-        <v>-1196.3599999999999</v>
+        <v>-1191.8800000000001</v>
       </c>
       <c r="H130">
-        <v>2524.35</v>
+        <v>2227.6</v>
       </c>
       <c r="K130">
-        <v>-1196.3599999999999</v>
+        <v>-1191.8800000000001</v>
       </c>
       <c r="O130" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P130">
+        <v>3</v>
       </c>
       <c r="U130" t="b">
         <v>1</v>
@@ -7343,45 +7235,57 @@
         <v>37</v>
       </c>
       <c r="X130" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI130" s="1">
-        <v>46210.35392361111</v>
+        <v>0</v>
+      </c>
+      <c r="AC130" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD130">
+        <v>2</v>
+      </c>
+      <c r="AE130" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF130" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI130" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="131" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>2806</v>
+        <v>26</v>
       </c>
       <c r="B131" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="C131">
-        <v>171358704</v>
+        <v>171358586</v>
       </c>
       <c r="D131" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E131">
-        <v>450545.14</v>
+        <v>449423.46</v>
       </c>
       <c r="F131">
-        <v>6851745.3499999996</v>
+        <v>6851149.6799999997</v>
       </c>
       <c r="G131">
-        <v>-1198.2</v>
+        <v>-1145.92</v>
       </c>
       <c r="H131">
-        <v>1837.1</v>
+        <v>1379.1</v>
       </c>
       <c r="K131">
-        <v>-1198.2</v>
+        <v>-1145.92</v>
       </c>
       <c r="O131" t="s">
         <v>36</v>
       </c>
       <c r="P131">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U131" t="b">
         <v>1</v>
@@ -7399,51 +7303,51 @@
         <v>46</v>
       </c>
       <c r="AD131">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE131" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AF131" t="s">
         <v>48</v>
       </c>
       <c r="AI131" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="132" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>2819</v>
+        <v>3038</v>
       </c>
       <c r="B132" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="C132">
-        <v>171358704</v>
+        <v>171358586</v>
       </c>
       <c r="D132" t="s">
         <v>40</v>
       </c>
       <c r="E132">
-        <v>450849.09</v>
+        <v>449701.81</v>
       </c>
       <c r="F132">
-        <v>6852370.1200000001</v>
+        <v>6851220.0499999998</v>
       </c>
       <c r="G132">
-        <v>-1196.4000000000001</v>
+        <v>-1192.8699999999999</v>
       </c>
       <c r="H132">
-        <v>2532.8000000000002</v>
+        <v>1672.5</v>
       </c>
       <c r="K132">
-        <v>-1196.4000000000001</v>
+        <v>-1192.8699999999999</v>
       </c>
       <c r="O132" t="s">
         <v>36</v>
       </c>
       <c r="P132">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U132" t="b">
         <v>1</v>
@@ -7461,51 +7365,51 @@
         <v>46</v>
       </c>
       <c r="AD132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE132" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AF132" t="s">
         <v>48</v>
       </c>
-      <c r="AI132" t="s">
+      <c r="AI132" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="133" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>2895</v>
+        <v>187</v>
       </c>
       <c r="B133" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C133">
-        <v>171358704</v>
+        <v>171358679</v>
       </c>
       <c r="D133" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E133">
-        <v>450854.73</v>
+        <v>448968.29</v>
       </c>
       <c r="F133">
-        <v>6852380.3499999996</v>
+        <v>6849117.6200000001</v>
       </c>
       <c r="G133">
-        <v>-1196.56</v>
+        <v>-1149.3599999999999</v>
       </c>
       <c r="H133">
-        <v>2544.4899999999998</v>
+        <v>1366.2</v>
       </c>
       <c r="K133">
-        <v>-1196.56</v>
+        <v>-1149.3599999999999</v>
       </c>
       <c r="O133" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="P133">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U133" t="b">
         <v>1</v>
@@ -7526,48 +7430,48 @@
         <v>1</v>
       </c>
       <c r="AE133" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AF133" t="s">
         <v>48</v>
       </c>
-      <c r="AI133" s="1">
-        <v>46210.351145833331</v>
+      <c r="AI133" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="134" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>2981</v>
+        <v>2821</v>
       </c>
       <c r="B134" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C134">
-        <v>171358704</v>
+        <v>171358679</v>
       </c>
       <c r="D134" t="s">
         <v>40</v>
       </c>
       <c r="E134">
-        <v>450845.66</v>
+        <v>449185.07</v>
       </c>
       <c r="F134">
-        <v>6852363.9000000004</v>
+        <v>6849334.2800000003</v>
       </c>
       <c r="G134">
-        <v>-1196.3599999999999</v>
+        <v>-1198.07</v>
       </c>
       <c r="H134">
-        <v>2525.6999999999998</v>
+        <v>1679.01</v>
       </c>
       <c r="K134">
-        <v>-1196.3599999999999</v>
+        <v>-1198.07</v>
       </c>
       <c r="O134" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P134">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U134" t="b">
         <v>1</v>
@@ -7585,51 +7489,51 @@
         <v>46</v>
       </c>
       <c r="AD134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE134" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AF134" t="s">
         <v>48</v>
       </c>
-      <c r="AI134" t="s">
-        <v>43</v>
+      <c r="AI134" s="1">
+        <v>46210.34814814815</v>
       </c>
     </row>
     <row r="135" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>3035</v>
+        <v>59</v>
       </c>
       <c r="B135" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C135">
         <v>171358704</v>
       </c>
       <c r="D135" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E135">
-        <v>450854.73</v>
+        <v>450281.34</v>
       </c>
       <c r="F135">
-        <v>6852380.3499999996</v>
+        <v>6851348.8200000003</v>
       </c>
       <c r="G135">
-        <v>-1196.56</v>
+        <v>-1145.3399999999999</v>
       </c>
       <c r="H135">
-        <v>2544.4899999999998</v>
+        <v>1352</v>
       </c>
       <c r="K135">
-        <v>-1196.56</v>
+        <v>-1145.3399999999999</v>
       </c>
       <c r="O135" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="P135">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="U135" t="b">
         <v>1</v>
@@ -7647,51 +7551,48 @@
         <v>46</v>
       </c>
       <c r="AD135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE135" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AF135" t="s">
         <v>48</v>
       </c>
-      <c r="AI135" s="1">
-        <v>46210.351145833331</v>
+      <c r="AI135" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="136" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>3051</v>
+        <v>9464</v>
       </c>
       <c r="B136" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C136">
         <v>171358704</v>
       </c>
       <c r="D136" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E136">
-        <v>450844.05</v>
+        <v>450515.09</v>
       </c>
       <c r="F136">
-        <v>6852361.0199999996</v>
+        <v>6851683.5599999996</v>
       </c>
       <c r="G136">
-        <v>-1196.3499999999999</v>
+        <v>-1196.98</v>
       </c>
       <c r="H136">
-        <v>2522.4</v>
+        <v>1768.35</v>
       </c>
       <c r="K136">
-        <v>-1196.3499999999999</v>
+        <v>-1196.98</v>
       </c>
       <c r="O136" t="s">
-        <v>36</v>
-      </c>
-      <c r="P136">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="U136" t="b">
         <v>1</v>
@@ -7703,57 +7604,42 @@
         <v>37</v>
       </c>
       <c r="X136" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC136" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD136">
-        <v>2</v>
-      </c>
-      <c r="AE136" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF136" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI136" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI136" s="1">
+        <v>46210.353865740741</v>
       </c>
     </row>
     <row r="137" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>3057</v>
+        <v>9465</v>
       </c>
       <c r="B137" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C137">
         <v>171358704</v>
       </c>
       <c r="D137" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E137">
-        <v>450516.11</v>
+        <v>450845</v>
       </c>
       <c r="F137">
-        <v>6851685.5700000003</v>
+        <v>6852362.7199999997</v>
       </c>
       <c r="G137">
-        <v>-1196.98</v>
+        <v>-1196.3599999999999</v>
       </c>
       <c r="H137">
-        <v>1770.6</v>
+        <v>2524.35</v>
       </c>
       <c r="K137">
-        <v>-1196.98</v>
+        <v>-1196.3599999999999</v>
       </c>
       <c r="O137" t="s">
-        <v>36</v>
-      </c>
-      <c r="P137">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="U137" t="b">
         <v>1</v>
@@ -7765,30 +7651,18 @@
         <v>37</v>
       </c>
       <c r="X137" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC137" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD137">
-        <v>2</v>
-      </c>
-      <c r="AE137" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF137" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI137" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI137" s="1">
+        <v>46210.35392361111</v>
       </c>
     </row>
     <row r="138" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>3141</v>
+        <v>3139</v>
       </c>
       <c r="B138" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C138">
         <v>171358704</v>
@@ -7847,37 +7721,37 @@
     </row>
     <row r="139" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>8950</v>
+        <v>3055</v>
       </c>
       <c r="B139" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C139">
-        <v>350114731796</v>
+        <v>171358704</v>
       </c>
       <c r="D139" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E139">
-        <v>445867.42</v>
+        <v>450516.11</v>
       </c>
       <c r="F139">
-        <v>6848091.5300000003</v>
+        <v>6851685.5700000003</v>
       </c>
       <c r="G139">
-        <v>-1210.57</v>
+        <v>-1196.98</v>
       </c>
       <c r="H139">
-        <v>2844</v>
+        <v>1770.6</v>
       </c>
       <c r="K139">
-        <v>-1210.57</v>
+        <v>-1196.98</v>
       </c>
       <c r="O139" t="s">
         <v>36</v>
       </c>
       <c r="P139">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U139" t="b">
         <v>1</v>
@@ -7891,49 +7765,55 @@
       <c r="X139" t="b">
         <v>0</v>
       </c>
+      <c r="AC139" t="s">
+        <v>46</v>
+      </c>
       <c r="AD139">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AE139" t="s">
+        <v>49</v>
       </c>
       <c r="AF139" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI139" t="s">
-        <v>42</v>
+        <v>48</v>
+      </c>
+      <c r="AI139" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="140" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>8954</v>
+        <v>2805</v>
       </c>
       <c r="B140" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C140">
-        <v>350114731796</v>
+        <v>171358704</v>
       </c>
       <c r="D140" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E140">
-        <v>446663.65</v>
+        <v>450545.14</v>
       </c>
       <c r="F140">
-        <v>6848482.0599999996</v>
+        <v>6851745.3499999996</v>
       </c>
       <c r="G140">
-        <v>-1206.75</v>
+        <v>-1198.2</v>
       </c>
       <c r="H140">
-        <v>1956</v>
+        <v>1837.1</v>
       </c>
       <c r="K140">
-        <v>-1206.75</v>
+        <v>-1198.2</v>
       </c>
       <c r="O140" t="s">
         <v>36</v>
       </c>
       <c r="P140">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U140" t="b">
         <v>1</v>
@@ -7947,49 +7827,55 @@
       <c r="X140" t="b">
         <v>0</v>
       </c>
+      <c r="AC140" t="s">
+        <v>46</v>
+      </c>
       <c r="AD140">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AE140" t="s">
+        <v>49</v>
       </c>
       <c r="AF140" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI140" t="s">
-        <v>42</v>
+        <v>48</v>
+      </c>
+      <c r="AI140" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="141" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>8956</v>
+        <v>3049</v>
       </c>
       <c r="B141" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C141">
-        <v>350114731796</v>
+        <v>171358704</v>
       </c>
       <c r="D141" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E141">
-        <v>447224.15</v>
+        <v>450844.05</v>
       </c>
       <c r="F141">
-        <v>6848743.5700000003</v>
+        <v>6852361.0199999996</v>
       </c>
       <c r="G141">
-        <v>-1162.3699999999999</v>
+        <v>-1196.3499999999999</v>
       </c>
       <c r="H141">
-        <v>1331.8</v>
+        <v>2522.4</v>
       </c>
       <c r="K141">
-        <v>-1162.3699999999999</v>
+        <v>-1196.3499999999999</v>
       </c>
       <c r="O141" t="s">
         <v>36</v>
       </c>
       <c r="P141">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U141" t="b">
         <v>1</v>
@@ -8003,46 +7889,55 @@
       <c r="X141" t="b">
         <v>0</v>
       </c>
+      <c r="AC141" t="s">
+        <v>46</v>
+      </c>
       <c r="AD141">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AE141" t="s">
+        <v>49</v>
       </c>
       <c r="AF141" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AI141" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="142" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>9466</v>
+        <v>2979</v>
       </c>
       <c r="B142" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C142">
-        <v>350114731796</v>
+        <v>171358704</v>
       </c>
       <c r="D142" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E142">
-        <v>446832.83</v>
+        <v>450845.66</v>
       </c>
       <c r="F142">
-        <v>6848568.25</v>
+        <v>6852363.9000000004</v>
       </c>
       <c r="G142">
-        <v>-1209.18</v>
+        <v>-1196.3599999999999</v>
       </c>
       <c r="H142">
-        <v>1765.88</v>
+        <v>2525.6999999999998</v>
       </c>
       <c r="K142">
-        <v>-1209.18</v>
+        <v>-1196.3599999999999</v>
       </c>
       <c r="O142" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P142">
+        <v>5</v>
       </c>
       <c r="U142" t="b">
         <v>1</v>
@@ -8054,110 +7949,119 @@
         <v>37</v>
       </c>
       <c r="X142" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI142" s="1">
-        <v>46210.353576388887</v>
+        <v>0</v>
+      </c>
+      <c r="AC142" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD142">
+        <v>2</v>
+      </c>
+      <c r="AE142" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF142" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI142" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="143" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>9467</v>
+        <v>2818</v>
       </c>
       <c r="B143" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C143">
-        <v>350114731796</v>
+        <v>171358704</v>
       </c>
       <c r="D143" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E143">
-        <v>446304.19</v>
+        <v>450849.09</v>
       </c>
       <c r="F143">
-        <v>6848314.9199999999</v>
+        <v>6852370.1200000001</v>
       </c>
       <c r="G143">
-        <v>-1207.74</v>
+        <v>-1196.4000000000001</v>
       </c>
       <c r="H143">
-        <v>2352.7399999999998</v>
+        <v>2532.8000000000002</v>
       </c>
       <c r="K143">
-        <v>-1207.74</v>
-      </c>
-      <c r="L143">
+        <v>-1196.4000000000001</v>
+      </c>
+      <c r="O143" t="s">
+        <v>36</v>
+      </c>
+      <c r="P143">
+        <v>6</v>
+      </c>
+      <c r="U143" t="b">
+        <v>1</v>
+      </c>
+      <c r="V143" t="b">
+        <v>1</v>
+      </c>
+      <c r="W143" t="s">
+        <v>37</v>
+      </c>
+      <c r="X143" t="b">
         <v>0</v>
       </c>
-      <c r="O143" t="s">
-        <v>39</v>
-      </c>
-      <c r="P143">
-        <v>0</v>
-      </c>
-      <c r="Q143">
-        <v>0</v>
-      </c>
-      <c r="R143">
-        <v>0</v>
-      </c>
-      <c r="S143">
-        <v>0</v>
-      </c>
-      <c r="T143">
-        <v>0</v>
-      </c>
-      <c r="U143" t="b">
-        <v>0</v>
-      </c>
-      <c r="V143" t="b">
-        <v>0</v>
-      </c>
-      <c r="W143" t="s">
-        <v>37</v>
-      </c>
-      <c r="X143" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI143" s="1">
-        <v>46210.353750000002</v>
+      <c r="AC143" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD143">
+        <v>2</v>
+      </c>
+      <c r="AE143" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF143" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI143" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="144" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>8944</v>
+        <v>2894</v>
       </c>
       <c r="B144" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C144">
-        <v>350114731796</v>
+        <v>171358704</v>
       </c>
       <c r="D144" t="s">
         <v>40</v>
       </c>
       <c r="E144">
-        <v>446952.4</v>
+        <v>450854.73</v>
       </c>
       <c r="F144">
-        <v>6848627.3499999996</v>
+        <v>6852380.3499999996</v>
       </c>
       <c r="G144">
-        <v>-1208.6099999999999</v>
+        <v>-1196.56</v>
       </c>
       <c r="H144">
-        <v>1632.38</v>
+        <v>2544.4899999999998</v>
       </c>
       <c r="K144">
-        <v>-1208.6099999999999</v>
+        <v>-1196.56</v>
       </c>
       <c r="O144" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P144">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U144" t="b">
         <v>1</v>
@@ -8171,49 +8075,55 @@
       <c r="X144" t="b">
         <v>0</v>
       </c>
+      <c r="AC144" t="s">
+        <v>46</v>
+      </c>
       <c r="AD144">
         <v>1</v>
       </c>
+      <c r="AE144" t="s">
+        <v>53</v>
+      </c>
       <c r="AF144" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI144" t="s">
-        <v>43</v>
+        <v>48</v>
+      </c>
+      <c r="AI144" s="1">
+        <v>46210.351145833331</v>
       </c>
     </row>
     <row r="145" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>8945</v>
+        <v>3033</v>
       </c>
       <c r="B145" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C145">
-        <v>350114731796</v>
+        <v>171358704</v>
       </c>
       <c r="D145" t="s">
         <v>40</v>
       </c>
       <c r="E145">
-        <v>446630.16</v>
+        <v>450854.73</v>
       </c>
       <c r="F145">
-        <v>6848466.4400000004</v>
+        <v>6852380.3499999996</v>
       </c>
       <c r="G145">
-        <v>-1208.27</v>
+        <v>-1196.56</v>
       </c>
       <c r="H145">
-        <v>1993</v>
+        <v>2544.4899999999998</v>
       </c>
       <c r="K145">
-        <v>-1208.27</v>
+        <v>-1196.56</v>
       </c>
       <c r="O145" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P145">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U145" t="b">
         <v>1</v>
@@ -8227,49 +8137,55 @@
       <c r="X145" t="b">
         <v>0</v>
       </c>
+      <c r="AC145" t="s">
+        <v>46</v>
+      </c>
       <c r="AD145">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AE145" t="s">
+        <v>49</v>
       </c>
       <c r="AF145" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI145" t="s">
-        <v>43</v>
+        <v>48</v>
+      </c>
+      <c r="AI145" s="1">
+        <v>46210.351145833331</v>
       </c>
     </row>
     <row r="146" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>8952</v>
+        <v>8953</v>
       </c>
       <c r="B146" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C146">
         <v>350114731796</v>
       </c>
       <c r="D146" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E146">
-        <v>445785.52</v>
+        <v>447224.15</v>
       </c>
       <c r="F146">
-        <v>6848042.9000000004</v>
+        <v>6848743.5700000003</v>
       </c>
       <c r="G146">
-        <v>-1211.6500000000001</v>
+        <v>-1162.3699999999999</v>
       </c>
       <c r="H146">
-        <v>2939.3</v>
+        <v>1331.8</v>
       </c>
       <c r="K146">
-        <v>-1211.6500000000001</v>
+        <v>-1162.3699999999999</v>
       </c>
       <c r="O146" t="s">
         <v>36</v>
       </c>
       <c r="P146">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U146" t="b">
         <v>1</v>
@@ -8289,37 +8205,37 @@
       <c r="AF146" t="s">
         <v>38</v>
       </c>
-      <c r="AI146" t="s">
-        <v>43</v>
+      <c r="AI146" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="147" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>9507</v>
+        <v>9462</v>
       </c>
       <c r="B147" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C147">
         <v>350114731796</v>
       </c>
       <c r="D147" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E147">
-        <v>446665.16</v>
+        <v>446832.83</v>
       </c>
       <c r="F147">
-        <v>6848482.75</v>
+        <v>6848568.25</v>
       </c>
       <c r="G147">
-        <v>-1206.7</v>
+        <v>-1209.18</v>
       </c>
       <c r="H147">
-        <v>1954.34</v>
+        <v>1765.88</v>
       </c>
       <c r="K147">
-        <v>-1206.7</v>
+        <v>-1209.18</v>
       </c>
       <c r="O147" t="s">
         <v>39</v>
@@ -8337,39 +8253,42 @@
         <v>1</v>
       </c>
       <c r="AI147" s="1">
-        <v>46210.357118055559</v>
+        <v>46210.353576388887</v>
       </c>
     </row>
     <row r="148" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>9508</v>
+        <v>8951</v>
       </c>
       <c r="B148" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C148">
         <v>350114731796</v>
       </c>
       <c r="D148" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E148">
-        <v>446831.67</v>
+        <v>446663.65</v>
       </c>
       <c r="F148">
-        <v>6848567.6100000003</v>
+        <v>6848482.0599999996</v>
       </c>
       <c r="G148">
-        <v>-1209.19</v>
+        <v>-1206.75</v>
       </c>
       <c r="H148">
-        <v>1767.21</v>
+        <v>1956</v>
       </c>
       <c r="K148">
-        <v>-1209.19</v>
+        <v>-1206.75</v>
       </c>
       <c r="O148" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P148">
+        <v>2</v>
       </c>
       <c r="U148" t="b">
         <v>1</v>
@@ -8381,48 +8300,72 @@
         <v>37</v>
       </c>
       <c r="X148" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI148" s="1">
-        <v>46210.357164351852</v>
+        <v>0</v>
+      </c>
+      <c r="AD148">
+        <v>1</v>
+      </c>
+      <c r="AF148" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI148" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="149" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>9509</v>
+        <v>9463</v>
       </c>
       <c r="B149" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C149">
         <v>350114731796</v>
       </c>
       <c r="D149" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E149">
-        <v>446303.17</v>
+        <v>446304.19</v>
       </c>
       <c r="F149">
-        <v>6848314.46</v>
+        <v>6848314.9199999999</v>
       </c>
       <c r="G149">
-        <v>-1207.75</v>
+        <v>-1207.74</v>
       </c>
       <c r="H149">
-        <v>2353.86</v>
+        <v>2352.7399999999998</v>
       </c>
       <c r="K149">
-        <v>-1207.75</v>
+        <v>-1207.74</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
       </c>
       <c r="O149" t="s">
         <v>39</v>
       </c>
+      <c r="P149">
+        <v>0</v>
+      </c>
+      <c r="Q149">
+        <v>0</v>
+      </c>
+      <c r="R149">
+        <v>0</v>
+      </c>
+      <c r="S149">
+        <v>0</v>
+      </c>
+      <c r="T149">
+        <v>0</v>
+      </c>
       <c r="U149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W149" t="s">
         <v>37</v>
@@ -8431,39 +8374,42 @@
         <v>1</v>
       </c>
       <c r="AI149" s="1">
-        <v>46210.357210648152</v>
+        <v>46210.353750000002</v>
       </c>
     </row>
     <row r="150" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>9510</v>
+        <v>8947</v>
       </c>
       <c r="B150" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C150">
         <v>350114731796</v>
       </c>
       <c r="D150" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E150">
-        <v>446263.94</v>
+        <v>445867.42</v>
       </c>
       <c r="F150">
-        <v>6848296.7199999997</v>
+        <v>6848091.5300000003</v>
       </c>
       <c r="G150">
-        <v>-1208.04</v>
+        <v>-1210.57</v>
       </c>
       <c r="H150">
-        <v>2396.9299999999998</v>
+        <v>2844</v>
       </c>
       <c r="K150">
-        <v>-1208.04</v>
+        <v>-1210.57</v>
       </c>
       <c r="O150" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P150">
+        <v>3</v>
       </c>
       <c r="U150" t="b">
         <v>1</v>
@@ -8475,18 +8421,24 @@
         <v>37</v>
       </c>
       <c r="X150" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI150" s="1">
-        <v>46210.357222222221</v>
+        <v>0</v>
+      </c>
+      <c r="AD150">
+        <v>1</v>
+      </c>
+      <c r="AF150" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI150" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="151" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>9511</v>
+        <v>8941</v>
       </c>
       <c r="B151" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C151">
         <v>350114731796</v>
@@ -8495,22 +8447,25 @@
         <v>40</v>
       </c>
       <c r="E151">
-        <v>445866.16</v>
+        <v>446952.4</v>
       </c>
       <c r="F151">
-        <v>6848090.79</v>
+        <v>6848627.3499999996</v>
       </c>
       <c r="G151">
-        <v>-1210.56</v>
+        <v>-1208.6099999999999</v>
       </c>
       <c r="H151">
-        <v>2845.46</v>
+        <v>1632.38</v>
       </c>
       <c r="K151">
-        <v>-1210.56</v>
+        <v>-1208.6099999999999</v>
       </c>
       <c r="O151" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P151">
+        <v>1</v>
       </c>
       <c r="U151" t="b">
         <v>1</v>
@@ -8522,45 +8477,48 @@
         <v>37</v>
       </c>
       <c r="X151" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI151" s="1">
-        <v>46210.357291666667</v>
+        <v>0</v>
+      </c>
+      <c r="AD151">
+        <v>1</v>
+      </c>
+      <c r="AF151" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI151" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="152" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>8961</v>
+        <v>9504</v>
       </c>
       <c r="B152" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C152">
-        <v>350162787955</v>
+        <v>350114731796</v>
       </c>
       <c r="D152" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E152">
-        <v>445984.03</v>
+        <v>446831.67</v>
       </c>
       <c r="F152">
-        <v>6848971.8899999997</v>
+        <v>6848567.6100000003</v>
       </c>
       <c r="G152">
-        <v>-1210.71</v>
+        <v>-1209.19</v>
       </c>
       <c r="H152">
-        <v>2515</v>
+        <v>1767.21</v>
       </c>
       <c r="K152">
-        <v>-1210.71</v>
+        <v>-1209.19</v>
       </c>
       <c r="O152" t="s">
-        <v>36</v>
-      </c>
-      <c r="P152">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="U152" t="b">
         <v>1</v>
@@ -8572,45 +8530,42 @@
         <v>37</v>
       </c>
       <c r="X152" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI152" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="AI152" s="1">
+        <v>46210.357164351852</v>
       </c>
     </row>
     <row r="153" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>8966</v>
+        <v>9503</v>
       </c>
       <c r="B153" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C153">
-        <v>350162787955</v>
+        <v>350114731796</v>
       </c>
       <c r="D153" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E153">
-        <v>446240.48</v>
+        <v>446665.16</v>
       </c>
       <c r="F153">
-        <v>6848957.0899999999</v>
+        <v>6848482.75</v>
       </c>
       <c r="G153">
-        <v>-1209.67</v>
+        <v>-1206.7</v>
       </c>
       <c r="H153">
-        <v>2258</v>
+        <v>1954.34</v>
       </c>
       <c r="K153">
-        <v>-1209.67</v>
+        <v>-1206.7</v>
       </c>
       <c r="O153" t="s">
-        <v>36</v>
-      </c>
-      <c r="P153">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="U153" t="b">
         <v>1</v>
@@ -8622,45 +8577,45 @@
         <v>37</v>
       </c>
       <c r="X153" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI153" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="AI153" s="1">
+        <v>46210.357118055559</v>
       </c>
     </row>
     <row r="154" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>8968</v>
+        <v>8942</v>
       </c>
       <c r="B154" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C154">
-        <v>350162787955</v>
+        <v>350114731796</v>
       </c>
       <c r="D154" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E154">
-        <v>447142.23</v>
+        <v>446630.16</v>
       </c>
       <c r="F154">
-        <v>6848910.25</v>
+        <v>6848466.4400000004</v>
       </c>
       <c r="G154">
-        <v>-1162.1300000000001</v>
+        <v>-1208.27</v>
       </c>
       <c r="H154">
-        <v>1349.33</v>
+        <v>1993</v>
       </c>
       <c r="K154">
-        <v>-1162.1300000000001</v>
+        <v>-1208.27</v>
       </c>
       <c r="O154" t="s">
         <v>36</v>
       </c>
       <c r="P154">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U154" t="b">
         <v>1</v>
@@ -8680,43 +8635,40 @@
       <c r="AF154" t="s">
         <v>38</v>
       </c>
-      <c r="AI154" t="s">
-        <v>42</v>
+      <c r="AI154" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="155" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>8971</v>
+        <v>9505</v>
       </c>
       <c r="B155" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C155">
-        <v>350162787955</v>
+        <v>350114731796</v>
       </c>
       <c r="D155" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E155">
-        <v>445733.28</v>
+        <v>446303.17</v>
       </c>
       <c r="F155">
-        <v>6848980.1799999997</v>
+        <v>6848314.46</v>
       </c>
       <c r="G155">
-        <v>-1211.8800000000001</v>
+        <v>-1207.75</v>
       </c>
       <c r="H155">
-        <v>2766</v>
+        <v>2353.86</v>
       </c>
       <c r="K155">
-        <v>-1211.8800000000001</v>
+        <v>-1207.75</v>
       </c>
       <c r="O155" t="s">
-        <v>36</v>
-      </c>
-      <c r="P155">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="U155" t="b">
         <v>1</v>
@@ -8728,39 +8680,39 @@
         <v>37</v>
       </c>
       <c r="X155" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI155" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="AI155" s="1">
+        <v>46210.357210648152</v>
       </c>
     </row>
     <row r="156" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>9465</v>
+        <v>9506</v>
       </c>
       <c r="B156" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C156">
-        <v>350162787955</v>
+        <v>350114731796</v>
       </c>
       <c r="D156" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E156">
-        <v>446387.48</v>
+        <v>446263.94</v>
       </c>
       <c r="F156">
-        <v>6848947.7199999997</v>
+        <v>6848296.7199999997</v>
       </c>
       <c r="G156">
-        <v>-1208.3699999999999</v>
+        <v>-1208.04</v>
       </c>
       <c r="H156">
-        <v>2110.62</v>
+        <v>2396.9299999999998</v>
       </c>
       <c r="K156">
-        <v>-1208.3699999999999</v>
+        <v>-1208.04</v>
       </c>
       <c r="O156" t="s">
         <v>39</v>
@@ -8778,42 +8730,39 @@
         <v>1</v>
       </c>
       <c r="AI156" s="1">
-        <v>46210.353530092594</v>
+        <v>46210.357222222221</v>
       </c>
     </row>
     <row r="157" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>8959</v>
+        <v>9507</v>
       </c>
       <c r="B157" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C157">
-        <v>350162787955</v>
+        <v>350114731796</v>
       </c>
       <c r="D157" t="s">
         <v>40</v>
       </c>
       <c r="E157">
-        <v>445659.46</v>
+        <v>445866.16</v>
       </c>
       <c r="F157">
-        <v>6848984.8600000003</v>
+        <v>6848090.79</v>
       </c>
       <c r="G157">
-        <v>-1212.2</v>
+        <v>-1210.56</v>
       </c>
       <c r="H157">
-        <v>2840</v>
+        <v>2845.46</v>
       </c>
       <c r="K157">
-        <v>-1212.2</v>
+        <v>-1210.56</v>
       </c>
       <c r="O157" t="s">
-        <v>36</v>
-      </c>
-      <c r="P157">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="U157" t="b">
         <v>1</v>
@@ -8825,45 +8774,45 @@
         <v>37</v>
       </c>
       <c r="X157" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI157" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI157" s="1">
+        <v>46210.357291666667</v>
       </c>
     </row>
     <row r="158" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>8960</v>
+        <v>8949</v>
       </c>
       <c r="B158" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C158">
-        <v>350162787955</v>
+        <v>350114731796</v>
       </c>
       <c r="D158" t="s">
         <v>40</v>
       </c>
       <c r="E158">
-        <v>446794.95</v>
+        <v>445785.52</v>
       </c>
       <c r="F158">
-        <v>6848929.8099999996</v>
+        <v>6848042.9000000004</v>
       </c>
       <c r="G158">
-        <v>-1209.81</v>
+        <v>-1211.6500000000001</v>
       </c>
       <c r="H158">
-        <v>1702.5</v>
+        <v>2939.3</v>
       </c>
       <c r="K158">
-        <v>-1209.81</v>
+        <v>-1211.6500000000001</v>
       </c>
       <c r="O158" t="s">
         <v>36</v>
       </c>
       <c r="P158">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U158" t="b">
         <v>1</v>
@@ -8883,43 +8832,43 @@
       <c r="AF158" t="s">
         <v>38</v>
       </c>
-      <c r="AI158" t="s">
+      <c r="AI158" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="159" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>8964</v>
+        <v>8965</v>
       </c>
       <c r="B159" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C159">
         <v>350162787955</v>
       </c>
       <c r="D159" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E159">
-        <v>445824.17</v>
+        <v>447142.23</v>
       </c>
       <c r="F159">
-        <v>6848976.5199999996</v>
+        <v>6848910.25</v>
       </c>
       <c r="G159">
-        <v>-1211.8900000000001</v>
+        <v>-1162.1300000000001</v>
       </c>
       <c r="H159">
-        <v>2675</v>
+        <v>1349.33</v>
       </c>
       <c r="K159">
-        <v>-1211.8900000000001</v>
+        <v>-1162.1300000000001</v>
       </c>
       <c r="O159" t="s">
         <v>36</v>
       </c>
       <c r="P159">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U159" t="b">
         <v>1</v>
@@ -8933,43 +8882,46 @@
       <c r="X159" t="b">
         <v>0</v>
       </c>
-      <c r="AI159" t="s">
-        <v>43</v>
+      <c r="AD159">
+        <v>1</v>
+      </c>
+      <c r="AF159" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI159" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="160" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>8969</v>
+        <v>9461</v>
       </c>
       <c r="B160" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C160">
         <v>350162787955</v>
       </c>
       <c r="D160" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E160">
-        <v>446192.59</v>
+        <v>446387.48</v>
       </c>
       <c r="F160">
-        <v>6848960.0499999998</v>
+        <v>6848947.7199999997</v>
       </c>
       <c r="G160">
-        <v>-1210.1600000000001</v>
+        <v>-1208.3699999999999</v>
       </c>
       <c r="H160">
-        <v>2306</v>
+        <v>2110.62</v>
       </c>
       <c r="K160">
-        <v>-1210.1600000000001</v>
+        <v>-1208.3699999999999</v>
       </c>
       <c r="O160" t="s">
-        <v>36</v>
-      </c>
-      <c r="P160">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="U160" t="b">
         <v>1</v>
@@ -8981,42 +8933,45 @@
         <v>37</v>
       </c>
       <c r="X160" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI160" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI160" s="1">
+        <v>46210.353530092594</v>
       </c>
     </row>
     <row r="161" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>9512</v>
+        <v>8963</v>
       </c>
       <c r="B161" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C161">
         <v>350162787955</v>
       </c>
       <c r="D161" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E161">
-        <v>446390.07</v>
+        <v>446240.48</v>
       </c>
       <c r="F161">
-        <v>6848947.5700000003</v>
+        <v>6848957.0899999999</v>
       </c>
       <c r="G161">
-        <v>-1208.3699999999999</v>
+        <v>-1209.67</v>
       </c>
       <c r="H161">
-        <v>2108.0300000000002</v>
+        <v>2258</v>
       </c>
       <c r="K161">
-        <v>-1208.3699999999999</v>
+        <v>-1209.67</v>
       </c>
       <c r="O161" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P161">
+        <v>2</v>
       </c>
       <c r="U161" t="b">
         <v>1</v>
@@ -9028,42 +8983,45 @@
         <v>37</v>
       </c>
       <c r="X161" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI161" s="1">
-        <v>46210.357349537036</v>
+        <v>0</v>
+      </c>
+      <c r="AI161" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="162" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>9513</v>
+        <v>8958</v>
       </c>
       <c r="B162" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C162">
         <v>350162787955</v>
       </c>
       <c r="D162" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E162">
-        <v>446243.41</v>
+        <v>445984.03</v>
       </c>
       <c r="F162">
-        <v>6848956.9100000001</v>
+        <v>6848971.8899999997</v>
       </c>
       <c r="G162">
-        <v>-1209.7</v>
+        <v>-1210.71</v>
       </c>
       <c r="H162">
-        <v>2255.06</v>
+        <v>2515</v>
       </c>
       <c r="K162">
-        <v>-1209.7</v>
+        <v>-1210.71</v>
       </c>
       <c r="O162" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P162">
+        <v>3</v>
       </c>
       <c r="U162" t="b">
         <v>1</v>
@@ -9075,42 +9033,45 @@
         <v>37</v>
       </c>
       <c r="X162" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI162" s="1">
-        <v>46210.35738425926</v>
+        <v>0</v>
+      </c>
+      <c r="AI162" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="163" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>9514</v>
+        <v>8968</v>
       </c>
       <c r="B163" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C163">
         <v>350162787955</v>
       </c>
       <c r="D163" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E163">
-        <v>446342.65</v>
+        <v>445733.28</v>
       </c>
       <c r="F163">
-        <v>6848950.4199999999</v>
+        <v>6848980.1799999997</v>
       </c>
       <c r="G163">
-        <v>-1208.9000000000001</v>
+        <v>-1211.8800000000001</v>
       </c>
       <c r="H163">
-        <v>2155.5500000000002</v>
+        <v>2766</v>
       </c>
       <c r="K163">
-        <v>-1208.9000000000001</v>
+        <v>-1211.8800000000001</v>
       </c>
       <c r="O163" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P163">
+        <v>4</v>
       </c>
       <c r="U163" t="b">
         <v>1</v>
@@ -9122,18 +9083,18 @@
         <v>37</v>
       </c>
       <c r="X163" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI163" s="1">
-        <v>46210.35738425926</v>
+        <v>0</v>
+      </c>
+      <c r="AI163" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="164" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>9515</v>
+        <v>8957</v>
       </c>
       <c r="B164" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C164">
         <v>350162787955</v>
@@ -9142,22 +9103,25 @@
         <v>40</v>
       </c>
       <c r="E164">
-        <v>445985.55</v>
+        <v>446794.95</v>
       </c>
       <c r="F164">
-        <v>6848971.8399999999</v>
+        <v>6848929.8099999996</v>
       </c>
       <c r="G164">
-        <v>-1210.71</v>
+        <v>-1209.81</v>
       </c>
       <c r="H164">
-        <v>2513.48</v>
+        <v>1702.5</v>
       </c>
       <c r="K164">
-        <v>-1210.71</v>
+        <v>-1209.81</v>
       </c>
       <c r="O164" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P164">
+        <v>1</v>
       </c>
       <c r="U164" t="b">
         <v>1</v>
@@ -9169,18 +9133,24 @@
         <v>37</v>
       </c>
       <c r="X164" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI164" s="1">
-        <v>46210.357442129629</v>
+        <v>0</v>
+      </c>
+      <c r="AD164">
+        <v>1</v>
+      </c>
+      <c r="AF164" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI164" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="165" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>9516</v>
+        <v>9508</v>
       </c>
       <c r="B165" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C165">
         <v>350162787955</v>
@@ -9189,19 +9159,19 @@
         <v>40</v>
       </c>
       <c r="E165">
-        <v>445733.31</v>
+        <v>446390.07</v>
       </c>
       <c r="F165">
-        <v>6848980.1699999999</v>
+        <v>6848947.5700000003</v>
       </c>
       <c r="G165">
-        <v>-1211.8800000000001</v>
+        <v>-1208.3699999999999</v>
       </c>
       <c r="H165">
-        <v>2765.97</v>
+        <v>2108.0300000000002</v>
       </c>
       <c r="K165">
-        <v>-1211.8800000000001</v>
+        <v>-1208.3699999999999</v>
       </c>
       <c r="O165" t="s">
         <v>39</v>
@@ -9219,42 +9189,39 @@
         <v>1</v>
       </c>
       <c r="AI165" s="1">
-        <v>46210.357476851852</v>
+        <v>46210.357349537036</v>
       </c>
     </row>
     <row r="166" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>9429</v>
+        <v>9510</v>
       </c>
       <c r="B166" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C166">
-        <v>350114731838</v>
+        <v>350162787955</v>
       </c>
       <c r="D166" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E166">
-        <v>440554.51</v>
+        <v>446334.79</v>
       </c>
       <c r="F166">
-        <v>6851109.8700000001</v>
+        <v>6848950.9199999999</v>
       </c>
       <c r="G166">
-        <v>-1172.54</v>
+        <v>-1209.07</v>
       </c>
       <c r="H166">
-        <v>1336.64</v>
+        <v>2163.4299999999998</v>
       </c>
       <c r="K166">
-        <v>-1172.54</v>
+        <v>-1209.07</v>
       </c>
       <c r="O166" t="s">
-        <v>36</v>
-      </c>
-      <c r="P166">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U166" t="b">
         <v>1</v>
@@ -9268,43 +9235,37 @@
       <c r="X166" t="b">
         <v>1</v>
       </c>
-      <c r="AD166">
-        <v>1</v>
-      </c>
-      <c r="AF166" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI166" t="s">
-        <v>42</v>
+      <c r="AI166" s="1">
+        <v>46210.446550925924</v>
       </c>
     </row>
     <row r="167" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>9461</v>
+        <v>9509</v>
       </c>
       <c r="B167" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C167">
-        <v>350114731838</v>
+        <v>350162787955</v>
       </c>
       <c r="D167" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E167">
-        <v>441102.5</v>
+        <v>446243.41</v>
       </c>
       <c r="F167">
-        <v>6851660.8499999996</v>
+        <v>6848956.9100000001</v>
       </c>
       <c r="G167">
-        <v>-1223.29</v>
+        <v>-1209.7</v>
       </c>
       <c r="H167">
-        <v>2119.17</v>
+        <v>2255.06</v>
       </c>
       <c r="K167">
-        <v>-1223.29</v>
+        <v>-1209.7</v>
       </c>
       <c r="O167" t="s">
         <v>39</v>
@@ -9322,39 +9283,42 @@
         <v>1</v>
       </c>
       <c r="AI167" s="1">
-        <v>46210.353229166663</v>
+        <v>46210.35738425926</v>
       </c>
     </row>
     <row r="168" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>9462</v>
+        <v>8966</v>
       </c>
       <c r="B168" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C168">
-        <v>350114731838</v>
+        <v>350162787955</v>
       </c>
       <c r="D168" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E168">
-        <v>441227.73</v>
+        <v>446192.59</v>
       </c>
       <c r="F168">
-        <v>6851777.4900000002</v>
+        <v>6848960.0499999998</v>
       </c>
       <c r="G168">
-        <v>-1223.8499999999999</v>
+        <v>-1210.1600000000001</v>
       </c>
       <c r="H168">
-        <v>2290.38</v>
+        <v>2306</v>
       </c>
       <c r="K168">
-        <v>-1223.8499999999999</v>
+        <v>-1210.1600000000001</v>
       </c>
       <c r="O168" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P168">
+        <v>2</v>
       </c>
       <c r="U168" t="b">
         <v>1</v>
@@ -9366,39 +9330,39 @@
         <v>37</v>
       </c>
       <c r="X168" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI168" s="1">
-        <v>46210.353263888886</v>
+        <v>0</v>
+      </c>
+      <c r="AI168" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="169" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>9463</v>
+        <v>9511</v>
       </c>
       <c r="B169" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C169">
-        <v>350114731838</v>
+        <v>350162787955</v>
       </c>
       <c r="D169" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E169">
-        <v>441273.84</v>
+        <v>445985.55</v>
       </c>
       <c r="F169">
-        <v>6851820.2300000004</v>
+        <v>6848971.8399999999</v>
       </c>
       <c r="G169">
-        <v>-1225.0999999999999</v>
+        <v>-1210.71</v>
       </c>
       <c r="H169">
-        <v>2353.3000000000002</v>
+        <v>2513.48</v>
       </c>
       <c r="K169">
-        <v>-1225.0999999999999</v>
+        <v>-1210.71</v>
       </c>
       <c r="O169" t="s">
         <v>39</v>
@@ -9416,39 +9380,42 @@
         <v>1</v>
       </c>
       <c r="AI169" s="1">
-        <v>46210.353275462963</v>
+        <v>46210.357442129629</v>
       </c>
     </row>
     <row r="170" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>9464</v>
+        <v>8961</v>
       </c>
       <c r="B170" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C170">
-        <v>350114731838</v>
+        <v>350162787955</v>
       </c>
       <c r="D170" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E170">
-        <v>441572.54</v>
+        <v>445824.17</v>
       </c>
       <c r="F170">
-        <v>6852119.9800000004</v>
+        <v>6848976.5199999996</v>
       </c>
       <c r="G170">
-        <v>-1222.8399999999999</v>
+        <v>-1211.8900000000001</v>
       </c>
       <c r="H170">
-        <v>2777.2</v>
+        <v>2675</v>
       </c>
       <c r="K170">
-        <v>-1222.8399999999999</v>
+        <v>-1211.8900000000001</v>
       </c>
       <c r="O170" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P170">
+        <v>3</v>
       </c>
       <c r="U170" t="b">
         <v>1</v>
@@ -9460,45 +9427,42 @@
         <v>37</v>
       </c>
       <c r="X170" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI170" s="1">
-        <v>46210.353310185186</v>
+        <v>0</v>
+      </c>
+      <c r="AI170" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="171" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>9435</v>
+        <v>9512</v>
       </c>
       <c r="B171" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C171">
-        <v>350114731838</v>
+        <v>350162787955</v>
       </c>
       <c r="D171" t="s">
         <v>40</v>
       </c>
       <c r="E171">
-        <v>440719.23</v>
+        <v>445733.31</v>
       </c>
       <c r="F171">
-        <v>6851274.0800000001</v>
+        <v>6848980.1699999999</v>
       </c>
       <c r="G171">
-        <v>-1218.1500000000001</v>
+        <v>-1211.8800000000001</v>
       </c>
       <c r="H171">
-        <v>1574.26</v>
+        <v>2765.97</v>
       </c>
       <c r="K171">
-        <v>-1218.1500000000001</v>
+        <v>-1211.8800000000001</v>
       </c>
       <c r="O171" t="s">
-        <v>36</v>
-      </c>
-      <c r="P171">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U171" t="b">
         <v>1</v>
@@ -9512,46 +9476,43 @@
       <c r="X171" t="b">
         <v>1</v>
       </c>
-      <c r="AD171">
-        <v>1</v>
-      </c>
-      <c r="AF171" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI171" t="s">
-        <v>43</v>
+      <c r="AI171" s="1">
+        <v>46210.357476851852</v>
       </c>
     </row>
     <row r="172" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>9517</v>
+        <v>8956</v>
       </c>
       <c r="B172" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C172">
-        <v>350114731838</v>
+        <v>350162787955</v>
       </c>
       <c r="D172" t="s">
         <v>40</v>
       </c>
       <c r="E172">
-        <v>441101.05</v>
+        <v>445659.46</v>
       </c>
       <c r="F172">
-        <v>6851659.5</v>
+        <v>6848984.8600000003</v>
       </c>
       <c r="G172">
-        <v>-1223.31</v>
+        <v>-1212.2</v>
       </c>
       <c r="H172">
-        <v>2117.1999999999998</v>
+        <v>2840</v>
       </c>
       <c r="K172">
-        <v>-1223.31</v>
+        <v>-1212.2</v>
       </c>
       <c r="O172" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P172">
+        <v>4</v>
       </c>
       <c r="U172" t="b">
         <v>1</v>
@@ -9563,42 +9524,45 @@
         <v>37</v>
       </c>
       <c r="X172" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI172" s="1">
-        <v>46210.357557870368</v>
+        <v>0</v>
+      </c>
+      <c r="AI172" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="173" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>9518</v>
+        <v>9426</v>
       </c>
       <c r="B173" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C173">
         <v>350114731838</v>
       </c>
       <c r="D173" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E173">
-        <v>441225.98</v>
+        <v>440554.51</v>
       </c>
       <c r="F173">
-        <v>6851775.8700000001</v>
+        <v>6851109.8700000001</v>
       </c>
       <c r="G173">
-        <v>-1223.83</v>
+        <v>-1172.54</v>
       </c>
       <c r="H173">
-        <v>2288</v>
+        <v>1336.64</v>
       </c>
       <c r="K173">
-        <v>-1223.83</v>
+        <v>-1172.54</v>
       </c>
       <c r="O173" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P173">
+        <v>1</v>
       </c>
       <c r="U173" t="b">
         <v>1</v>
@@ -9612,37 +9576,43 @@
       <c r="X173" t="b">
         <v>1</v>
       </c>
-      <c r="AI173" s="1">
-        <v>46210.357581018521</v>
+      <c r="AD173">
+        <v>1</v>
+      </c>
+      <c r="AF173" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI173" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="174" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>9519</v>
+        <v>9457</v>
       </c>
       <c r="B174" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C174">
         <v>350114731838</v>
       </c>
       <c r="D174" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E174">
-        <v>441271.7</v>
+        <v>441102.5</v>
       </c>
       <c r="F174">
-        <v>6851818.25</v>
+        <v>6851660.8499999996</v>
       </c>
       <c r="G174">
-        <v>-1225.03</v>
+        <v>-1223.29</v>
       </c>
       <c r="H174">
-        <v>2350.37</v>
+        <v>2119.17</v>
       </c>
       <c r="K174">
-        <v>-1225.03</v>
+        <v>-1223.29</v>
       </c>
       <c r="O174" t="s">
         <v>39</v>
@@ -9660,57 +9630,490 @@
         <v>1</v>
       </c>
       <c r="AI174" s="1">
-        <v>46210.357615740744</v>
+        <v>46210.353229166663</v>
       </c>
     </row>
     <row r="175" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>9520</v>
+        <v>9458</v>
       </c>
       <c r="B175" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C175">
         <v>350114731838</v>
       </c>
       <c r="D175" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E175">
+        <v>441227.73</v>
+      </c>
+      <c r="F175">
+        <v>6851777.4900000002</v>
+      </c>
+      <c r="G175">
+        <v>-1223.8499999999999</v>
+      </c>
+      <c r="H175">
+        <v>2290.38</v>
+      </c>
+      <c r="K175">
+        <v>-1223.8499999999999</v>
+      </c>
+      <c r="O175" t="s">
+        <v>39</v>
+      </c>
+      <c r="U175" t="b">
+        <v>1</v>
+      </c>
+      <c r="V175" t="b">
+        <v>1</v>
+      </c>
+      <c r="W175" t="s">
+        <v>37</v>
+      </c>
+      <c r="X175" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI175" s="1">
+        <v>46210.353263888886</v>
+      </c>
+    </row>
+    <row r="176" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>9459</v>
+      </c>
+      <c r="B176" t="s">
+        <v>71</v>
+      </c>
+      <c r="C176">
+        <v>350114731838</v>
+      </c>
+      <c r="D176" t="s">
+        <v>35</v>
+      </c>
+      <c r="E176">
+        <v>441271.83</v>
+      </c>
+      <c r="F176">
+        <v>6851818.3799999999</v>
+      </c>
+      <c r="G176">
+        <v>-1225.03</v>
+      </c>
+      <c r="H176">
+        <v>2350.56</v>
+      </c>
+      <c r="K176">
+        <v>-1225.03</v>
+      </c>
+      <c r="O176" t="s">
+        <v>39</v>
+      </c>
+      <c r="U176" t="b">
+        <v>1</v>
+      </c>
+      <c r="V176" t="b">
+        <v>1</v>
+      </c>
+      <c r="W176" t="s">
+        <v>37</v>
+      </c>
+      <c r="X176" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI176" s="1">
+        <v>46210.44604166667</v>
+      </c>
+    </row>
+    <row r="177" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>9460</v>
+      </c>
+      <c r="B177" t="s">
+        <v>71</v>
+      </c>
+      <c r="C177">
+        <v>350114731838</v>
+      </c>
+      <c r="D177" t="s">
+        <v>35</v>
+      </c>
+      <c r="E177">
+        <v>441572.54</v>
+      </c>
+      <c r="F177">
+        <v>6852119.9800000004</v>
+      </c>
+      <c r="G177">
+        <v>-1222.8399999999999</v>
+      </c>
+      <c r="H177">
+        <v>2777.2</v>
+      </c>
+      <c r="K177">
+        <v>-1222.8399999999999</v>
+      </c>
+      <c r="O177" t="s">
+        <v>39</v>
+      </c>
+      <c r="U177" t="b">
+        <v>1</v>
+      </c>
+      <c r="V177" t="b">
+        <v>1</v>
+      </c>
+      <c r="W177" t="s">
+        <v>37</v>
+      </c>
+      <c r="X177" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI177" s="1">
+        <v>46210.353310185186</v>
+      </c>
+    </row>
+    <row r="178" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>9432</v>
+      </c>
+      <c r="B178" t="s">
+        <v>71</v>
+      </c>
+      <c r="C178">
+        <v>350114731838</v>
+      </c>
+      <c r="D178" t="s">
+        <v>40</v>
+      </c>
+      <c r="E178">
+        <v>440719.23</v>
+      </c>
+      <c r="F178">
+        <v>6851274.0800000001</v>
+      </c>
+      <c r="G178">
+        <v>-1218.1500000000001</v>
+      </c>
+      <c r="H178">
+        <v>1574.26</v>
+      </c>
+      <c r="K178">
+        <v>-1218.1500000000001</v>
+      </c>
+      <c r="O178" t="s">
+        <v>36</v>
+      </c>
+      <c r="P178">
+        <v>1</v>
+      </c>
+      <c r="U178" t="b">
+        <v>1</v>
+      </c>
+      <c r="V178" t="b">
+        <v>1</v>
+      </c>
+      <c r="W178" t="s">
+        <v>37</v>
+      </c>
+      <c r="X178" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD178">
+        <v>1</v>
+      </c>
+      <c r="AF178" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI178" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="179" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>9513</v>
+      </c>
+      <c r="B179" t="s">
+        <v>71</v>
+      </c>
+      <c r="C179">
+        <v>350114731838</v>
+      </c>
+      <c r="D179" t="s">
+        <v>40</v>
+      </c>
+      <c r="E179">
+        <v>441101.05</v>
+      </c>
+      <c r="F179">
+        <v>6851659.5</v>
+      </c>
+      <c r="G179">
+        <v>-1223.31</v>
+      </c>
+      <c r="H179">
+        <v>2117.1999999999998</v>
+      </c>
+      <c r="K179">
+        <v>-1223.31</v>
+      </c>
+      <c r="O179" t="s">
+        <v>39</v>
+      </c>
+      <c r="U179" t="b">
+        <v>1</v>
+      </c>
+      <c r="V179" t="b">
+        <v>1</v>
+      </c>
+      <c r="W179" t="s">
+        <v>37</v>
+      </c>
+      <c r="X179" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI179" s="1">
+        <v>46210.357557870368</v>
+      </c>
+    </row>
+    <row r="180" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>9536</v>
+      </c>
+      <c r="B180" t="s">
+        <v>71</v>
+      </c>
+      <c r="C180">
+        <v>350114731838</v>
+      </c>
+      <c r="D180" t="s">
+        <v>40</v>
+      </c>
+      <c r="E180">
+        <v>441146.84</v>
+      </c>
+      <c r="F180">
+        <v>6851702.2800000003</v>
+      </c>
+      <c r="G180">
+        <v>-1223.68</v>
+      </c>
+      <c r="H180">
+        <v>2179.89</v>
+      </c>
+      <c r="K180">
+        <v>-1223.68</v>
+      </c>
+      <c r="O180" t="s">
+        <v>39</v>
+      </c>
+      <c r="U180" t="b">
+        <v>1</v>
+      </c>
+      <c r="V180" t="b">
+        <v>1</v>
+      </c>
+      <c r="W180" t="s">
+        <v>37</v>
+      </c>
+      <c r="X180" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI180" s="1">
+        <v>46210.446562500001</v>
+      </c>
+    </row>
+    <row r="181" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>9514</v>
+      </c>
+      <c r="B181" t="s">
+        <v>71</v>
+      </c>
+      <c r="C181">
+        <v>350114731838</v>
+      </c>
+      <c r="D181" t="s">
+        <v>40</v>
+      </c>
+      <c r="E181">
+        <v>441225.98</v>
+      </c>
+      <c r="F181">
+        <v>6851775.8700000001</v>
+      </c>
+      <c r="G181">
+        <v>-1223.83</v>
+      </c>
+      <c r="H181">
+        <v>2288</v>
+      </c>
+      <c r="K181">
+        <v>-1223.83</v>
+      </c>
+      <c r="O181" t="s">
+        <v>39</v>
+      </c>
+      <c r="U181" t="b">
+        <v>1</v>
+      </c>
+      <c r="V181" t="b">
+        <v>1</v>
+      </c>
+      <c r="W181" t="s">
+        <v>37</v>
+      </c>
+      <c r="X181" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI181" s="1">
+        <v>46210.357581018521</v>
+      </c>
+    </row>
+    <row r="182" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>9537</v>
+      </c>
+      <c r="B182" t="s">
+        <v>71</v>
+      </c>
+      <c r="C182">
+        <v>350114731838</v>
+      </c>
+      <c r="D182" t="s">
+        <v>40</v>
+      </c>
+      <c r="E182">
+        <v>441248.13</v>
+      </c>
+      <c r="F182">
+        <v>6851796.4699999997</v>
+      </c>
+      <c r="G182">
+        <v>-1224.25</v>
+      </c>
+      <c r="H182">
+        <v>2318.27</v>
+      </c>
+      <c r="K182">
+        <v>-1224.25</v>
+      </c>
+      <c r="O182" t="s">
+        <v>39</v>
+      </c>
+      <c r="U182" t="b">
+        <v>1</v>
+      </c>
+      <c r="V182" t="b">
+        <v>1</v>
+      </c>
+      <c r="W182" t="s">
+        <v>37</v>
+      </c>
+      <c r="X182" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI182" s="1">
+        <v>46210.446620370371</v>
+      </c>
+    </row>
+    <row r="183" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>9515</v>
+      </c>
+      <c r="B183" t="s">
+        <v>71</v>
+      </c>
+      <c r="C183">
+        <v>350114731838</v>
+      </c>
+      <c r="D183" t="s">
+        <v>40</v>
+      </c>
+      <c r="E183">
+        <v>441271.7</v>
+      </c>
+      <c r="F183">
+        <v>6851818.25</v>
+      </c>
+      <c r="G183">
+        <v>-1225.03</v>
+      </c>
+      <c r="H183">
+        <v>2350.37</v>
+      </c>
+      <c r="K183">
+        <v>-1225.03</v>
+      </c>
+      <c r="O183" t="s">
+        <v>39</v>
+      </c>
+      <c r="U183" t="b">
+        <v>1</v>
+      </c>
+      <c r="V183" t="b">
+        <v>1</v>
+      </c>
+      <c r="W183" t="s">
+        <v>37</v>
+      </c>
+      <c r="X183" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI183" s="1">
+        <v>46210.357615740744</v>
+      </c>
+    </row>
+    <row r="184" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>9516</v>
+      </c>
+      <c r="B184" t="s">
+        <v>71</v>
+      </c>
+      <c r="C184">
+        <v>350114731838</v>
+      </c>
+      <c r="D184" t="s">
+        <v>40</v>
+      </c>
+      <c r="E184">
         <v>441571.25</v>
       </c>
-      <c r="F175">
+      <c r="F184">
         <v>6852118.3799999999</v>
       </c>
-      <c r="G175">
+      <c r="G184">
         <v>-1222.8599999999999</v>
       </c>
-      <c r="H175">
+      <c r="H184">
         <v>2775.14</v>
       </c>
-      <c r="K175">
+      <c r="K184">
         <v>-1222.8599999999999</v>
       </c>
-      <c r="O175" t="s">
-        <v>39</v>
-      </c>
-      <c r="U175" t="b">
-        <v>1</v>
-      </c>
-      <c r="V175" t="b">
-        <v>1</v>
-      </c>
-      <c r="W175" t="s">
-        <v>37</v>
-      </c>
-      <c r="X175" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI175" s="1">
+      <c r="O184" t="s">
+        <v>39</v>
+      </c>
+      <c r="U184" t="b">
+        <v>1</v>
+      </c>
+      <c r="V184" t="b">
+        <v>1</v>
+      </c>
+      <c r="W184" t="s">
+        <v>37</v>
+      </c>
+      <c r="X184" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI184" s="1">
         <v>46210.357662037037</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AI183" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9728,15 +10131,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F058933DE679D84C844BCD5E6FE280F8" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7c3559ca4b0718cc0d1b32599faf4d2a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd" xmlns:ns3="416a3325-149f-4ed5-ad81-b499dd2029e2" xmlns:ns4="c4de8975-a9e2-4032-8275-674640ba9e13" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2290b9febe09ca40959ebaa4289d445c" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd"/>
@@ -10004,6 +10398,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1FB06A0-65DD-411D-8E4B-3E9354C1DCE0}">
   <ds:schemaRefs>
@@ -10016,14 +10419,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37A1D12C-989B-423F-BA14-C3F31107F7DB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C455A20A-045D-41D5-AA3F-22BD10EAC1B5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10043,6 +10438,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37A1D12C-989B-423F-BA14-C3F31107F7DB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{826c2670-3368-498f-a16b-70466cda23c0}" enabled="1" method="Standard" siteId="{447a9cb9-b230-46bf-b430-a7b9f50e3c1e}" contentBits="0" removed="0"/>

--- a/Mck_Murta.xlsx
+++ b/Mck_Murta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://santos.sharepoint.com/sites/Dev-CoopOil/Shared Documents/Limestone Creek (Area)/McKinlay/Horizontal Well Sample Description Spreadsheets/Well Tops/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_59B50741D280066C621D9BC3C55C92FFBC81284F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{300CC169-9450-42FB-B687-07A289D86DF8}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_59B50741D280066C621D9BC3C55C92FFBC81284F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAE3EAE8-0775-4A7E-936D-E1A2A781C105}"/>
   <bookViews>
     <workbookView xWindow="19185" yWindow="3960" windowWidth="26850" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="74">
   <si>
     <t>Well identifier (Well name)</t>
   </si>
@@ -579,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI184"/>
+  <dimension ref="A1:AI191"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="31.28515625" customWidth="1"/>
@@ -691,7 +691,7 @@
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>9402</v>
+        <v>9398</v>
       </c>
       <c r="B2" t="s">
         <v>34</v>
@@ -747,7 +747,7 @@
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>9528</v>
+        <v>9524</v>
       </c>
       <c r="B3" t="s">
         <v>34</v>
@@ -794,7 +794,7 @@
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>9534</v>
+        <v>9525</v>
       </c>
       <c r="B4" t="s">
         <v>34</v>
@@ -806,19 +806,19 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>436403.56</v>
+        <v>436404.99</v>
       </c>
       <c r="F4">
-        <v>6842645.7699999996</v>
+        <v>6842650.9199999999</v>
       </c>
       <c r="G4">
-        <v>-1196.8599999999999</v>
+        <v>-1196.72</v>
       </c>
       <c r="H4">
-        <v>2133.4299999999998</v>
+        <v>2138.77</v>
       </c>
       <c r="K4">
-        <v>-1196.8599999999999</v>
+        <v>-1196.72</v>
       </c>
       <c r="O4" t="s">
         <v>39</v>
@@ -836,12 +836,12 @@
         <v>1</v>
       </c>
       <c r="AI4" s="1">
-        <v>46210.364733796298</v>
+        <v>46210.364421296297</v>
       </c>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>9529</v>
+        <v>9526</v>
       </c>
       <c r="B5" t="s">
         <v>34</v>
@@ -853,19 +853,19 @@
         <v>35</v>
       </c>
       <c r="E5">
-        <v>436404.99</v>
+        <v>436464.85</v>
       </c>
       <c r="F5">
-        <v>6842650.9199999999</v>
+        <v>6842826.1699999999</v>
       </c>
       <c r="G5">
-        <v>-1196.72</v>
+        <v>-1194.7</v>
       </c>
       <c r="H5">
-        <v>2138.77</v>
+        <v>2324.12</v>
       </c>
       <c r="K5">
-        <v>-1196.72</v>
+        <v>-1194.7</v>
       </c>
       <c r="O5" t="s">
         <v>39</v>
@@ -883,12 +883,12 @@
         <v>1</v>
       </c>
       <c r="AI5" s="1">
-        <v>46210.364421296297</v>
+        <v>46210.364444444444</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>9530</v>
+        <v>9527</v>
       </c>
       <c r="B6" t="s">
         <v>34</v>
@@ -900,19 +900,19 @@
         <v>35</v>
       </c>
       <c r="E6">
-        <v>436464.85</v>
+        <v>436577.55</v>
       </c>
       <c r="F6">
-        <v>6842826.1699999999</v>
+        <v>6843126.1299999999</v>
       </c>
       <c r="G6">
-        <v>-1194.7</v>
+        <v>-1199.45</v>
       </c>
       <c r="H6">
-        <v>2324.12</v>
+        <v>2644.93</v>
       </c>
       <c r="K6">
-        <v>-1194.7</v>
+        <v>-1199.45</v>
       </c>
       <c r="O6" t="s">
         <v>39</v>
@@ -930,12 +930,12 @@
         <v>1</v>
       </c>
       <c r="AI6" s="1">
-        <v>46210.364444444444</v>
+        <v>46210.364490740743</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>9531</v>
+        <v>9528</v>
       </c>
       <c r="B7" t="s">
         <v>34</v>
@@ -947,19 +947,19 @@
         <v>35</v>
       </c>
       <c r="E7">
-        <v>436577.55</v>
+        <v>436783.43</v>
       </c>
       <c r="F7">
-        <v>6843126.1299999999</v>
+        <v>6843613.6100000003</v>
       </c>
       <c r="G7">
-        <v>-1199.45</v>
+        <v>-1194.3599999999999</v>
       </c>
       <c r="H7">
-        <v>2644.93</v>
+        <v>3176.03</v>
       </c>
       <c r="K7">
-        <v>-1199.45</v>
+        <v>-1194.3599999999999</v>
       </c>
       <c r="O7" t="s">
         <v>39</v>
@@ -977,12 +977,12 @@
         <v>1</v>
       </c>
       <c r="AI7" s="1">
-        <v>46210.364490740743</v>
+        <v>46210.364525462966</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>9532</v>
+        <v>9529</v>
       </c>
       <c r="B8" t="s">
         <v>34</v>
@@ -994,19 +994,19 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>436783.43</v>
+        <v>436892.21</v>
       </c>
       <c r="F8">
-        <v>6843613.6100000003</v>
+        <v>6843834.0800000001</v>
       </c>
       <c r="G8">
-        <v>-1194.3599999999999</v>
+        <v>-1194.96</v>
       </c>
       <c r="H8">
-        <v>3176.03</v>
+        <v>3421.98</v>
       </c>
       <c r="K8">
-        <v>-1194.3599999999999</v>
+        <v>-1194.96</v>
       </c>
       <c r="O8" t="s">
         <v>39</v>
@@ -1024,12 +1024,12 @@
         <v>1</v>
       </c>
       <c r="AI8" s="1">
-        <v>46210.364525462966</v>
+        <v>46210.364560185182</v>
       </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>9533</v>
+        <v>9530</v>
       </c>
       <c r="B9" t="s">
         <v>34</v>
@@ -1041,19 +1041,19 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>436892.21</v>
+        <v>436403.56</v>
       </c>
       <c r="F9">
-        <v>6843834.0800000001</v>
+        <v>6842645.7699999996</v>
       </c>
       <c r="G9">
-        <v>-1194.96</v>
+        <v>-1196.8599999999999</v>
       </c>
       <c r="H9">
-        <v>3421.98</v>
+        <v>2133.4299999999998</v>
       </c>
       <c r="K9">
-        <v>-1194.96</v>
+        <v>-1196.8599999999999</v>
       </c>
       <c r="O9" t="s">
         <v>39</v>
@@ -1071,12 +1071,12 @@
         <v>1</v>
       </c>
       <c r="AI9" s="1">
-        <v>46210.364560185182</v>
+        <v>46210.364733796298</v>
       </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>9399</v>
+        <v>9395</v>
       </c>
       <c r="B10" t="s">
         <v>34</v>
@@ -1132,7 +1132,7 @@
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>9517</v>
+        <v>9513</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
@@ -1179,7 +1179,7 @@
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>9520</v>
+        <v>9514</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
@@ -1191,19 +1191,19 @@
         <v>40</v>
       </c>
       <c r="E12">
-        <v>436389.76</v>
+        <v>436466.81</v>
       </c>
       <c r="F12">
-        <v>6842592.2999999998</v>
+        <v>6842831.1399999997</v>
       </c>
       <c r="G12">
-        <v>-1197.57</v>
+        <v>-1194.7</v>
       </c>
       <c r="H12">
-        <v>2078.1799999999998</v>
+        <v>2329.4699999999998</v>
       </c>
       <c r="K12">
-        <v>-1197.57</v>
+        <v>-1194.7</v>
       </c>
       <c r="O12" t="s">
         <v>39</v>
@@ -1221,12 +1221,12 @@
         <v>1</v>
       </c>
       <c r="AI12" s="1">
-        <v>46210.36409722222</v>
+        <v>46210.364050925928</v>
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>9519</v>
+        <v>9515</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
@@ -1273,7 +1273,7 @@
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>9535</v>
+        <v>9516</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
@@ -1285,19 +1285,19 @@
         <v>40</v>
       </c>
       <c r="E14">
-        <v>436414.48</v>
+        <v>436389.76</v>
       </c>
       <c r="F14">
-        <v>6842683.3899999997</v>
+        <v>6842592.2999999998</v>
       </c>
       <c r="G14">
-        <v>-1195.68</v>
+        <v>-1197.57</v>
       </c>
       <c r="H14">
-        <v>2172.63</v>
+        <v>2078.1799999999998</v>
       </c>
       <c r="K14">
-        <v>-1195.68</v>
+        <v>-1197.57</v>
       </c>
       <c r="O14" t="s">
         <v>39</v>
@@ -1315,12 +1315,12 @@
         <v>1</v>
       </c>
       <c r="AI14" s="1">
-        <v>46210.364756944444</v>
+        <v>46210.36409722222</v>
       </c>
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>9518</v>
+        <v>9517</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
@@ -1332,19 +1332,19 @@
         <v>40</v>
       </c>
       <c r="E15">
-        <v>436466.81</v>
+        <v>436502.51</v>
       </c>
       <c r="F15">
-        <v>6842831.1399999997</v>
+        <v>6842922.2400000002</v>
       </c>
       <c r="G15">
-        <v>-1194.7</v>
+        <v>-1199.3900000000001</v>
       </c>
       <c r="H15">
-        <v>2329.4699999999998</v>
+        <v>2427.4899999999998</v>
       </c>
       <c r="K15">
-        <v>-1194.7</v>
+        <v>-1199.3900000000001</v>
       </c>
       <c r="O15" t="s">
         <v>39</v>
@@ -1362,12 +1362,12 @@
         <v>1</v>
       </c>
       <c r="AI15" s="1">
-        <v>46210.364050925928</v>
+        <v>46210.364120370374</v>
       </c>
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>9521</v>
+        <v>9518</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
@@ -1379,19 +1379,19 @@
         <v>40</v>
       </c>
       <c r="E16">
-        <v>436502.51</v>
+        <v>436578.68</v>
       </c>
       <c r="F16">
-        <v>6842922.2400000002</v>
+        <v>6843129.5099999998</v>
       </c>
       <c r="G16">
-        <v>-1199.3900000000001</v>
+        <v>-1199.4000000000001</v>
       </c>
       <c r="H16">
-        <v>2427.4899999999998</v>
+        <v>2648.49</v>
       </c>
       <c r="K16">
-        <v>-1199.3900000000001</v>
+        <v>-1199.4000000000001</v>
       </c>
       <c r="O16" t="s">
         <v>39</v>
@@ -1409,12 +1409,12 @@
         <v>1</v>
       </c>
       <c r="AI16" s="1">
-        <v>46210.364120370374</v>
+        <v>46210.36414351852</v>
       </c>
     </row>
     <row r="17" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>9522</v>
+        <v>9519</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
@@ -1426,19 +1426,19 @@
         <v>40</v>
       </c>
       <c r="E17">
-        <v>436578.68</v>
+        <v>436607.87</v>
       </c>
       <c r="F17">
-        <v>6843129.5099999998</v>
+        <v>6843219.2800000003</v>
       </c>
       <c r="G17">
-        <v>-1199.4000000000001</v>
+        <v>-1201.1500000000001</v>
       </c>
       <c r="H17">
-        <v>2648.49</v>
+        <v>2742.95</v>
       </c>
       <c r="K17">
-        <v>-1199.4000000000001</v>
+        <v>-1201.1500000000001</v>
       </c>
       <c r="O17" t="s">
         <v>39</v>
@@ -1456,12 +1456,12 @@
         <v>1</v>
       </c>
       <c r="AI17" s="1">
-        <v>46210.36414351852</v>
+        <v>46210.364155092589</v>
       </c>
     </row>
     <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>9523</v>
+        <v>9520</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -1473,19 +1473,19 @@
         <v>40</v>
       </c>
       <c r="E18">
-        <v>436607.87</v>
+        <v>436782.63</v>
       </c>
       <c r="F18">
-        <v>6843219.2800000003</v>
+        <v>6843612.0199999996</v>
       </c>
       <c r="G18">
-        <v>-1201.1500000000001</v>
+        <v>-1194.3900000000001</v>
       </c>
       <c r="H18">
-        <v>2742.95</v>
+        <v>3174.25</v>
       </c>
       <c r="K18">
-        <v>-1201.1500000000001</v>
+        <v>-1194.3900000000001</v>
       </c>
       <c r="O18" t="s">
         <v>39</v>
@@ -1503,12 +1503,12 @@
         <v>1</v>
       </c>
       <c r="AI18" s="1">
-        <v>46210.364155092589</v>
+        <v>46210.364189814813</v>
       </c>
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>9524</v>
+        <v>9521</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
@@ -1520,19 +1520,19 @@
         <v>40</v>
       </c>
       <c r="E19">
-        <v>436782.63</v>
+        <v>436806.54</v>
       </c>
       <c r="F19">
-        <v>6843612.0199999996</v>
+        <v>6843659.8200000003</v>
       </c>
       <c r="G19">
-        <v>-1194.3900000000001</v>
+        <v>-1193.95</v>
       </c>
       <c r="H19">
-        <v>3174.25</v>
+        <v>3227.71</v>
       </c>
       <c r="K19">
-        <v>-1194.3900000000001</v>
+        <v>-1193.95</v>
       </c>
       <c r="O19" t="s">
         <v>39</v>
@@ -1550,12 +1550,12 @@
         <v>1</v>
       </c>
       <c r="AI19" s="1">
-        <v>46210.364189814813</v>
+        <v>46210.364201388889</v>
       </c>
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>9525</v>
+        <v>9522</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
@@ -1567,19 +1567,19 @@
         <v>40</v>
       </c>
       <c r="E20">
-        <v>436806.54</v>
+        <v>436891.45</v>
       </c>
       <c r="F20">
-        <v>6843659.8200000003</v>
+        <v>6843832.4699999997</v>
       </c>
       <c r="G20">
-        <v>-1193.95</v>
+        <v>-1194.94</v>
       </c>
       <c r="H20">
-        <v>3227.71</v>
+        <v>3420.2</v>
       </c>
       <c r="K20">
-        <v>-1193.95</v>
+        <v>-1194.94</v>
       </c>
       <c r="O20" t="s">
         <v>39</v>
@@ -1597,12 +1597,12 @@
         <v>1</v>
       </c>
       <c r="AI20" s="1">
-        <v>46210.364201388889</v>
+        <v>46210.364236111112</v>
       </c>
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>9526</v>
+        <v>9523</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
@@ -1614,19 +1614,19 @@
         <v>40</v>
       </c>
       <c r="E21">
-        <v>436891.45</v>
+        <v>436896.6</v>
       </c>
       <c r="F21">
-        <v>6843832.4699999997</v>
+        <v>6843843.8300000001</v>
       </c>
       <c r="G21">
-        <v>-1194.94</v>
+        <v>-1195.1199999999999</v>
       </c>
       <c r="H21">
-        <v>3420.2</v>
+        <v>3432.67</v>
       </c>
       <c r="K21">
-        <v>-1194.94</v>
+        <v>-1195.1199999999999</v>
       </c>
       <c r="O21" t="s">
         <v>39</v>
@@ -1644,12 +1644,12 @@
         <v>1</v>
       </c>
       <c r="AI21" s="1">
-        <v>46210.364236111112</v>
+        <v>46210.364259259259</v>
       </c>
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>9527</v>
+        <v>9531</v>
       </c>
       <c r="B22" t="s">
         <v>34</v>
@@ -1661,19 +1661,19 @@
         <v>40</v>
       </c>
       <c r="E22">
-        <v>436896.6</v>
+        <v>436414.48</v>
       </c>
       <c r="F22">
-        <v>6843843.8300000001</v>
+        <v>6842683.3899999997</v>
       </c>
       <c r="G22">
-        <v>-1195.1199999999999</v>
+        <v>-1195.68</v>
       </c>
       <c r="H22">
-        <v>3432.67</v>
+        <v>2172.63</v>
       </c>
       <c r="K22">
-        <v>-1195.1199999999999</v>
+        <v>-1195.68</v>
       </c>
       <c r="O22" t="s">
         <v>39</v>
@@ -1691,12 +1691,12 @@
         <v>1</v>
       </c>
       <c r="AI22" s="1">
-        <v>46210.364259259259</v>
+        <v>46210.364756944444</v>
       </c>
     </row>
     <row r="23" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>9420</v>
+        <v>9416</v>
       </c>
       <c r="B23" t="s">
         <v>41</v>
@@ -1752,7 +1752,7 @@
     </row>
     <row r="24" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>9475</v>
+        <v>9471</v>
       </c>
       <c r="B24" t="s">
         <v>41</v>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>9476</v>
+        <v>9472</v>
       </c>
       <c r="B25" t="s">
         <v>41</v>
@@ -1846,7 +1846,7 @@
     </row>
     <row r="26" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>9477</v>
+        <v>9473</v>
       </c>
       <c r="B26" t="s">
         <v>41</v>
@@ -1893,7 +1893,7 @@
     </row>
     <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>9478</v>
+        <v>9474</v>
       </c>
       <c r="B27" t="s">
         <v>41</v>
@@ -1940,7 +1940,7 @@
     </row>
     <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>9479</v>
+        <v>9475</v>
       </c>
       <c r="B28" t="s">
         <v>41</v>
@@ -1987,7 +1987,7 @@
     </row>
     <row r="29" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>9480</v>
+        <v>9476</v>
       </c>
       <c r="B29" t="s">
         <v>41</v>
@@ -2034,7 +2034,7 @@
     </row>
     <row r="30" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>9418</v>
+        <v>9414</v>
       </c>
       <c r="B30" t="s">
         <v>41</v>
@@ -2090,7 +2090,7 @@
     </row>
     <row r="31" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>9548</v>
+        <v>9544</v>
       </c>
       <c r="B31" t="s">
         <v>41</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="32" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>9549</v>
+        <v>9545</v>
       </c>
       <c r="B32" t="s">
         <v>41</v>
@@ -2184,7 +2184,7 @@
     </row>
     <row r="33" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>9550</v>
+        <v>9546</v>
       </c>
       <c r="B33" t="s">
         <v>41</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="34" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>9551</v>
+        <v>9547</v>
       </c>
       <c r="B34" t="s">
         <v>41</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="35" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>9552</v>
+        <v>9548</v>
       </c>
       <c r="B35" t="s">
         <v>41</v>
@@ -2325,7 +2325,7 @@
     </row>
     <row r="36" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>9553</v>
+        <v>9549</v>
       </c>
       <c r="B36" t="s">
         <v>41</v>
@@ -2372,7 +2372,7 @@
     </row>
     <row r="37" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>9554</v>
+        <v>9550</v>
       </c>
       <c r="B37" t="s">
         <v>41</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="38" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>9555</v>
+        <v>9551</v>
       </c>
       <c r="B38" t="s">
         <v>41</v>
@@ -2466,7 +2466,7 @@
     </row>
     <row r="39" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>9556</v>
+        <v>9552</v>
       </c>
       <c r="B39" t="s">
         <v>41</v>
@@ -2513,7 +2513,7 @@
     </row>
     <row r="40" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>9557</v>
+        <v>9553</v>
       </c>
       <c r="B40" t="s">
         <v>41</v>
@@ -2560,7 +2560,7 @@
     </row>
     <row r="41" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>9558</v>
+        <v>9554</v>
       </c>
       <c r="B41" t="s">
         <v>41</v>
@@ -2607,7 +2607,7 @@
     </row>
     <row r="42" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>9415</v>
+        <v>9411</v>
       </c>
       <c r="B42" t="s">
         <v>44</v>
@@ -2663,7 +2663,7 @@
     </row>
     <row r="43" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>9481</v>
+        <v>9477</v>
       </c>
       <c r="B43" t="s">
         <v>44</v>
@@ -2710,7 +2710,7 @@
     </row>
     <row r="44" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>9482</v>
+        <v>9478</v>
       </c>
       <c r="B44" t="s">
         <v>44</v>
@@ -2757,7 +2757,7 @@
     </row>
     <row r="45" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>9483</v>
+        <v>9479</v>
       </c>
       <c r="B45" t="s">
         <v>44</v>
@@ -2804,7 +2804,7 @@
     </row>
     <row r="46" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>9484</v>
+        <v>9480</v>
       </c>
       <c r="B46" t="s">
         <v>44</v>
@@ -2851,7 +2851,7 @@
     </row>
     <row r="47" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>9411</v>
+        <v>9407</v>
       </c>
       <c r="B47" t="s">
         <v>44</v>
@@ -2907,7 +2907,7 @@
     </row>
     <row r="48" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>9497</v>
+        <v>9493</v>
       </c>
       <c r="B48" t="s">
         <v>44</v>
@@ -2954,7 +2954,7 @@
     </row>
     <row r="49" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>9498</v>
+        <v>9494</v>
       </c>
       <c r="B49" t="s">
         <v>44</v>
@@ -3001,7 +3001,7 @@
     </row>
     <row r="50" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>9499</v>
+        <v>9495</v>
       </c>
       <c r="B50" t="s">
         <v>44</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="51" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>9500</v>
+        <v>9496</v>
       </c>
       <c r="B51" t="s">
         <v>44</v>
@@ -3095,37 +3095,34 @@
     </row>
     <row r="52" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>204</v>
+        <v>9557</v>
       </c>
       <c r="B52" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C52">
-        <v>170663036</v>
+        <v>350233020918</v>
       </c>
       <c r="D52" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E52">
-        <v>441222.09</v>
+        <v>439347.97</v>
       </c>
       <c r="F52">
-        <v>6851676.21</v>
+        <v>6844718.5899999999</v>
       </c>
       <c r="G52">
-        <v>-1171.48</v>
+        <v>-1193.1600000000001</v>
       </c>
       <c r="H52">
-        <v>1366.82</v>
+        <v>2213.5300000000002</v>
       </c>
       <c r="K52">
-        <v>-1171.48</v>
+        <v>-1193.1600000000001</v>
       </c>
       <c r="O52" t="s">
-        <v>36</v>
-      </c>
-      <c r="P52">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U52" t="b">
         <v>1</v>
@@ -3137,51 +3134,39 @@
         <v>37</v>
       </c>
       <c r="X52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC52" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD52">
-        <v>1</v>
-      </c>
-      <c r="AE52" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF52" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI52" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="AI52" s="1">
+        <v>46210.585659722223</v>
       </c>
     </row>
     <row r="53" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>9471</v>
+        <v>9558</v>
       </c>
       <c r="B53" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C53">
-        <v>170663036</v>
+        <v>350233020918</v>
       </c>
       <c r="D53" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E53">
-        <v>441033.44</v>
+        <v>439623.18</v>
       </c>
       <c r="F53">
-        <v>6851386.8600000003</v>
+        <v>6844925.6100000003</v>
       </c>
       <c r="G53">
-        <v>-1220.9100000000001</v>
+        <v>-1195.53</v>
       </c>
       <c r="H53">
-        <v>1719.13</v>
+        <v>2558.2600000000002</v>
       </c>
       <c r="K53">
-        <v>-1220.9100000000001</v>
+        <v>-1195.53</v>
       </c>
       <c r="O53" t="s">
         <v>39</v>
@@ -3199,36 +3184,36 @@
         <v>1</v>
       </c>
       <c r="AI53" s="1">
-        <v>46210.356400462966</v>
+        <v>46210.585682870369</v>
       </c>
     </row>
     <row r="54" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>9472</v>
+        <v>9559</v>
       </c>
       <c r="B54" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C54">
-        <v>170663036</v>
+        <v>350233020918</v>
       </c>
       <c r="D54" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E54">
-        <v>440512.21</v>
+        <v>439889.1</v>
       </c>
       <c r="F54">
-        <v>6850770.25</v>
+        <v>6845131.2699999996</v>
       </c>
       <c r="G54">
-        <v>-1224.01</v>
+        <v>-1192.57</v>
       </c>
       <c r="H54">
-        <v>2527.08</v>
+        <v>2894.77</v>
       </c>
       <c r="K54">
-        <v>-1224.01</v>
+        <v>-1192.57</v>
       </c>
       <c r="O54" t="s">
         <v>39</v>
@@ -3246,36 +3231,36 @@
         <v>1</v>
       </c>
       <c r="AI54" s="1">
-        <v>46210.354733796295</v>
+        <v>46210.585694444446</v>
       </c>
     </row>
     <row r="55" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>9473</v>
+        <v>9560</v>
       </c>
       <c r="B55" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C55">
-        <v>170663036</v>
+        <v>350233020918</v>
       </c>
       <c r="D55" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E55">
-        <v>440354.39</v>
+        <v>440127.61</v>
       </c>
       <c r="F55">
-        <v>6850579.9800000004</v>
+        <v>6845293.7599999998</v>
       </c>
       <c r="G55">
-        <v>-1223.6300000000001</v>
+        <v>-1194.8699999999999</v>
       </c>
       <c r="H55">
-        <v>2774.4</v>
+        <v>3183.68</v>
       </c>
       <c r="K55">
-        <v>-1223.6300000000001</v>
+        <v>-1194.8699999999999</v>
       </c>
       <c r="O55" t="s">
         <v>39</v>
@@ -3293,12 +3278,12 @@
         <v>1</v>
       </c>
       <c r="AI55" s="1">
-        <v>46210.471307870372</v>
+        <v>46210.585706018515</v>
       </c>
     </row>
     <row r="56" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>9474</v>
+        <v>204</v>
       </c>
       <c r="B56" t="s">
         <v>45</v>
@@ -3310,22 +3295,25 @@
         <v>35</v>
       </c>
       <c r="E56">
-        <v>439767.53</v>
+        <v>441222.09</v>
       </c>
       <c r="F56">
-        <v>6849879.8799999999</v>
+        <v>6851676.21</v>
       </c>
       <c r="G56">
-        <v>-1223.93</v>
+        <v>-1171.48</v>
       </c>
       <c r="H56">
-        <v>3688.49</v>
+        <v>1366.82</v>
       </c>
       <c r="K56">
-        <v>-1223.93</v>
+        <v>-1171.48</v>
       </c>
       <c r="O56" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P56">
+        <v>1</v>
       </c>
       <c r="U56" t="b">
         <v>1</v>
@@ -3337,15 +3325,27 @@
         <v>37</v>
       </c>
       <c r="X56" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI56" s="1">
-        <v>46210.354861111111</v>
+        <v>0</v>
+      </c>
+      <c r="AC56" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD56">
+        <v>1</v>
+      </c>
+      <c r="AE56" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF56" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI56" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>2888</v>
+        <v>9467</v>
       </c>
       <c r="B57" t="s">
         <v>45</v>
@@ -3354,28 +3354,25 @@
         <v>170663036</v>
       </c>
       <c r="D57" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E57">
-        <v>441096.49</v>
+        <v>441033.44</v>
       </c>
       <c r="F57">
-        <v>6851469.9900000002</v>
+        <v>6851386.8600000003</v>
       </c>
       <c r="G57">
-        <v>-1220.21</v>
+        <v>-1220.9100000000001</v>
       </c>
       <c r="H57">
-        <v>1614.73</v>
+        <v>1719.13</v>
       </c>
       <c r="K57">
-        <v>-1220.21</v>
+        <v>-1220.9100000000001</v>
       </c>
       <c r="O57" t="s">
-        <v>36</v>
-      </c>
-      <c r="P57">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U57" t="b">
         <v>1</v>
@@ -3387,27 +3384,15 @@
         <v>37</v>
       </c>
       <c r="X57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC57" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD57">
-        <v>1</v>
-      </c>
-      <c r="AE57" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF57" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI57" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI57" s="1">
+        <v>46210.356400462966</v>
       </c>
     </row>
     <row r="58" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>2828</v>
+        <v>9468</v>
       </c>
       <c r="B58" t="s">
         <v>45</v>
@@ -3416,28 +3401,25 @@
         <v>170663036</v>
       </c>
       <c r="D58" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E58">
-        <v>441032.23</v>
+        <v>440512.21</v>
       </c>
       <c r="F58">
-        <v>6851385.3399999999</v>
+        <v>6850770.25</v>
       </c>
       <c r="G58">
-        <v>-1220.92</v>
+        <v>-1224.01</v>
       </c>
       <c r="H58">
-        <v>1721.08</v>
+        <v>2527.08</v>
       </c>
       <c r="K58">
-        <v>-1220.92</v>
+        <v>-1224.01</v>
       </c>
       <c r="O58" t="s">
-        <v>36</v>
-      </c>
-      <c r="P58">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="U58" t="b">
         <v>1</v>
@@ -3449,27 +3431,15 @@
         <v>37</v>
       </c>
       <c r="X58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC58" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD58">
-        <v>2</v>
-      </c>
-      <c r="AE58" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF58" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI58" s="1" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI58" s="1">
+        <v>46210.354733796295</v>
       </c>
     </row>
     <row r="59" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>3135</v>
+        <v>9469</v>
       </c>
       <c r="B59" t="s">
         <v>45</v>
@@ -3478,28 +3448,25 @@
         <v>170663036</v>
       </c>
       <c r="D59" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E59">
-        <v>441009.95</v>
+        <v>440354.39</v>
       </c>
       <c r="F59">
-        <v>6851357.1299999999</v>
+        <v>6850579.9800000004</v>
       </c>
       <c r="G59">
-        <v>-1221.3699999999999</v>
+        <v>-1223.6300000000001</v>
       </c>
       <c r="H59">
-        <v>1757.04</v>
+        <v>2774.4</v>
       </c>
       <c r="K59">
-        <v>-1221.3699999999999</v>
+        <v>-1223.6300000000001</v>
       </c>
       <c r="O59" t="s">
-        <v>36</v>
-      </c>
-      <c r="P59">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="U59" t="b">
         <v>1</v>
@@ -3511,27 +3478,15 @@
         <v>37</v>
       </c>
       <c r="X59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC59" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD59">
-        <v>2</v>
-      </c>
-      <c r="AE59" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF59" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI59" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI59" s="1">
+        <v>46210.471307870372</v>
       </c>
     </row>
     <row r="60" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>2929</v>
+        <v>9470</v>
       </c>
       <c r="B60" t="s">
         <v>45</v>
@@ -3540,28 +3495,25 @@
         <v>170663036</v>
       </c>
       <c r="D60" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E60">
-        <v>440510.27</v>
+        <v>439767.53</v>
       </c>
       <c r="F60">
-        <v>6850767.8700000001</v>
+        <v>6849879.8799999999</v>
       </c>
       <c r="G60">
-        <v>-1224.02</v>
+        <v>-1223.93</v>
       </c>
       <c r="H60">
-        <v>2530.15</v>
+        <v>3688.49</v>
       </c>
       <c r="K60">
-        <v>-1224.02</v>
+        <v>-1223.93</v>
       </c>
       <c r="O60" t="s">
-        <v>36</v>
-      </c>
-      <c r="P60">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="U60" t="b">
         <v>1</v>
@@ -3573,27 +3525,15 @@
         <v>37</v>
       </c>
       <c r="X60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC60" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD60">
-        <v>2</v>
-      </c>
-      <c r="AE60" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF60" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI60" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI60" s="1">
+        <v>46210.354861111111</v>
       </c>
     </row>
     <row r="61" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>2841</v>
+        <v>2827</v>
       </c>
       <c r="B61" t="s">
         <v>45</v>
@@ -3605,25 +3545,25 @@
         <v>40</v>
       </c>
       <c r="E61">
-        <v>440418.16</v>
+        <v>441032.23</v>
       </c>
       <c r="F61">
-        <v>6850655.1900000004</v>
+        <v>6851385.3399999999</v>
       </c>
       <c r="G61">
-        <v>-1224.54</v>
+        <v>-1220.92</v>
       </c>
       <c r="H61">
-        <v>2675.74</v>
+        <v>1721.08</v>
       </c>
       <c r="K61">
-        <v>-1224.54</v>
+        <v>-1220.92</v>
       </c>
       <c r="O61" t="s">
         <v>36</v>
       </c>
       <c r="P61">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U61" t="b">
         <v>1</v>
@@ -3655,7 +3595,7 @@
     </row>
     <row r="62" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>3001</v>
+        <v>2840</v>
       </c>
       <c r="B62" t="s">
         <v>45</v>
@@ -3667,25 +3607,25 @@
         <v>40</v>
       </c>
       <c r="E62">
-        <v>440352.99</v>
+        <v>440418.16</v>
       </c>
       <c r="F62">
-        <v>6850578.3700000001</v>
+        <v>6850655.1900000004</v>
       </c>
       <c r="G62">
-        <v>-1223.5899999999999</v>
+        <v>-1224.54</v>
       </c>
       <c r="H62">
-        <v>2776.54</v>
+        <v>2675.74</v>
       </c>
       <c r="K62">
-        <v>-1223.5899999999999</v>
+        <v>-1224.54</v>
       </c>
       <c r="O62" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="P62">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U62" t="b">
         <v>1</v>
@@ -3711,13 +3651,13 @@
       <c r="AF62" t="s">
         <v>48</v>
       </c>
-      <c r="AI62" s="1">
-        <v>46210.471331018518</v>
+      <c r="AI62" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="63" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>9559</v>
+        <v>2887</v>
       </c>
       <c r="B63" t="s">
         <v>45</v>
@@ -3729,22 +3669,25 @@
         <v>40</v>
       </c>
       <c r="E63">
-        <v>440333.21</v>
+        <v>441096.49</v>
       </c>
       <c r="F63">
-        <v>6850555.9100000001</v>
+        <v>6851469.9900000002</v>
       </c>
       <c r="G63">
-        <v>-1223.3900000000001</v>
+        <v>-1220.21</v>
       </c>
       <c r="H63">
-        <v>2806.48</v>
+        <v>1614.73</v>
       </c>
       <c r="K63">
-        <v>-1223.3900000000001</v>
+        <v>-1220.21</v>
       </c>
       <c r="O63" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P63">
+        <v>1</v>
       </c>
       <c r="U63" t="b">
         <v>1</v>
@@ -3756,15 +3699,27 @@
         <v>37</v>
       </c>
       <c r="X63" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI63" s="1">
-        <v>46210.471365740741</v>
+        <v>0</v>
+      </c>
+      <c r="AC63" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD63">
+        <v>1</v>
+      </c>
+      <c r="AE63" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF63" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI63" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="64" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>3104</v>
+        <v>2927</v>
       </c>
       <c r="B64" t="s">
         <v>45</v>
@@ -3776,25 +3731,25 @@
         <v>40</v>
       </c>
       <c r="E64">
-        <v>439766.64</v>
+        <v>440510.27</v>
       </c>
       <c r="F64">
-        <v>6849878.79</v>
+        <v>6850767.8700000001</v>
       </c>
       <c r="G64">
-        <v>-1223.93</v>
+        <v>-1224.02</v>
       </c>
       <c r="H64">
-        <v>3689.9</v>
+        <v>2530.15</v>
       </c>
       <c r="K64">
-        <v>-1223.93</v>
+        <v>-1224.02</v>
       </c>
       <c r="O64" t="s">
         <v>36</v>
       </c>
       <c r="P64">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U64" t="b">
         <v>1</v>
@@ -3826,37 +3781,37 @@
     </row>
     <row r="65" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>8972</v>
+        <v>2998</v>
       </c>
       <c r="B65" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C65">
-        <v>350114731284</v>
+        <v>170663036</v>
       </c>
       <c r="D65" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E65">
-        <v>446199.44</v>
+        <v>440352.99</v>
       </c>
       <c r="F65">
-        <v>6850194.21</v>
+        <v>6850578.3700000001</v>
       </c>
       <c r="G65">
-        <v>-1158.96</v>
+        <v>-1223.5899999999999</v>
       </c>
       <c r="H65">
-        <v>1395.4</v>
+        <v>2776.54</v>
       </c>
       <c r="K65">
-        <v>-1158.96</v>
+        <v>-1223.5899999999999</v>
       </c>
       <c r="O65" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P65">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U65" t="b">
         <v>1</v>
@@ -3870,46 +3825,55 @@
       <c r="X65" t="b">
         <v>0</v>
       </c>
+      <c r="AC65" t="s">
+        <v>46</v>
+      </c>
       <c r="AD65">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AE65" t="s">
+        <v>49</v>
       </c>
       <c r="AF65" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI65" t="s">
-        <v>42</v>
+        <v>48</v>
+      </c>
+      <c r="AI65" s="1">
+        <v>46210.471331018518</v>
       </c>
     </row>
     <row r="66" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>9488</v>
+        <v>3100</v>
       </c>
       <c r="B66" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C66">
-        <v>350114731284</v>
+        <v>170663036</v>
       </c>
       <c r="D66" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E66">
-        <v>446427.76</v>
+        <v>439766.64</v>
       </c>
       <c r="F66">
-        <v>6849872.9299999997</v>
+        <v>6849878.79</v>
       </c>
       <c r="G66">
-        <v>-1202.22</v>
+        <v>-1223.93</v>
       </c>
       <c r="H66">
-        <v>1793.72</v>
+        <v>3689.9</v>
       </c>
       <c r="K66">
-        <v>-1202.22</v>
+        <v>-1223.93</v>
       </c>
       <c r="O66" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P66">
+        <v>10</v>
       </c>
       <c r="U66" t="b">
         <v>1</v>
@@ -3921,45 +3885,57 @@
         <v>37</v>
       </c>
       <c r="X66" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI66" s="1">
-        <v>46210.355532407404</v>
+        <v>0</v>
+      </c>
+      <c r="AC66" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD66">
+        <v>2</v>
+      </c>
+      <c r="AE66" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF66" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI66" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="67" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>8978</v>
+        <v>3131</v>
       </c>
       <c r="B67" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C67">
-        <v>350114731284</v>
+        <v>170663036</v>
       </c>
       <c r="D67" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E67">
-        <v>446583.23</v>
+        <v>441009.95</v>
       </c>
       <c r="F67">
-        <v>6849647.3499999996</v>
+        <v>6851357.1299999999</v>
       </c>
       <c r="G67">
-        <v>-1207.8499999999999</v>
+        <v>-1221.3699999999999</v>
       </c>
       <c r="H67">
-        <v>2068</v>
+        <v>1757.04</v>
       </c>
       <c r="K67">
-        <v>-1207.8499999999999</v>
+        <v>-1221.3699999999999</v>
       </c>
       <c r="O67" t="s">
         <v>36</v>
       </c>
       <c r="P67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U67" t="b">
         <v>1</v>
@@ -3973,49 +3949,52 @@
       <c r="X67" t="b">
         <v>0</v>
       </c>
+      <c r="AC67" t="s">
+        <v>46</v>
+      </c>
       <c r="AD67">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AE67" t="s">
+        <v>49</v>
       </c>
       <c r="AF67" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AI67" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>8970</v>
+        <v>9555</v>
       </c>
       <c r="B68" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C68">
-        <v>350114731284</v>
+        <v>170663036</v>
       </c>
       <c r="D68" t="s">
         <v>40</v>
       </c>
       <c r="E68">
-        <v>446360.95</v>
+        <v>440333.21</v>
       </c>
       <c r="F68">
-        <v>6849967.1799999997</v>
+        <v>6850555.9100000001</v>
       </c>
       <c r="G68">
-        <v>-1203.1600000000001</v>
+        <v>-1223.3900000000001</v>
       </c>
       <c r="H68">
-        <v>1678.1</v>
+        <v>2806.48</v>
       </c>
       <c r="K68">
-        <v>-1203.1600000000001</v>
+        <v>-1223.3900000000001</v>
       </c>
       <c r="O68" t="s">
-        <v>36</v>
-      </c>
-      <c r="P68">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U68" t="b">
         <v>1</v>
@@ -4027,21 +4006,15 @@
         <v>37</v>
       </c>
       <c r="X68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD68">
-        <v>1</v>
-      </c>
-      <c r="AF68" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI68" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI68" s="1">
+        <v>46210.471365740741</v>
       </c>
     </row>
     <row r="69" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>9489</v>
+        <v>8968</v>
       </c>
       <c r="B69" t="s">
         <v>50</v>
@@ -4050,25 +4023,28 @@
         <v>350114731284</v>
       </c>
       <c r="D69" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E69">
-        <v>446426.88</v>
+        <v>446199.44</v>
       </c>
       <c r="F69">
-        <v>6849874.1200000001</v>
+        <v>6850194.21</v>
       </c>
       <c r="G69">
-        <v>-1202.21</v>
+        <v>-1158.96</v>
       </c>
       <c r="H69">
-        <v>1792.24</v>
+        <v>1395.4</v>
       </c>
       <c r="K69">
-        <v>-1202.21</v>
+        <v>-1158.96</v>
       </c>
       <c r="O69" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P69">
+        <v>1</v>
       </c>
       <c r="U69" t="b">
         <v>1</v>
@@ -4080,15 +4056,21 @@
         <v>37</v>
       </c>
       <c r="X69" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI69" s="1">
-        <v>46210.35564814815</v>
+        <v>0</v>
+      </c>
+      <c r="AD69">
+        <v>1</v>
+      </c>
+      <c r="AF69" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI69" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="70" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>9560</v>
+        <v>8974</v>
       </c>
       <c r="B70" t="s">
         <v>50</v>
@@ -4097,25 +4079,28 @@
         <v>350114731284</v>
       </c>
       <c r="D70" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E70">
-        <v>446582.4</v>
+        <v>446583.23</v>
       </c>
       <c r="F70">
-        <v>6849648.5599999996</v>
+        <v>6849647.3499999996</v>
       </c>
       <c r="G70">
-        <v>-1207.8800000000001</v>
+        <v>-1207.8499999999999</v>
       </c>
       <c r="H70">
-        <v>2066.54</v>
+        <v>2068</v>
       </c>
       <c r="K70">
-        <v>-1207.8800000000001</v>
+        <v>-1207.8499999999999</v>
       </c>
       <c r="O70" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P70">
+        <v>2</v>
       </c>
       <c r="U70" t="b">
         <v>1</v>
@@ -4127,15 +4112,21 @@
         <v>37</v>
       </c>
       <c r="X70" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI70" s="1">
-        <v>46210.472997685189</v>
+        <v>0</v>
+      </c>
+      <c r="AD70">
+        <v>1</v>
+      </c>
+      <c r="AF70" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI70" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="71" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>8976</v>
+        <v>9484</v>
       </c>
       <c r="B71" t="s">
         <v>50</v>
@@ -4144,28 +4135,25 @@
         <v>350114731284</v>
       </c>
       <c r="D71" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E71">
-        <v>446595.09</v>
+        <v>446427.76</v>
       </c>
       <c r="F71">
-        <v>6849630.04</v>
+        <v>6849872.9299999997</v>
       </c>
       <c r="G71">
-        <v>-1207.8699999999999</v>
+        <v>-1202.22</v>
       </c>
       <c r="H71">
-        <v>2089</v>
+        <v>1793.72</v>
       </c>
       <c r="K71">
-        <v>-1207.8699999999999</v>
+        <v>-1202.22</v>
       </c>
       <c r="O71" t="s">
-        <v>36</v>
-      </c>
-      <c r="P71">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="U71" t="b">
         <v>1</v>
@@ -4177,45 +4165,39 @@
         <v>37</v>
       </c>
       <c r="X71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD71">
-        <v>1</v>
-      </c>
-      <c r="AF71" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI71" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI71" s="1">
+        <v>46210.355532407404</v>
       </c>
     </row>
     <row r="72" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>245</v>
+        <v>8966</v>
       </c>
       <c r="B72" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C72">
-        <v>171358708</v>
+        <v>350114731284</v>
       </c>
       <c r="D72" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E72">
-        <v>447157.34</v>
+        <v>446360.95</v>
       </c>
       <c r="F72">
-        <v>6851044.4000000004</v>
+        <v>6849967.1799999997</v>
       </c>
       <c r="G72">
-        <v>-1157.73</v>
+        <v>-1203.1600000000001</v>
       </c>
       <c r="H72">
-        <v>1353.5</v>
+        <v>1678.1</v>
       </c>
       <c r="K72">
-        <v>-1157.73</v>
+        <v>-1203.1600000000001</v>
       </c>
       <c r="O72" t="s">
         <v>36</v>
@@ -4235,52 +4217,49 @@
       <c r="X72" t="b">
         <v>0</v>
       </c>
-      <c r="AC72" t="s">
-        <v>46</v>
-      </c>
       <c r="AD72">
         <v>1</v>
       </c>
-      <c r="AE72" t="s">
-        <v>52</v>
-      </c>
       <c r="AF72" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AI72" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="73" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>9485</v>
+        <v>8972</v>
       </c>
       <c r="B73" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C73">
-        <v>171358708</v>
+        <v>350114731284</v>
       </c>
       <c r="D73" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E73">
-        <v>447229.67</v>
+        <v>446595.09</v>
       </c>
       <c r="F73">
-        <v>6851368.8399999999</v>
+        <v>6849630.04</v>
       </c>
       <c r="G73">
-        <v>-1206.44</v>
+        <v>-1207.8699999999999</v>
       </c>
       <c r="H73">
-        <v>1692.63</v>
+        <v>2089</v>
       </c>
       <c r="K73">
-        <v>-1206.44</v>
+        <v>-1207.8699999999999</v>
       </c>
       <c r="O73" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P73">
+        <v>2</v>
       </c>
       <c r="U73" t="b">
         <v>1</v>
@@ -4292,45 +4271,48 @@
         <v>37</v>
       </c>
       <c r="X73" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI73" s="1">
-        <v>46210.355243055557</v>
+        <v>0</v>
+      </c>
+      <c r="AD73">
+        <v>1</v>
+      </c>
+      <c r="AF73" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI73" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="74" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>2864</v>
+        <v>9485</v>
       </c>
       <c r="B74" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C74">
-        <v>171358708</v>
+        <v>350114731284</v>
       </c>
       <c r="D74" t="s">
         <v>40</v>
       </c>
       <c r="E74">
-        <v>447220.24</v>
+        <v>446426.88</v>
       </c>
       <c r="F74">
-        <v>6851308.7800000003</v>
+        <v>6849874.1200000001</v>
       </c>
       <c r="G74">
-        <v>-1206.0999999999999</v>
+        <v>-1202.21</v>
       </c>
       <c r="H74">
-        <v>1631.8</v>
+        <v>1792.24</v>
       </c>
       <c r="K74">
-        <v>-1206.0999999999999</v>
+        <v>-1202.21</v>
       </c>
       <c r="O74" t="s">
-        <v>36</v>
-      </c>
-      <c r="P74">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U74" t="b">
         <v>1</v>
@@ -4342,57 +4324,42 @@
         <v>37</v>
       </c>
       <c r="X74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC74" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD74">
-        <v>1</v>
-      </c>
-      <c r="AE74" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF74" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI74" s="1" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI74" s="1">
+        <v>46210.35564814815</v>
       </c>
     </row>
     <row r="75" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>3043</v>
+        <v>9556</v>
       </c>
       <c r="B75" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C75">
-        <v>171358708</v>
+        <v>350114731284</v>
       </c>
       <c r="D75" t="s">
         <v>40</v>
       </c>
       <c r="E75">
-        <v>447230.21</v>
+        <v>446582.4</v>
       </c>
       <c r="F75">
-        <v>6851372.5800000001</v>
+        <v>6849648.5599999996</v>
       </c>
       <c r="G75">
-        <v>-1206.48</v>
+        <v>-1207.8800000000001</v>
       </c>
       <c r="H75">
-        <v>1696.4</v>
+        <v>2066.54</v>
       </c>
       <c r="K75">
-        <v>-1206.48</v>
+        <v>-1207.8800000000001</v>
       </c>
       <c r="O75" t="s">
-        <v>36</v>
-      </c>
-      <c r="P75">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="U75" t="b">
         <v>1</v>
@@ -4404,58 +4371,43 @@
         <v>37</v>
       </c>
       <c r="X75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC75" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD75">
-        <v>2</v>
-      </c>
-      <c r="AE75" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF75" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI75" s="1" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI75" s="1">
+        <v>46210.472997685189</v>
       </c>
     </row>
     <row r="76" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>2984</v>
+        <v>9563</v>
       </c>
       <c r="B76" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C76">
-        <v>171358708</v>
+        <v>350114731284</v>
       </c>
       <c r="D76" t="s">
         <v>40</v>
       </c>
       <c r="E76">
-        <v>447241.46</v>
+        <v>446449.2</v>
       </c>
       <c r="F76">
-        <v>6851440.6200000001</v>
+        <v>6849844.3899999997</v>
       </c>
       <c r="G76">
-        <v>-1206.8800000000001</v>
+        <v>-1203.19</v>
       </c>
       <c r="H76">
-        <v>1765.4</v>
+        <v>1829.45</v>
       </c>
       <c r="K76">
-        <v>-1206.8800000000001</v>
+        <v>-1203.19</v>
       </c>
       <c r="O76" t="s">
         <v>39</v>
       </c>
-      <c r="P76">
-        <v>3</v>
-      </c>
       <c r="U76" t="b">
         <v>1</v>
       </c>
@@ -4466,27 +4418,15 @@
         <v>37</v>
       </c>
       <c r="X76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC76" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD76">
-        <v>2</v>
-      </c>
-      <c r="AE76" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF76" t="s">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="AI76" s="1">
-        <v>46210.355995370373</v>
+        <v>46210.586076388892</v>
       </c>
     </row>
     <row r="77" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>2804</v>
+        <v>245</v>
       </c>
       <c r="B77" t="s">
         <v>51</v>
@@ -4495,28 +4435,28 @@
         <v>171358708</v>
       </c>
       <c r="D77" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E77">
-        <v>447429.37</v>
+        <v>447157.34</v>
       </c>
       <c r="F77">
-        <v>6852318.0099999998</v>
+        <v>6851044.4000000004</v>
       </c>
       <c r="G77">
-        <v>-1204.4000000000001</v>
+        <v>-1157.73</v>
       </c>
       <c r="H77">
-        <v>2663.2</v>
+        <v>1353.5</v>
       </c>
       <c r="K77">
-        <v>-1204.4000000000001</v>
+        <v>-1157.73</v>
       </c>
       <c r="O77" t="s">
         <v>36</v>
       </c>
       <c r="P77">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U77" t="b">
         <v>1</v>
@@ -4537,48 +4477,45 @@
         <v>1</v>
       </c>
       <c r="AE77" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AF77" t="s">
         <v>48</v>
       </c>
       <c r="AI77" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="78" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>8996</v>
+        <v>9481</v>
       </c>
       <c r="B78" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C78">
-        <v>350114731303</v>
+        <v>171358708</v>
       </c>
       <c r="D78" t="s">
         <v>35</v>
       </c>
       <c r="E78">
-        <v>448579.78</v>
+        <v>447229.67</v>
       </c>
       <c r="F78">
-        <v>6851659.8300000001</v>
+        <v>6851368.8399999999</v>
       </c>
       <c r="G78">
-        <v>-1156.74</v>
+        <v>-1206.44</v>
       </c>
       <c r="H78">
-        <v>1366.67</v>
+        <v>1692.63</v>
       </c>
       <c r="K78">
-        <v>-1156.74</v>
+        <v>-1206.44</v>
       </c>
       <c r="O78" t="s">
-        <v>36</v>
-      </c>
-      <c r="P78">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U78" t="b">
         <v>1</v>
@@ -4590,51 +4527,45 @@
         <v>37</v>
       </c>
       <c r="X78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD78">
-        <v>1</v>
-      </c>
-      <c r="AF78" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI78" s="1" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="AI78" s="1">
+        <v>46210.355243055557</v>
       </c>
     </row>
     <row r="79" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>8989</v>
+        <v>2804</v>
       </c>
       <c r="B79" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C79">
-        <v>350114731303</v>
+        <v>171358708</v>
       </c>
       <c r="D79" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E79">
-        <v>448285.57</v>
+        <v>447429.37</v>
       </c>
       <c r="F79">
-        <v>6851907.6799999997</v>
+        <v>6852318.0099999998</v>
       </c>
       <c r="G79">
-        <v>-1203.48</v>
+        <v>-1204.4000000000001</v>
       </c>
       <c r="H79">
-        <v>1757</v>
+        <v>2663.2</v>
       </c>
       <c r="K79">
-        <v>-1203.48</v>
+        <v>-1204.4000000000001</v>
       </c>
       <c r="O79" t="s">
         <v>36</v>
       </c>
       <c r="P79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U79" t="b">
         <v>1</v>
@@ -4648,49 +4579,55 @@
       <c r="X79" t="b">
         <v>0</v>
       </c>
+      <c r="AC79" t="s">
+        <v>46</v>
+      </c>
       <c r="AD79">
         <v>1</v>
       </c>
+      <c r="AE79" t="s">
+        <v>53</v>
+      </c>
       <c r="AF79" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AI79" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="80" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>8982</v>
+        <v>2863</v>
       </c>
       <c r="B80" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C80">
-        <v>350114731303</v>
+        <v>171358708</v>
       </c>
       <c r="D80" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E80">
-        <v>448096.1</v>
+        <v>447220.24</v>
       </c>
       <c r="F80">
-        <v>6852067.3700000001</v>
+        <v>6851308.7800000003</v>
       </c>
       <c r="G80">
-        <v>-1207.47</v>
+        <v>-1206.0999999999999</v>
       </c>
       <c r="H80">
-        <v>2005</v>
+        <v>1631.8</v>
       </c>
       <c r="K80">
-        <v>-1207.47</v>
+        <v>-1206.0999999999999</v>
       </c>
       <c r="O80" t="s">
         <v>36</v>
       </c>
       <c r="P80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U80" t="b">
         <v>1</v>
@@ -4704,49 +4641,55 @@
       <c r="X80" t="b">
         <v>0</v>
       </c>
+      <c r="AC80" t="s">
+        <v>46</v>
+      </c>
       <c r="AD80">
         <v>1</v>
       </c>
+      <c r="AE80" t="s">
+        <v>47</v>
+      </c>
       <c r="AF80" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AI80" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="81" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>8991</v>
+        <v>2981</v>
       </c>
       <c r="B81" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C81">
-        <v>350114731303</v>
+        <v>171358708</v>
       </c>
       <c r="D81" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E81">
-        <v>447884.53</v>
+        <v>447241.46</v>
       </c>
       <c r="F81">
-        <v>6852236.4400000004</v>
+        <v>6851440.6200000001</v>
       </c>
       <c r="G81">
-        <v>-1208.18</v>
+        <v>-1206.8800000000001</v>
       </c>
       <c r="H81">
-        <v>2276</v>
+        <v>1765.4</v>
       </c>
       <c r="K81">
-        <v>-1208.18</v>
+        <v>-1206.8800000000001</v>
       </c>
       <c r="O81" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U81" t="b">
         <v>1</v>
@@ -4760,49 +4703,55 @@
       <c r="X81" t="b">
         <v>0</v>
       </c>
+      <c r="AC81" t="s">
+        <v>46</v>
+      </c>
       <c r="AD81">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AE81" t="s">
+        <v>49</v>
       </c>
       <c r="AF81" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI81" t="s">
-        <v>42</v>
+        <v>48</v>
+      </c>
+      <c r="AI81" s="1">
+        <v>46210.355995370373</v>
       </c>
     </row>
     <row r="82" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>8993</v>
+        <v>3039</v>
       </c>
       <c r="B82" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C82">
-        <v>350114731303</v>
+        <v>171358708</v>
       </c>
       <c r="D82" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E82">
-        <v>447688.97</v>
+        <v>447230.21</v>
       </c>
       <c r="F82">
-        <v>6852406.0199999996</v>
+        <v>6851372.5800000001</v>
       </c>
       <c r="G82">
-        <v>-1209.8699999999999</v>
+        <v>-1206.48</v>
       </c>
       <c r="H82">
-        <v>2535</v>
+        <v>1696.4</v>
       </c>
       <c r="K82">
-        <v>-1209.8699999999999</v>
+        <v>-1206.48</v>
       </c>
       <c r="O82" t="s">
         <v>36</v>
       </c>
       <c r="P82">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U82" t="b">
         <v>1</v>
@@ -4816,19 +4765,25 @@
       <c r="X82" t="b">
         <v>0</v>
       </c>
+      <c r="AC82" t="s">
+        <v>46</v>
+      </c>
       <c r="AD82">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AE82" t="s">
+        <v>49</v>
       </c>
       <c r="AF82" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AI82" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="83" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>8990</v>
+        <v>8978</v>
       </c>
       <c r="B83" t="s">
         <v>54</v>
@@ -4837,28 +4792,28 @@
         <v>350114731303</v>
       </c>
       <c r="D83" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E83">
-        <v>448328.5</v>
+        <v>448096.1</v>
       </c>
       <c r="F83">
-        <v>6851873.6500000004</v>
+        <v>6852067.3700000001</v>
       </c>
       <c r="G83">
-        <v>-1203.79</v>
+        <v>-1207.47</v>
       </c>
       <c r="H83">
-        <v>1702.19</v>
+        <v>2005</v>
       </c>
       <c r="K83">
-        <v>-1203.79</v>
+        <v>-1207.47</v>
       </c>
       <c r="O83" t="s">
         <v>36</v>
       </c>
       <c r="P83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U83" t="b">
         <v>1</v>
@@ -4879,12 +4834,12 @@
         <v>38</v>
       </c>
       <c r="AI83" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="84" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>9490</v>
+        <v>8985</v>
       </c>
       <c r="B84" t="s">
         <v>54</v>
@@ -4893,25 +4848,28 @@
         <v>350114731303</v>
       </c>
       <c r="D84" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E84">
-        <v>448284.31</v>
+        <v>448285.57</v>
       </c>
       <c r="F84">
-        <v>6851908.6799999997</v>
+        <v>6851907.6799999997</v>
       </c>
       <c r="G84">
         <v>-1203.48</v>
       </c>
       <c r="H84">
-        <v>1758.61</v>
+        <v>1757</v>
       </c>
       <c r="K84">
         <v>-1203.48</v>
       </c>
       <c r="O84" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P84">
+        <v>2</v>
       </c>
       <c r="U84" t="b">
         <v>1</v>
@@ -4923,15 +4881,21 @@
         <v>37</v>
       </c>
       <c r="X84" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI84" s="1">
-        <v>46210.355844907404</v>
+        <v>0</v>
+      </c>
+      <c r="AD84">
+        <v>1</v>
+      </c>
+      <c r="AF84" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI84" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="85" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>8981</v>
+        <v>8987</v>
       </c>
       <c r="B85" t="s">
         <v>54</v>
@@ -4940,28 +4904,28 @@
         <v>350114731303</v>
       </c>
       <c r="D85" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E85">
-        <v>448219.09</v>
+        <v>447884.53</v>
       </c>
       <c r="F85">
-        <v>6851962.1200000001</v>
+        <v>6852236.4400000004</v>
       </c>
       <c r="G85">
-        <v>-1205.44</v>
+        <v>-1208.18</v>
       </c>
       <c r="H85">
-        <v>1843</v>
+        <v>2276</v>
       </c>
       <c r="K85">
-        <v>-1205.44</v>
+        <v>-1208.18</v>
       </c>
       <c r="O85" t="s">
         <v>36</v>
       </c>
       <c r="P85">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U85" t="b">
         <v>1</v>
@@ -4982,12 +4946,12 @@
         <v>38</v>
       </c>
       <c r="AI85" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="86" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>9491</v>
+        <v>8989</v>
       </c>
       <c r="B86" t="s">
         <v>54</v>
@@ -4996,25 +4960,28 @@
         <v>350114731303</v>
       </c>
       <c r="D86" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E86">
-        <v>448097.12</v>
+        <v>447688.97</v>
       </c>
       <c r="F86">
-        <v>6852066.5099999998</v>
+        <v>6852406.0199999996</v>
       </c>
       <c r="G86">
-        <v>-1207.42</v>
+        <v>-1209.8699999999999</v>
       </c>
       <c r="H86">
-        <v>2003.67</v>
+        <v>2535</v>
       </c>
       <c r="K86">
-        <v>-1207.42</v>
+        <v>-1209.8699999999999</v>
       </c>
       <c r="O86" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P86">
+        <v>5</v>
       </c>
       <c r="U86" t="b">
         <v>1</v>
@@ -5026,15 +4993,21 @@
         <v>37</v>
       </c>
       <c r="X86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI86" s="1">
-        <v>46210.355694444443</v>
+        <v>0</v>
+      </c>
+      <c r="AD86">
+        <v>1</v>
+      </c>
+      <c r="AF86" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI86" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="87" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>8986</v>
+        <v>8992</v>
       </c>
       <c r="B87" t="s">
         <v>54</v>
@@ -5043,28 +5016,28 @@
         <v>350114731303</v>
       </c>
       <c r="D87" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E87">
-        <v>447968.5</v>
+        <v>448579.78</v>
       </c>
       <c r="F87">
-        <v>6852170.2400000002</v>
+        <v>6851659.8300000001</v>
       </c>
       <c r="G87">
-        <v>-1209.29</v>
+        <v>-1156.74</v>
       </c>
       <c r="H87">
-        <v>2169</v>
+        <v>1366.67</v>
       </c>
       <c r="K87">
-        <v>-1209.29</v>
+        <v>-1156.74</v>
       </c>
       <c r="O87" t="s">
         <v>36</v>
       </c>
       <c r="P87">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U87" t="b">
         <v>1</v>
@@ -5085,12 +5058,12 @@
         <v>38</v>
       </c>
       <c r="AI87" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="88" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>8985</v>
+        <v>8977</v>
       </c>
       <c r="B88" t="s">
         <v>54</v>
@@ -5102,25 +5075,25 @@
         <v>40</v>
       </c>
       <c r="E88">
-        <v>447883.8</v>
+        <v>448219.09</v>
       </c>
       <c r="F88">
-        <v>6852237.0300000003</v>
+        <v>6851962.1200000001</v>
       </c>
       <c r="G88">
-        <v>-1208.1600000000001</v>
+        <v>-1205.44</v>
       </c>
       <c r="H88">
-        <v>2276.94</v>
+        <v>1843</v>
       </c>
       <c r="K88">
-        <v>-1208.1600000000001</v>
+        <v>-1205.44</v>
       </c>
       <c r="O88" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="P88">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U88" t="b">
         <v>1</v>
@@ -5140,13 +5113,13 @@
       <c r="AF88" t="s">
         <v>38</v>
       </c>
-      <c r="AI88" s="1">
-        <v>46210.355763888889</v>
+      <c r="AI88" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="89" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>9492</v>
+        <v>8981</v>
       </c>
       <c r="B89" t="s">
         <v>54</v>
@@ -5158,23 +5131,26 @@
         <v>40</v>
       </c>
       <c r="E89">
-        <v>447855.09</v>
+        <v>447883.8</v>
       </c>
       <c r="F89">
-        <v>6852260.5499999998</v>
+        <v>6852237.0300000003</v>
       </c>
       <c r="G89">
-        <v>-1208.06</v>
+        <v>-1208.1600000000001</v>
       </c>
       <c r="H89">
-        <v>2314.0700000000002</v>
+        <v>2276.94</v>
       </c>
       <c r="K89">
-        <v>-1208.06</v>
+        <v>-1208.1600000000001</v>
       </c>
       <c r="O89" t="s">
         <v>39</v>
       </c>
+      <c r="P89">
+        <v>4</v>
+      </c>
       <c r="U89" t="b">
         <v>1</v>
       </c>
@@ -5185,15 +5161,21 @@
         <v>37</v>
       </c>
       <c r="X89" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AD89">
+        <v>1</v>
+      </c>
+      <c r="AF89" t="s">
+        <v>38</v>
       </c>
       <c r="AI89" s="1">
-        <v>46210.355775462966</v>
+        <v>46210.355763888889</v>
       </c>
     </row>
     <row r="90" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>9493</v>
+        <v>8982</v>
       </c>
       <c r="B90" t="s">
         <v>54</v>
@@ -5205,22 +5187,25 @@
         <v>40</v>
       </c>
       <c r="E90">
-        <v>447689.83</v>
+        <v>447968.5</v>
       </c>
       <c r="F90">
-        <v>6852405.3099999996</v>
+        <v>6852170.2400000002</v>
       </c>
       <c r="G90">
-        <v>-1209.8800000000001</v>
+        <v>-1209.29</v>
       </c>
       <c r="H90">
-        <v>2533.88</v>
+        <v>2169</v>
       </c>
       <c r="K90">
-        <v>-1209.8800000000001</v>
+        <v>-1209.29</v>
       </c>
       <c r="O90" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P90">
+        <v>3</v>
       </c>
       <c r="U90" t="b">
         <v>1</v>
@@ -5232,39 +5217,45 @@
         <v>37</v>
       </c>
       <c r="X90" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI90" s="1">
-        <v>46210.355798611112</v>
+        <v>0</v>
+      </c>
+      <c r="AD90">
+        <v>1</v>
+      </c>
+      <c r="AF90" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI90" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="91" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>8998</v>
+        <v>8986</v>
       </c>
       <c r="B91" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C91">
-        <v>350162787959</v>
+        <v>350114731303</v>
       </c>
       <c r="D91" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E91">
-        <v>448691.87</v>
+        <v>448328.5</v>
       </c>
       <c r="F91">
-        <v>6851989.5999999996</v>
+        <v>6851873.6500000004</v>
       </c>
       <c r="G91">
-        <v>-1155.94</v>
+        <v>-1203.79</v>
       </c>
       <c r="H91">
-        <v>1365.7</v>
+        <v>1702.19</v>
       </c>
       <c r="K91">
-        <v>-1155.94</v>
+        <v>-1203.79</v>
       </c>
       <c r="O91" t="s">
         <v>36</v>
@@ -5291,7 +5282,7 @@
         <v>38</v>
       </c>
       <c r="AI91" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="92" spans="1:35" x14ac:dyDescent="0.25">
@@ -5299,28 +5290,28 @@
         <v>9486</v>
       </c>
       <c r="B92" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C92">
-        <v>350162787959</v>
+        <v>350114731303</v>
       </c>
       <c r="D92" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E92">
-        <v>448465.03</v>
+        <v>448284.31</v>
       </c>
       <c r="F92">
-        <v>6851472</v>
+        <v>6851908.6799999997</v>
       </c>
       <c r="G92">
-        <v>-1203.0999999999999</v>
+        <v>-1203.48</v>
       </c>
       <c r="H92">
-        <v>1936.48</v>
+        <v>1758.61</v>
       </c>
       <c r="K92">
-        <v>-1203.0999999999999</v>
+        <v>-1203.48</v>
       </c>
       <c r="O92" t="s">
         <v>39</v>
@@ -5338,7 +5329,7 @@
         <v>1</v>
       </c>
       <c r="AI92" s="1">
-        <v>46210.35527777778</v>
+        <v>46210.355844907404</v>
       </c>
     </row>
     <row r="93" spans="1:35" x14ac:dyDescent="0.25">
@@ -5346,28 +5337,28 @@
         <v>9487</v>
       </c>
       <c r="B93" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C93">
-        <v>350162787959</v>
+        <v>350114731303</v>
       </c>
       <c r="D93" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E93">
-        <v>448424.85</v>
+        <v>448097.12</v>
       </c>
       <c r="F93">
-        <v>6851374.5700000003</v>
+        <v>6852066.5099999998</v>
       </c>
       <c r="G93">
-        <v>-1204.57</v>
+        <v>-1207.42</v>
       </c>
       <c r="H93">
-        <v>2041.92</v>
+        <v>2003.67</v>
       </c>
       <c r="K93">
-        <v>-1204.57</v>
+        <v>-1207.42</v>
       </c>
       <c r="O93" t="s">
         <v>39</v>
@@ -5385,42 +5376,39 @@
         <v>1</v>
       </c>
       <c r="AI93" s="1">
-        <v>46210.35528935185</v>
+        <v>46210.355694444443</v>
       </c>
     </row>
     <row r="94" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>9000</v>
+        <v>9488</v>
       </c>
       <c r="B94" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C94">
-        <v>350162787959</v>
+        <v>350114731303</v>
       </c>
       <c r="D94" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E94">
-        <v>448313.83</v>
+        <v>447855.09</v>
       </c>
       <c r="F94">
-        <v>6851106.7599999998</v>
+        <v>6852260.5499999998</v>
       </c>
       <c r="G94">
-        <v>-1206.3399999999999</v>
+        <v>-1208.06</v>
       </c>
       <c r="H94">
-        <v>2332</v>
+        <v>2314.0700000000002</v>
       </c>
       <c r="K94">
-        <v>-1206.3399999999999</v>
+        <v>-1208.06</v>
       </c>
       <c r="O94" t="s">
-        <v>36</v>
-      </c>
-      <c r="P94">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="U94" t="b">
         <v>1</v>
@@ -5432,51 +5420,42 @@
         <v>37</v>
       </c>
       <c r="X94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD94">
-        <v>1</v>
-      </c>
-      <c r="AF94" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI94" s="1" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="AI94" s="1">
+        <v>46210.355775462966</v>
       </c>
     </row>
     <row r="95" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>9005</v>
+        <v>9489</v>
       </c>
       <c r="B95" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C95">
-        <v>350162787959</v>
+        <v>350114731303</v>
       </c>
       <c r="D95" t="s">
         <v>40</v>
       </c>
       <c r="E95">
-        <v>448565.55</v>
+        <v>447689.83</v>
       </c>
       <c r="F95">
-        <v>6851701.5499999998</v>
+        <v>6852405.3099999996</v>
       </c>
       <c r="G95">
-        <v>-1204.78</v>
+        <v>-1209.8800000000001</v>
       </c>
       <c r="H95">
-        <v>1685.7</v>
+        <v>2533.88</v>
       </c>
       <c r="K95">
-        <v>-1204.78</v>
+        <v>-1209.8800000000001</v>
       </c>
       <c r="O95" t="s">
-        <v>36</v>
-      </c>
-      <c r="P95">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U95" t="b">
         <v>1</v>
@@ -5488,21 +5467,15 @@
         <v>37</v>
       </c>
       <c r="X95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD95">
-        <v>1</v>
-      </c>
-      <c r="AF95" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI95" s="1" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI95" s="1">
+        <v>46210.355798611112</v>
       </c>
     </row>
     <row r="96" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>9494</v>
+        <v>8994</v>
       </c>
       <c r="B96" t="s">
         <v>55</v>
@@ -5511,25 +5484,28 @@
         <v>350162787959</v>
       </c>
       <c r="D96" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E96">
-        <v>448465.59</v>
+        <v>448691.87</v>
       </c>
       <c r="F96">
-        <v>6851473.3700000001</v>
+        <v>6851989.5999999996</v>
       </c>
       <c r="G96">
-        <v>-1203.0999999999999</v>
+        <v>-1155.94</v>
       </c>
       <c r="H96">
-        <v>1934.99</v>
+        <v>1365.7</v>
       </c>
       <c r="K96">
-        <v>-1203.0999999999999</v>
+        <v>-1155.94</v>
       </c>
       <c r="O96" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P96">
+        <v>1</v>
       </c>
       <c r="U96" t="b">
         <v>1</v>
@@ -5541,15 +5517,21 @@
         <v>37</v>
       </c>
       <c r="X96" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI96" s="1">
-        <v>46210.355879629627</v>
+        <v>0</v>
+      </c>
+      <c r="AD96">
+        <v>1</v>
+      </c>
+      <c r="AF96" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI96" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="97" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>9495</v>
+        <v>8996</v>
       </c>
       <c r="B97" t="s">
         <v>55</v>
@@ -5558,25 +5540,28 @@
         <v>350162787959</v>
       </c>
       <c r="D97" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E97">
-        <v>448424.85</v>
+        <v>448313.83</v>
       </c>
       <c r="F97">
-        <v>6851374.5700000003</v>
+        <v>6851106.7599999998</v>
       </c>
       <c r="G97">
-        <v>-1204.57</v>
+        <v>-1206.3399999999999</v>
       </c>
       <c r="H97">
-        <v>2041.92</v>
+        <v>2332</v>
       </c>
       <c r="K97">
-        <v>-1204.57</v>
+        <v>-1206.3399999999999</v>
       </c>
       <c r="O97" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P97">
+        <v>2</v>
       </c>
       <c r="U97" t="b">
         <v>1</v>
@@ -5588,15 +5573,21 @@
         <v>37</v>
       </c>
       <c r="X97" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI97" s="1">
-        <v>46210.355902777781</v>
+        <v>0</v>
+      </c>
+      <c r="AD97">
+        <v>1</v>
+      </c>
+      <c r="AF97" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI97" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="98" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>9496</v>
+        <v>9482</v>
       </c>
       <c r="B98" t="s">
         <v>55</v>
@@ -5605,22 +5596,22 @@
         <v>350162787959</v>
       </c>
       <c r="D98" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E98">
-        <v>448312.87</v>
+        <v>448465.03</v>
       </c>
       <c r="F98">
-        <v>6851104.4400000004</v>
+        <v>6851472</v>
       </c>
       <c r="G98">
-        <v>-1206.3399999999999</v>
+        <v>-1203.0999999999999</v>
       </c>
       <c r="H98">
-        <v>2334.5100000000002</v>
+        <v>1936.48</v>
       </c>
       <c r="K98">
-        <v>-1206.3399999999999</v>
+        <v>-1203.0999999999999</v>
       </c>
       <c r="O98" t="s">
         <v>39</v>
@@ -5638,33 +5629,36 @@
         <v>1</v>
       </c>
       <c r="AI98" s="1">
-        <v>46210.355937499997</v>
+        <v>46210.35527777778</v>
       </c>
     </row>
     <row r="99" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>9451</v>
+        <v>9483</v>
       </c>
       <c r="B99" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="C99">
+        <v>350162787959</v>
       </c>
       <c r="D99" t="s">
         <v>35</v>
       </c>
       <c r="E99">
-        <v>431838.22</v>
+        <v>448424.85</v>
       </c>
       <c r="F99">
-        <v>6845908.3200000003</v>
+        <v>6851374.5700000003</v>
       </c>
       <c r="G99">
-        <v>-1190.68</v>
+        <v>-1204.57</v>
       </c>
       <c r="H99">
-        <v>2794.65</v>
+        <v>2041.92</v>
       </c>
       <c r="K99">
-        <v>-1190.68</v>
+        <v>-1204.57</v>
       </c>
       <c r="O99" t="s">
         <v>39</v>
@@ -5682,36 +5676,42 @@
         <v>1</v>
       </c>
       <c r="AI99" s="1">
-        <v>46210.446180555555</v>
+        <v>46210.35528935185</v>
       </c>
     </row>
     <row r="100" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>9452</v>
+        <v>9001</v>
       </c>
       <c r="B100" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="C100">
+        <v>350162787959</v>
       </c>
       <c r="D100" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E100">
-        <v>431751.39</v>
+        <v>448565.55</v>
       </c>
       <c r="F100">
-        <v>6845514.9100000001</v>
+        <v>6851701.5499999998</v>
       </c>
       <c r="G100">
-        <v>-1191.79</v>
+        <v>-1204.78</v>
       </c>
       <c r="H100">
-        <v>3197.73</v>
+        <v>1685.7</v>
       </c>
       <c r="K100">
-        <v>-1191.79</v>
+        <v>-1204.78</v>
       </c>
       <c r="O100" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P100">
+        <v>1</v>
       </c>
       <c r="U100" t="b">
         <v>1</v>
@@ -5723,36 +5723,45 @@
         <v>37</v>
       </c>
       <c r="X100" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI100" s="1">
-        <v>46210.352025462962</v>
+        <v>0</v>
+      </c>
+      <c r="AD100">
+        <v>1</v>
+      </c>
+      <c r="AF100" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI100" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="101" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>9454</v>
+        <v>9490</v>
       </c>
       <c r="B101" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="C101">
+        <v>350162787959</v>
       </c>
       <c r="D101" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E101">
-        <v>431723.49</v>
+        <v>448465.59</v>
       </c>
       <c r="F101">
-        <v>6845384.0999999996</v>
+        <v>6851473.3700000001</v>
       </c>
       <c r="G101">
-        <v>-1194.23</v>
+        <v>-1203.0999999999999</v>
       </c>
       <c r="H101">
-        <v>3331.56</v>
+        <v>1934.99</v>
       </c>
       <c r="K101">
-        <v>-1194.23</v>
+        <v>-1203.0999999999999</v>
       </c>
       <c r="O101" t="s">
         <v>39</v>
@@ -5770,33 +5779,36 @@
         <v>1</v>
       </c>
       <c r="AI101" s="1">
-        <v>46210.352210648147</v>
+        <v>46210.355879629627</v>
       </c>
     </row>
     <row r="102" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>9436</v>
+        <v>9491</v>
       </c>
       <c r="B102" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="C102">
+        <v>350162787959</v>
       </c>
       <c r="D102" t="s">
         <v>40</v>
       </c>
       <c r="E102">
-        <v>431952.53</v>
+        <v>448424.85</v>
       </c>
       <c r="F102">
-        <v>6846439.9100000001</v>
+        <v>6851374.5700000003</v>
       </c>
       <c r="G102">
-        <v>-1194.1400000000001</v>
+        <v>-1204.57</v>
       </c>
       <c r="H102">
-        <v>2250.62</v>
+        <v>2041.92</v>
       </c>
       <c r="K102">
-        <v>-1194.1400000000001</v>
+        <v>-1204.57</v>
       </c>
       <c r="O102" t="s">
         <v>39</v>
@@ -5814,33 +5826,36 @@
         <v>1</v>
       </c>
       <c r="AI102" s="1">
-        <v>46359.700694444444</v>
+        <v>46210.355902777781</v>
       </c>
     </row>
     <row r="103" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>9438</v>
+        <v>9492</v>
       </c>
       <c r="B103" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="C103">
+        <v>350162787959</v>
       </c>
       <c r="D103" t="s">
         <v>40</v>
       </c>
       <c r="E103">
-        <v>431838.19</v>
+        <v>448312.87</v>
       </c>
       <c r="F103">
-        <v>6845908.1699999999</v>
+        <v>6851104.4400000004</v>
       </c>
       <c r="G103">
-        <v>-1190.68</v>
+        <v>-1206.3399999999999</v>
       </c>
       <c r="H103">
-        <v>2794.81</v>
+        <v>2334.5100000000002</v>
       </c>
       <c r="K103">
-        <v>-1190.68</v>
+        <v>-1206.3399999999999</v>
       </c>
       <c r="O103" t="s">
         <v>39</v>
@@ -5857,34 +5872,37 @@
       <c r="X103" t="b">
         <v>1</v>
       </c>
-      <c r="AI103" s="1" t="s">
-        <v>56</v>
+      <c r="AI103" s="1">
+        <v>46210.355937499997</v>
       </c>
     </row>
     <row r="104" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>9446</v>
+        <v>9561</v>
       </c>
       <c r="B104" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="C104">
+        <v>350162787959</v>
       </c>
       <c r="D104" t="s">
         <v>40</v>
       </c>
       <c r="E104">
-        <v>431828.8</v>
+        <v>448453.28</v>
       </c>
       <c r="F104">
-        <v>6845861.2599999998</v>
+        <v>6851443.4699999997</v>
       </c>
       <c r="G104">
-        <v>-1190.75</v>
+        <v>-1203.51</v>
       </c>
       <c r="H104">
-        <v>2842.67</v>
+        <v>1967.35</v>
       </c>
       <c r="K104">
-        <v>-1190.75</v>
+        <v>-1203.51</v>
       </c>
       <c r="O104" t="s">
         <v>39</v>
@@ -5901,34 +5919,37 @@
       <c r="X104" t="b">
         <v>1</v>
       </c>
-      <c r="AI104" t="s">
-        <v>59</v>
+      <c r="AI104" s="1">
+        <v>46210.5858912037</v>
       </c>
     </row>
     <row r="105" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>9439</v>
+        <v>9562</v>
       </c>
       <c r="B105" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="C105">
+        <v>350162787959</v>
       </c>
       <c r="D105" t="s">
         <v>40</v>
       </c>
       <c r="E105">
-        <v>431751.39</v>
+        <v>448411.3</v>
       </c>
       <c r="F105">
-        <v>6845514.9100000001</v>
+        <v>6851341.8799999999</v>
       </c>
       <c r="G105">
-        <v>-1191.79</v>
+        <v>-1205.1300000000001</v>
       </c>
       <c r="H105">
-        <v>3197.73</v>
+        <v>2077.33</v>
       </c>
       <c r="K105">
-        <v>-1191.79</v>
+        <v>-1205.1300000000001</v>
       </c>
       <c r="O105" t="s">
         <v>39</v>
@@ -5945,8 +5966,8 @@
       <c r="X105" t="b">
         <v>1</v>
       </c>
-      <c r="AI105" s="1" t="s">
-        <v>57</v>
+      <c r="AI105" s="1">
+        <v>46210.585902777777</v>
       </c>
     </row>
     <row r="106" spans="1:35" x14ac:dyDescent="0.25">
@@ -5957,22 +5978,22 @@
         <v>73</v>
       </c>
       <c r="D106" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E106">
-        <v>431743.08</v>
+        <v>431838.22</v>
       </c>
       <c r="F106">
-        <v>6845475.5</v>
+        <v>6845908.3200000003</v>
       </c>
       <c r="G106">
-        <v>-1192.95</v>
+        <v>-1190.68</v>
       </c>
       <c r="H106">
-        <v>3238.04</v>
+        <v>2794.65</v>
       </c>
       <c r="K106">
-        <v>-1192.95</v>
+        <v>-1190.68</v>
       </c>
       <c r="O106" t="s">
         <v>39</v>
@@ -5990,33 +6011,33 @@
         <v>1</v>
       </c>
       <c r="AI106" s="1">
-        <v>46210.351273148146</v>
+        <v>46210.446180555555</v>
       </c>
     </row>
     <row r="107" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>9440</v>
+        <v>9448</v>
       </c>
       <c r="B107" t="s">
         <v>73</v>
       </c>
       <c r="D107" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E107">
-        <v>431723.31</v>
+        <v>431751.39</v>
       </c>
       <c r="F107">
-        <v>6845383.2800000003</v>
+        <v>6845514.9100000001</v>
       </c>
       <c r="G107">
-        <v>-1194.23</v>
+        <v>-1191.79</v>
       </c>
       <c r="H107">
-        <v>3332.41</v>
+        <v>3197.73</v>
       </c>
       <c r="K107">
-        <v>-1194.23</v>
+        <v>-1191.79</v>
       </c>
       <c r="O107" t="s">
         <v>39</v>
@@ -6033,37 +6054,34 @@
       <c r="X107" t="b">
         <v>1</v>
       </c>
-      <c r="AI107" s="1" t="s">
-        <v>58</v>
+      <c r="AI107" s="1">
+        <v>46210.352025462962</v>
       </c>
     </row>
     <row r="108" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>9545</v>
+        <v>9450</v>
       </c>
       <c r="B108" t="s">
-        <v>72</v>
-      </c>
-      <c r="C108">
-        <v>350370847072</v>
+        <v>73</v>
       </c>
       <c r="D108" t="s">
         <v>35</v>
       </c>
       <c r="E108">
-        <v>432539.86</v>
+        <v>431723.49</v>
       </c>
       <c r="F108">
-        <v>6846587.6299999999</v>
+        <v>6845384.0999999996</v>
       </c>
       <c r="G108">
-        <v>-1191.19</v>
+        <v>-1194.23</v>
       </c>
       <c r="H108">
-        <v>2375.4299999999998</v>
+        <v>3331.56</v>
       </c>
       <c r="K108">
-        <v>-1191.19</v>
+        <v>-1194.23</v>
       </c>
       <c r="O108" t="s">
         <v>39</v>
@@ -6081,36 +6099,33 @@
         <v>1</v>
       </c>
       <c r="AI108" s="1">
-        <v>46210.467766203707</v>
+        <v>46210.352210648147</v>
       </c>
     </row>
     <row r="109" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>9546</v>
+        <v>9432</v>
       </c>
       <c r="B109" t="s">
-        <v>72</v>
-      </c>
-      <c r="C109">
-        <v>350370847072</v>
+        <v>73</v>
       </c>
       <c r="D109" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E109">
-        <v>432868.05</v>
+        <v>431952.53</v>
       </c>
       <c r="F109">
-        <v>6846102.4199999999</v>
+        <v>6846439.9100000001</v>
       </c>
       <c r="G109">
-        <v>-1194.3800000000001</v>
+        <v>-1194.1400000000001</v>
       </c>
       <c r="H109">
-        <v>2967.84</v>
+        <v>2250.62</v>
       </c>
       <c r="K109">
-        <v>-1194.3800000000001</v>
+        <v>-1194.1400000000001</v>
       </c>
       <c r="O109" t="s">
         <v>39</v>
@@ -6128,36 +6143,33 @@
         <v>1</v>
       </c>
       <c r="AI109" s="1">
-        <v>46210.46802083333</v>
+        <v>46359.700694444444</v>
       </c>
     </row>
     <row r="110" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>9547</v>
+        <v>9434</v>
       </c>
       <c r="B110" t="s">
-        <v>72</v>
-      </c>
-      <c r="C110">
-        <v>350370847072</v>
+        <v>73</v>
       </c>
       <c r="D110" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E110">
-        <v>432920.68</v>
+        <v>431838.19</v>
       </c>
       <c r="F110">
-        <v>6845709.3099999996</v>
+        <v>6845908.1699999999</v>
       </c>
       <c r="G110">
-        <v>-1191.54</v>
+        <v>-1190.68</v>
       </c>
       <c r="H110">
-        <v>3365.64</v>
+        <v>2794.81</v>
       </c>
       <c r="K110">
-        <v>-1191.54</v>
+        <v>-1190.68</v>
       </c>
       <c r="O110" t="s">
         <v>39</v>
@@ -6174,37 +6186,34 @@
       <c r="X110" t="b">
         <v>1</v>
       </c>
-      <c r="AI110" s="1">
-        <v>46210.468263888892</v>
+      <c r="AI110" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="111" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>9538</v>
+        <v>9435</v>
       </c>
       <c r="B111" t="s">
-        <v>72</v>
-      </c>
-      <c r="C111">
-        <v>350370847072</v>
+        <v>73</v>
       </c>
       <c r="D111" t="s">
         <v>40</v>
       </c>
       <c r="E111">
-        <v>432274.21</v>
+        <v>431751.39</v>
       </c>
       <c r="F111">
-        <v>6846736.8700000001</v>
+        <v>6845514.9100000001</v>
       </c>
       <c r="G111">
-        <v>-1194.1300000000001</v>
+        <v>-1191.79</v>
       </c>
       <c r="H111">
-        <v>2067.46</v>
+        <v>3197.73</v>
       </c>
       <c r="K111">
-        <v>-1194.1300000000001</v>
+        <v>-1191.79</v>
       </c>
       <c r="O111" t="s">
         <v>39</v>
@@ -6221,37 +6230,34 @@
       <c r="X111" t="b">
         <v>1</v>
       </c>
-      <c r="AI111" s="1">
-        <v>46210.466782407406</v>
+      <c r="AI111" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="112" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>9539</v>
+        <v>9436</v>
       </c>
       <c r="B112" t="s">
-        <v>72</v>
-      </c>
-      <c r="C112">
-        <v>350370847072</v>
+        <v>73</v>
       </c>
       <c r="D112" t="s">
         <v>40</v>
       </c>
       <c r="E112">
-        <v>432541.44</v>
+        <v>431723.31</v>
       </c>
       <c r="F112">
-        <v>6846586.1799999997</v>
+        <v>6845383.2800000003</v>
       </c>
       <c r="G112">
-        <v>-1191.18</v>
+        <v>-1194.23</v>
       </c>
       <c r="H112">
-        <v>2377.5700000000002</v>
+        <v>3332.41</v>
       </c>
       <c r="K112">
-        <v>-1191.18</v>
+        <v>-1194.23</v>
       </c>
       <c r="O112" t="s">
         <v>39</v>
@@ -6268,37 +6274,34 @@
       <c r="X112" t="b">
         <v>1</v>
       </c>
-      <c r="AI112" s="1">
-        <v>46210.466863425929</v>
+      <c r="AI112" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="113" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>9540</v>
+        <v>9442</v>
       </c>
       <c r="B113" t="s">
-        <v>72</v>
-      </c>
-      <c r="C113">
-        <v>350370847072</v>
+        <v>73</v>
       </c>
       <c r="D113" t="s">
         <v>40</v>
       </c>
       <c r="E113">
-        <v>432563.25</v>
+        <v>431828.8</v>
       </c>
       <c r="F113">
-        <v>6846565.6900000004</v>
+        <v>6845861.2599999998</v>
       </c>
       <c r="G113">
-        <v>-1191.33</v>
+        <v>-1190.75</v>
       </c>
       <c r="H113">
-        <v>2407.5100000000002</v>
+        <v>2842.67</v>
       </c>
       <c r="K113">
-        <v>-1191.33</v>
+        <v>-1190.75</v>
       </c>
       <c r="O113" t="s">
         <v>39</v>
@@ -6315,37 +6318,34 @@
       <c r="X113" t="b">
         <v>1</v>
       </c>
-      <c r="AI113" s="1">
-        <v>46210.466967592591</v>
+      <c r="AI113" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="114" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>9541</v>
+        <v>9443</v>
       </c>
       <c r="B114" t="s">
-        <v>72</v>
-      </c>
-      <c r="C114">
-        <v>350370847072</v>
+        <v>73</v>
       </c>
       <c r="D114" t="s">
         <v>40</v>
       </c>
       <c r="E114">
-        <v>432867.5</v>
+        <v>431743.08</v>
       </c>
       <c r="F114">
-        <v>6846104.4800000004</v>
+        <v>6845475.5</v>
       </c>
       <c r="G114">
-        <v>-1194.3900000000001</v>
+        <v>-1192.95</v>
       </c>
       <c r="H114">
-        <v>2965.71</v>
+        <v>3238.04</v>
       </c>
       <c r="K114">
-        <v>-1194.3900000000001</v>
+        <v>-1192.95</v>
       </c>
       <c r="O114" t="s">
         <v>39</v>
@@ -6363,12 +6363,12 @@
         <v>1</v>
       </c>
       <c r="AI114" s="1">
-        <v>46210.467106481483</v>
+        <v>46210.351273148146</v>
       </c>
     </row>
     <row r="115" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>9542</v>
+        <v>9541</v>
       </c>
       <c r="B115" t="s">
         <v>72</v>
@@ -6377,22 +6377,22 @@
         <v>350370847072</v>
       </c>
       <c r="D115" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E115">
-        <v>432895.5</v>
+        <v>432539.86</v>
       </c>
       <c r="F115">
-        <v>6845828.3499999996</v>
+        <v>6846587.6299999999</v>
       </c>
       <c r="G115">
-        <v>-1194.1500000000001</v>
+        <v>-1191.19</v>
       </c>
       <c r="H115">
-        <v>3243.73</v>
+        <v>2375.4299999999998</v>
       </c>
       <c r="K115">
-        <v>-1194.1500000000001</v>
+        <v>-1191.19</v>
       </c>
       <c r="O115" t="s">
         <v>39</v>
@@ -6410,12 +6410,12 @@
         <v>1</v>
       </c>
       <c r="AI115" s="1">
-        <v>46210.467222222222</v>
+        <v>46210.467766203707</v>
       </c>
     </row>
     <row r="116" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>9543</v>
+        <v>9542</v>
       </c>
       <c r="B116" t="s">
         <v>72</v>
@@ -6424,22 +6424,22 @@
         <v>350370847072</v>
       </c>
       <c r="D116" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E116">
-        <v>432921.95</v>
+        <v>432868.05</v>
       </c>
       <c r="F116">
-        <v>6845705.2300000004</v>
+        <v>6846102.4199999999</v>
       </c>
       <c r="G116">
-        <v>-1191.42</v>
+        <v>-1194.3800000000001</v>
       </c>
       <c r="H116">
-        <v>3369.92</v>
+        <v>2967.84</v>
       </c>
       <c r="K116">
-        <v>-1191.42</v>
+        <v>-1194.3800000000001</v>
       </c>
       <c r="O116" t="s">
         <v>39</v>
@@ -6457,12 +6457,12 @@
         <v>1</v>
       </c>
       <c r="AI116" s="1">
-        <v>46210.467303240737</v>
+        <v>46210.46802083333</v>
       </c>
     </row>
     <row r="117" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>9544</v>
+        <v>9543</v>
       </c>
       <c r="B117" t="s">
         <v>72</v>
@@ -6471,22 +6471,22 @@
         <v>350370847072</v>
       </c>
       <c r="D117" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E117">
-        <v>432934.19</v>
+        <v>432920.68</v>
       </c>
       <c r="F117">
-        <v>6845666.5099999998</v>
+        <v>6845709.3099999996</v>
       </c>
       <c r="G117">
-        <v>-1191.3</v>
+        <v>-1191.54</v>
       </c>
       <c r="H117">
-        <v>3410.55</v>
+        <v>3365.64</v>
       </c>
       <c r="K117">
-        <v>-1191.3</v>
+        <v>-1191.54</v>
       </c>
       <c r="O117" t="s">
         <v>39</v>
@@ -6504,42 +6504,39 @@
         <v>1</v>
       </c>
       <c r="AI117" s="1">
-        <v>46210.467407407406</v>
+        <v>46210.468263888892</v>
       </c>
     </row>
     <row r="118" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>108</v>
+        <v>9534</v>
       </c>
       <c r="B118" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C118">
-        <v>171682391</v>
+        <v>350370847072</v>
       </c>
       <c r="D118" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E118">
-        <v>449073.88</v>
+        <v>432274.21</v>
       </c>
       <c r="F118">
-        <v>6850773.5499999998</v>
+        <v>6846736.8700000001</v>
       </c>
       <c r="G118">
-        <v>-1148.77</v>
+        <v>-1194.1300000000001</v>
       </c>
       <c r="H118">
-        <v>1335.1</v>
+        <v>2067.46</v>
       </c>
       <c r="K118">
-        <v>-1148.77</v>
+        <v>-1194.1300000000001</v>
       </c>
       <c r="O118" t="s">
-        <v>36</v>
-      </c>
-      <c r="P118">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U118" t="b">
         <v>1</v>
@@ -6551,51 +6548,39 @@
         <v>37</v>
       </c>
       <c r="X118" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC118" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD118">
-        <v>2</v>
-      </c>
-      <c r="AE118" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF118" t="s">
-        <v>62</v>
-      </c>
-      <c r="AI118" s="1" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="AI118" s="1">
+        <v>46210.466782407406</v>
       </c>
     </row>
     <row r="119" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>9468</v>
+        <v>9535</v>
       </c>
       <c r="B119" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C119">
-        <v>171682391</v>
+        <v>350370847072</v>
       </c>
       <c r="D119" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E119">
-        <v>450074.78</v>
+        <v>432541.44</v>
       </c>
       <c r="F119">
-        <v>6850786.1100000003</v>
+        <v>6846586.1799999997</v>
       </c>
       <c r="G119">
-        <v>-1190.1300000000001</v>
+        <v>-1191.18</v>
       </c>
       <c r="H119">
-        <v>2342.56</v>
+        <v>2377.5700000000002</v>
       </c>
       <c r="K119">
-        <v>-1190.1300000000001</v>
+        <v>-1191.18</v>
       </c>
       <c r="O119" t="s">
         <v>39</v>
@@ -6613,36 +6598,36 @@
         <v>1</v>
       </c>
       <c r="AI119" s="1">
-        <v>46210.354317129626</v>
+        <v>46210.466863425929</v>
       </c>
     </row>
     <row r="120" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>9501</v>
+        <v>9536</v>
       </c>
       <c r="B120" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C120">
-        <v>171682391</v>
+        <v>350370847072</v>
       </c>
       <c r="D120" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E120">
-        <v>450074.91</v>
+        <v>432563.25</v>
       </c>
       <c r="F120">
-        <v>6850786.1100000003</v>
+        <v>6846565.6900000004</v>
       </c>
       <c r="G120">
-        <v>-1190.1300000000001</v>
+        <v>-1191.33</v>
       </c>
       <c r="H120">
-        <v>2342.69</v>
+        <v>2407.5100000000002</v>
       </c>
       <c r="K120">
-        <v>-1190.1300000000001</v>
+        <v>-1191.33</v>
       </c>
       <c r="O120" t="s">
         <v>39</v>
@@ -6660,36 +6645,36 @@
         <v>1</v>
       </c>
       <c r="AI120" s="1">
-        <v>46210.356724537036</v>
+        <v>46210.466967592591</v>
       </c>
     </row>
     <row r="121" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>9469</v>
+        <v>9537</v>
       </c>
       <c r="B121" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C121">
-        <v>171682391</v>
+        <v>350370847072</v>
       </c>
       <c r="D121" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E121">
-        <v>450424.17</v>
+        <v>432867.5</v>
       </c>
       <c r="F121">
-        <v>6850785.9400000004</v>
+        <v>6846104.4800000004</v>
       </c>
       <c r="G121">
-        <v>-1195.07</v>
+        <v>-1194.3900000000001</v>
       </c>
       <c r="H121">
-        <v>2692.2</v>
+        <v>2965.71</v>
       </c>
       <c r="K121">
-        <v>-1195.07</v>
+        <v>-1194.3900000000001</v>
       </c>
       <c r="O121" t="s">
         <v>39</v>
@@ -6707,42 +6692,39 @@
         <v>1</v>
       </c>
       <c r="AI121" s="1">
-        <v>46210.354351851849</v>
+        <v>46210.467106481483</v>
       </c>
     </row>
     <row r="122" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>2884</v>
+        <v>9538</v>
       </c>
       <c r="B122" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C122">
-        <v>171682391</v>
+        <v>350370847072</v>
       </c>
       <c r="D122" t="s">
         <v>40</v>
       </c>
       <c r="E122">
-        <v>449366.27</v>
+        <v>432895.5</v>
       </c>
       <c r="F122">
-        <v>6850785.0499999998</v>
+        <v>6845828.3499999996</v>
       </c>
       <c r="G122">
-        <v>-1196.1300000000001</v>
+        <v>-1194.1500000000001</v>
       </c>
       <c r="H122">
-        <v>1633.5</v>
+        <v>3243.73</v>
       </c>
       <c r="K122">
-        <v>-1196.1300000000001</v>
+        <v>-1194.1500000000001</v>
       </c>
       <c r="O122" t="s">
-        <v>36</v>
-      </c>
-      <c r="P122">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U122" t="b">
         <v>1</v>
@@ -6754,58 +6736,43 @@
         <v>37</v>
       </c>
       <c r="X122" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC122" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD122">
-        <v>2</v>
-      </c>
-      <c r="AE122" t="s">
-        <v>63</v>
-      </c>
-      <c r="AF122" t="s">
-        <v>62</v>
-      </c>
-      <c r="AI122" s="1" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI122" s="1">
+        <v>46210.467222222222</v>
       </c>
     </row>
     <row r="123" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>3078</v>
+        <v>9539</v>
       </c>
       <c r="B123" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C123">
-        <v>171682391</v>
+        <v>350370847072</v>
       </c>
       <c r="D123" t="s">
         <v>40</v>
       </c>
       <c r="E123">
-        <v>450074.78</v>
+        <v>432921.95</v>
       </c>
       <c r="F123">
-        <v>6850786.1100000003</v>
+        <v>6845705.2300000004</v>
       </c>
       <c r="G123">
-        <v>-1190.1300000000001</v>
+        <v>-1191.42</v>
       </c>
       <c r="H123">
-        <v>2342.56</v>
+        <v>3369.92</v>
       </c>
       <c r="K123">
-        <v>-1190.1300000000001</v>
+        <v>-1191.42</v>
       </c>
       <c r="O123" t="s">
         <v>39</v>
       </c>
-      <c r="P123">
-        <v>2</v>
-      </c>
       <c r="U123" t="b">
         <v>1</v>
       </c>
@@ -6816,58 +6783,43 @@
         <v>37</v>
       </c>
       <c r="X123" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC123" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD123">
-        <v>2</v>
-      </c>
-      <c r="AE123" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF123" t="s">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="AI123" s="1">
-        <v>46210.354409722226</v>
+        <v>46210.467303240737</v>
       </c>
     </row>
     <row r="124" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>3086</v>
+        <v>9540</v>
       </c>
       <c r="B124" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C124">
-        <v>171682391</v>
+        <v>350370847072</v>
       </c>
       <c r="D124" t="s">
         <v>40</v>
       </c>
       <c r="E124">
-        <v>450107.56</v>
+        <v>432934.19</v>
       </c>
       <c r="F124">
-        <v>6850786.5300000003</v>
+        <v>6845666.5099999998</v>
       </c>
       <c r="G124">
-        <v>-1190.97</v>
+        <v>-1191.3</v>
       </c>
       <c r="H124">
-        <v>2375.37</v>
+        <v>3410.55</v>
       </c>
       <c r="K124">
-        <v>-1190.97</v>
+        <v>-1191.3</v>
       </c>
       <c r="O124" t="s">
         <v>39</v>
       </c>
-      <c r="P124">
-        <v>3</v>
-      </c>
       <c r="U124" t="b">
         <v>1</v>
       </c>
@@ -6878,27 +6830,15 @@
         <v>37</v>
       </c>
       <c r="X124" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC124" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD124">
-        <v>2</v>
-      </c>
-      <c r="AE124" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF124" t="s">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="AI124" s="1">
-        <v>46210.35670138889</v>
+        <v>46210.467407407406</v>
       </c>
     </row>
     <row r="125" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>3102</v>
+        <v>108</v>
       </c>
       <c r="B125" t="s">
         <v>60</v>
@@ -6907,28 +6847,28 @@
         <v>171682391</v>
       </c>
       <c r="D125" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E125">
-        <v>450425.21</v>
+        <v>449073.88</v>
       </c>
       <c r="F125">
-        <v>6850785.9299999997</v>
+        <v>6850773.5499999998</v>
       </c>
       <c r="G125">
-        <v>-1195.07</v>
+        <v>-1148.77</v>
       </c>
       <c r="H125">
-        <v>2693.23</v>
+        <v>1335.1</v>
       </c>
       <c r="K125">
-        <v>-1195.07</v>
+        <v>-1148.77</v>
       </c>
       <c r="O125" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="P125">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U125" t="b">
         <v>1</v>
@@ -6949,48 +6889,45 @@
         <v>2</v>
       </c>
       <c r="AE125" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="AF125" t="s">
         <v>62</v>
       </c>
-      <c r="AI125" s="1">
-        <v>46210.354375000003</v>
+      <c r="AI125" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="126" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>74</v>
+        <v>9464</v>
       </c>
       <c r="B126" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C126">
-        <v>171358584</v>
+        <v>171682391</v>
       </c>
       <c r="D126" t="s">
         <v>35</v>
       </c>
       <c r="E126">
-        <v>450318.68</v>
+        <v>450074.78</v>
       </c>
       <c r="F126">
-        <v>6849921.4400000004</v>
+        <v>6850786.1100000003</v>
       </c>
       <c r="G126">
-        <v>-1144.51</v>
+        <v>-1190.1300000000001</v>
       </c>
       <c r="H126">
-        <v>1433.4</v>
+        <v>2342.56</v>
       </c>
       <c r="K126">
-        <v>-1144.51</v>
+        <v>-1190.1300000000001</v>
       </c>
       <c r="O126" t="s">
-        <v>36</v>
-      </c>
-      <c r="P126">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U126" t="b">
         <v>1</v>
@@ -7002,51 +6939,39 @@
         <v>37</v>
       </c>
       <c r="X126" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC126" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD126">
-        <v>1</v>
-      </c>
-      <c r="AE126" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF126" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI126" s="1" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="AI126" s="1">
+        <v>46210.354317129626</v>
       </c>
     </row>
     <row r="127" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>9502</v>
+        <v>9465</v>
       </c>
       <c r="B127" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C127">
-        <v>171358584</v>
+        <v>171682391</v>
       </c>
       <c r="D127" t="s">
         <v>35</v>
       </c>
       <c r="E127">
-        <v>449862.88</v>
+        <v>450424.17</v>
       </c>
       <c r="F127">
-        <v>6850537.8499999996</v>
+        <v>6850785.9400000004</v>
       </c>
       <c r="G127">
-        <v>-1191.3699999999999</v>
+        <v>-1195.07</v>
       </c>
       <c r="H127">
-        <v>2210.33</v>
+        <v>2692.2</v>
       </c>
       <c r="K127">
-        <v>-1191.3699999999999</v>
+        <v>-1195.07</v>
       </c>
       <c r="O127" t="s">
         <v>39</v>
@@ -7064,42 +6989,39 @@
         <v>1</v>
       </c>
       <c r="AI127" s="1">
-        <v>46210.35696759259</v>
+        <v>46210.354351851849</v>
       </c>
     </row>
     <row r="128" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>2898</v>
+        <v>9497</v>
       </c>
       <c r="B128" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C128">
-        <v>171358584</v>
+        <v>171682391</v>
       </c>
       <c r="D128" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E128">
-        <v>450097.05</v>
+        <v>450074.91</v>
       </c>
       <c r="F128">
-        <v>6850165.4900000002</v>
+        <v>6850786.1100000003</v>
       </c>
       <c r="G128">
-        <v>-1192.58</v>
+        <v>-1190.1300000000001</v>
       </c>
       <c r="H128">
-        <v>1770.1</v>
+        <v>2342.69</v>
       </c>
       <c r="K128">
-        <v>-1192.58</v>
+        <v>-1190.1300000000001</v>
       </c>
       <c r="O128" t="s">
-        <v>36</v>
-      </c>
-      <c r="P128">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U128" t="b">
         <v>1</v>
@@ -7111,57 +7033,45 @@
         <v>37</v>
       </c>
       <c r="X128" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC128" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD128">
-        <v>1</v>
-      </c>
-      <c r="AE128" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF128" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI128" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI128" s="1">
+        <v>46210.356724537036</v>
       </c>
     </row>
     <row r="129" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>3068</v>
+        <v>2883</v>
       </c>
       <c r="B129" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C129">
-        <v>171358584</v>
+        <v>171682391</v>
       </c>
       <c r="D129" t="s">
         <v>40</v>
       </c>
       <c r="E129">
-        <v>449861.96</v>
+        <v>449366.27</v>
       </c>
       <c r="F129">
-        <v>6850539.2400000002</v>
+        <v>6850785.0499999998</v>
       </c>
       <c r="G129">
-        <v>-1191.42</v>
+        <v>-1196.1300000000001</v>
       </c>
       <c r="H129">
-        <v>2212</v>
+        <v>1633.5</v>
       </c>
       <c r="K129">
-        <v>-1191.42</v>
+        <v>-1196.1300000000001</v>
       </c>
       <c r="O129" t="s">
         <v>36</v>
       </c>
       <c r="P129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U129" t="b">
         <v>1</v>
@@ -7182,10 +7092,10 @@
         <v>2</v>
       </c>
       <c r="AE129" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="AF129" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="AI129" s="1" t="s">
         <v>43</v>
@@ -7193,37 +7103,37 @@
     </row>
     <row r="130" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>3141</v>
+        <v>3074</v>
       </c>
       <c r="B130" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C130">
-        <v>171358584</v>
+        <v>171682391</v>
       </c>
       <c r="D130" t="s">
         <v>40</v>
       </c>
       <c r="E130">
-        <v>449853.39</v>
+        <v>450074.78</v>
       </c>
       <c r="F130">
-        <v>6850552.25</v>
+        <v>6850786.1100000003</v>
       </c>
       <c r="G130">
-        <v>-1191.8800000000001</v>
+        <v>-1190.1300000000001</v>
       </c>
       <c r="H130">
-        <v>2227.6</v>
+        <v>2342.56</v>
       </c>
       <c r="K130">
-        <v>-1191.8800000000001</v>
+        <v>-1190.1300000000001</v>
       </c>
       <c r="O130" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P130">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U130" t="b">
         <v>1</v>
@@ -7244,48 +7154,48 @@
         <v>2</v>
       </c>
       <c r="AE130" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="AF130" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI130" s="1" t="s">
-        <v>43</v>
+        <v>62</v>
+      </c>
+      <c r="AI130" s="1">
+        <v>46210.354409722226</v>
       </c>
     </row>
     <row r="131" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>26</v>
+        <v>3082</v>
       </c>
       <c r="B131" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C131">
-        <v>171358586</v>
+        <v>171682391</v>
       </c>
       <c r="D131" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E131">
-        <v>449423.46</v>
+        <v>450107.56</v>
       </c>
       <c r="F131">
-        <v>6851149.6799999997</v>
+        <v>6850786.5300000003</v>
       </c>
       <c r="G131">
-        <v>-1145.92</v>
+        <v>-1190.97</v>
       </c>
       <c r="H131">
-        <v>1379.1</v>
+        <v>2375.37</v>
       </c>
       <c r="K131">
-        <v>-1145.92</v>
+        <v>-1190.97</v>
       </c>
       <c r="O131" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P131">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U131" t="b">
         <v>1</v>
@@ -7303,51 +7213,51 @@
         <v>46</v>
       </c>
       <c r="AD131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE131" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="AF131" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI131" t="s">
-        <v>42</v>
+        <v>62</v>
+      </c>
+      <c r="AI131" s="1">
+        <v>46210.35670138889</v>
       </c>
     </row>
     <row r="132" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>3038</v>
+        <v>3098</v>
       </c>
       <c r="B132" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C132">
-        <v>171358586</v>
+        <v>171682391</v>
       </c>
       <c r="D132" t="s">
         <v>40</v>
       </c>
       <c r="E132">
-        <v>449701.81</v>
+        <v>450425.21</v>
       </c>
       <c r="F132">
-        <v>6851220.0499999998</v>
+        <v>6850785.9299999997</v>
       </c>
       <c r="G132">
-        <v>-1192.8699999999999</v>
+        <v>-1195.07</v>
       </c>
       <c r="H132">
-        <v>1672.5</v>
+        <v>2693.23</v>
       </c>
       <c r="K132">
-        <v>-1192.8699999999999</v>
+        <v>-1195.07</v>
       </c>
       <c r="O132" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P132">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U132" t="b">
         <v>1</v>
@@ -7365,51 +7275,48 @@
         <v>46</v>
       </c>
       <c r="AD132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE132" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="AF132" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI132" s="1" t="s">
-        <v>43</v>
+        <v>62</v>
+      </c>
+      <c r="AI132" s="1">
+        <v>46210.354375000003</v>
       </c>
     </row>
     <row r="133" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>187</v>
+        <v>9564</v>
       </c>
       <c r="B133" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C133">
-        <v>171358679</v>
+        <v>171682391</v>
       </c>
       <c r="D133" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E133">
-        <v>448968.29</v>
+        <v>450472.94</v>
       </c>
       <c r="F133">
-        <v>6849117.6200000001</v>
+        <v>6850785.9800000004</v>
       </c>
       <c r="G133">
-        <v>-1149.3599999999999</v>
+        <v>-1196.04</v>
       </c>
       <c r="H133">
-        <v>1366.2</v>
+        <v>2741</v>
       </c>
       <c r="K133">
-        <v>-1149.3599999999999</v>
+        <v>-1196.04</v>
       </c>
       <c r="O133" t="s">
-        <v>36</v>
-      </c>
-      <c r="P133">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U133" t="b">
         <v>1</v>
@@ -7421,54 +7328,42 @@
         <v>37</v>
       </c>
       <c r="X133" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC133" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD133">
-        <v>1</v>
-      </c>
-      <c r="AE133" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF133" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI133" s="1" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="AI133" s="1">
+        <v>46210.586388888885</v>
       </c>
     </row>
     <row r="134" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>2821</v>
+        <v>74</v>
       </c>
       <c r="B134" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C134">
-        <v>171358679</v>
+        <v>171358584</v>
       </c>
       <c r="D134" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E134">
-        <v>449185.07</v>
+        <v>450318.68</v>
       </c>
       <c r="F134">
-        <v>6849334.2800000003</v>
+        <v>6849921.4400000004</v>
       </c>
       <c r="G134">
-        <v>-1198.07</v>
+        <v>-1144.51</v>
       </c>
       <c r="H134">
-        <v>1679.01</v>
+        <v>1433.4</v>
       </c>
       <c r="K134">
-        <v>-1198.07</v>
+        <v>-1144.51</v>
       </c>
       <c r="O134" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="P134">
         <v>1</v>
@@ -7492,48 +7387,45 @@
         <v>1</v>
       </c>
       <c r="AE134" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="AF134" t="s">
         <v>48</v>
       </c>
-      <c r="AI134" s="1">
-        <v>46210.34814814815</v>
+      <c r="AI134" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="135" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>59</v>
+        <v>9498</v>
       </c>
       <c r="B135" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C135">
-        <v>171358704</v>
+        <v>171358584</v>
       </c>
       <c r="D135" t="s">
         <v>35</v>
       </c>
       <c r="E135">
-        <v>450281.34</v>
+        <v>449862.88</v>
       </c>
       <c r="F135">
-        <v>6851348.8200000003</v>
+        <v>6850537.8499999996</v>
       </c>
       <c r="G135">
-        <v>-1145.3399999999999</v>
+        <v>-1191.3699999999999</v>
       </c>
       <c r="H135">
-        <v>1352</v>
+        <v>2210.33</v>
       </c>
       <c r="K135">
-        <v>-1145.3399999999999</v>
+        <v>-1191.3699999999999</v>
       </c>
       <c r="O135" t="s">
-        <v>36</v>
-      </c>
-      <c r="P135">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U135" t="b">
         <v>1</v>
@@ -7545,54 +7437,45 @@
         <v>37</v>
       </c>
       <c r="X135" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC135" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD135">
-        <v>1</v>
-      </c>
-      <c r="AE135" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF135" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI135" s="1" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="AI135" s="1">
+        <v>46210.35696759259</v>
       </c>
     </row>
     <row r="136" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>9464</v>
+        <v>2896</v>
       </c>
       <c r="B136" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C136">
-        <v>171358704</v>
+        <v>171358584</v>
       </c>
       <c r="D136" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E136">
-        <v>450515.09</v>
+        <v>450097.05</v>
       </c>
       <c r="F136">
-        <v>6851683.5599999996</v>
+        <v>6850165.4900000002</v>
       </c>
       <c r="G136">
-        <v>-1196.98</v>
+        <v>-1192.58</v>
       </c>
       <c r="H136">
-        <v>1768.35</v>
+        <v>1770.1</v>
       </c>
       <c r="K136">
-        <v>-1196.98</v>
+        <v>-1192.58</v>
       </c>
       <c r="O136" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P136">
+        <v>1</v>
       </c>
       <c r="U136" t="b">
         <v>1</v>
@@ -7604,42 +7487,57 @@
         <v>37</v>
       </c>
       <c r="X136" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI136" s="1">
-        <v>46210.353865740741</v>
+        <v>0</v>
+      </c>
+      <c r="AC136" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD136">
+        <v>1</v>
+      </c>
+      <c r="AE136" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF136" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI136" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="137" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>9465</v>
+        <v>3064</v>
       </c>
       <c r="B137" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C137">
-        <v>171358704</v>
+        <v>171358584</v>
       </c>
       <c r="D137" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E137">
-        <v>450845</v>
+        <v>449861.96</v>
       </c>
       <c r="F137">
-        <v>6852362.7199999997</v>
+        <v>6850539.2400000002</v>
       </c>
       <c r="G137">
-        <v>-1196.3599999999999</v>
+        <v>-1191.42</v>
       </c>
       <c r="H137">
-        <v>2524.35</v>
+        <v>2212</v>
       </c>
       <c r="K137">
-        <v>-1196.3599999999999</v>
+        <v>-1191.42</v>
       </c>
       <c r="O137" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P137">
+        <v>2</v>
       </c>
       <c r="U137" t="b">
         <v>1</v>
@@ -7651,45 +7549,57 @@
         <v>37</v>
       </c>
       <c r="X137" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI137" s="1">
-        <v>46210.35392361111</v>
+        <v>0</v>
+      </c>
+      <c r="AC137" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD137">
+        <v>2</v>
+      </c>
+      <c r="AE137" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF137" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI137" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="138" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>3139</v>
+        <v>3137</v>
       </c>
       <c r="B138" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C138">
-        <v>171358704</v>
+        <v>171358584</v>
       </c>
       <c r="D138" t="s">
         <v>40</v>
       </c>
       <c r="E138">
-        <v>450447.07</v>
+        <v>449853.39</v>
       </c>
       <c r="F138">
-        <v>6851561.6900000004</v>
+        <v>6850552.25</v>
       </c>
       <c r="G138">
-        <v>-1195.44</v>
+        <v>-1191.8800000000001</v>
       </c>
       <c r="H138">
-        <v>1628.6</v>
+        <v>2227.6</v>
       </c>
       <c r="K138">
-        <v>-1195.44</v>
+        <v>-1191.8800000000001</v>
       </c>
       <c r="O138" t="s">
         <v>36</v>
       </c>
       <c r="P138">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U138" t="b">
         <v>1</v>
@@ -7707,10 +7617,10 @@
         <v>46</v>
       </c>
       <c r="AD138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE138" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF138" t="s">
         <v>48</v>
@@ -7721,37 +7631,37 @@
     </row>
     <row r="139" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>3055</v>
+        <v>26</v>
       </c>
       <c r="B139" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C139">
-        <v>171358704</v>
+        <v>171358586</v>
       </c>
       <c r="D139" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E139">
-        <v>450516.11</v>
+        <v>449423.46</v>
       </c>
       <c r="F139">
-        <v>6851685.5700000003</v>
+        <v>6851149.6799999997</v>
       </c>
       <c r="G139">
-        <v>-1196.98</v>
+        <v>-1145.92</v>
       </c>
       <c r="H139">
-        <v>1770.6</v>
+        <v>1379.1</v>
       </c>
       <c r="K139">
-        <v>-1196.98</v>
+        <v>-1145.92</v>
       </c>
       <c r="O139" t="s">
         <v>36</v>
       </c>
       <c r="P139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U139" t="b">
         <v>1</v>
@@ -7769,51 +7679,51 @@
         <v>46</v>
       </c>
       <c r="AD139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE139" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AF139" t="s">
         <v>48</v>
       </c>
       <c r="AI139" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="140" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>2805</v>
+        <v>3034</v>
       </c>
       <c r="B140" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C140">
-        <v>171358704</v>
+        <v>171358586</v>
       </c>
       <c r="D140" t="s">
         <v>40</v>
       </c>
       <c r="E140">
-        <v>450545.14</v>
+        <v>449701.81</v>
       </c>
       <c r="F140">
-        <v>6851745.3499999996</v>
+        <v>6851220.0499999998</v>
       </c>
       <c r="G140">
-        <v>-1198.2</v>
+        <v>-1192.8699999999999</v>
       </c>
       <c r="H140">
-        <v>1837.1</v>
+        <v>1672.5</v>
       </c>
       <c r="K140">
-        <v>-1198.2</v>
+        <v>-1192.8699999999999</v>
       </c>
       <c r="O140" t="s">
         <v>36</v>
       </c>
       <c r="P140">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U140" t="b">
         <v>1</v>
@@ -7831,10 +7741,10 @@
         <v>46</v>
       </c>
       <c r="AD140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE140" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AF140" t="s">
         <v>48</v>
@@ -7845,37 +7755,37 @@
     </row>
     <row r="141" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>3049</v>
+        <v>187</v>
       </c>
       <c r="B141" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C141">
-        <v>171358704</v>
+        <v>171358679</v>
       </c>
       <c r="D141" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E141">
-        <v>450844.05</v>
+        <v>448968.29</v>
       </c>
       <c r="F141">
-        <v>6852361.0199999996</v>
+        <v>6849117.6200000001</v>
       </c>
       <c r="G141">
-        <v>-1196.3499999999999</v>
+        <v>-1149.3599999999999</v>
       </c>
       <c r="H141">
-        <v>2522.4</v>
+        <v>1366.2</v>
       </c>
       <c r="K141">
-        <v>-1196.3499999999999</v>
+        <v>-1149.3599999999999</v>
       </c>
       <c r="O141" t="s">
         <v>36</v>
       </c>
       <c r="P141">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U141" t="b">
         <v>1</v>
@@ -7893,51 +7803,51 @@
         <v>46</v>
       </c>
       <c r="AD141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE141" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AF141" t="s">
         <v>48</v>
       </c>
       <c r="AI141" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="142" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>2979</v>
+        <v>2820</v>
       </c>
       <c r="B142" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C142">
-        <v>171358704</v>
+        <v>171358679</v>
       </c>
       <c r="D142" t="s">
         <v>40</v>
       </c>
       <c r="E142">
-        <v>450845.66</v>
+        <v>449185.07</v>
       </c>
       <c r="F142">
-        <v>6852363.9000000004</v>
+        <v>6849334.2800000003</v>
       </c>
       <c r="G142">
-        <v>-1196.3599999999999</v>
+        <v>-1198.07</v>
       </c>
       <c r="H142">
-        <v>2525.6999999999998</v>
+        <v>1679.01</v>
       </c>
       <c r="K142">
-        <v>-1196.3599999999999</v>
+        <v>-1198.07</v>
       </c>
       <c r="O142" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P142">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U142" t="b">
         <v>1</v>
@@ -7955,21 +7865,21 @@
         <v>46</v>
       </c>
       <c r="AD142">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE142" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AF142" t="s">
         <v>48</v>
       </c>
-      <c r="AI142" s="1" t="s">
-        <v>43</v>
+      <c r="AI142" s="1">
+        <v>46210.34814814815</v>
       </c>
     </row>
     <row r="143" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>2818</v>
+        <v>59</v>
       </c>
       <c r="B143" t="s">
         <v>68</v>
@@ -7978,28 +7888,28 @@
         <v>171358704</v>
       </c>
       <c r="D143" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E143">
-        <v>450849.09</v>
+        <v>450281.34</v>
       </c>
       <c r="F143">
-        <v>6852370.1200000001</v>
+        <v>6851348.8200000003</v>
       </c>
       <c r="G143">
-        <v>-1196.4000000000001</v>
+        <v>-1145.3399999999999</v>
       </c>
       <c r="H143">
-        <v>2532.8000000000002</v>
+        <v>1352</v>
       </c>
       <c r="K143">
-        <v>-1196.4000000000001</v>
+        <v>-1145.3399999999999</v>
       </c>
       <c r="O143" t="s">
         <v>36</v>
       </c>
       <c r="P143">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U143" t="b">
         <v>1</v>
@@ -8017,21 +7927,21 @@
         <v>46</v>
       </c>
       <c r="AD143">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE143" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AF143" t="s">
         <v>48</v>
       </c>
       <c r="AI143" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="144" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>2894</v>
+        <v>9460</v>
       </c>
       <c r="B144" t="s">
         <v>68</v>
@@ -8040,29 +7950,26 @@
         <v>171358704</v>
       </c>
       <c r="D144" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E144">
-        <v>450854.73</v>
+        <v>450515.09</v>
       </c>
       <c r="F144">
-        <v>6852380.3499999996</v>
+        <v>6851683.5599999996</v>
       </c>
       <c r="G144">
-        <v>-1196.56</v>
+        <v>-1196.98</v>
       </c>
       <c r="H144">
-        <v>2544.4899999999998</v>
+        <v>1768.35</v>
       </c>
       <c r="K144">
-        <v>-1196.56</v>
+        <v>-1196.98</v>
       </c>
       <c r="O144" t="s">
         <v>39</v>
       </c>
-      <c r="P144">
-        <v>8</v>
-      </c>
       <c r="U144" t="b">
         <v>1</v>
       </c>
@@ -8073,27 +7980,15 @@
         <v>37</v>
       </c>
       <c r="X144" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC144" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD144">
-        <v>1</v>
-      </c>
-      <c r="AE144" t="s">
-        <v>53</v>
-      </c>
-      <c r="AF144" t="s">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="AI144" s="1">
-        <v>46210.351145833331</v>
+        <v>46210.353865740741</v>
       </c>
     </row>
     <row r="145" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>3033</v>
+        <v>9461</v>
       </c>
       <c r="B145" t="s">
         <v>68</v>
@@ -8102,29 +7997,26 @@
         <v>171358704</v>
       </c>
       <c r="D145" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E145">
-        <v>450854.73</v>
+        <v>450845</v>
       </c>
       <c r="F145">
-        <v>6852380.3499999996</v>
+        <v>6852362.7199999997</v>
       </c>
       <c r="G145">
-        <v>-1196.56</v>
+        <v>-1196.3599999999999</v>
       </c>
       <c r="H145">
-        <v>2544.4899999999998</v>
+        <v>2524.35</v>
       </c>
       <c r="K145">
-        <v>-1196.56</v>
+        <v>-1196.3599999999999</v>
       </c>
       <c r="O145" t="s">
         <v>39</v>
       </c>
-      <c r="P145">
-        <v>7</v>
-      </c>
       <c r="U145" t="b">
         <v>1</v>
       </c>
@@ -8135,57 +8027,45 @@
         <v>37</v>
       </c>
       <c r="X145" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC145" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD145">
-        <v>2</v>
-      </c>
-      <c r="AE145" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF145" t="s">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="AI145" s="1">
-        <v>46210.351145833331</v>
+        <v>46210.35392361111</v>
       </c>
     </row>
     <row r="146" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>8953</v>
+        <v>2805</v>
       </c>
       <c r="B146" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C146">
-        <v>350114731796</v>
+        <v>171358704</v>
       </c>
       <c r="D146" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E146">
-        <v>447224.15</v>
+        <v>450545.14</v>
       </c>
       <c r="F146">
-        <v>6848743.5700000003</v>
+        <v>6851745.3499999996</v>
       </c>
       <c r="G146">
-        <v>-1162.3699999999999</v>
+        <v>-1198.2</v>
       </c>
       <c r="H146">
-        <v>1331.8</v>
+        <v>1837.1</v>
       </c>
       <c r="K146">
-        <v>-1162.3699999999999</v>
+        <v>-1198.2</v>
       </c>
       <c r="O146" t="s">
         <v>36</v>
       </c>
       <c r="P146">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U146" t="b">
         <v>1</v>
@@ -8199,46 +8079,55 @@
       <c r="X146" t="b">
         <v>0</v>
       </c>
+      <c r="AC146" t="s">
+        <v>46</v>
+      </c>
       <c r="AD146">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AE146" t="s">
+        <v>49</v>
       </c>
       <c r="AF146" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AI146" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="147" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>9462</v>
+        <v>3045</v>
       </c>
       <c r="B147" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C147">
-        <v>350114731796</v>
+        <v>171358704</v>
       </c>
       <c r="D147" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E147">
-        <v>446832.83</v>
+        <v>450844.05</v>
       </c>
       <c r="F147">
-        <v>6848568.25</v>
+        <v>6852361.0199999996</v>
       </c>
       <c r="G147">
-        <v>-1209.18</v>
+        <v>-1196.3499999999999</v>
       </c>
       <c r="H147">
-        <v>1765.88</v>
+        <v>2522.4</v>
       </c>
       <c r="K147">
-        <v>-1209.18</v>
+        <v>-1196.3499999999999</v>
       </c>
       <c r="O147" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P147">
+        <v>4</v>
       </c>
       <c r="U147" t="b">
         <v>1</v>
@@ -8250,39 +8139,51 @@
         <v>37</v>
       </c>
       <c r="X147" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI147" s="1">
-        <v>46210.353576388887</v>
+        <v>0</v>
+      </c>
+      <c r="AC147" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD147">
+        <v>2</v>
+      </c>
+      <c r="AE147" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF147" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI147" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="148" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>8951</v>
+        <v>3051</v>
       </c>
       <c r="B148" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C148">
-        <v>350114731796</v>
+        <v>171358704</v>
       </c>
       <c r="D148" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E148">
-        <v>446663.65</v>
+        <v>450516.11</v>
       </c>
       <c r="F148">
-        <v>6848482.0599999996</v>
+        <v>6851685.5700000003</v>
       </c>
       <c r="G148">
-        <v>-1206.75</v>
+        <v>-1196.98</v>
       </c>
       <c r="H148">
-        <v>1956</v>
+        <v>1770.6</v>
       </c>
       <c r="K148">
-        <v>-1206.75</v>
+        <v>-1196.98</v>
       </c>
       <c r="O148" t="s">
         <v>36</v>
@@ -8302,84 +8203,87 @@
       <c r="X148" t="b">
         <v>0</v>
       </c>
+      <c r="AC148" t="s">
+        <v>46</v>
+      </c>
       <c r="AD148">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AE148" t="s">
+        <v>49</v>
       </c>
       <c r="AF148" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AI148" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="149" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>9463</v>
+        <v>3135</v>
       </c>
       <c r="B149" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C149">
-        <v>350114731796</v>
+        <v>171358704</v>
       </c>
       <c r="D149" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E149">
-        <v>446304.19</v>
+        <v>450447.07</v>
       </c>
       <c r="F149">
-        <v>6848314.9199999999</v>
+        <v>6851561.6900000004</v>
       </c>
       <c r="G149">
-        <v>-1207.74</v>
+        <v>-1195.44</v>
       </c>
       <c r="H149">
-        <v>2352.7399999999998</v>
+        <v>1628.6</v>
       </c>
       <c r="K149">
-        <v>-1207.74</v>
-      </c>
-      <c r="L149">
+        <v>-1195.44</v>
+      </c>
+      <c r="O149" t="s">
+        <v>36</v>
+      </c>
+      <c r="P149">
+        <v>1</v>
+      </c>
+      <c r="U149" t="b">
+        <v>1</v>
+      </c>
+      <c r="V149" t="b">
+        <v>1</v>
+      </c>
+      <c r="W149" t="s">
+        <v>37</v>
+      </c>
+      <c r="X149" t="b">
         <v>0</v>
       </c>
-      <c r="O149" t="s">
-        <v>39</v>
-      </c>
-      <c r="P149">
-        <v>0</v>
-      </c>
-      <c r="Q149">
-        <v>0</v>
-      </c>
-      <c r="R149">
-        <v>0</v>
-      </c>
-      <c r="S149">
-        <v>0</v>
-      </c>
-      <c r="T149">
-        <v>0</v>
-      </c>
-      <c r="U149" t="b">
-        <v>0</v>
-      </c>
-      <c r="V149" t="b">
-        <v>0</v>
-      </c>
-      <c r="W149" t="s">
-        <v>37</v>
-      </c>
-      <c r="X149" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI149" s="1">
-        <v>46210.353750000002</v>
+      <c r="AC149" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD149">
+        <v>1</v>
+      </c>
+      <c r="AE149" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF149" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI149" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="150" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>8947</v>
+        <v>8943</v>
       </c>
       <c r="B150" t="s">
         <v>69</v>
@@ -8435,7 +8339,7 @@
     </row>
     <row r="151" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>8941</v>
+        <v>8947</v>
       </c>
       <c r="B151" t="s">
         <v>69</v>
@@ -8444,28 +8348,28 @@
         <v>350114731796</v>
       </c>
       <c r="D151" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E151">
-        <v>446952.4</v>
+        <v>446663.65</v>
       </c>
       <c r="F151">
-        <v>6848627.3499999996</v>
+        <v>6848482.0599999996</v>
       </c>
       <c r="G151">
-        <v>-1208.6099999999999</v>
+        <v>-1206.75</v>
       </c>
       <c r="H151">
-        <v>1632.38</v>
+        <v>1956</v>
       </c>
       <c r="K151">
-        <v>-1208.6099999999999</v>
+        <v>-1206.75</v>
       </c>
       <c r="O151" t="s">
         <v>36</v>
       </c>
       <c r="P151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U151" t="b">
         <v>1</v>
@@ -8486,12 +8390,12 @@
         <v>38</v>
       </c>
       <c r="AI151" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="152" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>9504</v>
+        <v>8949</v>
       </c>
       <c r="B152" t="s">
         <v>69</v>
@@ -8500,25 +8404,28 @@
         <v>350114731796</v>
       </c>
       <c r="D152" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E152">
-        <v>446831.67</v>
+        <v>447224.15</v>
       </c>
       <c r="F152">
-        <v>6848567.6100000003</v>
+        <v>6848743.5700000003</v>
       </c>
       <c r="G152">
-        <v>-1209.19</v>
+        <v>-1162.3699999999999</v>
       </c>
       <c r="H152">
-        <v>1767.21</v>
+        <v>1331.8</v>
       </c>
       <c r="K152">
-        <v>-1209.19</v>
+        <v>-1162.3699999999999</v>
       </c>
       <c r="O152" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P152">
+        <v>1</v>
       </c>
       <c r="U152" t="b">
         <v>1</v>
@@ -8530,15 +8437,21 @@
         <v>37</v>
       </c>
       <c r="X152" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI152" s="1">
-        <v>46210.357164351852</v>
+        <v>0</v>
+      </c>
+      <c r="AD152">
+        <v>1</v>
+      </c>
+      <c r="AF152" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI152" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="153" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>9503</v>
+        <v>9458</v>
       </c>
       <c r="B153" t="s">
         <v>69</v>
@@ -8547,22 +8460,22 @@
         <v>350114731796</v>
       </c>
       <c r="D153" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E153">
-        <v>446665.16</v>
+        <v>446832.83</v>
       </c>
       <c r="F153">
-        <v>6848482.75</v>
+        <v>6848568.25</v>
       </c>
       <c r="G153">
-        <v>-1206.7</v>
+        <v>-1209.18</v>
       </c>
       <c r="H153">
-        <v>1954.34</v>
+        <v>1765.88</v>
       </c>
       <c r="K153">
-        <v>-1206.7</v>
+        <v>-1209.18</v>
       </c>
       <c r="O153" t="s">
         <v>39</v>
@@ -8580,12 +8493,12 @@
         <v>1</v>
       </c>
       <c r="AI153" s="1">
-        <v>46210.357118055559</v>
+        <v>46210.353576388887</v>
       </c>
     </row>
     <row r="154" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>8942</v>
+        <v>9459</v>
       </c>
       <c r="B154" t="s">
         <v>69</v>
@@ -8594,54 +8507,63 @@
         <v>350114731796</v>
       </c>
       <c r="D154" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E154">
-        <v>446630.16</v>
+        <v>446304.19</v>
       </c>
       <c r="F154">
-        <v>6848466.4400000004</v>
+        <v>6848314.9199999999</v>
       </c>
       <c r="G154">
-        <v>-1208.27</v>
+        <v>-1207.74</v>
       </c>
       <c r="H154">
-        <v>1993</v>
+        <v>2352.7399999999998</v>
       </c>
       <c r="K154">
-        <v>-1208.27</v>
+        <v>-1207.74</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
       </c>
       <c r="O154" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P154">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q154">
+        <v>0</v>
+      </c>
+      <c r="R154">
+        <v>0</v>
+      </c>
+      <c r="S154">
+        <v>0</v>
+      </c>
+      <c r="T154">
+        <v>0</v>
       </c>
       <c r="U154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W154" t="s">
         <v>37</v>
       </c>
       <c r="X154" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD154">
-        <v>1</v>
-      </c>
-      <c r="AF154" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI154" s="1" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI154" s="1">
+        <v>46210.353750000002</v>
       </c>
     </row>
     <row r="155" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>9505</v>
+        <v>8937</v>
       </c>
       <c r="B155" t="s">
         <v>69</v>
@@ -8653,22 +8575,25 @@
         <v>40</v>
       </c>
       <c r="E155">
-        <v>446303.17</v>
+        <v>446952.4</v>
       </c>
       <c r="F155">
-        <v>6848314.46</v>
+        <v>6848627.3499999996</v>
       </c>
       <c r="G155">
-        <v>-1207.75</v>
+        <v>-1208.6099999999999</v>
       </c>
       <c r="H155">
-        <v>2353.86</v>
+        <v>1632.38</v>
       </c>
       <c r="K155">
-        <v>-1207.75</v>
+        <v>-1208.6099999999999</v>
       </c>
       <c r="O155" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P155">
+        <v>1</v>
       </c>
       <c r="U155" t="b">
         <v>1</v>
@@ -8680,15 +8605,21 @@
         <v>37</v>
       </c>
       <c r="X155" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI155" s="1">
-        <v>46210.357210648152</v>
+        <v>0</v>
+      </c>
+      <c r="AD155">
+        <v>1</v>
+      </c>
+      <c r="AF155" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI155" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="156" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>9506</v>
+        <v>8938</v>
       </c>
       <c r="B156" t="s">
         <v>69</v>
@@ -8700,22 +8631,25 @@
         <v>40</v>
       </c>
       <c r="E156">
-        <v>446263.94</v>
+        <v>446630.16</v>
       </c>
       <c r="F156">
-        <v>6848296.7199999997</v>
+        <v>6848466.4400000004</v>
       </c>
       <c r="G156">
-        <v>-1208.04</v>
+        <v>-1208.27</v>
       </c>
       <c r="H156">
-        <v>2396.9299999999998</v>
+        <v>1993</v>
       </c>
       <c r="K156">
-        <v>-1208.04</v>
+        <v>-1208.27</v>
       </c>
       <c r="O156" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P156">
+        <v>2</v>
       </c>
       <c r="U156" t="b">
         <v>1</v>
@@ -8727,15 +8661,21 @@
         <v>37</v>
       </c>
       <c r="X156" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI156" s="1">
-        <v>46210.357222222221</v>
+        <v>0</v>
+      </c>
+      <c r="AD156">
+        <v>1</v>
+      </c>
+      <c r="AF156" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI156" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="157" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>9507</v>
+        <v>8945</v>
       </c>
       <c r="B157" t="s">
         <v>69</v>
@@ -8747,22 +8687,25 @@
         <v>40</v>
       </c>
       <c r="E157">
-        <v>445866.16</v>
+        <v>445785.52</v>
       </c>
       <c r="F157">
-        <v>6848090.79</v>
+        <v>6848042.9000000004</v>
       </c>
       <c r="G157">
-        <v>-1210.56</v>
+        <v>-1211.6500000000001</v>
       </c>
       <c r="H157">
-        <v>2845.46</v>
+        <v>2939.3</v>
       </c>
       <c r="K157">
-        <v>-1210.56</v>
+        <v>-1211.6500000000001</v>
       </c>
       <c r="O157" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P157">
+        <v>3</v>
       </c>
       <c r="U157" t="b">
         <v>1</v>
@@ -8774,15 +8717,21 @@
         <v>37</v>
       </c>
       <c r="X157" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI157" s="1">
-        <v>46210.357291666667</v>
+        <v>0</v>
+      </c>
+      <c r="AD157">
+        <v>1</v>
+      </c>
+      <c r="AF157" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI157" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="158" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>8949</v>
+        <v>9499</v>
       </c>
       <c r="B158" t="s">
         <v>69</v>
@@ -8794,25 +8743,22 @@
         <v>40</v>
       </c>
       <c r="E158">
-        <v>445785.52</v>
+        <v>446665.16</v>
       </c>
       <c r="F158">
-        <v>6848042.9000000004</v>
+        <v>6848482.75</v>
       </c>
       <c r="G158">
-        <v>-1211.6500000000001</v>
+        <v>-1206.7</v>
       </c>
       <c r="H158">
-        <v>2939.3</v>
+        <v>1954.34</v>
       </c>
       <c r="K158">
-        <v>-1211.6500000000001</v>
+        <v>-1206.7</v>
       </c>
       <c r="O158" t="s">
-        <v>36</v>
-      </c>
-      <c r="P158">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="U158" t="b">
         <v>1</v>
@@ -8824,51 +8770,42 @@
         <v>37</v>
       </c>
       <c r="X158" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD158">
-        <v>1</v>
-      </c>
-      <c r="AF158" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI158" s="1" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI158" s="1">
+        <v>46210.357118055559</v>
       </c>
     </row>
     <row r="159" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>8965</v>
+        <v>9500</v>
       </c>
       <c r="B159" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C159">
-        <v>350162787955</v>
+        <v>350114731796</v>
       </c>
       <c r="D159" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E159">
-        <v>447142.23</v>
+        <v>446831.67</v>
       </c>
       <c r="F159">
-        <v>6848910.25</v>
+        <v>6848567.6100000003</v>
       </c>
       <c r="G159">
-        <v>-1162.1300000000001</v>
+        <v>-1209.19</v>
       </c>
       <c r="H159">
-        <v>1349.33</v>
+        <v>1767.21</v>
       </c>
       <c r="K159">
-        <v>-1162.1300000000001</v>
+        <v>-1209.19</v>
       </c>
       <c r="O159" t="s">
-        <v>36</v>
-      </c>
-      <c r="P159">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U159" t="b">
         <v>1</v>
@@ -8880,45 +8817,39 @@
         <v>37</v>
       </c>
       <c r="X159" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD159">
-        <v>1</v>
-      </c>
-      <c r="AF159" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI159" s="1" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="AI159" s="1">
+        <v>46210.357164351852</v>
       </c>
     </row>
     <row r="160" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>9461</v>
+        <v>9501</v>
       </c>
       <c r="B160" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C160">
-        <v>350162787955</v>
+        <v>350114731796</v>
       </c>
       <c r="D160" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E160">
-        <v>446387.48</v>
+        <v>446303.17</v>
       </c>
       <c r="F160">
-        <v>6848947.7199999997</v>
+        <v>6848314.46</v>
       </c>
       <c r="G160">
-        <v>-1208.3699999999999</v>
+        <v>-1207.75</v>
       </c>
       <c r="H160">
-        <v>2110.62</v>
+        <v>2353.86</v>
       </c>
       <c r="K160">
-        <v>-1208.3699999999999</v>
+        <v>-1207.75</v>
       </c>
       <c r="O160" t="s">
         <v>39</v>
@@ -8936,42 +8867,39 @@
         <v>1</v>
       </c>
       <c r="AI160" s="1">
-        <v>46210.353530092594</v>
+        <v>46210.357210648152</v>
       </c>
     </row>
     <row r="161" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>8963</v>
+        <v>9502</v>
       </c>
       <c r="B161" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C161">
-        <v>350162787955</v>
+        <v>350114731796</v>
       </c>
       <c r="D161" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E161">
-        <v>446240.48</v>
+        <v>446263.94</v>
       </c>
       <c r="F161">
-        <v>6848957.0899999999</v>
+        <v>6848296.7199999997</v>
       </c>
       <c r="G161">
-        <v>-1209.67</v>
+        <v>-1208.04</v>
       </c>
       <c r="H161">
-        <v>2258</v>
+        <v>2396.9299999999998</v>
       </c>
       <c r="K161">
-        <v>-1209.67</v>
+        <v>-1208.04</v>
       </c>
       <c r="O161" t="s">
-        <v>36</v>
-      </c>
-      <c r="P161">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="U161" t="b">
         <v>1</v>
@@ -8983,45 +8911,42 @@
         <v>37</v>
       </c>
       <c r="X161" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI161" s="1" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="AI161" s="1">
+        <v>46210.357222222221</v>
       </c>
     </row>
     <row r="162" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>8958</v>
+        <v>9503</v>
       </c>
       <c r="B162" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C162">
-        <v>350162787955</v>
+        <v>350114731796</v>
       </c>
       <c r="D162" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E162">
-        <v>445984.03</v>
+        <v>445866.16</v>
       </c>
       <c r="F162">
-        <v>6848971.8899999997</v>
+        <v>6848090.79</v>
       </c>
       <c r="G162">
-        <v>-1210.71</v>
+        <v>-1210.56</v>
       </c>
       <c r="H162">
-        <v>2515</v>
+        <v>2845.46</v>
       </c>
       <c r="K162">
-        <v>-1210.71</v>
+        <v>-1210.56</v>
       </c>
       <c r="O162" t="s">
-        <v>36</v>
-      </c>
-      <c r="P162">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="U162" t="b">
         <v>1</v>
@@ -9033,45 +8958,42 @@
         <v>37</v>
       </c>
       <c r="X162" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI162" s="1" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="AI162" s="1">
+        <v>46210.357291666667</v>
       </c>
     </row>
     <row r="163" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>8968</v>
+        <v>9565</v>
       </c>
       <c r="B163" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C163">
-        <v>350162787955</v>
+        <v>350114731796</v>
       </c>
       <c r="D163" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E163">
-        <v>445733.28</v>
+        <v>446719.35</v>
       </c>
       <c r="F163">
-        <v>6848980.1799999997</v>
+        <v>6848507.6500000004</v>
       </c>
       <c r="G163">
-        <v>-1211.8800000000001</v>
+        <v>-1206.96</v>
       </c>
       <c r="H163">
-        <v>2766</v>
+        <v>1894.66</v>
       </c>
       <c r="K163">
-        <v>-1211.8800000000001</v>
+        <v>-1206.96</v>
       </c>
       <c r="O163" t="s">
-        <v>36</v>
-      </c>
-      <c r="P163">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="U163" t="b">
         <v>1</v>
@@ -9083,15 +9005,15 @@
         <v>37</v>
       </c>
       <c r="X163" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI163" s="1" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="AI163" s="1">
+        <v>46210.587106481478</v>
       </c>
     </row>
     <row r="164" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>8957</v>
+        <v>8954</v>
       </c>
       <c r="B164" t="s">
         <v>70</v>
@@ -9100,28 +9022,28 @@
         <v>350162787955</v>
       </c>
       <c r="D164" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E164">
-        <v>446794.95</v>
+        <v>445984.03</v>
       </c>
       <c r="F164">
-        <v>6848929.8099999996</v>
+        <v>6848971.8899999997</v>
       </c>
       <c r="G164">
-        <v>-1209.81</v>
+        <v>-1210.71</v>
       </c>
       <c r="H164">
-        <v>1702.5</v>
+        <v>2515</v>
       </c>
       <c r="K164">
-        <v>-1209.81</v>
+        <v>-1210.71</v>
       </c>
       <c r="O164" t="s">
         <v>36</v>
       </c>
       <c r="P164">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U164" t="b">
         <v>1</v>
@@ -9135,19 +9057,13 @@
       <c r="X164" t="b">
         <v>0</v>
       </c>
-      <c r="AD164">
-        <v>1</v>
-      </c>
-      <c r="AF164" t="s">
-        <v>38</v>
-      </c>
       <c r="AI164" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="165" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>9508</v>
+        <v>8959</v>
       </c>
       <c r="B165" t="s">
         <v>70</v>
@@ -9156,25 +9072,28 @@
         <v>350162787955</v>
       </c>
       <c r="D165" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E165">
-        <v>446390.07</v>
+        <v>446240.48</v>
       </c>
       <c r="F165">
-        <v>6848947.5700000003</v>
+        <v>6848957.0899999999</v>
       </c>
       <c r="G165">
-        <v>-1208.3699999999999</v>
+        <v>-1209.67</v>
       </c>
       <c r="H165">
-        <v>2108.0300000000002</v>
+        <v>2258</v>
       </c>
       <c r="K165">
-        <v>-1208.3699999999999</v>
+        <v>-1209.67</v>
       </c>
       <c r="O165" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P165">
+        <v>2</v>
       </c>
       <c r="U165" t="b">
         <v>1</v>
@@ -9186,15 +9105,15 @@
         <v>37</v>
       </c>
       <c r="X165" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI165" s="1">
-        <v>46210.357349537036</v>
+        <v>0</v>
+      </c>
+      <c r="AI165" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="166" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>9510</v>
+        <v>8961</v>
       </c>
       <c r="B166" t="s">
         <v>70</v>
@@ -9203,25 +9122,28 @@
         <v>350162787955</v>
       </c>
       <c r="D166" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E166">
-        <v>446334.79</v>
+        <v>447142.23</v>
       </c>
       <c r="F166">
-        <v>6848950.9199999999</v>
+        <v>6848910.25</v>
       </c>
       <c r="G166">
-        <v>-1209.07</v>
+        <v>-1162.1300000000001</v>
       </c>
       <c r="H166">
-        <v>2163.4299999999998</v>
+        <v>1349.33</v>
       </c>
       <c r="K166">
-        <v>-1209.07</v>
+        <v>-1162.1300000000001</v>
       </c>
       <c r="O166" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P166">
+        <v>1</v>
       </c>
       <c r="U166" t="b">
         <v>1</v>
@@ -9233,15 +9155,21 @@
         <v>37</v>
       </c>
       <c r="X166" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI166" s="1">
-        <v>46210.446550925924</v>
+        <v>0</v>
+      </c>
+      <c r="AD166">
+        <v>1</v>
+      </c>
+      <c r="AF166" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI166" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="167" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>9509</v>
+        <v>8964</v>
       </c>
       <c r="B167" t="s">
         <v>70</v>
@@ -9250,25 +9178,28 @@
         <v>350162787955</v>
       </c>
       <c r="D167" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E167">
-        <v>446243.41</v>
+        <v>445733.28</v>
       </c>
       <c r="F167">
-        <v>6848956.9100000001</v>
+        <v>6848980.1799999997</v>
       </c>
       <c r="G167">
-        <v>-1209.7</v>
+        <v>-1211.8800000000001</v>
       </c>
       <c r="H167">
-        <v>2255.06</v>
+        <v>2766</v>
       </c>
       <c r="K167">
-        <v>-1209.7</v>
+        <v>-1211.8800000000001</v>
       </c>
       <c r="O167" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P167">
+        <v>4</v>
       </c>
       <c r="U167" t="b">
         <v>1</v>
@@ -9280,15 +9211,15 @@
         <v>37</v>
       </c>
       <c r="X167" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI167" s="1">
-        <v>46210.35738425926</v>
+        <v>0</v>
+      </c>
+      <c r="AI167" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="168" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>8966</v>
+        <v>9457</v>
       </c>
       <c r="B168" t="s">
         <v>70</v>
@@ -9297,28 +9228,25 @@
         <v>350162787955</v>
       </c>
       <c r="D168" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E168">
-        <v>446192.59</v>
+        <v>446387.48</v>
       </c>
       <c r="F168">
-        <v>6848960.0499999998</v>
+        <v>6848947.7199999997</v>
       </c>
       <c r="G168">
-        <v>-1210.1600000000001</v>
+        <v>-1208.3699999999999</v>
       </c>
       <c r="H168">
-        <v>2306</v>
+        <v>2110.62</v>
       </c>
       <c r="K168">
-        <v>-1210.1600000000001</v>
+        <v>-1208.3699999999999</v>
       </c>
       <c r="O168" t="s">
-        <v>36</v>
-      </c>
-      <c r="P168">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="U168" t="b">
         <v>1</v>
@@ -9330,15 +9258,15 @@
         <v>37</v>
       </c>
       <c r="X168" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI168" s="1" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="AI168" s="1">
+        <v>46210.353530092594</v>
       </c>
     </row>
     <row r="169" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>9511</v>
+        <v>8952</v>
       </c>
       <c r="B169" t="s">
         <v>70</v>
@@ -9350,23 +9278,26 @@
         <v>40</v>
       </c>
       <c r="E169">
-        <v>445985.55</v>
+        <v>445673.48</v>
       </c>
       <c r="F169">
-        <v>6848971.8399999999</v>
+        <v>6848983.9400000004</v>
       </c>
       <c r="G169">
-        <v>-1210.71</v>
+        <v>-1212.2</v>
       </c>
       <c r="H169">
-        <v>2513.48</v>
+        <v>2825.94</v>
       </c>
       <c r="K169">
-        <v>-1210.71</v>
+        <v>-1212.2</v>
       </c>
       <c r="O169" t="s">
         <v>39</v>
       </c>
+      <c r="P169">
+        <v>4</v>
+      </c>
       <c r="U169" t="b">
         <v>1</v>
       </c>
@@ -9377,15 +9308,15 @@
         <v>37</v>
       </c>
       <c r="X169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI169" s="1">
-        <v>46210.357442129629</v>
+        <v>46210.587361111109</v>
       </c>
     </row>
     <row r="170" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>8961</v>
+        <v>8953</v>
       </c>
       <c r="B170" t="s">
         <v>70</v>
@@ -9397,25 +9328,25 @@
         <v>40</v>
       </c>
       <c r="E170">
-        <v>445824.17</v>
+        <v>446794.95</v>
       </c>
       <c r="F170">
-        <v>6848976.5199999996</v>
+        <v>6848929.8099999996</v>
       </c>
       <c r="G170">
-        <v>-1211.8900000000001</v>
+        <v>-1209.81</v>
       </c>
       <c r="H170">
-        <v>2675</v>
+        <v>1702.5</v>
       </c>
       <c r="K170">
-        <v>-1211.8900000000001</v>
+        <v>-1209.81</v>
       </c>
       <c r="O170" t="s">
         <v>36</v>
       </c>
       <c r="P170">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U170" t="b">
         <v>1</v>
@@ -9429,13 +9360,19 @@
       <c r="X170" t="b">
         <v>0</v>
       </c>
+      <c r="AD170">
+        <v>1</v>
+      </c>
+      <c r="AF170" t="s">
+        <v>38</v>
+      </c>
       <c r="AI170" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="171" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>9512</v>
+        <v>8957</v>
       </c>
       <c r="B171" t="s">
         <v>70</v>
@@ -9447,22 +9384,25 @@
         <v>40</v>
       </c>
       <c r="E171">
-        <v>445733.31</v>
+        <v>445824.17</v>
       </c>
       <c r="F171">
-        <v>6848980.1699999999</v>
+        <v>6848976.5199999996</v>
       </c>
       <c r="G171">
-        <v>-1211.8800000000001</v>
+        <v>-1211.8900000000001</v>
       </c>
       <c r="H171">
-        <v>2765.97</v>
+        <v>2675</v>
       </c>
       <c r="K171">
-        <v>-1211.8800000000001</v>
+        <v>-1211.8900000000001</v>
       </c>
       <c r="O171" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="P171">
+        <v>3</v>
       </c>
       <c r="U171" t="b">
         <v>1</v>
@@ -9474,15 +9414,15 @@
         <v>37</v>
       </c>
       <c r="X171" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI171" s="1">
-        <v>46210.357476851852</v>
+        <v>0</v>
+      </c>
+      <c r="AI171" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="172" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>8956</v>
+        <v>8962</v>
       </c>
       <c r="B172" t="s">
         <v>70</v>
@@ -9494,25 +9434,25 @@
         <v>40</v>
       </c>
       <c r="E172">
-        <v>445659.46</v>
+        <v>446192.59</v>
       </c>
       <c r="F172">
-        <v>6848984.8600000003</v>
+        <v>6848960.0499999998</v>
       </c>
       <c r="G172">
-        <v>-1212.2</v>
+        <v>-1210.1600000000001</v>
       </c>
       <c r="H172">
-        <v>2840</v>
+        <v>2306</v>
       </c>
       <c r="K172">
-        <v>-1212.2</v>
+        <v>-1210.1600000000001</v>
       </c>
       <c r="O172" t="s">
         <v>36</v>
       </c>
       <c r="P172">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U172" t="b">
         <v>1</v>
@@ -9532,37 +9472,34 @@
     </row>
     <row r="173" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>9426</v>
+        <v>9504</v>
       </c>
       <c r="B173" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C173">
-        <v>350114731838</v>
+        <v>350162787955</v>
       </c>
       <c r="D173" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E173">
-        <v>440554.51</v>
+        <v>446390.07</v>
       </c>
       <c r="F173">
-        <v>6851109.8700000001</v>
+        <v>6848947.5700000003</v>
       </c>
       <c r="G173">
-        <v>-1172.54</v>
+        <v>-1208.3699999999999</v>
       </c>
       <c r="H173">
-        <v>1336.64</v>
+        <v>2108.0300000000002</v>
       </c>
       <c r="K173">
-        <v>-1172.54</v>
+        <v>-1208.3699999999999</v>
       </c>
       <c r="O173" t="s">
-        <v>36</v>
-      </c>
-      <c r="P173">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="U173" t="b">
         <v>1</v>
@@ -9576,43 +9513,37 @@
       <c r="X173" t="b">
         <v>1</v>
       </c>
-      <c r="AD173">
-        <v>1</v>
-      </c>
-      <c r="AF173" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI173" s="1" t="s">
-        <v>42</v>
+      <c r="AI173" s="1">
+        <v>46210.357349537036</v>
       </c>
     </row>
     <row r="174" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>9457</v>
+        <v>9505</v>
       </c>
       <c r="B174" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C174">
-        <v>350114731838</v>
+        <v>350162787955</v>
       </c>
       <c r="D174" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E174">
-        <v>441102.5</v>
+        <v>446243.41</v>
       </c>
       <c r="F174">
-        <v>6851660.8499999996</v>
+        <v>6848956.9100000001</v>
       </c>
       <c r="G174">
-        <v>-1223.29</v>
+        <v>-1209.7</v>
       </c>
       <c r="H174">
-        <v>2119.17</v>
+        <v>2255.06</v>
       </c>
       <c r="K174">
-        <v>-1223.29</v>
+        <v>-1209.7</v>
       </c>
       <c r="O174" t="s">
         <v>39</v>
@@ -9630,36 +9561,36 @@
         <v>1</v>
       </c>
       <c r="AI174" s="1">
-        <v>46210.353229166663</v>
+        <v>46210.35738425926</v>
       </c>
     </row>
     <row r="175" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>9458</v>
+        <v>9506</v>
       </c>
       <c r="B175" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C175">
-        <v>350114731838</v>
+        <v>350162787955</v>
       </c>
       <c r="D175" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E175">
-        <v>441227.73</v>
+        <v>446334.79</v>
       </c>
       <c r="F175">
-        <v>6851777.4900000002</v>
+        <v>6848950.9199999999</v>
       </c>
       <c r="G175">
-        <v>-1223.8499999999999</v>
+        <v>-1209.07</v>
       </c>
       <c r="H175">
-        <v>2290.38</v>
+        <v>2163.4299999999998</v>
       </c>
       <c r="K175">
-        <v>-1223.8499999999999</v>
+        <v>-1209.07</v>
       </c>
       <c r="O175" t="s">
         <v>39</v>
@@ -9677,36 +9608,36 @@
         <v>1</v>
       </c>
       <c r="AI175" s="1">
-        <v>46210.353263888886</v>
+        <v>46210.446550925924</v>
       </c>
     </row>
     <row r="176" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>9459</v>
+        <v>9507</v>
       </c>
       <c r="B176" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C176">
-        <v>350114731838</v>
+        <v>350162787955</v>
       </c>
       <c r="D176" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E176">
-        <v>441271.83</v>
+        <v>445985.55</v>
       </c>
       <c r="F176">
-        <v>6851818.3799999999</v>
+        <v>6848971.8399999999</v>
       </c>
       <c r="G176">
-        <v>-1225.03</v>
+        <v>-1210.71</v>
       </c>
       <c r="H176">
-        <v>2350.56</v>
+        <v>2513.48</v>
       </c>
       <c r="K176">
-        <v>-1225.03</v>
+        <v>-1210.71</v>
       </c>
       <c r="O176" t="s">
         <v>39</v>
@@ -9724,36 +9655,36 @@
         <v>1</v>
       </c>
       <c r="AI176" s="1">
-        <v>46210.44604166667</v>
+        <v>46210.357442129629</v>
       </c>
     </row>
     <row r="177" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>9460</v>
+        <v>9508</v>
       </c>
       <c r="B177" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C177">
-        <v>350114731838</v>
+        <v>350162787955</v>
       </c>
       <c r="D177" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E177">
-        <v>441572.54</v>
+        <v>445733.31</v>
       </c>
       <c r="F177">
-        <v>6852119.9800000004</v>
+        <v>6848980.1699999999</v>
       </c>
       <c r="G177">
-        <v>-1222.8399999999999</v>
+        <v>-1211.8800000000001</v>
       </c>
       <c r="H177">
-        <v>2777.2</v>
+        <v>2765.97</v>
       </c>
       <c r="K177">
-        <v>-1222.8399999999999</v>
+        <v>-1211.8800000000001</v>
       </c>
       <c r="O177" t="s">
         <v>39</v>
@@ -9771,12 +9702,12 @@
         <v>1</v>
       </c>
       <c r="AI177" s="1">
-        <v>46210.353310185186</v>
+        <v>46210.357476851852</v>
       </c>
     </row>
     <row r="178" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>9432</v>
+        <v>9422</v>
       </c>
       <c r="B178" t="s">
         <v>71</v>
@@ -9785,22 +9716,22 @@
         <v>350114731838</v>
       </c>
       <c r="D178" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E178">
-        <v>440719.23</v>
+        <v>440554.51</v>
       </c>
       <c r="F178">
-        <v>6851274.0800000001</v>
+        <v>6851109.8700000001</v>
       </c>
       <c r="G178">
-        <v>-1218.1500000000001</v>
+        <v>-1172.54</v>
       </c>
       <c r="H178">
-        <v>1574.26</v>
+        <v>1336.64</v>
       </c>
       <c r="K178">
-        <v>-1218.1500000000001</v>
+        <v>-1172.54</v>
       </c>
       <c r="O178" t="s">
         <v>36</v>
@@ -9827,12 +9758,12 @@
         <v>38</v>
       </c>
       <c r="AI178" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="179" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>9513</v>
+        <v>9453</v>
       </c>
       <c r="B179" t="s">
         <v>71</v>
@@ -9841,22 +9772,22 @@
         <v>350114731838</v>
       </c>
       <c r="D179" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E179">
-        <v>441101.05</v>
+        <v>441102.5</v>
       </c>
       <c r="F179">
-        <v>6851659.5</v>
+        <v>6851660.8499999996</v>
       </c>
       <c r="G179">
-        <v>-1223.31</v>
+        <v>-1223.29</v>
       </c>
       <c r="H179">
-        <v>2117.1999999999998</v>
+        <v>2119.17</v>
       </c>
       <c r="K179">
-        <v>-1223.31</v>
+        <v>-1223.29</v>
       </c>
       <c r="O179" t="s">
         <v>39</v>
@@ -9874,12 +9805,12 @@
         <v>1</v>
       </c>
       <c r="AI179" s="1">
-        <v>46210.357557870368</v>
+        <v>46210.353229166663</v>
       </c>
     </row>
     <row r="180" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>9536</v>
+        <v>9454</v>
       </c>
       <c r="B180" t="s">
         <v>71</v>
@@ -9888,22 +9819,22 @@
         <v>350114731838</v>
       </c>
       <c r="D180" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E180">
-        <v>441146.84</v>
+        <v>441227.73</v>
       </c>
       <c r="F180">
-        <v>6851702.2800000003</v>
+        <v>6851777.4900000002</v>
       </c>
       <c r="G180">
-        <v>-1223.68</v>
+        <v>-1223.8499999999999</v>
       </c>
       <c r="H180">
-        <v>2179.89</v>
+        <v>2290.38</v>
       </c>
       <c r="K180">
-        <v>-1223.68</v>
+        <v>-1223.8499999999999</v>
       </c>
       <c r="O180" t="s">
         <v>39</v>
@@ -9921,12 +9852,12 @@
         <v>1</v>
       </c>
       <c r="AI180" s="1">
-        <v>46210.446562500001</v>
+        <v>46210.353263888886</v>
       </c>
     </row>
     <row r="181" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>9514</v>
+        <v>9455</v>
       </c>
       <c r="B181" t="s">
         <v>71</v>
@@ -9935,22 +9866,22 @@
         <v>350114731838</v>
       </c>
       <c r="D181" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E181">
-        <v>441225.98</v>
+        <v>441271.83</v>
       </c>
       <c r="F181">
-        <v>6851775.8700000001</v>
+        <v>6851818.3799999999</v>
       </c>
       <c r="G181">
-        <v>-1223.83</v>
+        <v>-1225.03</v>
       </c>
       <c r="H181">
-        <v>2288</v>
+        <v>2350.56</v>
       </c>
       <c r="K181">
-        <v>-1223.83</v>
+        <v>-1225.03</v>
       </c>
       <c r="O181" t="s">
         <v>39</v>
@@ -9968,12 +9899,12 @@
         <v>1</v>
       </c>
       <c r="AI181" s="1">
-        <v>46210.357581018521</v>
+        <v>46210.44604166667</v>
       </c>
     </row>
     <row r="182" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>9537</v>
+        <v>9456</v>
       </c>
       <c r="B182" t="s">
         <v>71</v>
@@ -9982,22 +9913,22 @@
         <v>350114731838</v>
       </c>
       <c r="D182" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E182">
-        <v>441248.13</v>
+        <v>441572.54</v>
       </c>
       <c r="F182">
-        <v>6851796.4699999997</v>
+        <v>6852119.9800000004</v>
       </c>
       <c r="G182">
-        <v>-1224.25</v>
+        <v>-1222.8399999999999</v>
       </c>
       <c r="H182">
-        <v>2318.27</v>
+        <v>2777.2</v>
       </c>
       <c r="K182">
-        <v>-1224.25</v>
+        <v>-1222.8399999999999</v>
       </c>
       <c r="O182" t="s">
         <v>39</v>
@@ -10015,12 +9946,12 @@
         <v>1</v>
       </c>
       <c r="AI182" s="1">
-        <v>46210.446620370371</v>
+        <v>46210.353310185186</v>
       </c>
     </row>
     <row r="183" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>9515</v>
+        <v>9428</v>
       </c>
       <c r="B183" t="s">
         <v>71</v>
@@ -10032,23 +9963,26 @@
         <v>40</v>
       </c>
       <c r="E183">
-        <v>441271.7</v>
+        <v>440783.6</v>
       </c>
       <c r="F183">
-        <v>6851818.25</v>
+        <v>6851339.4199999999</v>
       </c>
       <c r="G183">
-        <v>-1225.03</v>
+        <v>-1221.3699999999999</v>
       </c>
       <c r="H183">
-        <v>2350.37</v>
+        <v>1666.08</v>
       </c>
       <c r="K183">
-        <v>-1225.03</v>
+        <v>-1221.3699999999999</v>
       </c>
       <c r="O183" t="s">
         <v>39</v>
       </c>
+      <c r="P183">
+        <v>1</v>
+      </c>
       <c r="U183" t="b">
         <v>1</v>
       </c>
@@ -10061,13 +9995,19 @@
       <c r="X183" t="b">
         <v>1</v>
       </c>
+      <c r="AD183">
+        <v>1</v>
+      </c>
+      <c r="AF183" t="s">
+        <v>38</v>
+      </c>
       <c r="AI183" s="1">
-        <v>46210.357615740744</v>
+        <v>46210.587511574071</v>
       </c>
     </row>
     <row r="184" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>9516</v>
+        <v>9509</v>
       </c>
       <c r="B184" t="s">
         <v>71</v>
@@ -10079,37 +10019,366 @@
         <v>40</v>
       </c>
       <c r="E184">
+        <v>441101.05</v>
+      </c>
+      <c r="F184">
+        <v>6851659.5</v>
+      </c>
+      <c r="G184">
+        <v>-1223.31</v>
+      </c>
+      <c r="H184">
+        <v>2117.1999999999998</v>
+      </c>
+      <c r="K184">
+        <v>-1223.31</v>
+      </c>
+      <c r="O184" t="s">
+        <v>39</v>
+      </c>
+      <c r="U184" t="b">
+        <v>1</v>
+      </c>
+      <c r="V184" t="b">
+        <v>1</v>
+      </c>
+      <c r="W184" t="s">
+        <v>37</v>
+      </c>
+      <c r="X184" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI184" s="1">
+        <v>46210.357557870368</v>
+      </c>
+    </row>
+    <row r="185" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>9510</v>
+      </c>
+      <c r="B185" t="s">
+        <v>71</v>
+      </c>
+      <c r="C185">
+        <v>350114731838</v>
+      </c>
+      <c r="D185" t="s">
+        <v>40</v>
+      </c>
+      <c r="E185">
+        <v>441225.98</v>
+      </c>
+      <c r="F185">
+        <v>6851775.8700000001</v>
+      </c>
+      <c r="G185">
+        <v>-1223.83</v>
+      </c>
+      <c r="H185">
+        <v>2288</v>
+      </c>
+      <c r="K185">
+        <v>-1223.83</v>
+      </c>
+      <c r="O185" t="s">
+        <v>39</v>
+      </c>
+      <c r="U185" t="b">
+        <v>1</v>
+      </c>
+      <c r="V185" t="b">
+        <v>1</v>
+      </c>
+      <c r="W185" t="s">
+        <v>37</v>
+      </c>
+      <c r="X185" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI185" s="1">
+        <v>46210.357581018521</v>
+      </c>
+    </row>
+    <row r="186" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>9511</v>
+      </c>
+      <c r="B186" t="s">
+        <v>71</v>
+      </c>
+      <c r="C186">
+        <v>350114731838</v>
+      </c>
+      <c r="D186" t="s">
+        <v>40</v>
+      </c>
+      <c r="E186">
+        <v>441271.7</v>
+      </c>
+      <c r="F186">
+        <v>6851818.25</v>
+      </c>
+      <c r="G186">
+        <v>-1225.03</v>
+      </c>
+      <c r="H186">
+        <v>2350.37</v>
+      </c>
+      <c r="K186">
+        <v>-1225.03</v>
+      </c>
+      <c r="O186" t="s">
+        <v>39</v>
+      </c>
+      <c r="U186" t="b">
+        <v>1</v>
+      </c>
+      <c r="V186" t="b">
+        <v>1</v>
+      </c>
+      <c r="W186" t="s">
+        <v>37</v>
+      </c>
+      <c r="X186" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI186" s="1">
+        <v>46210.357615740744</v>
+      </c>
+    </row>
+    <row r="187" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>9512</v>
+      </c>
+      <c r="B187" t="s">
+        <v>71</v>
+      </c>
+      <c r="C187">
+        <v>350114731838</v>
+      </c>
+      <c r="D187" t="s">
+        <v>40</v>
+      </c>
+      <c r="E187">
         <v>441571.25</v>
       </c>
-      <c r="F184">
+      <c r="F187">
         <v>6852118.3799999999</v>
       </c>
-      <c r="G184">
+      <c r="G187">
         <v>-1222.8599999999999</v>
       </c>
-      <c r="H184">
+      <c r="H187">
         <v>2775.14</v>
       </c>
-      <c r="K184">
+      <c r="K187">
         <v>-1222.8599999999999</v>
       </c>
-      <c r="O184" t="s">
-        <v>39</v>
-      </c>
-      <c r="U184" t="b">
-        <v>1</v>
-      </c>
-      <c r="V184" t="b">
-        <v>1</v>
-      </c>
-      <c r="W184" t="s">
-        <v>37</v>
-      </c>
-      <c r="X184" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI184" s="1">
+      <c r="O187" t="s">
+        <v>39</v>
+      </c>
+      <c r="U187" t="b">
+        <v>1</v>
+      </c>
+      <c r="V187" t="b">
+        <v>1</v>
+      </c>
+      <c r="W187" t="s">
+        <v>37</v>
+      </c>
+      <c r="X187" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI187" s="1">
         <v>46210.357662037037</v>
+      </c>
+    </row>
+    <row r="188" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>9532</v>
+      </c>
+      <c r="B188" t="s">
+        <v>71</v>
+      </c>
+      <c r="C188">
+        <v>350114731838</v>
+      </c>
+      <c r="D188" t="s">
+        <v>40</v>
+      </c>
+      <c r="E188">
+        <v>441146.84</v>
+      </c>
+      <c r="F188">
+        <v>6851702.2800000003</v>
+      </c>
+      <c r="G188">
+        <v>-1223.68</v>
+      </c>
+      <c r="H188">
+        <v>2179.89</v>
+      </c>
+      <c r="K188">
+        <v>-1223.68</v>
+      </c>
+      <c r="O188" t="s">
+        <v>39</v>
+      </c>
+      <c r="U188" t="b">
+        <v>1</v>
+      </c>
+      <c r="V188" t="b">
+        <v>1</v>
+      </c>
+      <c r="W188" t="s">
+        <v>37</v>
+      </c>
+      <c r="X188" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI188" s="1">
+        <v>46210.446562500001</v>
+      </c>
+    </row>
+    <row r="189" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>9533</v>
+      </c>
+      <c r="B189" t="s">
+        <v>71</v>
+      </c>
+      <c r="C189">
+        <v>350114731838</v>
+      </c>
+      <c r="D189" t="s">
+        <v>40</v>
+      </c>
+      <c r="E189">
+        <v>441248.13</v>
+      </c>
+      <c r="F189">
+        <v>6851796.4699999997</v>
+      </c>
+      <c r="G189">
+        <v>-1224.25</v>
+      </c>
+      <c r="H189">
+        <v>2318.27</v>
+      </c>
+      <c r="K189">
+        <v>-1224.25</v>
+      </c>
+      <c r="O189" t="s">
+        <v>39</v>
+      </c>
+      <c r="U189" t="b">
+        <v>1</v>
+      </c>
+      <c r="V189" t="b">
+        <v>1</v>
+      </c>
+      <c r="W189" t="s">
+        <v>37</v>
+      </c>
+      <c r="X189" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI189" s="1">
+        <v>46210.446620370371</v>
+      </c>
+    </row>
+    <row r="190" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>9566</v>
+      </c>
+      <c r="B190" t="s">
+        <v>71</v>
+      </c>
+      <c r="C190">
+        <v>350114731838</v>
+      </c>
+      <c r="D190" t="s">
+        <v>40</v>
+      </c>
+      <c r="E190">
+        <v>441309.3</v>
+      </c>
+      <c r="F190">
+        <v>6851852.8600000003</v>
+      </c>
+      <c r="G190">
+        <v>-1225.5899999999999</v>
+      </c>
+      <c r="H190">
+        <v>2401.5</v>
+      </c>
+      <c r="K190">
+        <v>-1225.5899999999999</v>
+      </c>
+      <c r="O190" t="s">
+        <v>39</v>
+      </c>
+      <c r="U190" t="b">
+        <v>1</v>
+      </c>
+      <c r="V190" t="b">
+        <v>1</v>
+      </c>
+      <c r="W190" t="s">
+        <v>37</v>
+      </c>
+      <c r="X190" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI190" s="1">
+        <v>46210.587592592594</v>
+      </c>
+    </row>
+    <row r="191" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>9567</v>
+      </c>
+      <c r="B191" t="s">
+        <v>71</v>
+      </c>
+      <c r="C191">
+        <v>350114731838</v>
+      </c>
+      <c r="D191" t="s">
+        <v>40</v>
+      </c>
+      <c r="E191">
+        <v>441596.14</v>
+      </c>
+      <c r="F191">
+        <v>6852149.1500000004</v>
+      </c>
+      <c r="G191">
+        <v>-1222.94</v>
+      </c>
+      <c r="H191">
+        <v>2814.73</v>
+      </c>
+      <c r="K191">
+        <v>-1222.94</v>
+      </c>
+      <c r="O191" t="s">
+        <v>39</v>
+      </c>
+      <c r="U191" t="b">
+        <v>1</v>
+      </c>
+      <c r="V191" t="b">
+        <v>1</v>
+      </c>
+      <c r="W191" t="s">
+        <v>37</v>
+      </c>
+      <c r="X191" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI191" s="1">
+        <v>46210.587627314817</v>
       </c>
     </row>
   </sheetData>
@@ -10119,18 +10388,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c4de8975-a9e2-4032-8275-674640ba9e13" xsi:nil="true"/>
-    <Notes xmlns="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F058933DE679D84C844BCD5E6FE280F8" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7c3559ca4b0718cc0d1b32599faf4d2a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd" xmlns:ns3="416a3325-149f-4ed5-ad81-b499dd2029e2" xmlns:ns4="c4de8975-a9e2-4032-8275-674640ba9e13" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2290b9febe09ca40959ebaa4289d445c" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd"/>
@@ -10398,6 +10655,18 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c4de8975-a9e2-4032-8275-674640ba9e13" xsi:nil="true"/>
+    <Notes xmlns="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -10408,17 +10677,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1FB06A0-65DD-411D-8E4B-3E9354C1DCE0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c4de8975-a9e2-4032-8275-674640ba9e13"/>
-    <ds:schemaRef ds:uri="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C455A20A-045D-41D5-AA3F-22BD10EAC1B5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10438,6 +10696,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1FB06A0-65DD-411D-8E4B-3E9354C1DCE0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c4de8975-a9e2-4032-8275-674640ba9e13"/>
+    <ds:schemaRef ds:uri="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37A1D12C-989B-423F-BA14-C3F31107F7DB}">
   <ds:schemaRefs>

--- a/Mck_Murta.xlsx
+++ b/Mck_Murta.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://santos.sharepoint.com/sites/Dev-CoopOil/Shared Documents/Limestone Creek (Area)/McKinlay/Horizontal Well Sample Description Spreadsheets/Well Tops/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_59B50741D280066C621D9BC3C55C92FFBC81284F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAE3EAE8-0775-4A7E-936D-E1A2A781C105}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="11_59B50741D280066C621D9BC3C55C92FFBC81284F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A04755A-F5E8-4374-9371-DF2D58EFA037}"/>
   <bookViews>
-    <workbookView xWindow="19185" yWindow="3960" windowWidth="26850" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3495" yWindow="2355" windowWidth="26850" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AI$183</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AI$191</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="122">
   <si>
     <t>Well identifier (Well name)</t>
   </si>
@@ -261,6 +261,150 @@
   </si>
   <si>
     <t>JENA 31 OPS</t>
+  </si>
+  <si>
+    <t>MCKINLAY 10</t>
+  </si>
+  <si>
+    <t>SURFICIAL DEPOSITS</t>
+  </si>
+  <si>
+    <t>SOURCE: Daily Drilling Report. OK'd by Graca</t>
+  </si>
+  <si>
+    <t>ORLRI</t>
+  </si>
+  <si>
+    <t>EYRE FORMATION</t>
+  </si>
+  <si>
+    <t>picked from CBL PDF,  marked change in GR behaviour from interpreted interbeded fine and coarse grained clastics to stacked sands typical of the Eyre Formation, correlates with neighbouring wells.  OK'd by Graca. Using Gr-SBT log curve.</t>
+  </si>
+  <si>
+    <t>WINTON FORMATION</t>
+  </si>
+  <si>
+    <t>picked from PDF, lazy transition in GR baseline from Eyre to Winton between 448ft-456ftMD, best guess its 454ft, correlates well with neighbouring wells  OK'd by Graca. Using Gr-SBT log curve.</t>
+  </si>
+  <si>
+    <t>MACKUNDA FORMATION</t>
+  </si>
+  <si>
+    <t>Based on surrounding wells and logs. Behind surfcae casing shoe, generally defined by wells with more saline drilling mud produce deflection in SP response to the right across the Mackunda Formation. Using Gr-SBT log curve.</t>
+  </si>
+  <si>
+    <t>OODNADATTA FORMATION</t>
+  </si>
+  <si>
+    <t>Based on surrounding wells and logs (SP curve deflection to right from baseline). This pick behind SCS. Moderate quality logs correlated using the two resistivity peaks in the base MacKunda at the top of the intermediate ARC resistivity log with neighbouring wells (McKinlay 6, 9 and Gambero 1). Using Gr-SBT log curve.</t>
+  </si>
+  <si>
+    <t>COORIKIANA SANDSTONE</t>
+  </si>
+  <si>
+    <t>SP defelection to the right. Top of secondary reservoir that can contain oil. Based on surrounding wells and logs (JALBU Complex)</t>
+  </si>
+  <si>
+    <t>BULLDOG SHALE</t>
+  </si>
+  <si>
+    <t>Based on surrounding wells and logs (SP curve deflection to left from Coorikiana baseline). (JALBU Complex)</t>
+  </si>
+  <si>
+    <t>CADNA-OWIE FORMATION</t>
+  </si>
+  <si>
+    <t>Lithology pick associated with low gamma-ray pick.</t>
+  </si>
+  <si>
+    <t>Based on a typical correlation across the NM Horst.  Correlated with Gambero 1 and McKinlay 6.  Picked at the interface with the last sand at the top of Murta Fm tied in with offset well DT responses at that location. OK'd by Graca</t>
+  </si>
+  <si>
+    <t>Based on a typical correlation across the NM Horst.  Correlated with Gambero 1 and McKinlay 6.  Using the break in GR/RHOB slope. OK'd by Graca</t>
+  </si>
+  <si>
+    <t>Based on a GR/RES response from LWD</t>
+  </si>
+  <si>
+    <t>MCKINLAY 11</t>
+  </si>
+  <si>
+    <t>Sourced from the daily drilling report</t>
+  </si>
+  <si>
+    <t>Marked change in GR behaviour from interpreted interbeded fine and coarse grained clastics to stacked sands typical of the Eyre Formation, correlates with neighbouring wells.  Using Gr-SBT log curve.</t>
+  </si>
+  <si>
+    <t>Picked at a shale break at the top of a major fining upwards cycle.  Using Gr-SBT log curve.</t>
+  </si>
+  <si>
+    <t>Interpolated between M6 and M9, isopaching up from COOR horizon.  WSG has it at 1720ft, last coal logged at 1695ft. Using Gr-SBT log. Ok'd by Graca</t>
+  </si>
+  <si>
+    <t>Isopached up from COOR top interpolating between M6-M9, WSG pick @ 2170ft, seems very thick compared to other OODN on the NM Horst. Using Gr-SBT log. Ok'd by Graca</t>
+  </si>
+  <si>
+    <t>SP defelection to the right. Top of secondary reservoir that can contain oil. Based on surrounding wells and logs (JALBU Complex). Using Gr-SBT log.</t>
+  </si>
+  <si>
+    <t>Based on a typical correlation across the NM Horst.  Uncertainty in the order of 5ft. Using Gr-SBT log and Gr-LWD. Ok'd by Graca</t>
+  </si>
+  <si>
+    <t>Based on a typical correlation across the NM Horst.  Interpreted above the first small 'sand' sitting on top of the high GR response typical MURT as shown in offset wells by the DT response. Ok'd by Graca</t>
+  </si>
+  <si>
+    <t>Based on a typical correlation across the NM Horst.  Multiple intersections of the McKinlay occur along the length of the well that CANNOT be captured in dbMap.  These have been integrated using culture files to refine the depth/VAV grids.  Ok'd by Graca</t>
+  </si>
+  <si>
+    <t>MCKINLAY 12</t>
+  </si>
+  <si>
+    <t>WCR</t>
+  </si>
+  <si>
+    <t>Please note that all other shallower horizons have not been entered as to not create issues with isopach mapping for these formations. There are enough nearby vertical well penetrations for mapping purposes. Pick based on Gr-LWD log. and resistivty curves.</t>
+  </si>
+  <si>
+    <t>SP defelection to the right. Top of secondary reservoir that can contain oil. Based on surrounding wells and logs (JALBU Complex).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Based on surrounding wells and logs (SP curve deflection to left from Coorikiana baseline). (JALBU Complex). </t>
+  </si>
+  <si>
+    <t>Lithology pick associated with low gamma-ray pick. Based on Gr-LWD and resistivity curves.</t>
+  </si>
+  <si>
+    <t>Based on a typical correlation across the NM Horst. Ok'd by Graca</t>
+  </si>
+  <si>
+    <t>Picked on a GR decline with resistivity increase.  Alternative pick at 5488ftMD (1ftTVD higher). Ok'd by Graca.</t>
+  </si>
+  <si>
+    <t>MCKINLAY 13</t>
+  </si>
+  <si>
+    <t>From WCR.</t>
+  </si>
+  <si>
+    <t>Based on a typical correlation across the NM Horst. Ok'd by GRACA</t>
+  </si>
+  <si>
+    <t>Based on a typical correlation across the NM Horst. oK'D BY graca</t>
+  </si>
+  <si>
+    <t>MCKINLAY 14</t>
+  </si>
+  <si>
+    <t>wcr</t>
+  </si>
+  <si>
+    <t>MCKINLAY 15</t>
+  </si>
+  <si>
+    <t>Based on a typical correlation across the NM Horst. Correlated to McKinlay 1, 5 and 7. Ok'd by GRACA</t>
+  </si>
+  <si>
+    <t>Based on a typical correlation across the NM Horst. Correlated to McKinlay 1, 5 and 7. Ok'd by Graca</t>
   </si>
 </sst>
 </file>
@@ -579,9 +723,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI191"/>
+  <dimension ref="A1:AI295"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
     <col min="4" max="4" width="31.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10381,13 +10526,5801 @@
         <v>46210.587627314817</v>
       </c>
     </row>
+    <row r="192" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>344</v>
+      </c>
+      <c r="B192" t="s">
+        <v>74</v>
+      </c>
+      <c r="C192">
+        <v>25655223</v>
+      </c>
+      <c r="D192" t="s">
+        <v>75</v>
+      </c>
+      <c r="E192">
+        <v>450456.1</v>
+      </c>
+      <c r="F192">
+        <v>6849523.6100000003</v>
+      </c>
+      <c r="G192">
+        <v>45.42</v>
+      </c>
+      <c r="H192">
+        <v>7.16</v>
+      </c>
+      <c r="K192">
+        <v>45.42</v>
+      </c>
+      <c r="O192" t="s">
+        <v>36</v>
+      </c>
+      <c r="P192">
+        <v>1</v>
+      </c>
+      <c r="U192" t="b">
+        <v>1</v>
+      </c>
+      <c r="V192" t="b">
+        <v>1</v>
+      </c>
+      <c r="W192" t="s">
+        <v>37</v>
+      </c>
+      <c r="X192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC192" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD192">
+        <v>2</v>
+      </c>
+      <c r="AE192" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF192" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI192" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="193" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>2264</v>
+      </c>
+      <c r="B193" t="s">
+        <v>74</v>
+      </c>
+      <c r="C193">
+        <v>25655223</v>
+      </c>
+      <c r="D193" t="s">
+        <v>78</v>
+      </c>
+      <c r="E193">
+        <v>450456.31</v>
+      </c>
+      <c r="F193">
+        <v>6849523.21</v>
+      </c>
+      <c r="G193">
+        <v>-27.89</v>
+      </c>
+      <c r="H193">
+        <v>80.47</v>
+      </c>
+      <c r="K193">
+        <v>-27.89</v>
+      </c>
+      <c r="O193" t="s">
+        <v>36</v>
+      </c>
+      <c r="P193">
+        <v>1</v>
+      </c>
+      <c r="U193" t="b">
+        <v>1</v>
+      </c>
+      <c r="V193" t="b">
+        <v>1</v>
+      </c>
+      <c r="W193" t="s">
+        <v>37</v>
+      </c>
+      <c r="X193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC193" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD193">
+        <v>2</v>
+      </c>
+      <c r="AE193" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF193" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI193" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="194" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>823</v>
+      </c>
+      <c r="B194" t="s">
+        <v>74</v>
+      </c>
+      <c r="C194">
+        <v>25655223</v>
+      </c>
+      <c r="D194" t="s">
+        <v>80</v>
+      </c>
+      <c r="E194">
+        <v>450456.48</v>
+      </c>
+      <c r="F194">
+        <v>6849522.5800000001</v>
+      </c>
+      <c r="G194">
+        <v>-94.63</v>
+      </c>
+      <c r="H194">
+        <v>147.22</v>
+      </c>
+      <c r="K194">
+        <v>-94.63</v>
+      </c>
+      <c r="O194" t="s">
+        <v>36</v>
+      </c>
+      <c r="P194">
+        <v>1</v>
+      </c>
+      <c r="U194" t="b">
+        <v>1</v>
+      </c>
+      <c r="V194" t="b">
+        <v>1</v>
+      </c>
+      <c r="W194" t="s">
+        <v>37</v>
+      </c>
+      <c r="X194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC194" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD194">
+        <v>2</v>
+      </c>
+      <c r="AE194" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF194" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI194" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="195" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>3612</v>
+      </c>
+      <c r="B195" t="s">
+        <v>74</v>
+      </c>
+      <c r="C195">
+        <v>25655223</v>
+      </c>
+      <c r="D195" t="s">
+        <v>82</v>
+      </c>
+      <c r="E195">
+        <v>450456.98</v>
+      </c>
+      <c r="F195">
+        <v>6849520.8399999999</v>
+      </c>
+      <c r="G195">
+        <v>-499.7</v>
+      </c>
+      <c r="H195">
+        <v>552.29999999999995</v>
+      </c>
+      <c r="K195">
+        <v>-499.7</v>
+      </c>
+      <c r="O195" t="s">
+        <v>36</v>
+      </c>
+      <c r="P195">
+        <v>1</v>
+      </c>
+      <c r="U195" t="b">
+        <v>1</v>
+      </c>
+      <c r="V195" t="b">
+        <v>1</v>
+      </c>
+      <c r="W195" t="s">
+        <v>37</v>
+      </c>
+      <c r="X195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC195" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD195">
+        <v>3</v>
+      </c>
+      <c r="AE195" t="s">
+        <v>83</v>
+      </c>
+      <c r="AF195" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI195" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="196" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>842</v>
+      </c>
+      <c r="B196" t="s">
+        <v>74</v>
+      </c>
+      <c r="C196">
+        <v>25655223</v>
+      </c>
+      <c r="D196" t="s">
+        <v>84</v>
+      </c>
+      <c r="E196">
+        <v>450458.53</v>
+      </c>
+      <c r="F196">
+        <v>6849518.04</v>
+      </c>
+      <c r="G196">
+        <v>-646.89</v>
+      </c>
+      <c r="H196">
+        <v>699.52</v>
+      </c>
+      <c r="K196">
+        <v>-646.89</v>
+      </c>
+      <c r="O196" t="s">
+        <v>36</v>
+      </c>
+      <c r="P196">
+        <v>1</v>
+      </c>
+      <c r="U196" t="b">
+        <v>1</v>
+      </c>
+      <c r="V196" t="b">
+        <v>1</v>
+      </c>
+      <c r="W196" t="s">
+        <v>37</v>
+      </c>
+      <c r="X196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC196" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD196">
+        <v>2</v>
+      </c>
+      <c r="AE196" t="s">
+        <v>85</v>
+      </c>
+      <c r="AF196" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI196" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="197" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>1361</v>
+      </c>
+      <c r="B197" t="s">
+        <v>74</v>
+      </c>
+      <c r="C197">
+        <v>25655223</v>
+      </c>
+      <c r="D197" t="s">
+        <v>86</v>
+      </c>
+      <c r="E197">
+        <v>450433.36</v>
+      </c>
+      <c r="F197">
+        <v>6849544.0099999998</v>
+      </c>
+      <c r="G197">
+        <v>-845.61</v>
+      </c>
+      <c r="H197">
+        <v>902.51</v>
+      </c>
+      <c r="K197">
+        <v>-845.61</v>
+      </c>
+      <c r="O197" t="s">
+        <v>36</v>
+      </c>
+      <c r="P197">
+        <v>1</v>
+      </c>
+      <c r="U197" t="b">
+        <v>1</v>
+      </c>
+      <c r="V197" t="b">
+        <v>1</v>
+      </c>
+      <c r="W197" t="s">
+        <v>37</v>
+      </c>
+      <c r="X197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC197" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD197">
+        <v>1</v>
+      </c>
+      <c r="AE197" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF197" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI197" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="198" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>1688</v>
+      </c>
+      <c r="B198" t="s">
+        <v>74</v>
+      </c>
+      <c r="C198">
+        <v>25655223</v>
+      </c>
+      <c r="D198" t="s">
+        <v>88</v>
+      </c>
+      <c r="E198">
+        <v>450427.02</v>
+      </c>
+      <c r="F198">
+        <v>6849550.4000000004</v>
+      </c>
+      <c r="G198">
+        <v>-868.26</v>
+      </c>
+      <c r="H198">
+        <v>926.9</v>
+      </c>
+      <c r="K198">
+        <v>-868.26</v>
+      </c>
+      <c r="O198" t="s">
+        <v>36</v>
+      </c>
+      <c r="P198">
+        <v>1</v>
+      </c>
+      <c r="U198" t="b">
+        <v>1</v>
+      </c>
+      <c r="V198" t="b">
+        <v>1</v>
+      </c>
+      <c r="W198" t="s">
+        <v>37</v>
+      </c>
+      <c r="X198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC198" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD198">
+        <v>1</v>
+      </c>
+      <c r="AE198" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF198" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI198" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="199" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>2501</v>
+      </c>
+      <c r="B199" t="s">
+        <v>74</v>
+      </c>
+      <c r="C199">
+        <v>25655223</v>
+      </c>
+      <c r="D199" t="s">
+        <v>90</v>
+      </c>
+      <c r="E199">
+        <v>450302.88</v>
+      </c>
+      <c r="F199">
+        <v>6849667.4500000002</v>
+      </c>
+      <c r="G199">
+        <v>-1083.56</v>
+      </c>
+      <c r="H199">
+        <v>1205.48</v>
+      </c>
+      <c r="K199">
+        <v>-1083.56</v>
+      </c>
+      <c r="O199" t="s">
+        <v>36</v>
+      </c>
+      <c r="P199">
+        <v>1</v>
+      </c>
+      <c r="U199" t="b">
+        <v>1</v>
+      </c>
+      <c r="V199" t="b">
+        <v>1</v>
+      </c>
+      <c r="W199" t="s">
+        <v>37</v>
+      </c>
+      <c r="X199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC199" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD199">
+        <v>1</v>
+      </c>
+      <c r="AE199" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF199" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI199" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="200" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>230</v>
+      </c>
+      <c r="B200" t="s">
+        <v>74</v>
+      </c>
+      <c r="C200">
+        <v>25655223</v>
+      </c>
+      <c r="D200" t="s">
+        <v>35</v>
+      </c>
+      <c r="E200">
+        <v>450228.26</v>
+      </c>
+      <c r="F200">
+        <v>6849737.7699999996</v>
+      </c>
+      <c r="G200">
+        <v>-1142.8800000000001</v>
+      </c>
+      <c r="H200">
+        <v>1324.05</v>
+      </c>
+      <c r="K200">
+        <v>-1142.8800000000001</v>
+      </c>
+      <c r="O200" t="s">
+        <v>36</v>
+      </c>
+      <c r="P200">
+        <v>1</v>
+      </c>
+      <c r="U200" t="b">
+        <v>1</v>
+      </c>
+      <c r="V200" t="b">
+        <v>1</v>
+      </c>
+      <c r="W200" t="s">
+        <v>37</v>
+      </c>
+      <c r="X200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC200" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD200">
+        <v>1</v>
+      </c>
+      <c r="AE200" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF200" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI200" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="201" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>9555</v>
+      </c>
+      <c r="B201" t="s">
+        <v>74</v>
+      </c>
+      <c r="C201">
+        <v>25655223</v>
+      </c>
+      <c r="D201" t="s">
+        <v>35</v>
+      </c>
+      <c r="E201">
+        <v>449835.46</v>
+      </c>
+      <c r="F201">
+        <v>6850120.6299999999</v>
+      </c>
+      <c r="G201">
+        <v>-1190.08</v>
+      </c>
+      <c r="H201">
+        <v>1880.91</v>
+      </c>
+      <c r="K201">
+        <v>-1190.08</v>
+      </c>
+      <c r="O201" t="s">
+        <v>39</v>
+      </c>
+      <c r="U201" t="b">
+        <v>1</v>
+      </c>
+      <c r="V201" t="b">
+        <v>1</v>
+      </c>
+      <c r="W201" t="s">
+        <v>37</v>
+      </c>
+      <c r="X201" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI201" s="1">
+        <v>46272.679606481484</v>
+      </c>
+    </row>
+    <row r="202" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>9556</v>
+      </c>
+      <c r="B202" t="s">
+        <v>74</v>
+      </c>
+      <c r="C202">
+        <v>25655223</v>
+      </c>
+      <c r="D202" t="s">
+        <v>35</v>
+      </c>
+      <c r="E202">
+        <v>449746.18</v>
+      </c>
+      <c r="F202">
+        <v>6850201.9699999997</v>
+      </c>
+      <c r="G202">
+        <v>-1194.02</v>
+      </c>
+      <c r="H202">
+        <v>2001.78</v>
+      </c>
+      <c r="K202">
+        <v>-1194.02</v>
+      </c>
+      <c r="O202" t="s">
+        <v>39</v>
+      </c>
+      <c r="U202" t="b">
+        <v>1</v>
+      </c>
+      <c r="V202" t="b">
+        <v>1</v>
+      </c>
+      <c r="W202" t="s">
+        <v>37</v>
+      </c>
+      <c r="X202" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI202" s="1">
+        <v>46272.6796412037</v>
+      </c>
+    </row>
+    <row r="203" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>2909</v>
+      </c>
+      <c r="B203" t="s">
+        <v>74</v>
+      </c>
+      <c r="C203">
+        <v>25655223</v>
+      </c>
+      <c r="D203" t="s">
+        <v>40</v>
+      </c>
+      <c r="E203">
+        <v>450053.73</v>
+      </c>
+      <c r="F203">
+        <v>6849915.9400000004</v>
+      </c>
+      <c r="G203">
+        <v>-1192.56</v>
+      </c>
+      <c r="H203">
+        <v>1581.45</v>
+      </c>
+      <c r="K203">
+        <v>-1192.56</v>
+      </c>
+      <c r="O203" t="s">
+        <v>36</v>
+      </c>
+      <c r="P203">
+        <v>1</v>
+      </c>
+      <c r="U203" t="b">
+        <v>1</v>
+      </c>
+      <c r="V203" t="b">
+        <v>1</v>
+      </c>
+      <c r="W203" t="s">
+        <v>37</v>
+      </c>
+      <c r="X203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC203" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD203">
+        <v>1</v>
+      </c>
+      <c r="AE203" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF203" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI203" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="204" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>3119</v>
+      </c>
+      <c r="B204" t="s">
+        <v>74</v>
+      </c>
+      <c r="C204">
+        <v>25655223</v>
+      </c>
+      <c r="D204" t="s">
+        <v>40</v>
+      </c>
+      <c r="E204">
+        <v>449835</v>
+      </c>
+      <c r="F204">
+        <v>6850121.04</v>
+      </c>
+      <c r="G204">
+        <v>-1190.0899999999999</v>
+      </c>
+      <c r="H204">
+        <v>1881.53</v>
+      </c>
+      <c r="K204">
+        <v>-1190.0899999999999</v>
+      </c>
+      <c r="O204" t="s">
+        <v>36</v>
+      </c>
+      <c r="P204">
+        <v>2</v>
+      </c>
+      <c r="U204" t="b">
+        <v>1</v>
+      </c>
+      <c r="V204" t="b">
+        <v>1</v>
+      </c>
+      <c r="W204" t="s">
+        <v>37</v>
+      </c>
+      <c r="X204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC204" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD204">
+        <v>1</v>
+      </c>
+      <c r="AE204" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF204" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI204" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="205" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>3059</v>
+      </c>
+      <c r="B205" t="s">
+        <v>74</v>
+      </c>
+      <c r="C205">
+        <v>25655223</v>
+      </c>
+      <c r="D205" t="s">
+        <v>40</v>
+      </c>
+      <c r="E205">
+        <v>449812.29</v>
+      </c>
+      <c r="F205">
+        <v>6850140.8899999997</v>
+      </c>
+      <c r="G205">
+        <v>-1191.08</v>
+      </c>
+      <c r="H205">
+        <v>1911.71</v>
+      </c>
+      <c r="K205">
+        <v>-1191.08</v>
+      </c>
+      <c r="O205" t="s">
+        <v>36</v>
+      </c>
+      <c r="P205">
+        <v>3</v>
+      </c>
+      <c r="U205" t="b">
+        <v>1</v>
+      </c>
+      <c r="V205" t="b">
+        <v>1</v>
+      </c>
+      <c r="W205" t="s">
+        <v>37</v>
+      </c>
+      <c r="X205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC205" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD205">
+        <v>1</v>
+      </c>
+      <c r="AE205" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF205" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI205" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="206" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>3066</v>
+      </c>
+      <c r="B206" t="s">
+        <v>74</v>
+      </c>
+      <c r="C206">
+        <v>25655223</v>
+      </c>
+      <c r="D206" t="s">
+        <v>40</v>
+      </c>
+      <c r="E206">
+        <v>449745.2</v>
+      </c>
+      <c r="F206">
+        <v>6850202.9100000001</v>
+      </c>
+      <c r="G206">
+        <v>-1194.04</v>
+      </c>
+      <c r="H206">
+        <v>2003.15</v>
+      </c>
+      <c r="K206">
+        <v>-1194.04</v>
+      </c>
+      <c r="O206" t="s">
+        <v>36</v>
+      </c>
+      <c r="P206">
+        <v>4</v>
+      </c>
+      <c r="U206" t="b">
+        <v>1</v>
+      </c>
+      <c r="V206" t="b">
+        <v>1</v>
+      </c>
+      <c r="W206" t="s">
+        <v>37</v>
+      </c>
+      <c r="X206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC206" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD206">
+        <v>1</v>
+      </c>
+      <c r="AE206" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF206" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI206" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="207" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>2808</v>
+      </c>
+      <c r="B207" t="s">
+        <v>74</v>
+      </c>
+      <c r="C207">
+        <v>25655223</v>
+      </c>
+      <c r="D207" t="s">
+        <v>40</v>
+      </c>
+      <c r="E207">
+        <v>449736.49</v>
+      </c>
+      <c r="F207">
+        <v>6850211.4400000004</v>
+      </c>
+      <c r="G207">
+        <v>-1194.1600000000001</v>
+      </c>
+      <c r="H207">
+        <v>2015.34</v>
+      </c>
+      <c r="K207">
+        <v>-1194.1600000000001</v>
+      </c>
+      <c r="O207" t="s">
+        <v>36</v>
+      </c>
+      <c r="P207">
+        <v>5</v>
+      </c>
+      <c r="U207" t="b">
+        <v>1</v>
+      </c>
+      <c r="V207" t="b">
+        <v>1</v>
+      </c>
+      <c r="W207" t="s">
+        <v>37</v>
+      </c>
+      <c r="X207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC207" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD207">
+        <v>1</v>
+      </c>
+      <c r="AE207" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF207" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI207" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="208" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>433</v>
+      </c>
+      <c r="B208" t="s">
+        <v>95</v>
+      </c>
+      <c r="C208">
+        <v>25655225</v>
+      </c>
+      <c r="D208" t="s">
+        <v>75</v>
+      </c>
+      <c r="E208">
+        <v>448865.15</v>
+      </c>
+      <c r="F208">
+        <v>6849222</v>
+      </c>
+      <c r="G208">
+        <v>38.36</v>
+      </c>
+      <c r="H208">
+        <v>7.16</v>
+      </c>
+      <c r="K208">
+        <v>38.36</v>
+      </c>
+      <c r="O208" t="s">
+        <v>36</v>
+      </c>
+      <c r="P208">
+        <v>1</v>
+      </c>
+      <c r="U208" t="b">
+        <v>1</v>
+      </c>
+      <c r="V208" t="b">
+        <v>1</v>
+      </c>
+      <c r="W208" t="s">
+        <v>37</v>
+      </c>
+      <c r="X208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC208" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD208">
+        <v>2</v>
+      </c>
+      <c r="AE208" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="209" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>2265</v>
+      </c>
+      <c r="B209" t="s">
+        <v>95</v>
+      </c>
+      <c r="C209">
+        <v>25655225</v>
+      </c>
+      <c r="D209" t="s">
+        <v>78</v>
+      </c>
+      <c r="E209">
+        <v>448864.94</v>
+      </c>
+      <c r="F209">
+        <v>6849222.1299999999</v>
+      </c>
+      <c r="G209">
+        <v>-34.950000000000003</v>
+      </c>
+      <c r="H209">
+        <v>80.47</v>
+      </c>
+      <c r="K209">
+        <v>-34.950000000000003</v>
+      </c>
+      <c r="O209" t="s">
+        <v>36</v>
+      </c>
+      <c r="P209">
+        <v>1</v>
+      </c>
+      <c r="U209" t="b">
+        <v>1</v>
+      </c>
+      <c r="V209" t="b">
+        <v>1</v>
+      </c>
+      <c r="W209" t="s">
+        <v>37</v>
+      </c>
+      <c r="X209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC209" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD209">
+        <v>2</v>
+      </c>
+      <c r="AE209" t="s">
+        <v>97</v>
+      </c>
+      <c r="AF209" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI209" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="210" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>784</v>
+      </c>
+      <c r="B210" t="s">
+        <v>95</v>
+      </c>
+      <c r="C210">
+        <v>25655225</v>
+      </c>
+      <c r="D210" t="s">
+        <v>80</v>
+      </c>
+      <c r="E210">
+        <v>448863.66</v>
+      </c>
+      <c r="F210">
+        <v>6849221.5499999998</v>
+      </c>
+      <c r="G210">
+        <v>-101.68</v>
+      </c>
+      <c r="H210">
+        <v>147.22</v>
+      </c>
+      <c r="K210">
+        <v>-101.68</v>
+      </c>
+      <c r="O210" t="s">
+        <v>36</v>
+      </c>
+      <c r="P210">
+        <v>1</v>
+      </c>
+      <c r="U210" t="b">
+        <v>1</v>
+      </c>
+      <c r="V210" t="b">
+        <v>1</v>
+      </c>
+      <c r="W210" t="s">
+        <v>37</v>
+      </c>
+      <c r="X210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC210" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD210">
+        <v>2</v>
+      </c>
+      <c r="AE210" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF210" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI210" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="211" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>3460</v>
+      </c>
+      <c r="B211" t="s">
+        <v>95</v>
+      </c>
+      <c r="C211">
+        <v>25655225</v>
+      </c>
+      <c r="D211" t="s">
+        <v>82</v>
+      </c>
+      <c r="E211">
+        <v>448826.21</v>
+      </c>
+      <c r="F211">
+        <v>6849184.3499999996</v>
+      </c>
+      <c r="G211">
+        <v>-506.67</v>
+      </c>
+      <c r="H211">
+        <v>555.96</v>
+      </c>
+      <c r="K211">
+        <v>-506.67</v>
+      </c>
+      <c r="O211" t="s">
+        <v>36</v>
+      </c>
+      <c r="P211">
+        <v>1</v>
+      </c>
+      <c r="U211" t="b">
+        <v>1</v>
+      </c>
+      <c r="V211" t="b">
+        <v>1</v>
+      </c>
+      <c r="W211" t="s">
+        <v>37</v>
+      </c>
+      <c r="X211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC211" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD211">
+        <v>2</v>
+      </c>
+      <c r="AE211" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF211" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI211" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="212" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>1000</v>
+      </c>
+      <c r="B212" t="s">
+        <v>95</v>
+      </c>
+      <c r="C212">
+        <v>25655225</v>
+      </c>
+      <c r="D212" t="s">
+        <v>84</v>
+      </c>
+      <c r="E212">
+        <v>448828.18</v>
+      </c>
+      <c r="F212">
+        <v>6849181.5599999996</v>
+      </c>
+      <c r="G212">
+        <v>-650.07000000000005</v>
+      </c>
+      <c r="H212">
+        <v>699.52</v>
+      </c>
+      <c r="K212">
+        <v>-650.07000000000005</v>
+      </c>
+      <c r="O212" t="s">
+        <v>36</v>
+      </c>
+      <c r="P212">
+        <v>1</v>
+      </c>
+      <c r="U212" t="b">
+        <v>1</v>
+      </c>
+      <c r="V212" t="b">
+        <v>1</v>
+      </c>
+      <c r="W212" t="s">
+        <v>37</v>
+      </c>
+      <c r="X212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC212" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD212">
+        <v>2</v>
+      </c>
+      <c r="AE212" t="s">
+        <v>100</v>
+      </c>
+      <c r="AF212" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI212" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="213" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>1261</v>
+      </c>
+      <c r="B213" t="s">
+        <v>95</v>
+      </c>
+      <c r="C213">
+        <v>25655225</v>
+      </c>
+      <c r="D213" t="s">
+        <v>86</v>
+      </c>
+      <c r="E213">
+        <v>448865.72</v>
+      </c>
+      <c r="F213">
+        <v>6849221.21</v>
+      </c>
+      <c r="G213">
+        <v>-858.64</v>
+      </c>
+      <c r="H213">
+        <v>916.23</v>
+      </c>
+      <c r="K213">
+        <v>-858.64</v>
+      </c>
+      <c r="O213" t="s">
+        <v>36</v>
+      </c>
+      <c r="P213">
+        <v>1</v>
+      </c>
+      <c r="U213" t="b">
+        <v>1</v>
+      </c>
+      <c r="V213" t="b">
+        <v>1</v>
+      </c>
+      <c r="W213" t="s">
+        <v>37</v>
+      </c>
+      <c r="X213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC213" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD213">
+        <v>1</v>
+      </c>
+      <c r="AE213" t="s">
+        <v>101</v>
+      </c>
+      <c r="AF213" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI213" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="214" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>1699</v>
+      </c>
+      <c r="B214" t="s">
+        <v>95</v>
+      </c>
+      <c r="C214">
+        <v>25655225</v>
+      </c>
+      <c r="D214" t="s">
+        <v>88</v>
+      </c>
+      <c r="E214">
+        <v>448872.04</v>
+      </c>
+      <c r="F214">
+        <v>6849228.2800000003</v>
+      </c>
+      <c r="G214">
+        <v>-877.74</v>
+      </c>
+      <c r="H214">
+        <v>937.56</v>
+      </c>
+      <c r="K214">
+        <v>-877.74</v>
+      </c>
+      <c r="O214" t="s">
+        <v>36</v>
+      </c>
+      <c r="P214">
+        <v>1</v>
+      </c>
+      <c r="U214" t="b">
+        <v>1</v>
+      </c>
+      <c r="V214" t="b">
+        <v>1</v>
+      </c>
+      <c r="W214" t="s">
+        <v>37</v>
+      </c>
+      <c r="X214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC214" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD214">
+        <v>2</v>
+      </c>
+      <c r="AE214" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF214" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI214" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="215" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>2560</v>
+      </c>
+      <c r="B215" t="s">
+        <v>95</v>
+      </c>
+      <c r="C215">
+        <v>25655225</v>
+      </c>
+      <c r="D215" t="s">
+        <v>90</v>
+      </c>
+      <c r="E215">
+        <v>449017.94</v>
+      </c>
+      <c r="F215">
+        <v>6849376.1299999999</v>
+      </c>
+      <c r="G215">
+        <v>-1090.31</v>
+      </c>
+      <c r="H215">
+        <v>1239.6199999999999</v>
+      </c>
+      <c r="K215">
+        <v>-1090.31</v>
+      </c>
+      <c r="O215" t="s">
+        <v>36</v>
+      </c>
+      <c r="P215">
+        <v>1</v>
+      </c>
+      <c r="U215" t="b">
+        <v>1</v>
+      </c>
+      <c r="V215" t="b">
+        <v>1</v>
+      </c>
+      <c r="W215" t="s">
+        <v>37</v>
+      </c>
+      <c r="X215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC215" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD215">
+        <v>1</v>
+      </c>
+      <c r="AE215" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF215" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI215" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="216" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>306</v>
+      </c>
+      <c r="B216" t="s">
+        <v>95</v>
+      </c>
+      <c r="C216">
+        <v>25655225</v>
+      </c>
+      <c r="D216" t="s">
+        <v>35</v>
+      </c>
+      <c r="E216">
+        <v>449104.9</v>
+      </c>
+      <c r="F216">
+        <v>6849460.8399999999</v>
+      </c>
+      <c r="G216">
+        <v>-1148.25</v>
+      </c>
+      <c r="H216">
+        <v>1374.34</v>
+      </c>
+      <c r="K216">
+        <v>-1148.25</v>
+      </c>
+      <c r="O216" t="s">
+        <v>36</v>
+      </c>
+      <c r="P216">
+        <v>1</v>
+      </c>
+      <c r="U216" t="b">
+        <v>1</v>
+      </c>
+      <c r="V216" t="b">
+        <v>1</v>
+      </c>
+      <c r="W216" t="s">
+        <v>37</v>
+      </c>
+      <c r="X216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC216" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD216">
+        <v>1</v>
+      </c>
+      <c r="AE216" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF216" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI216" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="217" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>9553</v>
+      </c>
+      <c r="B217" t="s">
+        <v>95</v>
+      </c>
+      <c r="C217">
+        <v>25655225</v>
+      </c>
+      <c r="D217" t="s">
+        <v>35</v>
+      </c>
+      <c r="E217">
+        <v>449452.6</v>
+      </c>
+      <c r="F217">
+        <v>6849813.0999999996</v>
+      </c>
+      <c r="G217">
+        <v>-1194.8599999999999</v>
+      </c>
+      <c r="H217">
+        <v>1875.35</v>
+      </c>
+      <c r="K217">
+        <v>-1194.8599999999999</v>
+      </c>
+      <c r="O217" t="s">
+        <v>39</v>
+      </c>
+      <c r="U217" t="b">
+        <v>1</v>
+      </c>
+      <c r="V217" t="b">
+        <v>1</v>
+      </c>
+      <c r="W217" t="s">
+        <v>37</v>
+      </c>
+      <c r="X217" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI217" s="1">
+        <v>46272.679537037038</v>
+      </c>
+    </row>
+    <row r="218" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>9554</v>
+      </c>
+      <c r="B218" t="s">
+        <v>95</v>
+      </c>
+      <c r="C218">
+        <v>25655225</v>
+      </c>
+      <c r="D218" t="s">
+        <v>35</v>
+      </c>
+      <c r="E218">
+        <v>449522.88</v>
+      </c>
+      <c r="F218">
+        <v>6849886.8399999999</v>
+      </c>
+      <c r="G218">
+        <v>-1191.19</v>
+      </c>
+      <c r="H218">
+        <v>1977.29</v>
+      </c>
+      <c r="K218">
+        <v>-1191.19</v>
+      </c>
+      <c r="O218" t="s">
+        <v>39</v>
+      </c>
+      <c r="U218" t="b">
+        <v>1</v>
+      </c>
+      <c r="V218" t="b">
+        <v>1</v>
+      </c>
+      <c r="W218" t="s">
+        <v>37</v>
+      </c>
+      <c r="X218" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI218" s="1">
+        <v>46272.679571759261</v>
+      </c>
+    </row>
+    <row r="219" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>3030</v>
+      </c>
+      <c r="B219" t="s">
+        <v>95</v>
+      </c>
+      <c r="C219">
+        <v>25655225</v>
+      </c>
+      <c r="D219" t="s">
+        <v>40</v>
+      </c>
+      <c r="E219">
+        <v>449262.59</v>
+      </c>
+      <c r="F219">
+        <v>6849618.4199999999</v>
+      </c>
+      <c r="G219">
+        <v>-1196.1099999999999</v>
+      </c>
+      <c r="H219">
+        <v>1603.25</v>
+      </c>
+      <c r="K219">
+        <v>-1196.1099999999999</v>
+      </c>
+      <c r="O219" t="s">
+        <v>36</v>
+      </c>
+      <c r="P219">
+        <v>1</v>
+      </c>
+      <c r="U219" t="b">
+        <v>1</v>
+      </c>
+      <c r="V219" t="b">
+        <v>1</v>
+      </c>
+      <c r="W219" t="s">
+        <v>37</v>
+      </c>
+      <c r="X219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC219" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD219">
+        <v>1</v>
+      </c>
+      <c r="AE219" t="s">
+        <v>104</v>
+      </c>
+      <c r="AF219" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI219" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="220" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>9528</v>
+      </c>
+      <c r="B220" t="s">
+        <v>95</v>
+      </c>
+      <c r="C220">
+        <v>25655225</v>
+      </c>
+      <c r="D220" t="s">
+        <v>40</v>
+      </c>
+      <c r="E220">
+        <v>449453.62</v>
+      </c>
+      <c r="F220">
+        <v>6849814.1500000004</v>
+      </c>
+      <c r="G220">
+        <v>-1194.82</v>
+      </c>
+      <c r="H220">
+        <v>1876.81</v>
+      </c>
+      <c r="K220">
+        <v>-1194.82</v>
+      </c>
+      <c r="O220" t="s">
+        <v>39</v>
+      </c>
+      <c r="U220" t="b">
+        <v>1</v>
+      </c>
+      <c r="V220" t="b">
+        <v>1</v>
+      </c>
+      <c r="W220" t="s">
+        <v>37</v>
+      </c>
+      <c r="X220" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI220" s="1">
+        <v>46272.677974537037</v>
+      </c>
+    </row>
+    <row r="221" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>9529</v>
+      </c>
+      <c r="B221" t="s">
+        <v>95</v>
+      </c>
+      <c r="C221">
+        <v>25655225</v>
+      </c>
+      <c r="D221" t="s">
+        <v>40</v>
+      </c>
+      <c r="E221">
+        <v>449490.88</v>
+      </c>
+      <c r="F221">
+        <v>6849853.0300000003</v>
+      </c>
+      <c r="G221">
+        <v>-1193.1300000000001</v>
+      </c>
+      <c r="H221">
+        <v>1930.69</v>
+      </c>
+      <c r="K221">
+        <v>-1193.1300000000001</v>
+      </c>
+      <c r="O221" t="s">
+        <v>39</v>
+      </c>
+      <c r="U221" t="b">
+        <v>1</v>
+      </c>
+      <c r="V221" t="b">
+        <v>1</v>
+      </c>
+      <c r="W221" t="s">
+        <v>37</v>
+      </c>
+      <c r="X221" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI221" s="1">
+        <v>46272.677997685183</v>
+      </c>
+    </row>
+    <row r="222" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>2977</v>
+      </c>
+      <c r="B222" t="s">
+        <v>95</v>
+      </c>
+      <c r="C222">
+        <v>25655225</v>
+      </c>
+      <c r="D222" t="s">
+        <v>40</v>
+      </c>
+      <c r="E222">
+        <v>449523.9</v>
+      </c>
+      <c r="F222">
+        <v>6849887.9100000001</v>
+      </c>
+      <c r="G222">
+        <v>-1191.1300000000001</v>
+      </c>
+      <c r="H222">
+        <v>1978.76</v>
+      </c>
+      <c r="K222">
+        <v>-1191.1300000000001</v>
+      </c>
+      <c r="O222" t="s">
+        <v>36</v>
+      </c>
+      <c r="P222">
+        <v>2</v>
+      </c>
+      <c r="U222" t="b">
+        <v>1</v>
+      </c>
+      <c r="V222" t="b">
+        <v>1</v>
+      </c>
+      <c r="W222" t="s">
+        <v>37</v>
+      </c>
+      <c r="X222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC222" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD222">
+        <v>1</v>
+      </c>
+      <c r="AE222" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF222" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI222" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="223" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>2876</v>
+      </c>
+      <c r="B223" t="s">
+        <v>95</v>
+      </c>
+      <c r="C223">
+        <v>25655225</v>
+      </c>
+      <c r="D223" t="s">
+        <v>40</v>
+      </c>
+      <c r="E223">
+        <v>449557.91</v>
+      </c>
+      <c r="F223">
+        <v>6849924.0999999996</v>
+      </c>
+      <c r="G223">
+        <v>-1191.19</v>
+      </c>
+      <c r="H223">
+        <v>2028.44</v>
+      </c>
+      <c r="K223">
+        <v>-1191.19</v>
+      </c>
+      <c r="O223" t="s">
+        <v>36</v>
+      </c>
+      <c r="P223">
+        <v>3</v>
+      </c>
+      <c r="U223" t="b">
+        <v>1</v>
+      </c>
+      <c r="V223" t="b">
+        <v>1</v>
+      </c>
+      <c r="W223" t="s">
+        <v>37</v>
+      </c>
+      <c r="X223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC223" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD223">
+        <v>1</v>
+      </c>
+      <c r="AE223" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF223" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI223" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="224" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>473</v>
+      </c>
+      <c r="B224" t="s">
+        <v>105</v>
+      </c>
+      <c r="C224">
+        <v>36386254</v>
+      </c>
+      <c r="D224" t="s">
+        <v>75</v>
+      </c>
+      <c r="E224">
+        <v>450941.89</v>
+      </c>
+      <c r="F224">
+        <v>6851190.5599999996</v>
+      </c>
+      <c r="G224">
+        <v>45.46</v>
+      </c>
+      <c r="H224">
+        <v>7.16</v>
+      </c>
+      <c r="K224">
+        <v>45.46</v>
+      </c>
+      <c r="O224" t="s">
+        <v>36</v>
+      </c>
+      <c r="P224">
+        <v>1</v>
+      </c>
+      <c r="U224" t="b">
+        <v>1</v>
+      </c>
+      <c r="V224" t="b">
+        <v>1</v>
+      </c>
+      <c r="W224" t="s">
+        <v>37</v>
+      </c>
+      <c r="X224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC224" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD224">
+        <v>2</v>
+      </c>
+      <c r="AE224" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF224" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI224" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="225" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>1138</v>
+      </c>
+      <c r="B225" t="s">
+        <v>105</v>
+      </c>
+      <c r="C225">
+        <v>36386254</v>
+      </c>
+      <c r="D225" t="s">
+        <v>84</v>
+      </c>
+      <c r="E225">
+        <v>450946.81</v>
+      </c>
+      <c r="F225">
+        <v>6851187.9299999997</v>
+      </c>
+      <c r="G225">
+        <v>-634.66999999999996</v>
+      </c>
+      <c r="H225">
+        <v>687.32</v>
+      </c>
+      <c r="K225">
+        <v>-634.66999999999996</v>
+      </c>
+      <c r="O225" t="s">
+        <v>36</v>
+      </c>
+      <c r="P225">
+        <v>1</v>
+      </c>
+      <c r="U225" t="b">
+        <v>1</v>
+      </c>
+      <c r="V225" t="b">
+        <v>1</v>
+      </c>
+      <c r="W225" t="s">
+        <v>37</v>
+      </c>
+      <c r="X225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC225" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD225">
+        <v>1</v>
+      </c>
+      <c r="AE225" t="s">
+        <v>107</v>
+      </c>
+      <c r="AF225" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI225" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="226" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>1232</v>
+      </c>
+      <c r="B226" t="s">
+        <v>105</v>
+      </c>
+      <c r="C226">
+        <v>36386254</v>
+      </c>
+      <c r="D226" t="s">
+        <v>86</v>
+      </c>
+      <c r="E226">
+        <v>450897.03</v>
+      </c>
+      <c r="F226">
+        <v>6851172.5499999998</v>
+      </c>
+      <c r="G226">
+        <v>-852</v>
+      </c>
+      <c r="H226">
+        <v>912.88</v>
+      </c>
+      <c r="K226">
+        <v>-852</v>
+      </c>
+      <c r="O226" t="s">
+        <v>36</v>
+      </c>
+      <c r="P226">
+        <v>1</v>
+      </c>
+      <c r="U226" t="b">
+        <v>1</v>
+      </c>
+      <c r="V226" t="b">
+        <v>1</v>
+      </c>
+      <c r="W226" t="s">
+        <v>37</v>
+      </c>
+      <c r="X226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC226" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD226">
+        <v>1</v>
+      </c>
+      <c r="AE226" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF226" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI226" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="227" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>1626</v>
+      </c>
+      <c r="B227" t="s">
+        <v>105</v>
+      </c>
+      <c r="C227">
+        <v>36386254</v>
+      </c>
+      <c r="D227" t="s">
+        <v>88</v>
+      </c>
+      <c r="E227">
+        <v>450885.14</v>
+      </c>
+      <c r="F227">
+        <v>6851171.21</v>
+      </c>
+      <c r="G227">
+        <v>-876</v>
+      </c>
+      <c r="H227">
+        <v>939.7</v>
+      </c>
+      <c r="K227">
+        <v>-876</v>
+      </c>
+      <c r="O227" t="s">
+        <v>36</v>
+      </c>
+      <c r="P227">
+        <v>1</v>
+      </c>
+      <c r="U227" t="b">
+        <v>1</v>
+      </c>
+      <c r="V227" t="b">
+        <v>1</v>
+      </c>
+      <c r="W227" t="s">
+        <v>37</v>
+      </c>
+      <c r="X227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC227" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD227">
+        <v>1</v>
+      </c>
+      <c r="AE227" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="228" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>2297</v>
+      </c>
+      <c r="B228" t="s">
+        <v>105</v>
+      </c>
+      <c r="C228">
+        <v>36386254</v>
+      </c>
+      <c r="D228" t="s">
+        <v>90</v>
+      </c>
+      <c r="E228">
+        <v>450699.81</v>
+      </c>
+      <c r="F228">
+        <v>6851159.54</v>
+      </c>
+      <c r="G228">
+        <v>-1085.52</v>
+      </c>
+      <c r="H228">
+        <v>1223.1600000000001</v>
+      </c>
+      <c r="K228">
+        <v>-1085.52</v>
+      </c>
+      <c r="O228" t="s">
+        <v>36</v>
+      </c>
+      <c r="P228">
+        <v>1</v>
+      </c>
+      <c r="U228" t="b">
+        <v>1</v>
+      </c>
+      <c r="V228" t="b">
+        <v>1</v>
+      </c>
+      <c r="W228" t="s">
+        <v>37</v>
+      </c>
+      <c r="X228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC228" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD228">
+        <v>1</v>
+      </c>
+      <c r="AE228" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="229" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>172</v>
+      </c>
+      <c r="B229" t="s">
+        <v>105</v>
+      </c>
+      <c r="C229">
+        <v>36386254</v>
+      </c>
+      <c r="D229" t="s">
+        <v>35</v>
+      </c>
+      <c r="E229">
+        <v>450571.12</v>
+      </c>
+      <c r="F229">
+        <v>6851150.3300000001</v>
+      </c>
+      <c r="G229">
+        <v>-1145.4100000000001</v>
+      </c>
+      <c r="H229">
+        <v>1365.81</v>
+      </c>
+      <c r="K229">
+        <v>-1145.4100000000001</v>
+      </c>
+      <c r="O229" t="s">
+        <v>36</v>
+      </c>
+      <c r="P229">
+        <v>1</v>
+      </c>
+      <c r="U229" t="b">
+        <v>1</v>
+      </c>
+      <c r="V229" t="b">
+        <v>1</v>
+      </c>
+      <c r="W229" t="s">
+        <v>37</v>
+      </c>
+      <c r="X229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC229" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD229">
+        <v>1</v>
+      </c>
+      <c r="AE229" t="s">
+        <v>111</v>
+      </c>
+      <c r="AF229" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI229" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="230" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>9549</v>
+      </c>
+      <c r="B230" t="s">
+        <v>105</v>
+      </c>
+      <c r="C230">
+        <v>36386254</v>
+      </c>
+      <c r="D230" t="s">
+        <v>35</v>
+      </c>
+      <c r="E230">
+        <v>450086.91</v>
+      </c>
+      <c r="F230">
+        <v>6851110.4500000002</v>
+      </c>
+      <c r="G230">
+        <v>-1194.98</v>
+      </c>
+      <c r="H230">
+        <v>1857.95</v>
+      </c>
+      <c r="K230">
+        <v>-1194.98</v>
+      </c>
+      <c r="O230" t="s">
+        <v>39</v>
+      </c>
+      <c r="U230" t="b">
+        <v>1</v>
+      </c>
+      <c r="V230" t="b">
+        <v>1</v>
+      </c>
+      <c r="W230" t="s">
+        <v>37</v>
+      </c>
+      <c r="X230" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI230" s="1">
+        <v>46272.679236111115</v>
+      </c>
+    </row>
+    <row r="231" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>9550</v>
+      </c>
+      <c r="B231" t="s">
+        <v>105</v>
+      </c>
+      <c r="C231">
+        <v>36386254</v>
+      </c>
+      <c r="D231" t="s">
+        <v>35</v>
+      </c>
+      <c r="E231">
+        <v>449747.74</v>
+      </c>
+      <c r="F231">
+        <v>6851079.8700000001</v>
+      </c>
+      <c r="G231">
+        <v>-1194.93</v>
+      </c>
+      <c r="H231">
+        <v>2198.71</v>
+      </c>
+      <c r="K231">
+        <v>-1194.93</v>
+      </c>
+      <c r="O231" t="s">
+        <v>39</v>
+      </c>
+      <c r="U231" t="b">
+        <v>1</v>
+      </c>
+      <c r="V231" t="b">
+        <v>1</v>
+      </c>
+      <c r="W231" t="s">
+        <v>37</v>
+      </c>
+      <c r="X231" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI231" s="1">
+        <v>46272.679270833331</v>
+      </c>
+    </row>
+    <row r="232" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>9551</v>
+      </c>
+      <c r="B232" t="s">
+        <v>105</v>
+      </c>
+      <c r="C232">
+        <v>36386254</v>
+      </c>
+      <c r="D232" t="s">
+        <v>35</v>
+      </c>
+      <c r="E232">
+        <v>449304.58</v>
+      </c>
+      <c r="F232">
+        <v>6851034.6600000001</v>
+      </c>
+      <c r="G232">
+        <v>-1198.92</v>
+      </c>
+      <c r="H232">
+        <v>2644.32</v>
+      </c>
+      <c r="K232">
+        <v>-1198.92</v>
+      </c>
+      <c r="O232" t="s">
+        <v>39</v>
+      </c>
+      <c r="U232" t="b">
+        <v>1</v>
+      </c>
+      <c r="V232" t="b">
+        <v>1</v>
+      </c>
+      <c r="W232" t="s">
+        <v>37</v>
+      </c>
+      <c r="X232" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI232" s="1">
+        <v>46272.679351851853</v>
+      </c>
+    </row>
+    <row r="233" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>9552</v>
+      </c>
+      <c r="B233" t="s">
+        <v>105</v>
+      </c>
+      <c r="C233">
+        <v>36386254</v>
+      </c>
+      <c r="D233" t="s">
+        <v>35</v>
+      </c>
+      <c r="E233">
+        <v>449275.58</v>
+      </c>
+      <c r="F233">
+        <v>6851032.04</v>
+      </c>
+      <c r="G233">
+        <v>-1199.29</v>
+      </c>
+      <c r="H233">
+        <v>2673.45</v>
+      </c>
+      <c r="K233">
+        <v>-1199.29</v>
+      </c>
+      <c r="O233" t="s">
+        <v>39</v>
+      </c>
+      <c r="U233" t="b">
+        <v>1</v>
+      </c>
+      <c r="V233" t="b">
+        <v>1</v>
+      </c>
+      <c r="W233" t="s">
+        <v>37</v>
+      </c>
+      <c r="X233" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI233" s="1">
+        <v>46272.679409722223</v>
+      </c>
+    </row>
+    <row r="234" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>2936</v>
+      </c>
+      <c r="B234" t="s">
+        <v>105</v>
+      </c>
+      <c r="C234">
+        <v>36386254</v>
+      </c>
+      <c r="D234" t="s">
+        <v>40</v>
+      </c>
+      <c r="E234">
+        <v>450263.89</v>
+      </c>
+      <c r="F234">
+        <v>6851124.2199999997</v>
+      </c>
+      <c r="G234">
+        <v>-1196.6099999999999</v>
+      </c>
+      <c r="H234">
+        <v>1680.36</v>
+      </c>
+      <c r="K234">
+        <v>-1196.6099999999999</v>
+      </c>
+      <c r="O234" t="s">
+        <v>36</v>
+      </c>
+      <c r="P234">
+        <v>1</v>
+      </c>
+      <c r="U234" t="b">
+        <v>1</v>
+      </c>
+      <c r="V234" t="b">
+        <v>1</v>
+      </c>
+      <c r="W234" t="s">
+        <v>37</v>
+      </c>
+      <c r="X234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC234" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD234">
+        <v>1</v>
+      </c>
+      <c r="AE234" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF234" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI234" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="235" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>3076</v>
+      </c>
+      <c r="B235" t="s">
+        <v>105</v>
+      </c>
+      <c r="C235">
+        <v>36386254</v>
+      </c>
+      <c r="D235" t="s">
+        <v>40</v>
+      </c>
+      <c r="E235">
+        <v>450085.45</v>
+      </c>
+      <c r="F235">
+        <v>6851110.3399999999</v>
+      </c>
+      <c r="G235">
+        <v>-1194.94</v>
+      </c>
+      <c r="H235">
+        <v>1859.4</v>
+      </c>
+      <c r="K235">
+        <v>-1194.94</v>
+      </c>
+      <c r="O235" t="s">
+        <v>39</v>
+      </c>
+      <c r="P235">
+        <v>2</v>
+      </c>
+      <c r="U235" t="b">
+        <v>1</v>
+      </c>
+      <c r="V235" t="b">
+        <v>1</v>
+      </c>
+      <c r="W235" t="s">
+        <v>37</v>
+      </c>
+      <c r="X235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC235" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD235">
+        <v>2</v>
+      </c>
+      <c r="AI235" s="1">
+        <v>46272.677731481483</v>
+      </c>
+    </row>
+    <row r="236" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>2917</v>
+      </c>
+      <c r="B236" t="s">
+        <v>105</v>
+      </c>
+      <c r="C236">
+        <v>36386254</v>
+      </c>
+      <c r="D236" t="s">
+        <v>40</v>
+      </c>
+      <c r="E236">
+        <v>450072.82</v>
+      </c>
+      <c r="F236">
+        <v>6851109.3600000003</v>
+      </c>
+      <c r="G236">
+        <v>-1194.6500000000001</v>
+      </c>
+      <c r="H236">
+        <v>1872.08</v>
+      </c>
+      <c r="K236">
+        <v>-1194.6500000000001</v>
+      </c>
+      <c r="O236" t="s">
+        <v>36</v>
+      </c>
+      <c r="P236">
+        <v>3</v>
+      </c>
+      <c r="U236" t="b">
+        <v>1</v>
+      </c>
+      <c r="V236" t="b">
+        <v>1</v>
+      </c>
+      <c r="W236" t="s">
+        <v>37</v>
+      </c>
+      <c r="X236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC236" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD236">
+        <v>2</v>
+      </c>
+      <c r="AI236" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="237" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>2940</v>
+      </c>
+      <c r="B237" t="s">
+        <v>105</v>
+      </c>
+      <c r="C237">
+        <v>36386254</v>
+      </c>
+      <c r="D237" t="s">
+        <v>40</v>
+      </c>
+      <c r="E237">
+        <v>449746.71</v>
+      </c>
+      <c r="F237">
+        <v>6851079.7699999996</v>
+      </c>
+      <c r="G237">
+        <v>-1194.93</v>
+      </c>
+      <c r="H237">
+        <v>2199.7399999999998</v>
+      </c>
+      <c r="K237">
+        <v>-1194.93</v>
+      </c>
+      <c r="O237" t="s">
+        <v>36</v>
+      </c>
+      <c r="P237">
+        <v>4</v>
+      </c>
+      <c r="U237" t="b">
+        <v>1</v>
+      </c>
+      <c r="V237" t="b">
+        <v>1</v>
+      </c>
+      <c r="W237" t="s">
+        <v>37</v>
+      </c>
+      <c r="X237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC237" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD237">
+        <v>2</v>
+      </c>
+      <c r="AI237" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="238" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>2919</v>
+      </c>
+      <c r="B238" t="s">
+        <v>105</v>
+      </c>
+      <c r="C238">
+        <v>36386254</v>
+      </c>
+      <c r="D238" t="s">
+        <v>40</v>
+      </c>
+      <c r="E238">
+        <v>449657.37</v>
+      </c>
+      <c r="F238">
+        <v>6851069.8499999996</v>
+      </c>
+      <c r="G238">
+        <v>-1196.6300000000001</v>
+      </c>
+      <c r="H238">
+        <v>2289.66</v>
+      </c>
+      <c r="K238">
+        <v>-1196.6300000000001</v>
+      </c>
+      <c r="O238" t="s">
+        <v>36</v>
+      </c>
+      <c r="P238">
+        <v>5</v>
+      </c>
+      <c r="U238" t="b">
+        <v>1</v>
+      </c>
+      <c r="V238" t="b">
+        <v>1</v>
+      </c>
+      <c r="W238" t="s">
+        <v>37</v>
+      </c>
+      <c r="X238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC238" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD238">
+        <v>2</v>
+      </c>
+      <c r="AI238" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="239" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>2988</v>
+      </c>
+      <c r="B239" t="s">
+        <v>105</v>
+      </c>
+      <c r="C239">
+        <v>36386254</v>
+      </c>
+      <c r="D239" t="s">
+        <v>40</v>
+      </c>
+      <c r="E239">
+        <v>449306.89</v>
+      </c>
+      <c r="F239">
+        <v>6851034.8499999996</v>
+      </c>
+      <c r="G239">
+        <v>-1198.8699999999999</v>
+      </c>
+      <c r="H239">
+        <v>2642.01</v>
+      </c>
+      <c r="K239">
+        <v>-1198.8699999999999</v>
+      </c>
+      <c r="O239" t="s">
+        <v>36</v>
+      </c>
+      <c r="P239">
+        <v>6</v>
+      </c>
+      <c r="U239" t="b">
+        <v>1</v>
+      </c>
+      <c r="V239" t="b">
+        <v>1</v>
+      </c>
+      <c r="W239" t="s">
+        <v>37</v>
+      </c>
+      <c r="X239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC239" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD239">
+        <v>2</v>
+      </c>
+      <c r="AI239" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="240" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>2838</v>
+      </c>
+      <c r="B240" t="s">
+        <v>105</v>
+      </c>
+      <c r="C240">
+        <v>36386254</v>
+      </c>
+      <c r="D240" t="s">
+        <v>40</v>
+      </c>
+      <c r="E240">
+        <v>449290.19</v>
+      </c>
+      <c r="F240">
+        <v>6851033.4000000004</v>
+      </c>
+      <c r="G240">
+        <v>-1199.1500000000001</v>
+      </c>
+      <c r="H240">
+        <v>2658.77</v>
+      </c>
+      <c r="K240">
+        <v>-1199.1500000000001</v>
+      </c>
+      <c r="O240" t="s">
+        <v>36</v>
+      </c>
+      <c r="P240">
+        <v>7</v>
+      </c>
+      <c r="U240" t="b">
+        <v>1</v>
+      </c>
+      <c r="V240" t="b">
+        <v>1</v>
+      </c>
+      <c r="W240" t="s">
+        <v>37</v>
+      </c>
+      <c r="X240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC240" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD240">
+        <v>2</v>
+      </c>
+      <c r="AI240" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="241" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>3147</v>
+      </c>
+      <c r="B241" t="s">
+        <v>105</v>
+      </c>
+      <c r="C241">
+        <v>36386254</v>
+      </c>
+      <c r="D241" t="s">
+        <v>40</v>
+      </c>
+      <c r="E241">
+        <v>449277.45</v>
+      </c>
+      <c r="F241">
+        <v>6851032.2199999997</v>
+      </c>
+      <c r="G241">
+        <v>-1199.27</v>
+      </c>
+      <c r="H241">
+        <v>2671.57</v>
+      </c>
+      <c r="K241">
+        <v>-1199.27</v>
+      </c>
+      <c r="O241" t="s">
+        <v>36</v>
+      </c>
+      <c r="P241">
+        <v>8</v>
+      </c>
+      <c r="U241" t="b">
+        <v>1</v>
+      </c>
+      <c r="V241" t="b">
+        <v>1</v>
+      </c>
+      <c r="W241" t="s">
+        <v>37</v>
+      </c>
+      <c r="X241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC241" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD241">
+        <v>2</v>
+      </c>
+      <c r="AI241" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="242" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>3049</v>
+      </c>
+      <c r="B242" t="s">
+        <v>105</v>
+      </c>
+      <c r="C242">
+        <v>36386254</v>
+      </c>
+      <c r="D242" t="s">
+        <v>40</v>
+      </c>
+      <c r="E242">
+        <v>449057.76</v>
+      </c>
+      <c r="F242">
+        <v>6851011.4299999997</v>
+      </c>
+      <c r="G242">
+        <v>-1198.8499999999999</v>
+      </c>
+      <c r="H242">
+        <v>2892.25</v>
+      </c>
+      <c r="K242">
+        <v>-1198.8499999999999</v>
+      </c>
+      <c r="O242" t="s">
+        <v>36</v>
+      </c>
+      <c r="P242">
+        <v>10</v>
+      </c>
+      <c r="U242" t="b">
+        <v>1</v>
+      </c>
+      <c r="V242" t="b">
+        <v>1</v>
+      </c>
+      <c r="W242" t="s">
+        <v>37</v>
+      </c>
+      <c r="X242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC242" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD242">
+        <v>2</v>
+      </c>
+      <c r="AI242" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="243" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>517</v>
+      </c>
+      <c r="B243" t="s">
+        <v>113</v>
+      </c>
+      <c r="C243">
+        <v>36393645</v>
+      </c>
+      <c r="D243" t="s">
+        <v>75</v>
+      </c>
+      <c r="E243">
+        <v>448848.91</v>
+      </c>
+      <c r="F243">
+        <v>6848951.3899999997</v>
+      </c>
+      <c r="G243">
+        <v>38.5</v>
+      </c>
+      <c r="H243">
+        <v>7.16</v>
+      </c>
+      <c r="K243">
+        <v>38.5</v>
+      </c>
+      <c r="O243" t="s">
+        <v>36</v>
+      </c>
+      <c r="P243">
+        <v>1</v>
+      </c>
+      <c r="U243" t="b">
+        <v>1</v>
+      </c>
+      <c r="V243" t="b">
+        <v>1</v>
+      </c>
+      <c r="W243" t="s">
+        <v>37</v>
+      </c>
+      <c r="X243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC243" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD243">
+        <v>2</v>
+      </c>
+      <c r="AE243" t="s">
+        <v>114</v>
+      </c>
+      <c r="AF243" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI243" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="244" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>1297</v>
+      </c>
+      <c r="B244" t="s">
+        <v>113</v>
+      </c>
+      <c r="C244">
+        <v>36393645</v>
+      </c>
+      <c r="D244" t="s">
+        <v>86</v>
+      </c>
+      <c r="E244">
+        <v>448890.57</v>
+      </c>
+      <c r="F244">
+        <v>6848971.7300000004</v>
+      </c>
+      <c r="G244">
+        <v>-855.01</v>
+      </c>
+      <c r="H244">
+        <v>907.69</v>
+      </c>
+      <c r="K244">
+        <v>-855.01</v>
+      </c>
+      <c r="O244" t="s">
+        <v>36</v>
+      </c>
+      <c r="P244">
+        <v>1</v>
+      </c>
+      <c r="U244" t="b">
+        <v>1</v>
+      </c>
+      <c r="V244" t="b">
+        <v>1</v>
+      </c>
+      <c r="W244" t="s">
+        <v>37</v>
+      </c>
+      <c r="X244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC244" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD244">
+        <v>1</v>
+      </c>
+      <c r="AE244" t="s">
+        <v>107</v>
+      </c>
+      <c r="AF244" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI244" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="245" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>1831</v>
+      </c>
+      <c r="B245" t="s">
+        <v>113</v>
+      </c>
+      <c r="C245">
+        <v>36393645</v>
+      </c>
+      <c r="D245" t="s">
+        <v>88</v>
+      </c>
+      <c r="E245">
+        <v>448900.03</v>
+      </c>
+      <c r="F245">
+        <v>6848975.7300000004</v>
+      </c>
+      <c r="G245">
+        <v>-876.79</v>
+      </c>
+      <c r="H245">
+        <v>931.77</v>
+      </c>
+      <c r="K245">
+        <v>-876.79</v>
+      </c>
+      <c r="O245" t="s">
+        <v>36</v>
+      </c>
+      <c r="P245">
+        <v>1</v>
+      </c>
+      <c r="U245" t="b">
+        <v>1</v>
+      </c>
+      <c r="V245" t="b">
+        <v>1</v>
+      </c>
+      <c r="W245" t="s">
+        <v>37</v>
+      </c>
+      <c r="X245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC245" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD245">
+        <v>1</v>
+      </c>
+      <c r="AE245" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF245" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI245" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="246" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>2559</v>
+      </c>
+      <c r="B246" t="s">
+        <v>113</v>
+      </c>
+      <c r="C246">
+        <v>36393645</v>
+      </c>
+      <c r="D246" t="s">
+        <v>90</v>
+      </c>
+      <c r="E246">
+        <v>449094.1</v>
+      </c>
+      <c r="F246">
+        <v>6849057.6399999997</v>
+      </c>
+      <c r="G246">
+        <v>-1088.8399999999999</v>
+      </c>
+      <c r="H246">
+        <v>1235.96</v>
+      </c>
+      <c r="K246">
+        <v>-1088.8399999999999</v>
+      </c>
+      <c r="O246" t="s">
+        <v>36</v>
+      </c>
+      <c r="P246">
+        <v>1</v>
+      </c>
+      <c r="U246" t="b">
+        <v>1</v>
+      </c>
+      <c r="V246" t="b">
+        <v>1</v>
+      </c>
+      <c r="W246" t="s">
+        <v>37</v>
+      </c>
+      <c r="X246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC246" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD246">
+        <v>1</v>
+      </c>
+      <c r="AE246" t="s">
+        <v>115</v>
+      </c>
+      <c r="AF246" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI246" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="247" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>42</v>
+      </c>
+      <c r="B247" t="s">
+        <v>113</v>
+      </c>
+      <c r="C247">
+        <v>36393645</v>
+      </c>
+      <c r="D247" t="s">
+        <v>35</v>
+      </c>
+      <c r="E247">
+        <v>449214.13</v>
+      </c>
+      <c r="F247">
+        <v>6849114.0499999998</v>
+      </c>
+      <c r="G247">
+        <v>-1149.28</v>
+      </c>
+      <c r="H247">
+        <v>1381.96</v>
+      </c>
+      <c r="K247">
+        <v>-1149.28</v>
+      </c>
+      <c r="O247" t="s">
+        <v>36</v>
+      </c>
+      <c r="P247">
+        <v>1</v>
+      </c>
+      <c r="U247" t="b">
+        <v>1</v>
+      </c>
+      <c r="V247" t="b">
+        <v>1</v>
+      </c>
+      <c r="W247" t="s">
+        <v>37</v>
+      </c>
+      <c r="X247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC247" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD247">
+        <v>1</v>
+      </c>
+      <c r="AE247" t="s">
+        <v>115</v>
+      </c>
+      <c r="AF247" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI247" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="248" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>9545</v>
+      </c>
+      <c r="B248" t="s">
+        <v>113</v>
+      </c>
+      <c r="C248">
+        <v>36393645</v>
+      </c>
+      <c r="D248" t="s">
+        <v>35</v>
+      </c>
+      <c r="E248">
+        <v>450020.14</v>
+      </c>
+      <c r="F248">
+        <v>6849707.7300000004</v>
+      </c>
+      <c r="G248">
+        <v>-1191.74</v>
+      </c>
+      <c r="H248">
+        <v>2389.4499999999998</v>
+      </c>
+      <c r="K248">
+        <v>-1191.74</v>
+      </c>
+      <c r="O248" t="s">
+        <v>39</v>
+      </c>
+      <c r="U248" t="b">
+        <v>1</v>
+      </c>
+      <c r="V248" t="b">
+        <v>1</v>
+      </c>
+      <c r="W248" t="s">
+        <v>37</v>
+      </c>
+      <c r="X248" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI248" s="1">
+        <v>46272.679016203707</v>
+      </c>
+    </row>
+    <row r="249" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>9546</v>
+      </c>
+      <c r="B249" t="s">
+        <v>113</v>
+      </c>
+      <c r="C249">
+        <v>36393645</v>
+      </c>
+      <c r="D249" t="s">
+        <v>35</v>
+      </c>
+      <c r="E249">
+        <v>450178.57</v>
+      </c>
+      <c r="F249">
+        <v>6849844.9800000004</v>
+      </c>
+      <c r="G249">
+        <v>-1193.93</v>
+      </c>
+      <c r="H249">
+        <v>2599.15</v>
+      </c>
+      <c r="K249">
+        <v>-1193.93</v>
+      </c>
+      <c r="O249" t="s">
+        <v>39</v>
+      </c>
+      <c r="U249" t="b">
+        <v>1</v>
+      </c>
+      <c r="V249" t="b">
+        <v>1</v>
+      </c>
+      <c r="W249" t="s">
+        <v>37</v>
+      </c>
+      <c r="X249" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI249" s="1">
+        <v>46272.679074074076</v>
+      </c>
+    </row>
+    <row r="250" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>9547</v>
+      </c>
+      <c r="B250" t="s">
+        <v>113</v>
+      </c>
+      <c r="C250">
+        <v>36393645</v>
+      </c>
+      <c r="D250" t="s">
+        <v>35</v>
+      </c>
+      <c r="E250">
+        <v>450398.4</v>
+      </c>
+      <c r="F250">
+        <v>6850010.3700000001</v>
+      </c>
+      <c r="G250">
+        <v>-1191.6400000000001</v>
+      </c>
+      <c r="H250">
+        <v>2874.38</v>
+      </c>
+      <c r="K250">
+        <v>-1191.6400000000001</v>
+      </c>
+      <c r="O250" t="s">
+        <v>39</v>
+      </c>
+      <c r="U250" t="b">
+        <v>1</v>
+      </c>
+      <c r="V250" t="b">
+        <v>1</v>
+      </c>
+      <c r="W250" t="s">
+        <v>37</v>
+      </c>
+      <c r="X250" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI250" s="1">
+        <v>46272.679131944446</v>
+      </c>
+    </row>
+    <row r="251" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>9548</v>
+      </c>
+      <c r="B251" t="s">
+        <v>113</v>
+      </c>
+      <c r="C251">
+        <v>36393645</v>
+      </c>
+      <c r="D251" t="s">
+        <v>35</v>
+      </c>
+      <c r="E251">
+        <v>450494.98</v>
+      </c>
+      <c r="F251">
+        <v>6850080.5499999998</v>
+      </c>
+      <c r="G251">
+        <v>-1191.54</v>
+      </c>
+      <c r="H251">
+        <v>2993.8</v>
+      </c>
+      <c r="K251">
+        <v>-1191.54</v>
+      </c>
+      <c r="O251" t="s">
+        <v>39</v>
+      </c>
+      <c r="U251" t="b">
+        <v>1</v>
+      </c>
+      <c r="V251" t="b">
+        <v>1</v>
+      </c>
+      <c r="W251" t="s">
+        <v>37</v>
+      </c>
+      <c r="X251" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI251" s="1">
+        <v>46272.679166666669</v>
+      </c>
+    </row>
+    <row r="252" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>2959</v>
+      </c>
+      <c r="B252" t="s">
+        <v>113</v>
+      </c>
+      <c r="C252">
+        <v>36393645</v>
+      </c>
+      <c r="D252" t="s">
+        <v>40</v>
+      </c>
+      <c r="E252">
+        <v>449583.18</v>
+      </c>
+      <c r="F252">
+        <v>6849361.1500000004</v>
+      </c>
+      <c r="G252">
+        <v>-1194.93</v>
+      </c>
+      <c r="H252">
+        <v>1831.54</v>
+      </c>
+      <c r="K252">
+        <v>-1194.93</v>
+      </c>
+      <c r="O252" t="s">
+        <v>36</v>
+      </c>
+      <c r="P252">
+        <v>1</v>
+      </c>
+      <c r="U252" t="b">
+        <v>1</v>
+      </c>
+      <c r="V252" t="b">
+        <v>1</v>
+      </c>
+      <c r="W252" t="s">
+        <v>37</v>
+      </c>
+      <c r="X252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC252" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD252">
+        <v>1</v>
+      </c>
+      <c r="AE252" t="s">
+        <v>116</v>
+      </c>
+      <c r="AF252" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI252" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="253" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>9520</v>
+      </c>
+      <c r="B253" t="s">
+        <v>113</v>
+      </c>
+      <c r="C253">
+        <v>36393645</v>
+      </c>
+      <c r="D253" t="s">
+        <v>40</v>
+      </c>
+      <c r="E253">
+        <v>450021.24</v>
+      </c>
+      <c r="F253">
+        <v>6849708.6799999997</v>
+      </c>
+      <c r="G253">
+        <v>-1191.79</v>
+      </c>
+      <c r="H253">
+        <v>2390.91</v>
+      </c>
+      <c r="K253">
+        <v>-1191.79</v>
+      </c>
+      <c r="O253" t="s">
+        <v>39</v>
+      </c>
+      <c r="U253" t="b">
+        <v>1</v>
+      </c>
+      <c r="V253" t="b">
+        <v>1</v>
+      </c>
+      <c r="W253" t="s">
+        <v>37</v>
+      </c>
+      <c r="X253" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI253" s="1">
+        <v>46272.677754629629</v>
+      </c>
+    </row>
+    <row r="254" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>9521</v>
+      </c>
+      <c r="B254" t="s">
+        <v>113</v>
+      </c>
+      <c r="C254">
+        <v>36393645</v>
+      </c>
+      <c r="D254" t="s">
+        <v>40</v>
+      </c>
+      <c r="E254">
+        <v>450037.69</v>
+      </c>
+      <c r="F254">
+        <v>6849723.0300000003</v>
+      </c>
+      <c r="G254">
+        <v>-1192.68</v>
+      </c>
+      <c r="H254">
+        <v>2412.75</v>
+      </c>
+      <c r="K254">
+        <v>-1192.68</v>
+      </c>
+      <c r="O254" t="s">
+        <v>39</v>
+      </c>
+      <c r="U254" t="b">
+        <v>1</v>
+      </c>
+      <c r="V254" t="b">
+        <v>1</v>
+      </c>
+      <c r="W254" t="s">
+        <v>37</v>
+      </c>
+      <c r="X254" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI254" s="1">
+        <v>46272.677777777775</v>
+      </c>
+    </row>
+    <row r="255" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>9522</v>
+      </c>
+      <c r="B255" t="s">
+        <v>113</v>
+      </c>
+      <c r="C255">
+        <v>36393645</v>
+      </c>
+      <c r="D255" t="s">
+        <v>40</v>
+      </c>
+      <c r="E255">
+        <v>450180.82</v>
+      </c>
+      <c r="F255">
+        <v>6849846.8300000001</v>
+      </c>
+      <c r="G255">
+        <v>-1193.92</v>
+      </c>
+      <c r="H255">
+        <v>2602.06</v>
+      </c>
+      <c r="K255">
+        <v>-1193.92</v>
+      </c>
+      <c r="O255" t="s">
+        <v>39</v>
+      </c>
+      <c r="U255" t="b">
+        <v>1</v>
+      </c>
+      <c r="V255" t="b">
+        <v>1</v>
+      </c>
+      <c r="W255" t="s">
+        <v>37</v>
+      </c>
+      <c r="X255" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI255" s="1">
+        <v>46272.677789351852</v>
+      </c>
+    </row>
+    <row r="256" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>9523</v>
+      </c>
+      <c r="B256" t="s">
+        <v>113</v>
+      </c>
+      <c r="C256">
+        <v>36393645</v>
+      </c>
+      <c r="D256" t="s">
+        <v>40</v>
+      </c>
+      <c r="E256">
+        <v>450225.42</v>
+      </c>
+      <c r="F256">
+        <v>6849881.9699999997</v>
+      </c>
+      <c r="G256">
+        <v>-1195.08</v>
+      </c>
+      <c r="H256">
+        <v>2658.86</v>
+      </c>
+      <c r="K256">
+        <v>-1195.08</v>
+      </c>
+      <c r="O256" t="s">
+        <v>39</v>
+      </c>
+      <c r="U256" t="b">
+        <v>1</v>
+      </c>
+      <c r="V256" t="b">
+        <v>1</v>
+      </c>
+      <c r="W256" t="s">
+        <v>37</v>
+      </c>
+      <c r="X256" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI256" s="1">
+        <v>46272.677800925929</v>
+      </c>
+    </row>
+    <row r="257" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>9524</v>
+      </c>
+      <c r="B257" t="s">
+        <v>113</v>
+      </c>
+      <c r="C257">
+        <v>36393645</v>
+      </c>
+      <c r="D257" t="s">
+        <v>40</v>
+      </c>
+      <c r="E257">
+        <v>450397.24</v>
+      </c>
+      <c r="F257">
+        <v>6850009.4900000002</v>
+      </c>
+      <c r="G257">
+        <v>-1191.6400000000001</v>
+      </c>
+      <c r="H257">
+        <v>2872.93</v>
+      </c>
+      <c r="K257">
+        <v>-1191.6400000000001</v>
+      </c>
+      <c r="O257" t="s">
+        <v>39</v>
+      </c>
+      <c r="U257" t="b">
+        <v>1</v>
+      </c>
+      <c r="V257" t="b">
+        <v>1</v>
+      </c>
+      <c r="W257" t="s">
+        <v>37</v>
+      </c>
+      <c r="X257" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI257" s="1">
+        <v>46272.677835648145</v>
+      </c>
+    </row>
+    <row r="258" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>9525</v>
+      </c>
+      <c r="B258" t="s">
+        <v>113</v>
+      </c>
+      <c r="C258">
+        <v>36393645</v>
+      </c>
+      <c r="D258" t="s">
+        <v>40</v>
+      </c>
+      <c r="E258">
+        <v>450412.3</v>
+      </c>
+      <c r="F258">
+        <v>6850020.9699999997</v>
+      </c>
+      <c r="G258">
+        <v>-1191.57</v>
+      </c>
+      <c r="H258">
+        <v>2891.86</v>
+      </c>
+      <c r="K258">
+        <v>-1191.57</v>
+      </c>
+      <c r="O258" t="s">
+        <v>39</v>
+      </c>
+      <c r="U258" t="b">
+        <v>1</v>
+      </c>
+      <c r="V258" t="b">
+        <v>1</v>
+      </c>
+      <c r="W258" t="s">
+        <v>37</v>
+      </c>
+      <c r="X258" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI258" s="1">
+        <v>46272.677847222221</v>
+      </c>
+    </row>
+    <row r="259" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>9526</v>
+      </c>
+      <c r="B259" t="s">
+        <v>113</v>
+      </c>
+      <c r="C259">
+        <v>36393645</v>
+      </c>
+      <c r="D259" t="s">
+        <v>40</v>
+      </c>
+      <c r="E259">
+        <v>450494.98</v>
+      </c>
+      <c r="F259">
+        <v>6850080.5499999998</v>
+      </c>
+      <c r="G259">
+        <v>-1191.54</v>
+      </c>
+      <c r="H259">
+        <v>2993.8</v>
+      </c>
+      <c r="K259">
+        <v>-1191.54</v>
+      </c>
+      <c r="O259" t="s">
+        <v>39</v>
+      </c>
+      <c r="U259" t="b">
+        <v>1</v>
+      </c>
+      <c r="V259" t="b">
+        <v>1</v>
+      </c>
+      <c r="W259" t="s">
+        <v>37</v>
+      </c>
+      <c r="X259" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI259" s="1">
+        <v>46272.677870370368</v>
+      </c>
+    </row>
+    <row r="260" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>9527</v>
+      </c>
+      <c r="B260" t="s">
+        <v>113</v>
+      </c>
+      <c r="C260">
+        <v>36393645</v>
+      </c>
+      <c r="D260" t="s">
+        <v>40</v>
+      </c>
+      <c r="E260">
+        <v>450525.92</v>
+      </c>
+      <c r="F260">
+        <v>6850104.7699999996</v>
+      </c>
+      <c r="G260">
+        <v>-1192.53</v>
+      </c>
+      <c r="H260">
+        <v>3033.11</v>
+      </c>
+      <c r="K260">
+        <v>-1192.53</v>
+      </c>
+      <c r="O260" t="s">
+        <v>39</v>
+      </c>
+      <c r="U260" t="b">
+        <v>1</v>
+      </c>
+      <c r="V260" t="b">
+        <v>1</v>
+      </c>
+      <c r="W260" t="s">
+        <v>37</v>
+      </c>
+      <c r="X260" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI260" s="1">
+        <v>46272.677893518521</v>
+      </c>
+    </row>
+    <row r="261" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>519</v>
+      </c>
+      <c r="B261" t="s">
+        <v>117</v>
+      </c>
+      <c r="C261">
+        <v>36393646</v>
+      </c>
+      <c r="D261" t="s">
+        <v>75</v>
+      </c>
+      <c r="E261">
+        <v>449421.18</v>
+      </c>
+      <c r="F261">
+        <v>6849851.2400000002</v>
+      </c>
+      <c r="G261">
+        <v>35.97</v>
+      </c>
+      <c r="H261">
+        <v>7.16</v>
+      </c>
+      <c r="K261">
+        <v>35.97</v>
+      </c>
+      <c r="O261" t="s">
+        <v>36</v>
+      </c>
+      <c r="P261">
+        <v>1</v>
+      </c>
+      <c r="U261" t="b">
+        <v>1</v>
+      </c>
+      <c r="V261" t="b">
+        <v>1</v>
+      </c>
+      <c r="W261" t="s">
+        <v>37</v>
+      </c>
+      <c r="X261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC261" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD261">
+        <v>2</v>
+      </c>
+      <c r="AE261" t="s">
+        <v>118</v>
+      </c>
+      <c r="AF261" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI261" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="262" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>1251</v>
+      </c>
+      <c r="B262" t="s">
+        <v>117</v>
+      </c>
+      <c r="C262">
+        <v>36393646</v>
+      </c>
+      <c r="D262" t="s">
+        <v>86</v>
+      </c>
+      <c r="E262">
+        <v>449417.75</v>
+      </c>
+      <c r="F262">
+        <v>6849824.1799999997</v>
+      </c>
+      <c r="G262">
+        <v>-818.06</v>
+      </c>
+      <c r="H262">
+        <v>864.41</v>
+      </c>
+      <c r="K262">
+        <v>-818.06</v>
+      </c>
+      <c r="O262" t="s">
+        <v>36</v>
+      </c>
+      <c r="P262">
+        <v>1</v>
+      </c>
+      <c r="U262" t="b">
+        <v>1</v>
+      </c>
+      <c r="V262" t="b">
+        <v>1</v>
+      </c>
+      <c r="W262" t="s">
+        <v>37</v>
+      </c>
+      <c r="X262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC262" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD262">
+        <v>1</v>
+      </c>
+      <c r="AE262" t="s">
+        <v>107</v>
+      </c>
+      <c r="AF262" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI262" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="263" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>1640</v>
+      </c>
+      <c r="B263" t="s">
+        <v>117</v>
+      </c>
+      <c r="C263">
+        <v>36393646</v>
+      </c>
+      <c r="D263" t="s">
+        <v>88</v>
+      </c>
+      <c r="E263">
+        <v>449415.54</v>
+      </c>
+      <c r="F263">
+        <v>6849815.46</v>
+      </c>
+      <c r="G263">
+        <v>-841.37</v>
+      </c>
+      <c r="H263">
+        <v>889.41</v>
+      </c>
+      <c r="K263">
+        <v>-841.37</v>
+      </c>
+      <c r="O263" t="s">
+        <v>36</v>
+      </c>
+      <c r="P263">
+        <v>1</v>
+      </c>
+      <c r="U263" t="b">
+        <v>1</v>
+      </c>
+      <c r="V263" t="b">
+        <v>1</v>
+      </c>
+      <c r="W263" t="s">
+        <v>37</v>
+      </c>
+      <c r="X263" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC263" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD263">
+        <v>1</v>
+      </c>
+      <c r="AE263" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF263" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI263" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="264" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>2324</v>
+      </c>
+      <c r="B264" t="s">
+        <v>117</v>
+      </c>
+      <c r="C264">
+        <v>36393646</v>
+      </c>
+      <c r="D264" t="s">
+        <v>90</v>
+      </c>
+      <c r="E264">
+        <v>449341.62</v>
+      </c>
+      <c r="F264">
+        <v>6849621.3399999999</v>
+      </c>
+      <c r="G264">
+        <v>-1080.57</v>
+      </c>
+      <c r="H264">
+        <v>1212.8</v>
+      </c>
+      <c r="K264">
+        <v>-1080.57</v>
+      </c>
+      <c r="O264" t="s">
+        <v>36</v>
+      </c>
+      <c r="P264">
+        <v>1</v>
+      </c>
+      <c r="U264" t="b">
+        <v>1</v>
+      </c>
+      <c r="V264" t="b">
+        <v>1</v>
+      </c>
+      <c r="W264" t="s">
+        <v>37</v>
+      </c>
+      <c r="X264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC264" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD264">
+        <v>1</v>
+      </c>
+      <c r="AE264" t="s">
+        <v>115</v>
+      </c>
+      <c r="AF264" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI264" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="265" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>122</v>
+      </c>
+      <c r="B265" t="s">
+        <v>117</v>
+      </c>
+      <c r="C265">
+        <v>36393646</v>
+      </c>
+      <c r="D265" t="s">
+        <v>35</v>
+      </c>
+      <c r="E265">
+        <v>449277.09</v>
+      </c>
+      <c r="F265">
+        <v>6849459.1299999999</v>
+      </c>
+      <c r="G265">
+        <v>-1145.43</v>
+      </c>
+      <c r="H265">
+        <v>1399.34</v>
+      </c>
+      <c r="K265">
+        <v>-1145.43</v>
+      </c>
+      <c r="O265" t="s">
+        <v>36</v>
+      </c>
+      <c r="P265">
+        <v>1</v>
+      </c>
+      <c r="U265" t="b">
+        <v>1</v>
+      </c>
+      <c r="V265" t="b">
+        <v>1</v>
+      </c>
+      <c r="W265" t="s">
+        <v>37</v>
+      </c>
+      <c r="X265" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC265" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD265">
+        <v>1</v>
+      </c>
+      <c r="AE265" t="s">
+        <v>116</v>
+      </c>
+      <c r="AF265" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI265" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="266" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>9540</v>
+      </c>
+      <c r="B266" t="s">
+        <v>117</v>
+      </c>
+      <c r="C266">
+        <v>36393646</v>
+      </c>
+      <c r="D266" t="s">
+        <v>35</v>
+      </c>
+      <c r="E266">
+        <v>448987.41</v>
+      </c>
+      <c r="F266">
+        <v>6849009.6399999997</v>
+      </c>
+      <c r="G266">
+        <v>-1198.95</v>
+      </c>
+      <c r="H266">
+        <v>1943.6</v>
+      </c>
+      <c r="K266">
+        <v>-1198.95</v>
+      </c>
+      <c r="O266" t="s">
+        <v>39</v>
+      </c>
+      <c r="U266" t="b">
+        <v>1</v>
+      </c>
+      <c r="V266" t="b">
+        <v>1</v>
+      </c>
+      <c r="W266" t="s">
+        <v>37</v>
+      </c>
+      <c r="X266" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI266" s="1">
+        <v>46272.678807870368</v>
+      </c>
+    </row>
+    <row r="267" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>9541</v>
+      </c>
+      <c r="B267" t="s">
+        <v>117</v>
+      </c>
+      <c r="C267">
+        <v>36393646</v>
+      </c>
+      <c r="D267" t="s">
+        <v>35</v>
+      </c>
+      <c r="E267">
+        <v>448925.41</v>
+      </c>
+      <c r="F267">
+        <v>6848936.2199999997</v>
+      </c>
+      <c r="G267">
+        <v>-1199.57</v>
+      </c>
+      <c r="H267">
+        <v>2039.72</v>
+      </c>
+      <c r="K267">
+        <v>-1199.57</v>
+      </c>
+      <c r="O267" t="s">
+        <v>39</v>
+      </c>
+      <c r="U267" t="b">
+        <v>1</v>
+      </c>
+      <c r="V267" t="b">
+        <v>1</v>
+      </c>
+      <c r="W267" t="s">
+        <v>37</v>
+      </c>
+      <c r="X267" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI267" s="1">
+        <v>46272.678854166668</v>
+      </c>
+    </row>
+    <row r="268" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>9542</v>
+      </c>
+      <c r="B268" t="s">
+        <v>117</v>
+      </c>
+      <c r="C268">
+        <v>36393646</v>
+      </c>
+      <c r="D268" t="s">
+        <v>35</v>
+      </c>
+      <c r="E268">
+        <v>448846.84</v>
+      </c>
+      <c r="F268">
+        <v>6848833.1799999997</v>
+      </c>
+      <c r="G268">
+        <v>-1201.1099999999999</v>
+      </c>
+      <c r="H268">
+        <v>2169.3200000000002</v>
+      </c>
+      <c r="K268">
+        <v>-1201.1099999999999</v>
+      </c>
+      <c r="O268" t="s">
+        <v>39</v>
+      </c>
+      <c r="U268" t="b">
+        <v>1</v>
+      </c>
+      <c r="V268" t="b">
+        <v>1</v>
+      </c>
+      <c r="W268" t="s">
+        <v>37</v>
+      </c>
+      <c r="X268" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI268" s="1">
+        <v>46272.678877314815</v>
+      </c>
+    </row>
+    <row r="269" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>9543</v>
+      </c>
+      <c r="B269" t="s">
+        <v>117</v>
+      </c>
+      <c r="C269">
+        <v>36393646</v>
+      </c>
+      <c r="D269" t="s">
+        <v>35</v>
+      </c>
+      <c r="E269">
+        <v>448710.04</v>
+      </c>
+      <c r="F269">
+        <v>6848648.2800000003</v>
+      </c>
+      <c r="G269">
+        <v>-1200.93</v>
+      </c>
+      <c r="H269">
+        <v>2399.41</v>
+      </c>
+      <c r="K269">
+        <v>-1200.93</v>
+      </c>
+      <c r="O269" t="s">
+        <v>39</v>
+      </c>
+      <c r="U269" t="b">
+        <v>1</v>
+      </c>
+      <c r="V269" t="b">
+        <v>1</v>
+      </c>
+      <c r="W269" t="s">
+        <v>37</v>
+      </c>
+      <c r="X269" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI269" s="1">
+        <v>46272.678923611114</v>
+      </c>
+    </row>
+    <row r="270" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>9544</v>
+      </c>
+      <c r="B270" t="s">
+        <v>117</v>
+      </c>
+      <c r="C270">
+        <v>36393646</v>
+      </c>
+      <c r="D270" t="s">
+        <v>35</v>
+      </c>
+      <c r="E270">
+        <v>448632.22</v>
+      </c>
+      <c r="F270">
+        <v>6848552.0300000003</v>
+      </c>
+      <c r="G270">
+        <v>-1201.82</v>
+      </c>
+      <c r="H270">
+        <v>2523.19</v>
+      </c>
+      <c r="K270">
+        <v>-1201.82</v>
+      </c>
+      <c r="O270" t="s">
+        <v>39</v>
+      </c>
+      <c r="U270" t="b">
+        <v>1</v>
+      </c>
+      <c r="V270" t="b">
+        <v>1</v>
+      </c>
+      <c r="W270" t="s">
+        <v>37</v>
+      </c>
+      <c r="X270" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI270" s="1">
+        <v>46272.678981481484</v>
+      </c>
+    </row>
+    <row r="271" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>2882</v>
+      </c>
+      <c r="B271" t="s">
+        <v>117</v>
+      </c>
+      <c r="C271">
+        <v>36393646</v>
+      </c>
+      <c r="D271" t="s">
+        <v>40</v>
+      </c>
+      <c r="E271">
+        <v>449059.36</v>
+      </c>
+      <c r="F271">
+        <v>6849093.8799999999</v>
+      </c>
+      <c r="G271">
+        <v>-1199.1099999999999</v>
+      </c>
+      <c r="H271">
+        <v>1832.76</v>
+      </c>
+      <c r="K271">
+        <v>-1199.1099999999999</v>
+      </c>
+      <c r="O271" t="s">
+        <v>36</v>
+      </c>
+      <c r="P271">
+        <v>1</v>
+      </c>
+      <c r="U271" t="b">
+        <v>1</v>
+      </c>
+      <c r="V271" t="b">
+        <v>1</v>
+      </c>
+      <c r="W271" t="s">
+        <v>37</v>
+      </c>
+      <c r="X271" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC271" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD271">
+        <v>1</v>
+      </c>
+      <c r="AE271" t="s">
+        <v>115</v>
+      </c>
+      <c r="AF271" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI271" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="272" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>9530</v>
+      </c>
+      <c r="B272" t="s">
+        <v>117</v>
+      </c>
+      <c r="C272">
+        <v>36393646</v>
+      </c>
+      <c r="D272" t="s">
+        <v>40</v>
+      </c>
+      <c r="E272">
+        <v>448987.41</v>
+      </c>
+      <c r="F272">
+        <v>6849009.6399999997</v>
+      </c>
+      <c r="G272">
+        <v>-1198.95</v>
+      </c>
+      <c r="H272">
+        <v>1943.6</v>
+      </c>
+      <c r="K272">
+        <v>-1198.95</v>
+      </c>
+      <c r="O272" t="s">
+        <v>39</v>
+      </c>
+      <c r="U272" t="b">
+        <v>1</v>
+      </c>
+      <c r="V272" t="b">
+        <v>1</v>
+      </c>
+      <c r="W272" t="s">
+        <v>37</v>
+      </c>
+      <c r="X272" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI272" s="1">
+        <v>46272.678043981483</v>
+      </c>
+    </row>
+    <row r="273" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>9531</v>
+      </c>
+      <c r="B273" t="s">
+        <v>117</v>
+      </c>
+      <c r="C273">
+        <v>36393646</v>
+      </c>
+      <c r="D273" t="s">
+        <v>40</v>
+      </c>
+      <c r="E273">
+        <v>448952.4</v>
+      </c>
+      <c r="F273">
+        <v>6848968.7000000002</v>
+      </c>
+      <c r="G273">
+        <v>-1198.78</v>
+      </c>
+      <c r="H273">
+        <v>1997.49</v>
+      </c>
+      <c r="K273">
+        <v>-1198.78</v>
+      </c>
+      <c r="O273" t="s">
+        <v>39</v>
+      </c>
+      <c r="U273" t="b">
+        <v>1</v>
+      </c>
+      <c r="V273" t="b">
+        <v>1</v>
+      </c>
+      <c r="W273" t="s">
+        <v>37</v>
+      </c>
+      <c r="X273" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI273" s="1">
+        <v>46272.678055555552</v>
+      </c>
+    </row>
+    <row r="274" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>9532</v>
+      </c>
+      <c r="B274" t="s">
+        <v>117</v>
+      </c>
+      <c r="C274">
+        <v>36393646</v>
+      </c>
+      <c r="D274" t="s">
+        <v>40</v>
+      </c>
+      <c r="E274">
+        <v>448924.49</v>
+      </c>
+      <c r="F274">
+        <v>6848935.0999999996</v>
+      </c>
+      <c r="G274">
+        <v>-1199.5999999999999</v>
+      </c>
+      <c r="H274">
+        <v>2041.17</v>
+      </c>
+      <c r="K274">
+        <v>-1199.5999999999999</v>
+      </c>
+      <c r="O274" t="s">
+        <v>39</v>
+      </c>
+      <c r="U274" t="b">
+        <v>1</v>
+      </c>
+      <c r="V274" t="b">
+        <v>1</v>
+      </c>
+      <c r="W274" t="s">
+        <v>37</v>
+      </c>
+      <c r="X274" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI274" s="1">
+        <v>46272.678078703706</v>
+      </c>
+    </row>
+    <row r="275" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A275">
+        <v>9533</v>
+      </c>
+      <c r="B275" t="s">
+        <v>117</v>
+      </c>
+      <c r="C275">
+        <v>36393646</v>
+      </c>
+      <c r="D275" t="s">
+        <v>40</v>
+      </c>
+      <c r="E275">
+        <v>448891.17</v>
+      </c>
+      <c r="F275">
+        <v>6848892.7699999996</v>
+      </c>
+      <c r="G275">
+        <v>-1200.4000000000001</v>
+      </c>
+      <c r="H275">
+        <v>2095.0500000000002</v>
+      </c>
+      <c r="K275">
+        <v>-1200.4000000000001</v>
+      </c>
+      <c r="O275" t="s">
+        <v>39</v>
+      </c>
+      <c r="U275" t="b">
+        <v>1</v>
+      </c>
+      <c r="V275" t="b">
+        <v>1</v>
+      </c>
+      <c r="W275" t="s">
+        <v>37</v>
+      </c>
+      <c r="X275" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI275" s="1">
+        <v>46272.678090277775</v>
+      </c>
+    </row>
+    <row r="276" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A276">
+        <v>9534</v>
+      </c>
+      <c r="B276" t="s">
+        <v>117</v>
+      </c>
+      <c r="C276">
+        <v>36393646</v>
+      </c>
+      <c r="D276" t="s">
+        <v>40</v>
+      </c>
+      <c r="E276">
+        <v>448846.84</v>
+      </c>
+      <c r="F276">
+        <v>6848833.1799999997</v>
+      </c>
+      <c r="G276">
+        <v>-1201.1099999999999</v>
+      </c>
+      <c r="H276">
+        <v>2169.3200000000002</v>
+      </c>
+      <c r="K276">
+        <v>-1201.1099999999999</v>
+      </c>
+      <c r="O276" t="s">
+        <v>39</v>
+      </c>
+      <c r="U276" t="b">
+        <v>1</v>
+      </c>
+      <c r="V276" t="b">
+        <v>1</v>
+      </c>
+      <c r="W276" t="s">
+        <v>37</v>
+      </c>
+      <c r="X276" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI276" s="1">
+        <v>46272.678101851852</v>
+      </c>
+    </row>
+    <row r="277" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A277">
+        <v>9535</v>
+      </c>
+      <c r="B277" t="s">
+        <v>117</v>
+      </c>
+      <c r="C277">
+        <v>36393646</v>
+      </c>
+      <c r="D277" t="s">
+        <v>40</v>
+      </c>
+      <c r="E277">
+        <v>448827.3</v>
+      </c>
+      <c r="F277">
+        <v>6848805.9900000002</v>
+      </c>
+      <c r="G277">
+        <v>-1201.3800000000001</v>
+      </c>
+      <c r="H277">
+        <v>2202.8200000000002</v>
+      </c>
+      <c r="K277">
+        <v>-1201.3800000000001</v>
+      </c>
+      <c r="O277" t="s">
+        <v>39</v>
+      </c>
+      <c r="U277" t="b">
+        <v>1</v>
+      </c>
+      <c r="V277" t="b">
+        <v>1</v>
+      </c>
+      <c r="W277" t="s">
+        <v>37</v>
+      </c>
+      <c r="X277" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI277" s="1">
+        <v>46272.678113425929</v>
+      </c>
+    </row>
+    <row r="278" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>9536</v>
+      </c>
+      <c r="B278" t="s">
+        <v>117</v>
+      </c>
+      <c r="C278">
+        <v>36393646</v>
+      </c>
+      <c r="D278" t="s">
+        <v>40</v>
+      </c>
+      <c r="E278">
+        <v>448708.21</v>
+      </c>
+      <c r="F278">
+        <v>6848646.0199999996</v>
+      </c>
+      <c r="G278">
+        <v>-1200.92</v>
+      </c>
+      <c r="H278">
+        <v>2402.3200000000002</v>
+      </c>
+      <c r="K278">
+        <v>-1200.92</v>
+      </c>
+      <c r="O278" t="s">
+        <v>39</v>
+      </c>
+      <c r="U278" t="b">
+        <v>1</v>
+      </c>
+      <c r="V278" t="b">
+        <v>1</v>
+      </c>
+      <c r="W278" t="s">
+        <v>37</v>
+      </c>
+      <c r="X278" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI278" s="1">
+        <v>46272.678124999999</v>
+      </c>
+    </row>
+    <row r="279" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A279">
+        <v>9537</v>
+      </c>
+      <c r="B279" t="s">
+        <v>117</v>
+      </c>
+      <c r="C279">
+        <v>36393646</v>
+      </c>
+      <c r="D279" t="s">
+        <v>40</v>
+      </c>
+      <c r="E279">
+        <v>448681.6</v>
+      </c>
+      <c r="F279">
+        <v>6848613.2199999997</v>
+      </c>
+      <c r="G279">
+        <v>-1201.1600000000001</v>
+      </c>
+      <c r="H279">
+        <v>2444.5500000000002</v>
+      </c>
+      <c r="K279">
+        <v>-1201.1600000000001</v>
+      </c>
+      <c r="O279" t="s">
+        <v>39</v>
+      </c>
+      <c r="U279" t="b">
+        <v>1</v>
+      </c>
+      <c r="V279" t="b">
+        <v>1</v>
+      </c>
+      <c r="W279" t="s">
+        <v>37</v>
+      </c>
+      <c r="X279" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI279" s="1">
+        <v>46272.678136574075</v>
+      </c>
+    </row>
+    <row r="280" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>9538</v>
+      </c>
+      <c r="B280" t="s">
+        <v>117</v>
+      </c>
+      <c r="C280">
+        <v>36393646</v>
+      </c>
+      <c r="D280" t="s">
+        <v>40</v>
+      </c>
+      <c r="E280">
+        <v>448631.31</v>
+      </c>
+      <c r="F280">
+        <v>6848550.8899999997</v>
+      </c>
+      <c r="G280">
+        <v>-1201.83</v>
+      </c>
+      <c r="H280">
+        <v>2524.65</v>
+      </c>
+      <c r="K280">
+        <v>-1201.83</v>
+      </c>
+      <c r="O280" t="s">
+        <v>39</v>
+      </c>
+      <c r="U280" t="b">
+        <v>1</v>
+      </c>
+      <c r="V280" t="b">
+        <v>1</v>
+      </c>
+      <c r="W280" t="s">
+        <v>37</v>
+      </c>
+      <c r="X280" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI280" s="1">
+        <v>46272.678148148145</v>
+      </c>
+    </row>
+    <row r="281" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>9539</v>
+      </c>
+      <c r="B281" t="s">
+        <v>117</v>
+      </c>
+      <c r="C281">
+        <v>36393646</v>
+      </c>
+      <c r="D281" t="s">
+        <v>40</v>
+      </c>
+      <c r="E281">
+        <v>448608.57</v>
+      </c>
+      <c r="F281">
+        <v>6848522.46</v>
+      </c>
+      <c r="G281">
+        <v>-1202.07</v>
+      </c>
+      <c r="H281">
+        <v>2561.0500000000002</v>
+      </c>
+      <c r="K281">
+        <v>-1202.07</v>
+      </c>
+      <c r="O281" t="s">
+        <v>39</v>
+      </c>
+      <c r="U281" t="b">
+        <v>1</v>
+      </c>
+      <c r="V281" t="b">
+        <v>1</v>
+      </c>
+      <c r="W281" t="s">
+        <v>37</v>
+      </c>
+      <c r="X281" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI281" s="1">
+        <v>46272.678206018521</v>
+      </c>
+    </row>
+    <row r="282" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>475</v>
+      </c>
+      <c r="B282" t="s">
+        <v>119</v>
+      </c>
+      <c r="C282">
+        <v>36393647</v>
+      </c>
+      <c r="D282" t="s">
+        <v>75</v>
+      </c>
+      <c r="E282">
+        <v>450211.74</v>
+      </c>
+      <c r="F282">
+        <v>6850409.21</v>
+      </c>
+      <c r="G282">
+        <v>38.56</v>
+      </c>
+      <c r="H282">
+        <v>7.16</v>
+      </c>
+      <c r="K282">
+        <v>38.56</v>
+      </c>
+      <c r="O282" t="s">
+        <v>36</v>
+      </c>
+      <c r="P282">
+        <v>1</v>
+      </c>
+      <c r="U282" t="b">
+        <v>1</v>
+      </c>
+      <c r="V282" t="b">
+        <v>1</v>
+      </c>
+      <c r="W282" t="s">
+        <v>37</v>
+      </c>
+      <c r="X282" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC282" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD282">
+        <v>2</v>
+      </c>
+      <c r="AE282" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF282" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI282" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="283" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>1182</v>
+      </c>
+      <c r="B283" t="s">
+        <v>119</v>
+      </c>
+      <c r="C283">
+        <v>36393647</v>
+      </c>
+      <c r="D283" t="s">
+        <v>84</v>
+      </c>
+      <c r="E283">
+        <v>450209.74</v>
+      </c>
+      <c r="F283">
+        <v>6850408.1799999997</v>
+      </c>
+      <c r="G283">
+        <v>-635.17999999999995</v>
+      </c>
+      <c r="H283">
+        <v>680.92</v>
+      </c>
+      <c r="K283">
+        <v>-635.17999999999995</v>
+      </c>
+      <c r="O283" t="s">
+        <v>36</v>
+      </c>
+      <c r="P283">
+        <v>1</v>
+      </c>
+      <c r="U283" t="b">
+        <v>1</v>
+      </c>
+      <c r="V283" t="b">
+        <v>1</v>
+      </c>
+      <c r="W283" t="s">
+        <v>37</v>
+      </c>
+      <c r="X283" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC283" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD283">
+        <v>2</v>
+      </c>
+      <c r="AE283" t="s">
+        <v>107</v>
+      </c>
+      <c r="AF283" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI283" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="284" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>1504</v>
+      </c>
+      <c r="B284" t="s">
+        <v>119</v>
+      </c>
+      <c r="C284">
+        <v>36393647</v>
+      </c>
+      <c r="D284" t="s">
+        <v>86</v>
+      </c>
+      <c r="E284">
+        <v>450173.39</v>
+      </c>
+      <c r="F284">
+        <v>6850409.6100000003</v>
+      </c>
+      <c r="G284">
+        <v>-825.78</v>
+      </c>
+      <c r="H284">
+        <v>876</v>
+      </c>
+      <c r="K284">
+        <v>-825.78</v>
+      </c>
+      <c r="O284" t="s">
+        <v>36</v>
+      </c>
+      <c r="P284">
+        <v>1</v>
+      </c>
+      <c r="U284" t="b">
+        <v>1</v>
+      </c>
+      <c r="V284" t="b">
+        <v>1</v>
+      </c>
+      <c r="W284" t="s">
+        <v>37</v>
+      </c>
+      <c r="X284" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC284" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD284">
+        <v>1</v>
+      </c>
+      <c r="AE284" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF284" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI284" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="285" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>1590</v>
+      </c>
+      <c r="B285" t="s">
+        <v>119</v>
+      </c>
+      <c r="C285">
+        <v>36393647</v>
+      </c>
+      <c r="D285" t="s">
+        <v>88</v>
+      </c>
+      <c r="E285">
+        <v>450164.34</v>
+      </c>
+      <c r="F285">
+        <v>6850410.2999999998</v>
+      </c>
+      <c r="G285">
+        <v>-848.73</v>
+      </c>
+      <c r="H285">
+        <v>900.68</v>
+      </c>
+      <c r="K285">
+        <v>-848.73</v>
+      </c>
+      <c r="O285" t="s">
+        <v>36</v>
+      </c>
+      <c r="P285">
+        <v>1</v>
+      </c>
+      <c r="U285" t="b">
+        <v>1</v>
+      </c>
+      <c r="V285" t="b">
+        <v>1</v>
+      </c>
+      <c r="W285" t="s">
+        <v>37</v>
+      </c>
+      <c r="X285" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC285" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD285">
+        <v>1</v>
+      </c>
+      <c r="AE285" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF285" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI285" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="286" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>2390</v>
+      </c>
+      <c r="B286" t="s">
+        <v>119</v>
+      </c>
+      <c r="C286">
+        <v>36393647</v>
+      </c>
+      <c r="D286" t="s">
+        <v>90</v>
+      </c>
+      <c r="E286">
+        <v>449976.03</v>
+      </c>
+      <c r="F286">
+        <v>6850419.5</v>
+      </c>
+      <c r="G286">
+        <v>-1075.55</v>
+      </c>
+      <c r="H286">
+        <v>1200.3</v>
+      </c>
+      <c r="K286">
+        <v>-1075.55</v>
+      </c>
+      <c r="O286" t="s">
+        <v>36</v>
+      </c>
+      <c r="P286">
+        <v>1</v>
+      </c>
+      <c r="U286" t="b">
+        <v>1</v>
+      </c>
+      <c r="V286" t="b">
+        <v>1</v>
+      </c>
+      <c r="W286" t="s">
+        <v>37</v>
+      </c>
+      <c r="X286" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC286" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD286">
+        <v>1</v>
+      </c>
+      <c r="AE286" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF286" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI286" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="287" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>208</v>
+      </c>
+      <c r="B287" t="s">
+        <v>119</v>
+      </c>
+      <c r="C287">
+        <v>36393647</v>
+      </c>
+      <c r="D287" t="s">
+        <v>35</v>
+      </c>
+      <c r="E287">
+        <v>449829.06</v>
+      </c>
+      <c r="F287">
+        <v>6850425.0700000003</v>
+      </c>
+      <c r="G287">
+        <v>-1142.6199999999999</v>
+      </c>
+      <c r="H287">
+        <v>1362.46</v>
+      </c>
+      <c r="K287">
+        <v>-1142.6199999999999</v>
+      </c>
+      <c r="O287" t="s">
+        <v>36</v>
+      </c>
+      <c r="P287">
+        <v>1</v>
+      </c>
+      <c r="U287" t="b">
+        <v>1</v>
+      </c>
+      <c r="V287" t="b">
+        <v>1</v>
+      </c>
+      <c r="W287" t="s">
+        <v>37</v>
+      </c>
+      <c r="X287" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC287" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD287">
+        <v>1</v>
+      </c>
+      <c r="AE287" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF287" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI287" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="288" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>9469</v>
+      </c>
+      <c r="B288" t="s">
+        <v>119</v>
+      </c>
+      <c r="C288">
+        <v>36393647</v>
+      </c>
+      <c r="D288" t="s">
+        <v>35</v>
+      </c>
+      <c r="E288">
+        <v>449356.52</v>
+      </c>
+      <c r="F288">
+        <v>6850450.2400000002</v>
+      </c>
+      <c r="G288">
+        <v>-1194.9000000000001</v>
+      </c>
+      <c r="H288">
+        <v>1841.35</v>
+      </c>
+      <c r="K288">
+        <v>-1194.9000000000001</v>
+      </c>
+      <c r="O288" t="s">
+        <v>39</v>
+      </c>
+      <c r="U288" t="b">
+        <v>1</v>
+      </c>
+      <c r="V288" t="b">
+        <v>1</v>
+      </c>
+      <c r="W288" t="s">
+        <v>37</v>
+      </c>
+      <c r="X288" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI288" s="1">
+        <v>46210.354212962964</v>
+      </c>
+    </row>
+    <row r="289" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A289">
+        <v>9470</v>
+      </c>
+      <c r="B289" t="s">
+        <v>119</v>
+      </c>
+      <c r="C289">
+        <v>36393647</v>
+      </c>
+      <c r="D289" t="s">
+        <v>35</v>
+      </c>
+      <c r="E289">
+        <v>449149.75</v>
+      </c>
+      <c r="F289">
+        <v>6850456.8899999997</v>
+      </c>
+      <c r="G289">
+        <v>-1200.33</v>
+      </c>
+      <c r="H289">
+        <v>2048.35</v>
+      </c>
+      <c r="K289">
+        <v>-1200.33</v>
+      </c>
+      <c r="O289" t="s">
+        <v>39</v>
+      </c>
+      <c r="U289" t="b">
+        <v>1</v>
+      </c>
+      <c r="V289" t="b">
+        <v>1</v>
+      </c>
+      <c r="W289" t="s">
+        <v>37</v>
+      </c>
+      <c r="X289" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI289" s="1">
+        <v>46272.678680555553</v>
+      </c>
+    </row>
+    <row r="290" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A290">
+        <v>9473</v>
+      </c>
+      <c r="B290" t="s">
+        <v>119</v>
+      </c>
+      <c r="C290">
+        <v>36393647</v>
+      </c>
+      <c r="D290" t="s">
+        <v>35</v>
+      </c>
+      <c r="E290">
+        <v>449149.75</v>
+      </c>
+      <c r="F290">
+        <v>6850456.8899999997</v>
+      </c>
+      <c r="G290">
+        <v>-1200.33</v>
+      </c>
+      <c r="H290">
+        <v>2048.35</v>
+      </c>
+      <c r="K290">
+        <v>-1200.33</v>
+      </c>
+      <c r="O290" t="s">
+        <v>39</v>
+      </c>
+      <c r="U290" t="b">
+        <v>1</v>
+      </c>
+      <c r="V290" t="b">
+        <v>1</v>
+      </c>
+      <c r="W290" t="s">
+        <v>37</v>
+      </c>
+      <c r="X290" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI290" s="1">
+        <v>46272.678680555553</v>
+      </c>
+    </row>
+    <row r="291" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A291">
+        <v>2982</v>
+      </c>
+      <c r="B291" t="s">
+        <v>119</v>
+      </c>
+      <c r="C291">
+        <v>36393647</v>
+      </c>
+      <c r="D291" t="s">
+        <v>40</v>
+      </c>
+      <c r="E291">
+        <v>449479.85</v>
+      </c>
+      <c r="F291">
+        <v>6850444.2699999996</v>
+      </c>
+      <c r="G291">
+        <v>-1192.8399999999999</v>
+      </c>
+      <c r="H291">
+        <v>1717.85</v>
+      </c>
+      <c r="K291">
+        <v>-1192.8399999999999</v>
+      </c>
+      <c r="O291" t="s">
+        <v>36</v>
+      </c>
+      <c r="P291">
+        <v>1</v>
+      </c>
+      <c r="U291" t="b">
+        <v>1</v>
+      </c>
+      <c r="V291" t="b">
+        <v>1</v>
+      </c>
+      <c r="W291" t="s">
+        <v>37</v>
+      </c>
+      <c r="X291" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC291" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD291">
+        <v>1</v>
+      </c>
+      <c r="AE291" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF291" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI291" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="292" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A292">
+        <v>3106</v>
+      </c>
+      <c r="B292" t="s">
+        <v>119</v>
+      </c>
+      <c r="C292">
+        <v>36393647</v>
+      </c>
+      <c r="D292" t="s">
+        <v>40</v>
+      </c>
+      <c r="E292">
+        <v>449359.63</v>
+      </c>
+      <c r="F292">
+        <v>6850450.1200000001</v>
+      </c>
+      <c r="G292">
+        <v>-1194.8900000000001</v>
+      </c>
+      <c r="H292">
+        <v>1838.25</v>
+      </c>
+      <c r="K292">
+        <v>-1194.8900000000001</v>
+      </c>
+      <c r="O292" t="s">
+        <v>36</v>
+      </c>
+      <c r="P292">
+        <v>2</v>
+      </c>
+      <c r="U292" t="b">
+        <v>1</v>
+      </c>
+      <c r="V292" t="b">
+        <v>1</v>
+      </c>
+      <c r="W292" t="s">
+        <v>37</v>
+      </c>
+      <c r="X292" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC292" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD292">
+        <v>1</v>
+      </c>
+      <c r="AE292" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF292" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI292" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="293" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A293">
+        <v>2960</v>
+      </c>
+      <c r="B293" t="s">
+        <v>119</v>
+      </c>
+      <c r="C293">
+        <v>36393647</v>
+      </c>
+      <c r="D293" t="s">
+        <v>40</v>
+      </c>
+      <c r="E293">
+        <v>449229.93</v>
+      </c>
+      <c r="F293">
+        <v>6850454.4299999997</v>
+      </c>
+      <c r="G293">
+        <v>-1198.94</v>
+      </c>
+      <c r="H293">
+        <v>1968.09</v>
+      </c>
+      <c r="K293">
+        <v>-1198.94</v>
+      </c>
+      <c r="O293" t="s">
+        <v>36</v>
+      </c>
+      <c r="P293">
+        <v>3</v>
+      </c>
+      <c r="U293" t="b">
+        <v>1</v>
+      </c>
+      <c r="V293" t="b">
+        <v>1</v>
+      </c>
+      <c r="W293" t="s">
+        <v>37</v>
+      </c>
+      <c r="X293" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC293" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD293">
+        <v>1</v>
+      </c>
+      <c r="AE293" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF293" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI293" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="294" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A294">
+        <v>2868</v>
+      </c>
+      <c r="B294" t="s">
+        <v>119</v>
+      </c>
+      <c r="C294">
+        <v>36393647</v>
+      </c>
+      <c r="D294" t="s">
+        <v>40</v>
+      </c>
+      <c r="E294">
+        <v>449149.75</v>
+      </c>
+      <c r="F294">
+        <v>6850456.8899999997</v>
+      </c>
+      <c r="G294">
+        <v>-1200.33</v>
+      </c>
+      <c r="H294">
+        <v>2048.35</v>
+      </c>
+      <c r="K294">
+        <v>-1200.33</v>
+      </c>
+      <c r="O294" t="s">
+        <v>39</v>
+      </c>
+      <c r="P294">
+        <v>4</v>
+      </c>
+      <c r="U294" t="b">
+        <v>1</v>
+      </c>
+      <c r="V294" t="b">
+        <v>1</v>
+      </c>
+      <c r="W294" t="s">
+        <v>37</v>
+      </c>
+      <c r="X294" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC294" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD294">
+        <v>1</v>
+      </c>
+      <c r="AE294" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF294" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI294" s="1">
+        <v>46272.678680555553</v>
+      </c>
+    </row>
+    <row r="295" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A295">
+        <v>9557</v>
+      </c>
+      <c r="B295" t="s">
+        <v>119</v>
+      </c>
+      <c r="C295">
+        <v>36393647</v>
+      </c>
+      <c r="D295" t="s">
+        <v>40</v>
+      </c>
+      <c r="E295">
+        <v>448702.96</v>
+      </c>
+      <c r="F295">
+        <v>6850471.5300000003</v>
+      </c>
+      <c r="G295">
+        <v>-1201.58</v>
+      </c>
+      <c r="H295">
+        <v>2495.41</v>
+      </c>
+      <c r="K295">
+        <v>-1201.58</v>
+      </c>
+      <c r="O295" t="s">
+        <v>39</v>
+      </c>
+      <c r="U295" t="b">
+        <v>1</v>
+      </c>
+      <c r="V295" t="b">
+        <v>1</v>
+      </c>
+      <c r="W295" t="s">
+        <v>37</v>
+      </c>
+      <c r="X295" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI295" s="1">
+        <v>46272.680439814816</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AI183" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AI191" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c4de8975-a9e2-4032-8275-674640ba9e13" xsi:nil="true"/>
+    <Notes xmlns="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F058933DE679D84C844BCD5E6FE280F8" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7c3559ca4b0718cc0d1b32599faf4d2a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd" xmlns:ns3="416a3325-149f-4ed5-ad81-b499dd2029e2" xmlns:ns4="c4de8975-a9e2-4032-8275-674640ba9e13" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2290b9febe09ca40959ebaa4289d445c" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd"/>
@@ -10655,28 +16588,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c4de8975-a9e2-4032-8275-674640ba9e13" xsi:nil="true"/>
-    <Notes xmlns="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37A1D12C-989B-423F-BA14-C3F31107F7DB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1FB06A0-65DD-411D-8E4B-3E9354C1DCE0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c4de8975-a9e2-4032-8275-674640ba9e13"/>
+    <ds:schemaRef ds:uri="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C455A20A-045D-41D5-AA3F-22BD10EAC1B5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10696,25 +16627,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1FB06A0-65DD-411D-8E4B-3E9354C1DCE0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c4de8975-a9e2-4032-8275-674640ba9e13"/>
-    <ds:schemaRef ds:uri="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37A1D12C-989B-423F-BA14-C3F31107F7DB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{826c2670-3368-498f-a16b-70466cda23c0}" enabled="1" method="Standard" siteId="{447a9cb9-b230-46bf-b430-a7b9f50e3c1e}" contentBits="0" removed="0"/>
